--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="125">
   <si>
     <t>League</t>
   </si>
@@ -265,9 +265,15 @@
     <t>South Korean K1 League</t>
   </si>
   <si>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
     <t>South African Premier Division</t>
   </si>
   <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
@@ -286,9 +292,15 @@
     <t>10:30:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>17:30:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -310,6 +322,9 @@
     <t>Gangwon</t>
   </si>
   <si>
+    <t>Al Faisaly ( KSA )</t>
+  </si>
+  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
@@ -322,6 +337,12 @@
     <t>Richards Bay FC</t>
   </si>
   <si>
+    <t>Al Draih</t>
+  </si>
+  <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
     <t>Real Madrid</t>
   </si>
   <si>
@@ -343,6 +364,9 @@
     <t>Gwangju FC</t>
   </si>
   <si>
+    <t>Al-Fateh (KSA)</t>
+  </si>
+  <si>
     <t>AmaZulu</t>
   </si>
   <si>
@@ -355,10 +379,16 @@
     <t>Kaizer Chiefs</t>
   </si>
   <si>
+    <t>Al-Kholood Club</t>
+  </si>
+  <si>
+    <t>The Strongest</t>
+  </si>
+  <si>
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-08-24 10:29:12</t>
+    <t>2026-08-24 12:49:40</t>
   </si>
 </sst>
 </file>
@@ -690,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -940,43 +970,43 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F2">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O2">
         <v>1.43</v>
@@ -985,7 +1015,7 @@
         <v>1.68</v>
       </c>
       <c r="Q2">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R2">
         <v>1.25</v>
@@ -994,58 +1024,58 @@
         <v>4.4</v>
       </c>
       <c r="T2">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
         <v>1.68</v>
       </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X2">
         <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>18.5</v>
+        <v>950</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AB2">
         <v>6.8</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>950</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE2">
         <v>150</v>
       </c>
       <c r="AF2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI2">
         <v>180</v>
       </c>
       <c r="AJ2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL2">
         <v>55</v>
@@ -1066,115 +1096,115 @@
         <v>14.5</v>
       </c>
       <c r="AR2">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="AT2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU2">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AV2">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW2">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AX2">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2">
         <v>25</v>
       </c>
       <c r="BA2">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="BB2">
         <v>13.5</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD2">
-        <v>42</v>
+        <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="BF2">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="BG2">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="BH2">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.48</v>
+        <v>1.6</v>
       </c>
       <c r="BJ2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BK2">
-        <v>8.4</v>
+        <v>1.46</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="BN2">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BO2">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="BP2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BS2">
-        <v>5.1</v>
+        <v>1.55</v>
       </c>
       <c r="BT2">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BU2">
-        <v>6.6</v>
+        <v>1.45</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="BZ2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CA2">
-        <v>4.9</v>
+        <v>1.53</v>
       </c>
       <c r="CB2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1182,19 +1212,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F3">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="G3">
         <v>2.54</v>
@@ -1203,31 +1233,31 @@
         <v>3.35</v>
       </c>
       <c r="I3">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P3">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q3">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R3">
         <v>1.21</v>
@@ -1236,16 +1266,16 @@
         <v>4.8</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U3">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="X3">
         <v>10</v>
@@ -1254,7 +1284,7 @@
         <v>11</v>
       </c>
       <c r="Z3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA3">
         <v>95</v>
@@ -1263,10 +1293,10 @@
         <v>8.4</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE3">
         <v>65</v>
@@ -1275,13 +1305,13 @@
         <v>15</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
         <v>42</v>
@@ -1296,7 +1326,7 @@
         <v>190</v>
       </c>
       <c r="AN3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO3">
         <v>80</v>
@@ -1305,13 +1335,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3">
         <v>20</v>
       </c>
       <c r="AS3">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1323,7 +1353,7 @@
         <v>13</v>
       </c>
       <c r="AW3">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AX3">
         <v>12</v>
@@ -1332,91 +1362,91 @@
         <v>10</v>
       </c>
       <c r="AZ3">
+        <v>18.5</v>
+      </c>
+      <c r="BA3">
         <v>6.4</v>
       </c>
-      <c r="BA3">
-        <v>8.4</v>
-      </c>
       <c r="BB3">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC3">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BD3">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BE3">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
-        <v>23</v>
+        <v>5.8</v>
       </c>
       <c r="BG3">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BH3">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1424,52 +1454,52 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F4">
         <v>1.34</v>
       </c>
       <c r="G4">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="I4">
         <v>13</v>
       </c>
       <c r="J4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K4">
         <v>5.6</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>1.96</v>
       </c>
       <c r="Q4">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R4">
         <v>1.37</v>
@@ -1478,43 +1508,43 @@
         <v>3.2</v>
       </c>
       <c r="T4">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U4">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V4">
         <v>1.08</v>
       </c>
       <c r="W4">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="X4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z4">
         <v>140</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>650</v>
       </c>
       <c r="AB4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AD4">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AE4">
         <v>280</v>
       </c>
       <c r="AF4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG4">
         <v>11</v>
@@ -1526,139 +1556,139 @@
         <v>220</v>
       </c>
       <c r="AJ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK4">
         <v>17</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM4">
         <v>270</v>
       </c>
       <c r="AN4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO4">
         <v>470</v>
       </c>
       <c r="AP4">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="AQ4">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AR4">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AW4">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AX4">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4">
+        <v>5.8</v>
+      </c>
+      <c r="BA4">
+        <v>6.8</v>
+      </c>
+      <c r="BB4">
+        <v>9.4</v>
+      </c>
+      <c r="BC4">
+        <v>13.5</v>
+      </c>
+      <c r="BD4">
+        <v>6.2</v>
+      </c>
+      <c r="BE4">
+        <v>6.8</v>
+      </c>
+      <c r="BF4">
         <v>5.3</v>
       </c>
-      <c r="AZ4">
-        <v>7.8</v>
-      </c>
-      <c r="BA4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB4">
-        <v>5.4</v>
-      </c>
-      <c r="BC4">
-        <v>6.4</v>
-      </c>
-      <c r="BD4">
-        <v>8.4</v>
-      </c>
-      <c r="BE4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF4">
-        <v>6</v>
-      </c>
       <c r="BG4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BH4">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1666,19 +1696,19 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G5">
         <v>3.6</v>
@@ -1690,10 +1720,10 @@
         <v>2.52</v>
       </c>
       <c r="J5">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K5">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L5">
         <v>1.37</v>
@@ -1702,28 +1732,28 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="O5">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="Q5">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="V5">
         <v>1.66</v>
@@ -1732,25 +1762,25 @@
         <v>1.38</v>
       </c>
       <c r="X5">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y5">
         <v>8.800000000000001</v>
       </c>
       <c r="Z5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB5">
         <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
         <v>34</v>
@@ -1762,88 +1792,88 @@
         <v>17</v>
       </c>
       <c r="AH5">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>95</v>
       </c>
       <c r="AK5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
         <v>75</v>
-      </c>
-      <c r="AM5">
-        <v>150</v>
-      </c>
-      <c r="AN5">
-        <v>65</v>
       </c>
       <c r="AO5">
         <v>30</v>
       </c>
       <c r="AP5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ5">
+        <v>6.6</v>
+      </c>
+      <c r="AR5">
+        <v>10.5</v>
+      </c>
+      <c r="AS5">
+        <v>21</v>
+      </c>
+      <c r="AT5">
         <v>8.4</v>
-      </c>
-      <c r="AQ5">
-        <v>7.8</v>
-      </c>
-      <c r="AR5">
-        <v>11.5</v>
-      </c>
-      <c r="AS5">
-        <v>7.6</v>
-      </c>
-      <c r="AT5">
-        <v>10</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AW5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AY5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA5">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="BB5">
-        <v>8.4</v>
+        <v>3.55</v>
       </c>
       <c r="BC5">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="BD5">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="BE5">
-        <v>8.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="BF5">
-        <v>8.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="BG5">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
@@ -1900,7 +1930,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1908,19 +1938,19 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F6">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="G6">
         <v>2.5</v>
@@ -1929,10 +1959,10 @@
         <v>2.98</v>
       </c>
       <c r="I6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J6">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
         <v>3.95</v>
@@ -1944,16 +1974,16 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="O6">
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="R6">
         <v>1.44</v>
@@ -1968,118 +1998,118 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
         <v>1.68</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2142,7 +2172,7 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2150,79 +2180,79 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F7">
         <v>1.54</v>
       </c>
       <c r="G7">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="I7">
         <v>8.6</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L7">
         <v>1.35</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q7">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
         <v>1.25</v>
       </c>
       <c r="S7">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="T7">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V7">
         <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="X7">
         <v>1000</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z7">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
         <v>1000</v>
@@ -2234,7 +2264,7 @@
         <v>1000</v>
       </c>
       <c r="AD7">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
         <v>1000</v>
@@ -2246,13 +2276,13 @@
         <v>1000</v>
       </c>
       <c r="AH7">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
         <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK7">
         <v>1000</v>
@@ -2270,58 +2300,58 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR7">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AS7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AT7">
-        <v>5.6</v>
+        <v>1.11</v>
       </c>
       <c r="AU7">
-        <v>1.32</v>
+        <v>8</v>
       </c>
       <c r="AV7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AW7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AX7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AY7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AZ7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BB7">
-        <v>1.23</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BD7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BE7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BF7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BG7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2384,7 +2414,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2392,34 +2422,34 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G8">
-        <v>600</v>
+        <v>2.86</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="I8">
-        <v>870</v>
+        <v>3.2</v>
       </c>
       <c r="J8">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2434,10 +2464,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2446,10 +2476,10 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -2458,112 +2488,112 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
         <v>0</v>
@@ -2626,24 +2656,24 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F9">
         <v>1.04</v>
@@ -2868,24 +2898,24 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F10">
         <v>1.04</v>
@@ -2900,7 +2930,7 @@
         <v>870</v>
       </c>
       <c r="J10">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3110,24 +3140,24 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F11">
         <v>1.04</v>
@@ -3142,7 +3172,7 @@
         <v>870</v>
       </c>
       <c r="J11">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K11">
         <v>950</v>
@@ -3352,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3360,241 +3390,967 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12">
+        <v>1.04</v>
+      </c>
+      <c r="G12">
+        <v>600</v>
+      </c>
+      <c r="H12">
+        <v>1.04</v>
+      </c>
+      <c r="I12">
+        <v>870</v>
+      </c>
+      <c r="J12">
+        <v>1.09</v>
+      </c>
+      <c r="K12">
+        <v>950</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.24</v>
+      </c>
+      <c r="Q12">
+        <v>1.01</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13">
+        <v>1.75</v>
+      </c>
+      <c r="G13">
+        <v>1.9</v>
+      </c>
+      <c r="H13">
+        <v>4.5</v>
+      </c>
+      <c r="I13">
+        <v>5.4</v>
+      </c>
+      <c r="J13">
+        <v>3.95</v>
+      </c>
+      <c r="K13">
+        <v>4.3</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>2.04</v>
+      </c>
+      <c r="Q13">
+        <v>1.8</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>1.76</v>
+      </c>
+      <c r="U13">
+        <v>2.1</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>18</v>
+      </c>
+      <c r="Y13">
+        <v>22</v>
+      </c>
+      <c r="Z13">
+        <v>46</v>
+      </c>
+      <c r="AA13">
+        <v>130</v>
+      </c>
+      <c r="AB13">
+        <v>10</v>
+      </c>
+      <c r="AC13">
+        <v>10.5</v>
+      </c>
+      <c r="AD13">
+        <v>23</v>
+      </c>
+      <c r="AE13">
+        <v>70</v>
+      </c>
+      <c r="AF13">
+        <v>13.5</v>
+      </c>
+      <c r="AG13">
+        <v>12</v>
+      </c>
+      <c r="AH13">
+        <v>22</v>
+      </c>
+      <c r="AI13">
+        <v>75</v>
+      </c>
+      <c r="AJ13">
+        <v>23</v>
+      </c>
+      <c r="AK13">
+        <v>22</v>
+      </c>
+      <c r="AL13">
+        <v>38</v>
+      </c>
+      <c r="AM13">
+        <v>110</v>
+      </c>
+      <c r="AN13">
+        <v>12.5</v>
+      </c>
+      <c r="AO13">
+        <v>75</v>
+      </c>
+      <c r="AP13">
+        <v>14.5</v>
+      </c>
+      <c r="AQ13">
+        <v>15.5</v>
+      </c>
+      <c r="AR13">
+        <v>4.8</v>
+      </c>
+      <c r="AS13">
+        <v>5.2</v>
+      </c>
+      <c r="AT13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU13">
+        <v>7.8</v>
+      </c>
+      <c r="AV13">
+        <v>16</v>
+      </c>
+      <c r="AW13">
+        <v>5</v>
+      </c>
+      <c r="AX13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ13">
+        <v>15.5</v>
+      </c>
+      <c r="BA13">
+        <v>5.1</v>
+      </c>
+      <c r="BB13">
+        <v>16.5</v>
+      </c>
+      <c r="BC13">
+        <v>15.5</v>
+      </c>
+      <c r="BD13">
+        <v>4.7</v>
+      </c>
+      <c r="BE13">
+        <v>5.2</v>
+      </c>
+      <c r="BF13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG13">
+        <v>5.1</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
         <v>85</v>
       </c>
-      <c r="C12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12">
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14">
+        <v>1.04</v>
+      </c>
+      <c r="G14">
+        <v>1000</v>
+      </c>
+      <c r="H14">
+        <v>1.04</v>
+      </c>
+      <c r="I14">
+        <v>1000</v>
+      </c>
+      <c r="J14">
+        <v>1.09</v>
+      </c>
+      <c r="K14">
+        <v>1000</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.01</v>
+      </c>
+      <c r="Q14">
+        <v>1.01</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15">
+        <v>1.37</v>
+      </c>
+      <c r="G15">
         <v>1.38</v>
       </c>
-      <c r="G12">
-        <v>1.39</v>
-      </c>
-      <c r="H12">
+      <c r="H15">
         <v>9.199999999999999</v>
       </c>
-      <c r="I12">
+      <c r="I15">
         <v>9.4</v>
       </c>
-      <c r="J12">
-        <v>5.8</v>
-      </c>
-      <c r="K12">
+      <c r="J15">
         <v>5.9</v>
       </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
+      <c r="K15">
+        <v>6</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
         <v>1.03</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
+      <c r="N15">
+        <v>6.6</v>
+      </c>
+      <c r="O15">
+        <v>1.16</v>
+      </c>
+      <c r="P15">
         <v>2.9</v>
       </c>
-      <c r="Q12">
-        <v>1.5</v>
-      </c>
-      <c r="R12">
-        <v>1.76</v>
-      </c>
-      <c r="S12">
-        <v>2.24</v>
-      </c>
-      <c r="T12">
+      <c r="Q15">
+        <v>1.48</v>
+      </c>
+      <c r="R15">
+        <v>1.75</v>
+      </c>
+      <c r="S15">
+        <v>2.22</v>
+      </c>
+      <c r="T15">
         <v>1.78</v>
       </c>
-      <c r="U12">
-        <v>2.2</v>
-      </c>
-      <c r="V12">
-        <v>1.12</v>
-      </c>
-      <c r="W12">
-        <v>3.55</v>
-      </c>
-      <c r="X12">
-        <v>32</v>
-      </c>
-      <c r="Y12">
-        <v>38</v>
-      </c>
-      <c r="Z12">
+      <c r="U15">
+        <v>2.22</v>
+      </c>
+      <c r="V15">
+        <v>1.11</v>
+      </c>
+      <c r="W15">
+        <v>3.6</v>
+      </c>
+      <c r="X15">
+        <v>34</v>
+      </c>
+      <c r="Y15">
+        <v>40</v>
+      </c>
+      <c r="Z15">
         <v>85</v>
       </c>
-      <c r="AA12">
-        <v>250</v>
-      </c>
-      <c r="AB12">
+      <c r="AA15">
+        <v>310</v>
+      </c>
+      <c r="AB15">
+        <v>12.5</v>
+      </c>
+      <c r="AC15">
+        <v>13.5</v>
+      </c>
+      <c r="AD15">
+        <v>34</v>
+      </c>
+      <c r="AE15">
+        <v>120</v>
+      </c>
+      <c r="AF15">
+        <v>10.5</v>
+      </c>
+      <c r="AG15">
+        <v>10.5</v>
+      </c>
+      <c r="AH15">
+        <v>23</v>
+      </c>
+      <c r="AI15">
+        <v>90</v>
+      </c>
+      <c r="AJ15">
+        <v>12.5</v>
+      </c>
+      <c r="AK15">
+        <v>13</v>
+      </c>
+      <c r="AL15">
+        <v>29</v>
+      </c>
+      <c r="AM15">
+        <v>100</v>
+      </c>
+      <c r="AN15">
+        <v>4.6</v>
+      </c>
+      <c r="AO15">
+        <v>120</v>
+      </c>
+      <c r="AP15">
+        <v>28</v>
+      </c>
+      <c r="AQ15">
+        <v>24</v>
+      </c>
+      <c r="AR15">
+        <v>36</v>
+      </c>
+      <c r="AS15">
+        <v>14.5</v>
+      </c>
+      <c r="AT15">
+        <v>11</v>
+      </c>
+      <c r="AU15">
         <v>12</v>
       </c>
-      <c r="AC12">
+      <c r="AV15">
+        <v>21</v>
+      </c>
+      <c r="AW15">
         <v>13.5</v>
       </c>
-      <c r="AD12">
-        <v>32</v>
-      </c>
-      <c r="AE12">
-        <v>110</v>
-      </c>
-      <c r="AF12">
-        <v>10.5</v>
-      </c>
-      <c r="AG12">
-        <v>10.5</v>
-      </c>
-      <c r="AH12">
-        <v>23</v>
-      </c>
-      <c r="AI12">
-        <v>90</v>
-      </c>
-      <c r="AJ12">
-        <v>12.5</v>
-      </c>
-      <c r="AK12">
-        <v>13.5</v>
-      </c>
-      <c r="AL12">
-        <v>29</v>
-      </c>
-      <c r="AM12">
-        <v>100</v>
-      </c>
-      <c r="AN12">
-        <v>4.6</v>
-      </c>
-      <c r="AO12">
-        <v>110</v>
-      </c>
-      <c r="AP12">
-        <v>25</v>
-      </c>
-      <c r="AQ12">
-        <v>23</v>
-      </c>
-      <c r="AR12">
+      <c r="AX15">
+        <v>9.4</v>
+      </c>
+      <c r="AY15">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15">
+        <v>20</v>
+      </c>
+      <c r="BA15">
         <v>36</v>
       </c>
-      <c r="AS12">
-        <v>17</v>
-      </c>
-      <c r="AT12">
-        <v>10.5</v>
-      </c>
-      <c r="AU12">
+      <c r="BB15">
+        <v>11</v>
+      </c>
+      <c r="BC15">
         <v>12</v>
       </c>
-      <c r="AV12">
-        <v>27</v>
-      </c>
-      <c r="AW12">
+      <c r="BD15">
+        <v>24</v>
+      </c>
+      <c r="BE15">
+        <v>13</v>
+      </c>
+      <c r="BF15">
+        <v>4.3</v>
+      </c>
+      <c r="BG15">
         <v>40</v>
       </c>
-      <c r="AX12">
-        <v>9</v>
-      </c>
-      <c r="AY12">
-        <v>9.4</v>
-      </c>
-      <c r="AZ12">
-        <v>19.5</v>
-      </c>
-      <c r="BA12">
-        <v>36</v>
-      </c>
-      <c r="BB12">
-        <v>11</v>
-      </c>
-      <c r="BC12">
-        <v>11.5</v>
-      </c>
-      <c r="BD12">
-        <v>18.5</v>
-      </c>
-      <c r="BE12">
-        <v>38</v>
-      </c>
-      <c r="BF12">
-        <v>4.3</v>
-      </c>
-      <c r="BG12">
-        <v>15.5</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.04</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.04</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.04</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.04</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.04</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>1.04</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>1.04</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>1.04</v>
-      </c>
-      <c r="BZ12">
-        <v>1000</v>
-      </c>
-      <c r="CA12">
-        <v>1.04</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>114</v>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.04</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.04</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.04</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.04</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.04</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.04</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.04</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.04</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.04</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="158">
   <si>
     <t>League</t>
   </si>
@@ -265,12 +265,24 @@
     <t>South Korean K1 League</t>
   </si>
   <si>
+    <t>Estonian Premier League</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
     <t>South African Premier Division</t>
   </si>
   <si>
+    <t>UEFA Champions League Qualifiers</t>
+  </si>
+  <si>
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
@@ -295,6 +307,9 @@
     <t>16:00:00</t>
   </si>
   <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
     <t>17:30:00</t>
   </si>
   <si>
@@ -322,9 +337,39 @@
     <t>Gangwon</t>
   </si>
   <si>
+    <t>Tammeka Tartu</t>
+  </si>
+  <si>
+    <t>Strommen</t>
+  </si>
+  <si>
     <t>Al Faisaly ( KSA )</t>
   </si>
   <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Odds BK</t>
+  </si>
+  <si>
+    <t>Stromsgodset</t>
+  </si>
+  <si>
+    <t>Asane</t>
+  </si>
+  <si>
+    <t>Stabaek</t>
+  </si>
+  <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
+    <t>National Bank</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
@@ -340,12 +385,24 @@
     <t>Al Draih</t>
   </si>
   <si>
+    <t>Lyon</t>
+  </si>
+  <si>
     <t>San Antonio Bulo Bulo</t>
   </si>
   <si>
     <t>Real Madrid</t>
   </si>
   <si>
+    <t>NK Celje</t>
+  </si>
+  <si>
+    <t>AEK Athens</t>
+  </si>
+  <si>
+    <t>Viking</t>
+  </si>
+  <si>
     <t>Tolima</t>
   </si>
   <si>
@@ -364,9 +421,39 @@
     <t>Gwangju FC</t>
   </si>
   <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>Al-Fateh (KSA)</t>
   </si>
   <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Hodd</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Ranheim IL</t>
+  </si>
+  <si>
+    <t>El Geish</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
     <t>AmaZulu</t>
   </si>
   <si>
@@ -382,13 +469,25 @@
     <t>Al-Kholood Club</t>
   </si>
   <si>
+    <t>Fenerbahce</t>
+  </si>
+  <si>
     <t>The Strongest</t>
   </si>
   <si>
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-08-24 12:49:40</t>
+    <t>Slovan Bratislava</t>
+  </si>
+  <si>
+    <t>PFC Levski Sofia</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>2026-08-24 14:54:40</t>
   </si>
 </sst>
 </file>
@@ -720,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -970,34 +1069,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1006,19 +1105,19 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>1.43</v>
       </c>
       <c r="P2">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
         <v>4.4</v>
@@ -1027,7 +1126,7 @@
         <v>2.28</v>
       </c>
       <c r="U2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V2">
         <v>1.16</v>
@@ -1039,7 +1138,7 @@
         <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>950</v>
+        <v>18.5</v>
       </c>
       <c r="Z2">
         <v>60</v>
@@ -1051,34 +1150,34 @@
         <v>6.8</v>
       </c>
       <c r="AC2">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE2">
         <v>150</v>
       </c>
       <c r="AF2">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AI2">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AJ2">
         <v>15.5</v>
       </c>
       <c r="AK2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AM2">
         <v>250</v>
@@ -1096,25 +1195,25 @@
         <v>14.5</v>
       </c>
       <c r="AR2">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AS2">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="AT2">
         <v>6</v>
       </c>
       <c r="AU2">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>4.7</v>
+        <v>24</v>
       </c>
       <c r="AW2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX2">
         <v>7.4</v>
-      </c>
-      <c r="AX2">
-        <v>5.1</v>
       </c>
       <c r="AY2">
         <v>9.6</v>
@@ -1123,7 +1222,7 @@
         <v>25</v>
       </c>
       <c r="BA2">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2">
         <v>13.5</v>
@@ -1132,79 +1231,79 @@
         <v>18</v>
       </c>
       <c r="BD2">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="BF2">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="BG2">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.46</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1212,55 +1311,55 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="F3">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="G3">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I3">
         <v>3.55</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O3">
         <v>1.49</v>
       </c>
       <c r="P3">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q3">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
         <v>4.8</v>
@@ -1269,43 +1368,43 @@
         <v>2.08</v>
       </c>
       <c r="U3">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X3">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AA3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC3">
         <v>8.4</v>
       </c>
-      <c r="AC3">
-        <v>7.8</v>
-      </c>
       <c r="AD3">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AE3">
         <v>65</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG3">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
         <v>25</v>
@@ -1314,19 +1413,19 @@
         <v>85</v>
       </c>
       <c r="AJ3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM3">
         <v>190</v>
       </c>
       <c r="AN3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO3">
         <v>80</v>
@@ -1335,25 +1434,25 @@
         <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="AX3">
         <v>12</v>
@@ -1365,25 +1464,25 @@
         <v>18.5</v>
       </c>
       <c r="BA3">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB3">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BC3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD3">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE3">
+        <v>8.4</v>
+      </c>
+      <c r="BF3">
         <v>6.8</v>
       </c>
-      <c r="BF3">
-        <v>5.8</v>
-      </c>
       <c r="BG3">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1446,7 +1545,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1454,16 +1553,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="F4">
         <v>1.34</v>
@@ -1484,22 +1583,22 @@
         <v>5.6</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M4">
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P4">
         <v>1.96</v>
       </c>
       <c r="Q4">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R4">
         <v>1.37</v>
@@ -1508,16 +1607,16 @@
         <v>3.2</v>
       </c>
       <c r="T4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U4">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V4">
         <v>1.08</v>
       </c>
       <c r="W4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X4">
         <v>21</v>
@@ -1535,7 +1634,7 @@
         <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AD4">
         <v>55</v>
@@ -1577,13 +1676,13 @@
         <v>14</v>
       </c>
       <c r="AQ4">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
@@ -1592,10 +1691,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="AW4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX4">
         <v>6.4</v>
@@ -1604,10 +1703,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB4">
         <v>9.4</v>
@@ -1616,79 +1715,79 @@
         <v>13.5</v>
       </c>
       <c r="BD4">
+        <v>6.8</v>
+      </c>
+      <c r="BE4">
+        <v>7.4</v>
+      </c>
+      <c r="BF4">
+        <v>6</v>
+      </c>
+      <c r="BG4">
+        <v>7.6</v>
+      </c>
+      <c r="BH4">
+        <v>3.75</v>
+      </c>
+      <c r="BI4">
+        <v>2.86</v>
+      </c>
+      <c r="BJ4">
+        <v>13.5</v>
+      </c>
+      <c r="BK4">
+        <v>6</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>10.5</v>
+      </c>
+      <c r="BN4">
+        <v>3.75</v>
+      </c>
+      <c r="BO4">
+        <v>2.88</v>
+      </c>
+      <c r="BP4">
+        <v>8.6</v>
+      </c>
+      <c r="BQ4">
+        <v>4.8</v>
+      </c>
+      <c r="BR4">
+        <v>29</v>
+      </c>
+      <c r="BS4">
+        <v>8</v>
+      </c>
+      <c r="BT4">
+        <v>14.5</v>
+      </c>
+      <c r="BU4">
         <v>6.2</v>
       </c>
-      <c r="BE4">
-        <v>6.8</v>
-      </c>
-      <c r="BF4">
-        <v>5.3</v>
-      </c>
-      <c r="BG4">
-        <v>7</v>
-      </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>1.04</v>
-      </c>
-      <c r="BJ4">
-        <v>1000</v>
-      </c>
-      <c r="BK4">
-        <v>1.04</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.04</v>
-      </c>
-      <c r="BN4">
-        <v>1000</v>
-      </c>
-      <c r="BO4">
-        <v>1.04</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>1.04</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>1.04</v>
-      </c>
-      <c r="BT4">
-        <v>1000</v>
-      </c>
-      <c r="BU4">
-        <v>1.04</v>
-      </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1696,34 +1795,34 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="F5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G5">
         <v>3.6</v>
       </c>
       <c r="H5">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I5">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L5">
         <v>1.37</v>
@@ -1732,31 +1831,31 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="O5">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P5">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="Q5">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="R5">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S5">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="U5">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="V5">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W5">
         <v>1.38</v>
@@ -1765,79 +1864,79 @@
         <v>11.5</v>
       </c>
       <c r="Y5">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB5">
         <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD5">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF5">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AG5">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
         <v>95</v>
       </c>
       <c r="AK5">
+        <v>60</v>
+      </c>
+      <c r="AL5">
+        <v>85</v>
+      </c>
+      <c r="AM5">
+        <v>150</v>
+      </c>
+      <c r="AN5">
         <v>65</v>
       </c>
-      <c r="AL5">
-        <v>1000</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>75</v>
-      </c>
       <c r="AO5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP5">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ5">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR5">
         <v>10.5</v>
       </c>
       <c r="AS5">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AW5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX5">
         <v>20</v>
@@ -1849,25 +1948,25 @@
         <v>14</v>
       </c>
       <c r="BA5">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB5">
-        <v>3.55</v>
+        <v>7.4</v>
       </c>
       <c r="BC5">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD5">
-        <v>3.7</v>
+        <v>38</v>
       </c>
       <c r="BE5">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="BF5">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG5">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1930,7 +2029,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1938,34 +2037,34 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="F6">
         <v>2.3</v>
       </c>
       <c r="G6">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>3.4</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1974,7 +2073,7 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
         <v>1.21</v>
@@ -1989,7 +2088,7 @@
         <v>1.44</v>
       </c>
       <c r="S6">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T6">
         <v>1.54</v>
@@ -2172,7 +2271,7 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2180,34 +2279,34 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="F7">
         <v>1.54</v>
       </c>
       <c r="G7">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="H7">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>8.6</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
         <v>1.35</v>
@@ -2216,142 +2315,142 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V7">
         <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AB7">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ7">
+        <v>15</v>
+      </c>
+      <c r="AK7">
+        <v>20</v>
+      </c>
+      <c r="AL7">
+        <v>60</v>
+      </c>
+      <c r="AM7">
+        <v>250</v>
+      </c>
+      <c r="AN7">
+        <v>13</v>
+      </c>
+      <c r="AO7">
+        <v>330</v>
+      </c>
+      <c r="AP7">
+        <v>10.5</v>
+      </c>
+      <c r="AQ7">
         <v>18</v>
       </c>
-      <c r="AK7">
-        <v>1000</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>1000</v>
-      </c>
-      <c r="AO7">
-        <v>1000</v>
-      </c>
-      <c r="AP7">
-        <v>1.25</v>
-      </c>
-      <c r="AQ7">
-        <v>15</v>
-      </c>
       <c r="AR7">
-        <v>1.25</v>
+        <v>5.5</v>
       </c>
       <c r="AS7">
-        <v>1.25</v>
+        <v>5.8</v>
       </c>
       <c r="AT7">
-        <v>1.11</v>
+        <v>6</v>
       </c>
       <c r="AU7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV7">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="AW7">
-        <v>1.25</v>
+        <v>5.7</v>
       </c>
       <c r="AX7">
-        <v>1.25</v>
+        <v>7.2</v>
       </c>
       <c r="AY7">
-        <v>1.25</v>
+        <v>9</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>5.1</v>
       </c>
       <c r="BA7">
-        <v>1.25</v>
+        <v>5.7</v>
       </c>
       <c r="BB7">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BC7">
-        <v>1.25</v>
+        <v>16</v>
       </c>
       <c r="BD7">
-        <v>1.25</v>
+        <v>5.3</v>
       </c>
       <c r="BE7">
-        <v>1.25</v>
+        <v>5.7</v>
       </c>
       <c r="BF7">
-        <v>1.25</v>
+        <v>9.6</v>
       </c>
       <c r="BG7">
-        <v>1.25</v>
+        <v>5.8</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2414,7 +2513,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2422,70 +2521,70 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="F8">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="G8">
-        <v>2.86</v>
+        <v>600</v>
       </c>
       <c r="H8">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="I8">
-        <v>3.2</v>
+        <v>870</v>
       </c>
       <c r="J8">
-        <v>3.4</v>
+        <v>1.09</v>
       </c>
       <c r="K8">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.78</v>
+        <v>1.12</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2542,52 +2641,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2596,67 +2695,67 @@
         <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2664,483 +2763,483 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>2.04</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="I9">
-        <v>870</v>
+        <v>4.1</v>
       </c>
       <c r="J9">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>2.62</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G10">
-        <v>600</v>
+        <v>2.76</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="I10">
-        <v>870</v>
+        <v>3.1</v>
       </c>
       <c r="J10">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P10">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3148,241 +3247,241 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G11">
-        <v>600</v>
+        <v>1.78</v>
       </c>
       <c r="H11">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I11">
-        <v>870</v>
+        <v>4.8</v>
       </c>
       <c r="J11">
-        <v>1.09</v>
+        <v>4.8</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="P11">
-        <v>1.24</v>
+        <v>3.9</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3390,757 +3489,757 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="G12">
-        <v>600</v>
+        <v>2.88</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="I12">
-        <v>870</v>
+        <v>2.5</v>
       </c>
       <c r="J12">
-        <v>1.09</v>
+        <v>4.3</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>3.7</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="F13">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="G13">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="H13">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="I13">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="J13">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="K13">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P13">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="Q13">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T13">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="U13">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X13">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="Z13">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AC13">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="AD13">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AE13">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AG13">
+        <v>17.5</v>
+      </c>
+      <c r="AH13">
+        <v>32</v>
+      </c>
+      <c r="AI13">
+        <v>95</v>
+      </c>
+      <c r="AJ13">
+        <v>19</v>
+      </c>
+      <c r="AK13">
+        <v>18.5</v>
+      </c>
+      <c r="AL13">
+        <v>34</v>
+      </c>
+      <c r="AM13">
+        <v>95</v>
+      </c>
+      <c r="AN13">
+        <v>3.85</v>
+      </c>
+      <c r="AO13">
+        <v>100</v>
+      </c>
+      <c r="AP13">
+        <v>3</v>
+      </c>
+      <c r="AQ13">
+        <v>2.9</v>
+      </c>
+      <c r="AR13">
+        <v>3</v>
+      </c>
+      <c r="AS13">
+        <v>3</v>
+      </c>
+      <c r="AT13">
+        <v>12.5</v>
+      </c>
+      <c r="AU13">
         <v>12</v>
       </c>
-      <c r="AH13">
-        <v>22</v>
-      </c>
-      <c r="AI13">
-        <v>75</v>
-      </c>
-      <c r="AJ13">
-        <v>23</v>
-      </c>
-      <c r="AK13">
-        <v>22</v>
-      </c>
-      <c r="AL13">
-        <v>38</v>
-      </c>
-      <c r="AM13">
-        <v>110</v>
-      </c>
-      <c r="AN13">
-        <v>12.5</v>
-      </c>
-      <c r="AO13">
-        <v>75</v>
-      </c>
-      <c r="AP13">
+      <c r="AV13">
+        <v>2.84</v>
+      </c>
+      <c r="AW13">
+        <v>3</v>
+      </c>
+      <c r="AX13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ13">
         <v>14.5</v>
       </c>
-      <c r="AQ13">
-        <v>15.5</v>
-      </c>
-      <c r="AR13">
-        <v>4.8</v>
-      </c>
-      <c r="AS13">
-        <v>5.2</v>
-      </c>
-      <c r="AT13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU13">
-        <v>7.8</v>
-      </c>
-      <c r="AV13">
-        <v>16</v>
-      </c>
-      <c r="AW13">
-        <v>5</v>
-      </c>
-      <c r="AX13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY13">
+      <c r="BA13">
+        <v>2.92</v>
+      </c>
+      <c r="BB13">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ13">
-        <v>15.5</v>
-      </c>
-      <c r="BA13">
-        <v>5.1</v>
-      </c>
-      <c r="BB13">
-        <v>16.5</v>
-      </c>
       <c r="BC13">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD13">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="BE13">
-        <v>5.2</v>
+        <v>2.92</v>
       </c>
       <c r="BF13">
-        <v>8.199999999999999</v>
+        <v>2.24</v>
       </c>
       <c r="BG13">
-        <v>5.1</v>
+        <v>2.92</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F14">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="H14">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="J14">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="K14">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P14">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="F15">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="G15">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="H15">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="I15">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="J15">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="K15">
         <v>6</v>
@@ -4149,208 +4248,3596 @@
         <v>1.01</v>
       </c>
       <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>7.2</v>
+      </c>
+      <c r="O15">
+        <v>1.06</v>
+      </c>
+      <c r="P15">
+        <v>3.7</v>
+      </c>
+      <c r="Q15">
+        <v>1.29</v>
+      </c>
+      <c r="R15">
+        <v>2.02</v>
+      </c>
+      <c r="S15">
+        <v>1.59</v>
+      </c>
+      <c r="T15">
+        <v>1.35</v>
+      </c>
+      <c r="U15">
+        <v>2.66</v>
+      </c>
+      <c r="V15">
+        <v>1.18</v>
+      </c>
+      <c r="W15">
+        <v>2.64</v>
+      </c>
+      <c r="X15">
+        <v>75</v>
+      </c>
+      <c r="Y15">
+        <v>50</v>
+      </c>
+      <c r="Z15">
+        <v>75</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>26</v>
+      </c>
+      <c r="AC15">
+        <v>19</v>
+      </c>
+      <c r="AD15">
+        <v>32</v>
+      </c>
+      <c r="AE15">
+        <v>70</v>
+      </c>
+      <c r="AF15">
+        <v>22</v>
+      </c>
+      <c r="AG15">
+        <v>15.5</v>
+      </c>
+      <c r="AH15">
+        <v>21</v>
+      </c>
+      <c r="AI15">
+        <v>55</v>
+      </c>
+      <c r="AJ15">
+        <v>24</v>
+      </c>
+      <c r="AK15">
+        <v>20</v>
+      </c>
+      <c r="AL15">
+        <v>25</v>
+      </c>
+      <c r="AM15">
+        <v>60</v>
+      </c>
+      <c r="AN15">
+        <v>5.1</v>
+      </c>
+      <c r="AO15">
+        <v>36</v>
+      </c>
+      <c r="AP15">
         <v>1.03</v>
       </c>
-      <c r="N15">
+      <c r="AQ15">
+        <v>1.03</v>
+      </c>
+      <c r="AR15">
+        <v>1.03</v>
+      </c>
+      <c r="AS15">
+        <v>1.03</v>
+      </c>
+      <c r="AT15">
+        <v>14.5</v>
+      </c>
+      <c r="AU15">
+        <v>10</v>
+      </c>
+      <c r="AV15">
+        <v>18</v>
+      </c>
+      <c r="AW15">
+        <v>1.03</v>
+      </c>
+      <c r="AX15">
+        <v>11</v>
+      </c>
+      <c r="AY15">
+        <v>8.6</v>
+      </c>
+      <c r="AZ15">
+        <v>11.5</v>
+      </c>
+      <c r="BA15">
+        <v>1.03</v>
+      </c>
+      <c r="BB15">
+        <v>12.5</v>
+      </c>
+      <c r="BC15">
+        <v>10</v>
+      </c>
+      <c r="BD15">
+        <v>13.5</v>
+      </c>
+      <c r="BE15">
+        <v>1.03</v>
+      </c>
+      <c r="BF15">
+        <v>2.92</v>
+      </c>
+      <c r="BG15">
+        <v>18.5</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" t="s">
+        <v>143</v>
+      </c>
+      <c r="F16">
+        <v>3.55</v>
+      </c>
+      <c r="G16">
+        <v>3.75</v>
+      </c>
+      <c r="H16">
+        <v>2.58</v>
+      </c>
+      <c r="I16">
+        <v>2.72</v>
+      </c>
+      <c r="J16">
+        <v>2.84</v>
+      </c>
+      <c r="K16">
+        <v>3.05</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>2.52</v>
+      </c>
+      <c r="O16">
+        <v>1.5</v>
+      </c>
+      <c r="P16">
+        <v>1.52</v>
+      </c>
+      <c r="Q16">
+        <v>2.62</v>
+      </c>
+      <c r="R16">
+        <v>1.19</v>
+      </c>
+      <c r="S16">
+        <v>4.8</v>
+      </c>
+      <c r="T16">
+        <v>1.01</v>
+      </c>
+      <c r="U16">
+        <v>1.75</v>
+      </c>
+      <c r="V16">
+        <v>1.58</v>
+      </c>
+      <c r="W16">
+        <v>1.36</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>8</v>
+      </c>
+      <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>1000</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>17</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>65</v>
+      </c>
+      <c r="AJ16">
+        <v>75</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>95</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>75</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16">
+        <v>6.8</v>
+      </c>
+      <c r="AR16">
+        <v>1.03</v>
+      </c>
+      <c r="AS16">
+        <v>1.03</v>
+      </c>
+      <c r="AT16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU16">
+        <v>6</v>
+      </c>
+      <c r="AV16">
+        <v>1.03</v>
+      </c>
+      <c r="AW16">
+        <v>1.03</v>
+      </c>
+      <c r="AX16">
+        <v>1.03</v>
+      </c>
+      <c r="AY16">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16">
+        <v>1.03</v>
+      </c>
+      <c r="BA16">
+        <v>1.03</v>
+      </c>
+      <c r="BB16">
+        <v>1.03</v>
+      </c>
+      <c r="BC16">
+        <v>1.03</v>
+      </c>
+      <c r="BD16">
+        <v>1.03</v>
+      </c>
+      <c r="BE16">
+        <v>1.03</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.01</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.01</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.01</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.01</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.01</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.01</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" t="s">
+        <v>144</v>
+      </c>
+      <c r="F17">
+        <v>3.3</v>
+      </c>
+      <c r="G17">
+        <v>3.7</v>
+      </c>
+      <c r="H17">
+        <v>2.4</v>
+      </c>
+      <c r="I17">
+        <v>2.64</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17">
+        <v>3.4</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.1</v>
+      </c>
+      <c r="N17">
+        <v>2.56</v>
+      </c>
+      <c r="O17">
+        <v>1.43</v>
+      </c>
+      <c r="P17">
+        <v>1.53</v>
+      </c>
+      <c r="Q17">
+        <v>2.28</v>
+      </c>
+      <c r="R17">
+        <v>1.2</v>
+      </c>
+      <c r="S17">
+        <v>3.9</v>
+      </c>
+      <c r="T17">
+        <v>1.01</v>
+      </c>
+      <c r="U17">
+        <v>1.01</v>
+      </c>
+      <c r="V17">
+        <v>1.6</v>
+      </c>
+      <c r="W17">
+        <v>1.37</v>
+      </c>
+      <c r="X17">
+        <v>12.5</v>
+      </c>
+      <c r="Y17">
+        <v>9</v>
+      </c>
+      <c r="Z17">
+        <v>16</v>
+      </c>
+      <c r="AA17">
+        <v>40</v>
+      </c>
+      <c r="AB17">
+        <v>11</v>
+      </c>
+      <c r="AC17">
+        <v>7.6</v>
+      </c>
+      <c r="AD17">
+        <v>12.5</v>
+      </c>
+      <c r="AE17">
+        <v>34</v>
+      </c>
+      <c r="AF17">
+        <v>24</v>
+      </c>
+      <c r="AG17">
+        <v>15.5</v>
+      </c>
+      <c r="AH17">
+        <v>22</v>
+      </c>
+      <c r="AI17">
+        <v>65</v>
+      </c>
+      <c r="AJ17">
+        <v>85</v>
+      </c>
+      <c r="AK17">
+        <v>60</v>
+      </c>
+      <c r="AL17">
+        <v>80</v>
+      </c>
+      <c r="AM17">
+        <v>170</v>
+      </c>
+      <c r="AN17">
+        <v>70</v>
+      </c>
+      <c r="AO17">
+        <v>34</v>
+      </c>
+      <c r="AP17">
+        <v>7.6</v>
+      </c>
+      <c r="AQ17">
+        <v>7.2</v>
+      </c>
+      <c r="AR17">
+        <v>12.5</v>
+      </c>
+      <c r="AS17">
+        <v>30</v>
+      </c>
+      <c r="AT17">
+        <v>9</v>
+      </c>
+      <c r="AU17">
+        <v>6.2</v>
+      </c>
+      <c r="AV17">
+        <v>10</v>
+      </c>
+      <c r="AW17">
+        <v>1.03</v>
+      </c>
+      <c r="AX17">
+        <v>19</v>
+      </c>
+      <c r="AY17">
+        <v>12.5</v>
+      </c>
+      <c r="AZ17">
+        <v>17</v>
+      </c>
+      <c r="BA17">
+        <v>1.03</v>
+      </c>
+      <c r="BB17">
+        <v>1.03</v>
+      </c>
+      <c r="BC17">
+        <v>1.03</v>
+      </c>
+      <c r="BD17">
+        <v>1.03</v>
+      </c>
+      <c r="BE17">
+        <v>1.03</v>
+      </c>
+      <c r="BF17">
+        <v>48</v>
+      </c>
+      <c r="BG17">
+        <v>26</v>
+      </c>
+      <c r="BH17">
+        <v>3.5</v>
+      </c>
+      <c r="BI17">
+        <v>2.36</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.01</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.01</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.01</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.01</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F18">
+        <v>2.42</v>
+      </c>
+      <c r="G18">
+        <v>2.72</v>
+      </c>
+      <c r="H18">
+        <v>2.38</v>
+      </c>
+      <c r="I18">
+        <v>2.72</v>
+      </c>
+      <c r="J18">
+        <v>4.3</v>
+      </c>
+      <c r="K18">
+        <v>5</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>8.6</v>
+      </c>
+      <c r="O18">
+        <v>1.09</v>
+      </c>
+      <c r="P18">
+        <v>3.65</v>
+      </c>
+      <c r="Q18">
+        <v>1.3</v>
+      </c>
+      <c r="R18">
+        <v>2.08</v>
+      </c>
+      <c r="S18">
+        <v>1.75</v>
+      </c>
+      <c r="T18">
+        <v>1.01</v>
+      </c>
+      <c r="U18">
+        <v>1.01</v>
+      </c>
+      <c r="V18">
+        <v>1.58</v>
+      </c>
+      <c r="W18">
+        <v>1.58</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>40</v>
+      </c>
+      <c r="Z18">
+        <v>44</v>
+      </c>
+      <c r="AA18">
+        <v>55</v>
+      </c>
+      <c r="AB18">
+        <v>40</v>
+      </c>
+      <c r="AC18">
+        <v>20</v>
+      </c>
+      <c r="AD18">
+        <v>21</v>
+      </c>
+      <c r="AE18">
+        <v>34</v>
+      </c>
+      <c r="AF18">
+        <v>44</v>
+      </c>
+      <c r="AG18">
+        <v>21</v>
+      </c>
+      <c r="AH18">
+        <v>20</v>
+      </c>
+      <c r="AI18">
+        <v>34</v>
+      </c>
+      <c r="AJ18">
+        <v>55</v>
+      </c>
+      <c r="AK18">
+        <v>34</v>
+      </c>
+      <c r="AL18">
+        <v>34</v>
+      </c>
+      <c r="AM18">
+        <v>50</v>
+      </c>
+      <c r="AN18">
+        <v>12.5</v>
+      </c>
+      <c r="AO18">
+        <v>12.5</v>
+      </c>
+      <c r="AP18">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18">
+        <v>16.5</v>
+      </c>
+      <c r="AR18">
+        <v>16.5</v>
+      </c>
+      <c r="AS18">
+        <v>1.03</v>
+      </c>
+      <c r="AT18">
+        <v>16.5</v>
+      </c>
+      <c r="AU18">
+        <v>8.4</v>
+      </c>
+      <c r="AV18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW18">
+        <v>14</v>
+      </c>
+      <c r="AX18">
+        <v>16.5</v>
+      </c>
+      <c r="AY18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ18">
+        <v>8.4</v>
+      </c>
+      <c r="BA18">
+        <v>14</v>
+      </c>
+      <c r="BB18">
+        <v>1.03</v>
+      </c>
+      <c r="BC18">
+        <v>13.5</v>
+      </c>
+      <c r="BD18">
+        <v>14</v>
+      </c>
+      <c r="BE18">
+        <v>1.03</v>
+      </c>
+      <c r="BF18">
+        <v>5.4</v>
+      </c>
+      <c r="BG18">
+        <v>5.4</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>1.01</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.01</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.01</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.01</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.01</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>1.01</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.01</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F19">
+        <v>1.33</v>
+      </c>
+      <c r="G19">
+        <v>1.5</v>
+      </c>
+      <c r="H19">
+        <v>3.05</v>
+      </c>
+      <c r="I19">
+        <v>870</v>
+      </c>
+      <c r="J19">
+        <v>4.3</v>
+      </c>
+      <c r="K19">
+        <v>950</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>3</v>
+      </c>
+      <c r="O19">
+        <v>1.01</v>
+      </c>
+      <c r="P19">
+        <v>1.91</v>
+      </c>
+      <c r="Q19">
+        <v>1.78</v>
+      </c>
+      <c r="R19">
+        <v>1.13</v>
+      </c>
+      <c r="S19">
+        <v>1.31</v>
+      </c>
+      <c r="T19">
+        <v>1.01</v>
+      </c>
+      <c r="U19">
+        <v>1.01</v>
+      </c>
+      <c r="V19">
+        <v>1.02</v>
+      </c>
+      <c r="W19">
+        <v>3</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>1000</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.01</v>
+      </c>
+      <c r="AQ19">
+        <v>1.01</v>
+      </c>
+      <c r="AR19">
+        <v>1.01</v>
+      </c>
+      <c r="AS19">
+        <v>1.01</v>
+      </c>
+      <c r="AT19">
+        <v>1.01</v>
+      </c>
+      <c r="AU19">
+        <v>1.01</v>
+      </c>
+      <c r="AV19">
+        <v>1.01</v>
+      </c>
+      <c r="AW19">
+        <v>1.01</v>
+      </c>
+      <c r="AX19">
+        <v>1.01</v>
+      </c>
+      <c r="AY19">
+        <v>1.01</v>
+      </c>
+      <c r="AZ19">
+        <v>1.01</v>
+      </c>
+      <c r="BA19">
+        <v>1.01</v>
+      </c>
+      <c r="BB19">
+        <v>1.01</v>
+      </c>
+      <c r="BC19">
+        <v>1.01</v>
+      </c>
+      <c r="BD19">
+        <v>1.01</v>
+      </c>
+      <c r="BE19">
+        <v>1.01</v>
+      </c>
+      <c r="BF19">
+        <v>1.01</v>
+      </c>
+      <c r="BG19">
+        <v>1.01</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.01</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.01</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20">
+        <v>2.76</v>
+      </c>
+      <c r="G20">
+        <v>3.3</v>
+      </c>
+      <c r="H20">
+        <v>2.76</v>
+      </c>
+      <c r="I20">
+        <v>3.5</v>
+      </c>
+      <c r="J20">
+        <v>2.6</v>
+      </c>
+      <c r="K20">
+        <v>3.45</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.01</v>
+      </c>
+      <c r="N20">
+        <v>1.36</v>
+      </c>
+      <c r="O20">
+        <v>1.01</v>
+      </c>
+      <c r="P20">
+        <v>1.36</v>
+      </c>
+      <c r="Q20">
+        <v>2.38</v>
+      </c>
+      <c r="R20">
+        <v>1.13</v>
+      </c>
+      <c r="S20">
+        <v>2.38</v>
+      </c>
+      <c r="T20">
+        <v>1.01</v>
+      </c>
+      <c r="U20">
+        <v>1.01</v>
+      </c>
+      <c r="V20">
+        <v>1.4</v>
+      </c>
+      <c r="W20">
+        <v>1.43</v>
+      </c>
+      <c r="X20">
+        <v>1000</v>
+      </c>
+      <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>1000</v>
+      </c>
+      <c r="AC20">
+        <v>1000</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20">
+        <v>1.01</v>
+      </c>
+      <c r="AR20">
+        <v>1.01</v>
+      </c>
+      <c r="AS20">
+        <v>1.01</v>
+      </c>
+      <c r="AT20">
+        <v>1.01</v>
+      </c>
+      <c r="AU20">
+        <v>1.01</v>
+      </c>
+      <c r="AV20">
+        <v>1.01</v>
+      </c>
+      <c r="AW20">
+        <v>1.01</v>
+      </c>
+      <c r="AX20">
+        <v>1.01</v>
+      </c>
+      <c r="AY20">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20">
+        <v>1.01</v>
+      </c>
+      <c r="BA20">
+        <v>1.01</v>
+      </c>
+      <c r="BB20">
+        <v>1.01</v>
+      </c>
+      <c r="BC20">
+        <v>1.01</v>
+      </c>
+      <c r="BD20">
+        <v>1.01</v>
+      </c>
+      <c r="BE20">
+        <v>1.01</v>
+      </c>
+      <c r="BF20">
+        <v>1.01</v>
+      </c>
+      <c r="BG20">
+        <v>1.01</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.01</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.01</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.01</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.01</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21">
+        <v>2.02</v>
+      </c>
+      <c r="G21">
+        <v>2.56</v>
+      </c>
+      <c r="H21">
+        <v>3.7</v>
+      </c>
+      <c r="I21">
+        <v>6.8</v>
+      </c>
+      <c r="J21">
+        <v>2.48</v>
+      </c>
+      <c r="K21">
+        <v>4.3</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.11</v>
+      </c>
+      <c r="N21">
+        <v>1.91</v>
+      </c>
+      <c r="O21">
+        <v>1.6</v>
+      </c>
+      <c r="P21">
+        <v>1.3</v>
+      </c>
+      <c r="Q21">
+        <v>2.62</v>
+      </c>
+      <c r="R21">
+        <v>1.13</v>
+      </c>
+      <c r="S21">
+        <v>2.62</v>
+      </c>
+      <c r="T21">
+        <v>1.01</v>
+      </c>
+      <c r="U21">
+        <v>1.01</v>
+      </c>
+      <c r="V21">
+        <v>1.16</v>
+      </c>
+      <c r="W21">
+        <v>1.64</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>15</v>
+      </c>
+      <c r="Z21">
+        <v>46</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>1000</v>
+      </c>
+      <c r="AC21">
+        <v>1000</v>
+      </c>
+      <c r="AD21">
+        <v>30</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>1000</v>
+      </c>
+      <c r="AG21">
+        <v>16.5</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>48</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21">
+        <v>1.01</v>
+      </c>
+      <c r="AR21">
+        <v>1.01</v>
+      </c>
+      <c r="AS21">
+        <v>1.01</v>
+      </c>
+      <c r="AT21">
+        <v>1.01</v>
+      </c>
+      <c r="AU21">
+        <v>1.01</v>
+      </c>
+      <c r="AV21">
+        <v>1.01</v>
+      </c>
+      <c r="AW21">
+        <v>1.01</v>
+      </c>
+      <c r="AX21">
+        <v>1.01</v>
+      </c>
+      <c r="AY21">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21">
+        <v>1.01</v>
+      </c>
+      <c r="BA21">
+        <v>1.01</v>
+      </c>
+      <c r="BB21">
+        <v>1.01</v>
+      </c>
+      <c r="BC21">
+        <v>1.01</v>
+      </c>
+      <c r="BD21">
+        <v>1.01</v>
+      </c>
+      <c r="BE21">
+        <v>1.01</v>
+      </c>
+      <c r="BF21">
+        <v>1.01</v>
+      </c>
+      <c r="BG21">
+        <v>1.01</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.01</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>1.01</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.01</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>1.01</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>1.01</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.01</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>1.01</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>1.01</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" t="s">
+        <v>149</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>5.6</v>
+      </c>
+      <c r="H22">
+        <v>1.98</v>
+      </c>
+      <c r="I22">
+        <v>2.26</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22">
+        <v>4.1</v>
+      </c>
+      <c r="L22">
+        <v>1.51</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>2.08</v>
+      </c>
+      <c r="O22">
+        <v>1.35</v>
+      </c>
+      <c r="P22">
+        <v>1.39</v>
+      </c>
+      <c r="Q22">
+        <v>2.7</v>
+      </c>
+      <c r="R22">
+        <v>1.13</v>
+      </c>
+      <c r="S22">
+        <v>2.7</v>
+      </c>
+      <c r="T22">
+        <v>1.01</v>
+      </c>
+      <c r="U22">
+        <v>1.01</v>
+      </c>
+      <c r="V22">
+        <v>1.79</v>
+      </c>
+      <c r="W22">
+        <v>1.21</v>
+      </c>
+      <c r="X22">
+        <v>1000</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>1000</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22">
+        <v>1.01</v>
+      </c>
+      <c r="AR22">
+        <v>1.01</v>
+      </c>
+      <c r="AS22">
+        <v>1.01</v>
+      </c>
+      <c r="AT22">
+        <v>1.01</v>
+      </c>
+      <c r="AU22">
+        <v>1.01</v>
+      </c>
+      <c r="AV22">
+        <v>1.01</v>
+      </c>
+      <c r="AW22">
+        <v>1.01</v>
+      </c>
+      <c r="AX22">
+        <v>1.01</v>
+      </c>
+      <c r="AY22">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22">
+        <v>1.01</v>
+      </c>
+      <c r="BA22">
+        <v>1.01</v>
+      </c>
+      <c r="BB22">
+        <v>1.01</v>
+      </c>
+      <c r="BC22">
+        <v>1.01</v>
+      </c>
+      <c r="BD22">
+        <v>1.01</v>
+      </c>
+      <c r="BE22">
+        <v>1.01</v>
+      </c>
+      <c r="BF22">
+        <v>1.01</v>
+      </c>
+      <c r="BG22">
+        <v>1.01</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>1.01</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.01</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>1.01</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>1.01</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.01</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>1.01</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.01</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23">
+        <v>1.75</v>
+      </c>
+      <c r="G23">
+        <v>1.89</v>
+      </c>
+      <c r="H23">
+        <v>4.5</v>
+      </c>
+      <c r="I23">
+        <v>5.4</v>
+      </c>
+      <c r="J23">
+        <v>3.95</v>
+      </c>
+      <c r="K23">
+        <v>4.3</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>2.04</v>
+      </c>
+      <c r="Q23">
+        <v>1.8</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>1.76</v>
+      </c>
+      <c r="U23">
+        <v>2.1</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>18</v>
+      </c>
+      <c r="Y23">
+        <v>22</v>
+      </c>
+      <c r="Z23">
+        <v>46</v>
+      </c>
+      <c r="AA23">
+        <v>130</v>
+      </c>
+      <c r="AB23">
+        <v>10</v>
+      </c>
+      <c r="AC23">
+        <v>9.6</v>
+      </c>
+      <c r="AD23">
+        <v>23</v>
+      </c>
+      <c r="AE23">
+        <v>65</v>
+      </c>
+      <c r="AF23">
+        <v>13.5</v>
+      </c>
+      <c r="AG23">
+        <v>12</v>
+      </c>
+      <c r="AH23">
+        <v>22</v>
+      </c>
+      <c r="AI23">
+        <v>75</v>
+      </c>
+      <c r="AJ23">
+        <v>23</v>
+      </c>
+      <c r="AK23">
+        <v>22</v>
+      </c>
+      <c r="AL23">
+        <v>38</v>
+      </c>
+      <c r="AM23">
+        <v>110</v>
+      </c>
+      <c r="AN23">
+        <v>12.5</v>
+      </c>
+      <c r="AO23">
+        <v>75</v>
+      </c>
+      <c r="AP23">
+        <v>14.5</v>
+      </c>
+      <c r="AQ23">
+        <v>15.5</v>
+      </c>
+      <c r="AR23">
+        <v>5.1</v>
+      </c>
+      <c r="AS23">
+        <v>5.6</v>
+      </c>
+      <c r="AT23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU23">
+        <v>7.8</v>
+      </c>
+      <c r="AV23">
+        <v>16</v>
+      </c>
+      <c r="AW23">
+        <v>5.3</v>
+      </c>
+      <c r="AX23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ23">
+        <v>15.5</v>
+      </c>
+      <c r="BA23">
+        <v>5.3</v>
+      </c>
+      <c r="BB23">
+        <v>16.5</v>
+      </c>
+      <c r="BC23">
+        <v>15.5</v>
+      </c>
+      <c r="BD23">
+        <v>5</v>
+      </c>
+      <c r="BE23">
+        <v>5.5</v>
+      </c>
+      <c r="BF23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG23">
+        <v>5.4</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" t="s">
+        <v>123</v>
+      </c>
+      <c r="E24" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24">
+        <v>1.96</v>
+      </c>
+      <c r="G24">
+        <v>2.02</v>
+      </c>
+      <c r="H24">
+        <v>4</v>
+      </c>
+      <c r="I24">
+        <v>4.3</v>
+      </c>
+      <c r="J24">
+        <v>3.9</v>
+      </c>
+      <c r="K24">
+        <v>3.95</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1.06</v>
+      </c>
+      <c r="N24">
+        <v>4.2</v>
+      </c>
+      <c r="O24">
+        <v>1.28</v>
+      </c>
+      <c r="P24">
+        <v>2.1</v>
+      </c>
+      <c r="Q24">
+        <v>1.84</v>
+      </c>
+      <c r="R24">
+        <v>1.43</v>
+      </c>
+      <c r="S24">
+        <v>3.1</v>
+      </c>
+      <c r="T24">
+        <v>1.75</v>
+      </c>
+      <c r="U24">
+        <v>2.26</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>18</v>
+      </c>
+      <c r="Y24">
+        <v>19.5</v>
+      </c>
+      <c r="Z24">
+        <v>34</v>
+      </c>
+      <c r="AA24">
+        <v>100</v>
+      </c>
+      <c r="AB24">
+        <v>10.5</v>
+      </c>
+      <c r="AC24">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD24">
+        <v>18</v>
+      </c>
+      <c r="AE24">
+        <v>60</v>
+      </c>
+      <c r="AF24">
+        <v>14.5</v>
+      </c>
+      <c r="AG24">
+        <v>11</v>
+      </c>
+      <c r="AH24">
+        <v>19</v>
+      </c>
+      <c r="AI24">
+        <v>65</v>
+      </c>
+      <c r="AJ24">
+        <v>23</v>
+      </c>
+      <c r="AK24">
+        <v>23</v>
+      </c>
+      <c r="AL24">
+        <v>36</v>
+      </c>
+      <c r="AM24">
+        <v>110</v>
+      </c>
+      <c r="AN24">
+        <v>12.5</v>
+      </c>
+      <c r="AO24">
+        <v>55</v>
+      </c>
+      <c r="AP24">
+        <v>15</v>
+      </c>
+      <c r="AQ24">
+        <v>14.5</v>
+      </c>
+      <c r="AR24">
+        <v>21</v>
+      </c>
+      <c r="AS24">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU24">
+        <v>7.8</v>
+      </c>
+      <c r="AV24">
+        <v>15</v>
+      </c>
+      <c r="AW24">
+        <v>40</v>
+      </c>
+      <c r="AX24">
+        <v>11</v>
+      </c>
+      <c r="AY24">
+        <v>9.4</v>
+      </c>
+      <c r="AZ24">
+        <v>15.5</v>
+      </c>
+      <c r="BA24">
+        <v>28</v>
+      </c>
+      <c r="BB24">
+        <v>18.5</v>
+      </c>
+      <c r="BC24">
+        <v>16.5</v>
+      </c>
+      <c r="BD24">
+        <v>22</v>
+      </c>
+      <c r="BE24">
+        <v>36</v>
+      </c>
+      <c r="BF24">
+        <v>10.5</v>
+      </c>
+      <c r="BG24">
+        <v>26</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.04</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.04</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.04</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.04</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.04</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.04</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.04</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.04</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.04</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>1.04</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>124</v>
+      </c>
+      <c r="E25" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25">
+        <v>1.04</v>
+      </c>
+      <c r="G25">
+        <v>1000</v>
+      </c>
+      <c r="H25">
+        <v>1.04</v>
+      </c>
+      <c r="I25">
+        <v>1000</v>
+      </c>
+      <c r="J25">
+        <v>1.04</v>
+      </c>
+      <c r="K25">
+        <v>950</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1.24</v>
+      </c>
+      <c r="Q25">
+        <v>1.01</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
+      </c>
+      <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
+        <v>0</v>
+      </c>
+      <c r="BU25">
+        <v>0</v>
+      </c>
+      <c r="BV25">
+        <v>0</v>
+      </c>
+      <c r="BW25">
+        <v>0</v>
+      </c>
+      <c r="BX25">
+        <v>0</v>
+      </c>
+      <c r="BY25">
+        <v>0</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F26">
+        <v>1.37</v>
+      </c>
+      <c r="G26">
+        <v>1.39</v>
+      </c>
+      <c r="H26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I26">
+        <v>9.4</v>
+      </c>
+      <c r="J26">
+        <v>5.9</v>
+      </c>
+      <c r="K26">
+        <v>6</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.03</v>
+      </c>
+      <c r="N26">
+        <v>6.4</v>
+      </c>
+      <c r="O26">
+        <v>1.17</v>
+      </c>
+      <c r="P26">
+        <v>2.9</v>
+      </c>
+      <c r="Q26">
+        <v>1.49</v>
+      </c>
+      <c r="R26">
+        <v>1.75</v>
+      </c>
+      <c r="S26">
+        <v>2.26</v>
+      </c>
+      <c r="T26">
+        <v>1.78</v>
+      </c>
+      <c r="U26">
+        <v>2.2</v>
+      </c>
+      <c r="V26">
+        <v>1.11</v>
+      </c>
+      <c r="W26">
+        <v>3.55</v>
+      </c>
+      <c r="X26">
+        <v>34</v>
+      </c>
+      <c r="Y26">
+        <v>40</v>
+      </c>
+      <c r="Z26">
+        <v>85</v>
+      </c>
+      <c r="AA26">
+        <v>310</v>
+      </c>
+      <c r="AB26">
+        <v>12.5</v>
+      </c>
+      <c r="AC26">
+        <v>13.5</v>
+      </c>
+      <c r="AD26">
+        <v>34</v>
+      </c>
+      <c r="AE26">
+        <v>120</v>
+      </c>
+      <c r="AF26">
+        <v>10.5</v>
+      </c>
+      <c r="AG26">
+        <v>10.5</v>
+      </c>
+      <c r="AH26">
+        <v>23</v>
+      </c>
+      <c r="AI26">
+        <v>90</v>
+      </c>
+      <c r="AJ26">
+        <v>12.5</v>
+      </c>
+      <c r="AK26">
+        <v>13.5</v>
+      </c>
+      <c r="AL26">
+        <v>29</v>
+      </c>
+      <c r="AM26">
+        <v>95</v>
+      </c>
+      <c r="AN26">
+        <v>4.6</v>
+      </c>
+      <c r="AO26">
+        <v>110</v>
+      </c>
+      <c r="AP26">
+        <v>28</v>
+      </c>
+      <c r="AQ26">
+        <v>23</v>
+      </c>
+      <c r="AR26">
+        <v>36</v>
+      </c>
+      <c r="AS26">
+        <v>14.5</v>
+      </c>
+      <c r="AT26">
+        <v>11</v>
+      </c>
+      <c r="AU26">
+        <v>12</v>
+      </c>
+      <c r="AV26">
+        <v>21</v>
+      </c>
+      <c r="AW26">
+        <v>13.5</v>
+      </c>
+      <c r="AX26">
+        <v>9.4</v>
+      </c>
+      <c r="AY26">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26">
+        <v>20</v>
+      </c>
+      <c r="BA26">
+        <v>36</v>
+      </c>
+      <c r="BB26">
+        <v>11</v>
+      </c>
+      <c r="BC26">
+        <v>12</v>
+      </c>
+      <c r="BD26">
+        <v>25</v>
+      </c>
+      <c r="BE26">
+        <v>38</v>
+      </c>
+      <c r="BF26">
+        <v>4.3</v>
+      </c>
+      <c r="BG26">
+        <v>40</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
+        <v>1.04</v>
+      </c>
+      <c r="BJ26">
+        <v>1000</v>
+      </c>
+      <c r="BK26">
+        <v>1.04</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>1.04</v>
+      </c>
+      <c r="BN26">
+        <v>1000</v>
+      </c>
+      <c r="BO26">
+        <v>1.04</v>
+      </c>
+      <c r="BP26">
+        <v>1000</v>
+      </c>
+      <c r="BQ26">
+        <v>1.04</v>
+      </c>
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
+        <v>1.04</v>
+      </c>
+      <c r="BT26">
+        <v>1000</v>
+      </c>
+      <c r="BU26">
+        <v>1.04</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>1.04</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>1.04</v>
+      </c>
+      <c r="BZ26">
+        <v>1000</v>
+      </c>
+      <c r="CA26">
+        <v>1.04</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" t="s">
+        <v>154</v>
+      </c>
+      <c r="F27">
+        <v>2.5</v>
+      </c>
+      <c r="G27">
+        <v>2.54</v>
+      </c>
+      <c r="H27">
+        <v>3.2</v>
+      </c>
+      <c r="I27">
+        <v>3.3</v>
+      </c>
+      <c r="J27">
+        <v>3.4</v>
+      </c>
+      <c r="K27">
+        <v>3.45</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>1.08</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>1.81</v>
+      </c>
+      <c r="Q27">
+        <v>2.16</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>1.85</v>
+      </c>
+      <c r="U27">
+        <v>2.04</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>13</v>
+      </c>
+      <c r="Y27">
+        <v>12</v>
+      </c>
+      <c r="Z27">
+        <v>28</v>
+      </c>
+      <c r="AA27">
+        <v>360</v>
+      </c>
+      <c r="AB27">
+        <v>10</v>
+      </c>
+      <c r="AC27">
+        <v>7.6</v>
+      </c>
+      <c r="AD27">
+        <v>15.5</v>
+      </c>
+      <c r="AE27">
+        <v>85</v>
+      </c>
+      <c r="AF27">
+        <v>18</v>
+      </c>
+      <c r="AG27">
+        <v>12.5</v>
+      </c>
+      <c r="AH27">
+        <v>24</v>
+      </c>
+      <c r="AI27">
+        <v>290</v>
+      </c>
+      <c r="AJ27">
+        <v>75</v>
+      </c>
+      <c r="AK27">
+        <v>44</v>
+      </c>
+      <c r="AL27">
+        <v>140</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>26</v>
+      </c>
+      <c r="AO27">
+        <v>75</v>
+      </c>
+      <c r="AP27">
+        <v>10.5</v>
+      </c>
+      <c r="AQ27">
+        <v>10</v>
+      </c>
+      <c r="AR27">
+        <v>18</v>
+      </c>
+      <c r="AS27">
+        <v>28</v>
+      </c>
+      <c r="AT27">
+        <v>8.4</v>
+      </c>
+      <c r="AU27">
         <v>6.6</v>
       </c>
-      <c r="O15">
-        <v>1.16</v>
-      </c>
-      <c r="P15">
+      <c r="AV27">
+        <v>13</v>
+      </c>
+      <c r="AW27">
+        <v>23</v>
+      </c>
+      <c r="AX27">
+        <v>13</v>
+      </c>
+      <c r="AY27">
+        <v>10.5</v>
+      </c>
+      <c r="AZ27">
+        <v>16</v>
+      </c>
+      <c r="BA27">
+        <v>28</v>
+      </c>
+      <c r="BB27">
+        <v>22</v>
+      </c>
+      <c r="BC27">
+        <v>18.5</v>
+      </c>
+      <c r="BD27">
+        <v>25</v>
+      </c>
+      <c r="BE27">
+        <v>38</v>
+      </c>
+      <c r="BF27">
+        <v>21</v>
+      </c>
+      <c r="BG27">
+        <v>22</v>
+      </c>
+      <c r="BH27">
+        <v>0</v>
+      </c>
+      <c r="BI27">
+        <v>0</v>
+      </c>
+      <c r="BJ27">
+        <v>0</v>
+      </c>
+      <c r="BK27">
+        <v>0</v>
+      </c>
+      <c r="BL27">
+        <v>0</v>
+      </c>
+      <c r="BM27">
+        <v>0</v>
+      </c>
+      <c r="BN27">
+        <v>0</v>
+      </c>
+      <c r="BO27">
+        <v>0</v>
+      </c>
+      <c r="BP27">
+        <v>0</v>
+      </c>
+      <c r="BQ27">
+        <v>0</v>
+      </c>
+      <c r="BR27">
+        <v>0</v>
+      </c>
+      <c r="BS27">
+        <v>0</v>
+      </c>
+      <c r="BT27">
+        <v>0</v>
+      </c>
+      <c r="BU27">
+        <v>0</v>
+      </c>
+      <c r="BV27">
+        <v>0</v>
+      </c>
+      <c r="BW27">
+        <v>0</v>
+      </c>
+      <c r="BX27">
+        <v>0</v>
+      </c>
+      <c r="BY27">
+        <v>0</v>
+      </c>
+      <c r="BZ27">
+        <v>0</v>
+      </c>
+      <c r="CA27">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28">
+        <v>1.55</v>
+      </c>
+      <c r="G28">
+        <v>1.6</v>
+      </c>
+      <c r="H28">
+        <v>6.8</v>
+      </c>
+      <c r="I28">
+        <v>8</v>
+      </c>
+      <c r="J28">
+        <v>4.2</v>
+      </c>
+      <c r="K28">
+        <v>4.6</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>1.79</v>
+      </c>
+      <c r="Q28">
+        <v>2.1</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28">
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <v>0</v>
+      </c>
+      <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <v>0</v>
+      </c>
+      <c r="BO28">
+        <v>0</v>
+      </c>
+      <c r="BP28">
+        <v>0</v>
+      </c>
+      <c r="BQ28">
+        <v>0</v>
+      </c>
+      <c r="BR28">
+        <v>0</v>
+      </c>
+      <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
+        <v>0</v>
+      </c>
+      <c r="BU28">
+        <v>0</v>
+      </c>
+      <c r="BV28">
+        <v>0</v>
+      </c>
+      <c r="BW28">
+        <v>0</v>
+      </c>
+      <c r="BX28">
+        <v>0</v>
+      </c>
+      <c r="BY28">
+        <v>0</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29">
+        <v>2.46</v>
+      </c>
+      <c r="G29">
+        <v>2.54</v>
+      </c>
+      <c r="H29">
         <v>2.9</v>
       </c>
-      <c r="Q15">
-        <v>1.48</v>
-      </c>
-      <c r="R15">
-        <v>1.75</v>
-      </c>
-      <c r="S15">
-        <v>2.22</v>
-      </c>
-      <c r="T15">
-        <v>1.78</v>
-      </c>
-      <c r="U15">
-        <v>2.22</v>
-      </c>
-      <c r="V15">
-        <v>1.11</v>
-      </c>
-      <c r="W15">
-        <v>3.6</v>
-      </c>
-      <c r="X15">
-        <v>34</v>
-      </c>
-      <c r="Y15">
-        <v>40</v>
-      </c>
-      <c r="Z15">
-        <v>85</v>
-      </c>
-      <c r="AA15">
-        <v>310</v>
-      </c>
-      <c r="AB15">
-        <v>12.5</v>
-      </c>
-      <c r="AC15">
-        <v>13.5</v>
-      </c>
-      <c r="AD15">
-        <v>34</v>
-      </c>
-      <c r="AE15">
-        <v>120</v>
-      </c>
-      <c r="AF15">
-        <v>10.5</v>
-      </c>
-      <c r="AG15">
-        <v>10.5</v>
-      </c>
-      <c r="AH15">
-        <v>23</v>
-      </c>
-      <c r="AI15">
-        <v>90</v>
-      </c>
-      <c r="AJ15">
-        <v>12.5</v>
-      </c>
-      <c r="AK15">
-        <v>13</v>
-      </c>
-      <c r="AL15">
-        <v>29</v>
-      </c>
-      <c r="AM15">
-        <v>100</v>
-      </c>
-      <c r="AN15">
-        <v>4.6</v>
-      </c>
-      <c r="AO15">
-        <v>120</v>
-      </c>
-      <c r="AP15">
-        <v>28</v>
-      </c>
-      <c r="AQ15">
-        <v>24</v>
-      </c>
-      <c r="AR15">
-        <v>36</v>
-      </c>
-      <c r="AS15">
-        <v>14.5</v>
-      </c>
-      <c r="AT15">
-        <v>11</v>
-      </c>
-      <c r="AU15">
-        <v>12</v>
-      </c>
-      <c r="AV15">
-        <v>21</v>
-      </c>
-      <c r="AW15">
-        <v>13.5</v>
-      </c>
-      <c r="AX15">
-        <v>9.4</v>
-      </c>
-      <c r="AY15">
-        <v>9.4</v>
-      </c>
-      <c r="AZ15">
-        <v>20</v>
-      </c>
-      <c r="BA15">
-        <v>36</v>
-      </c>
-      <c r="BB15">
-        <v>11</v>
-      </c>
-      <c r="BC15">
-        <v>12</v>
-      </c>
-      <c r="BD15">
-        <v>24</v>
-      </c>
-      <c r="BE15">
-        <v>13</v>
-      </c>
-      <c r="BF15">
-        <v>4.3</v>
-      </c>
-      <c r="BG15">
-        <v>40</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.04</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>1.04</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.04</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>1.04</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>1.04</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>1.04</v>
-      </c>
-      <c r="BT15">
-        <v>1000</v>
-      </c>
-      <c r="BU15">
-        <v>1.04</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>1.04</v>
-      </c>
-      <c r="BX15">
-        <v>1000</v>
-      </c>
-      <c r="BY15">
-        <v>1.04</v>
-      </c>
-      <c r="BZ15">
-        <v>1000</v>
-      </c>
-      <c r="CA15">
-        <v>1.04</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>124</v>
+      <c r="I29">
+        <v>3</v>
+      </c>
+      <c r="J29">
+        <v>3.7</v>
+      </c>
+      <c r="K29">
+        <v>3.8</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>2.5</v>
+      </c>
+      <c r="Q29">
+        <v>1.58</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29">
+        <v>0</v>
+      </c>
+      <c r="BK29">
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
+        <v>0</v>
+      </c>
+      <c r="BN29">
+        <v>0</v>
+      </c>
+      <c r="BO29">
+        <v>0</v>
+      </c>
+      <c r="BP29">
+        <v>0</v>
+      </c>
+      <c r="BQ29">
+        <v>0</v>
+      </c>
+      <c r="BR29">
+        <v>0</v>
+      </c>
+      <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29">
+        <v>0</v>
+      </c>
+      <c r="BU29">
+        <v>0</v>
+      </c>
+      <c r="BV29">
+        <v>0</v>
+      </c>
+      <c r="BW29">
+        <v>0</v>
+      </c>
+      <c r="BX29">
+        <v>0</v>
+      </c>
+      <c r="BY29">
+        <v>0</v>
+      </c>
+      <c r="BZ29">
+        <v>0</v>
+      </c>
+      <c r="CA29">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -487,7 +487,7 @@
     <t>Dinamo Zagreb</t>
   </si>
   <si>
-    <t>2026-08-24 14:54:40</t>
+    <t>2026-08-24 17:16:20</t>
   </si>
 </sst>
 </file>
@@ -1123,7 +1123,7 @@
         <v>4.4</v>
       </c>
       <c r="T2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U2">
         <v>1.69</v>
@@ -1144,7 +1144,7 @@
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AB2">
         <v>6.8</v>
@@ -1180,7 +1180,7 @@
         <v>70</v>
       </c>
       <c r="AM2">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN2">
         <v>13</v>
@@ -1195,7 +1195,7 @@
         <v>14.5</v>
       </c>
       <c r="AR2">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="AS2">
         <v>9</v>
@@ -1210,7 +1210,7 @@
         <v>24</v>
       </c>
       <c r="AW2">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2">
         <v>7.4</v>
@@ -1231,7 +1231,7 @@
         <v>18</v>
       </c>
       <c r="BD2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE2">
         <v>9</v>
@@ -1323,22 +1323,22 @@
         <v>130</v>
       </c>
       <c r="F3">
+        <v>2.36</v>
+      </c>
+      <c r="G3">
         <v>2.38</v>
       </c>
-      <c r="G3">
-        <v>2.5</v>
-      </c>
       <c r="H3">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1347,34 +1347,34 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q3">
         <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T3">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U3">
         <v>1.85</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="X3">
         <v>12.5</v>
@@ -1401,13 +1401,13 @@
         <v>65</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG3">
         <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI3">
         <v>85</v>
@@ -1428,7 +1428,7 @@
         <v>34</v>
       </c>
       <c r="AO3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP3">
         <v>8.4</v>
@@ -1440,7 +1440,7 @@
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1455,7 +1455,7 @@
         <v>36</v>
       </c>
       <c r="AX3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY3">
         <v>10</v>
@@ -1464,25 +1464,25 @@
         <v>18.5</v>
       </c>
       <c r="BA3">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BC3">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BD3">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE3">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF3">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG3">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1592,13 +1592,13 @@
         <v>3.8</v>
       </c>
       <c r="O4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P4">
         <v>1.96</v>
       </c>
       <c r="Q4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R4">
         <v>1.37</v>
@@ -1637,7 +1637,7 @@
         <v>12</v>
       </c>
       <c r="AD4">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AE4">
         <v>280</v>
@@ -1655,13 +1655,13 @@
         <v>220</v>
       </c>
       <c r="AJ4">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AK4">
         <v>17</v>
       </c>
       <c r="AL4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM4">
         <v>270</v>
@@ -1676,13 +1676,13 @@
         <v>14</v>
       </c>
       <c r="AQ4">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AR4">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
@@ -1694,7 +1694,7 @@
         <v>34</v>
       </c>
       <c r="AW4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX4">
         <v>6.4</v>
@@ -1703,10 +1703,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB4">
         <v>9.4</v>
@@ -1715,16 +1715,16 @@
         <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF4">
         <v>6</v>
       </c>
       <c r="BG4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4">
         <v>3.75</v>
@@ -1813,7 +1813,7 @@
         <v>3.6</v>
       </c>
       <c r="H5">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I5">
         <v>2.5</v>
@@ -1822,7 +1822,7 @@
         <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L5">
         <v>1.37</v>
@@ -1849,16 +1849,16 @@
         <v>4.2</v>
       </c>
       <c r="T5">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U5">
         <v>1.98</v>
       </c>
       <c r="V5">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X5">
         <v>11.5</v>
@@ -1951,10 +1951,10 @@
         <v>7.2</v>
       </c>
       <c r="BB5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BC5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD5">
         <v>38</v>
@@ -1963,7 +1963,7 @@
         <v>7.4</v>
       </c>
       <c r="BF5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG5">
         <v>6.2</v>
@@ -2055,16 +2055,16 @@
         <v>2.46</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="I6">
         <v>3.4</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2073,7 +2073,7 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>1.21</v>
@@ -2085,10 +2085,10 @@
         <v>1.65</v>
       </c>
       <c r="R6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S6">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T6">
         <v>1.54</v>
@@ -2097,7 +2097,7 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.68</v>
@@ -2294,7 +2294,7 @@
         <v>1.54</v>
       </c>
       <c r="G7">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="H7">
         <v>7.4</v>
@@ -2315,22 +2315,22 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q7">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S7">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="T7">
         <v>2.2</v>
@@ -2342,7 +2342,7 @@
         <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="X7">
         <v>15.5</v>
@@ -2429,7 +2429,7 @@
         <v>9</v>
       </c>
       <c r="AZ7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BA7">
         <v>5.7</v>
@@ -2533,13 +2533,13 @@
         <v>135</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G8">
         <v>600</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I8">
         <v>870</v>
@@ -2581,10 +2581,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2802,13 +2802,13 @@
         <v>5.7</v>
       </c>
       <c r="O9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P9">
         <v>2.62</v>
       </c>
       <c r="Q9">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="R9">
         <v>1.64</v>
@@ -2934,7 +2934,7 @@
         <v>7.6</v>
       </c>
       <c r="BG9">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3367,16 +3367,16 @@
         <v>24</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AT11">
         <v>14.5</v>
@@ -3388,7 +3388,7 @@
         <v>13.5</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AX11">
         <v>14</v>
@@ -3400,7 +3400,7 @@
         <v>10</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="BB11">
         <v>14</v>
@@ -3412,7 +3412,7 @@
         <v>12.5</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="BF11">
         <v>3.2</v>
@@ -3424,7 +3424,7 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ11">
         <v>11.5</v>
@@ -3436,7 +3436,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>21</v>
+        <v>2.26</v>
       </c>
       <c r="BN11">
         <v>7.6</v>
@@ -3448,31 +3448,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ11">
-        <v>6.8</v>
+        <v>2.02</v>
       </c>
       <c r="BR11">
         <v>21</v>
       </c>
       <c r="BS11">
-        <v>9.6</v>
+        <v>2.1</v>
       </c>
       <c r="BT11">
         <v>13</v>
       </c>
       <c r="BU11">
-        <v>6.2</v>
+        <v>1.99</v>
       </c>
       <c r="BV11">
         <v>38</v>
       </c>
       <c r="BW11">
-        <v>16.5</v>
+        <v>2.2</v>
       </c>
       <c r="BX11">
         <v>34</v>
       </c>
       <c r="BY11">
-        <v>16</v>
+        <v>2.2</v>
       </c>
       <c r="BZ11">
         <v>11</v>
@@ -3525,28 +3525,28 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P12">
         <v>3.7</v>
       </c>
       <c r="Q12">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R12">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="S12">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="T12">
         <v>1.29</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="V12">
         <v>1.66</v>
@@ -3555,61 +3555,61 @@
         <v>1.53</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
         <v>20</v>
@@ -3618,7 +3618,7 @@
         <v>20</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
         <v>1.03</v>
@@ -3645,7 +3645,7 @@
         <v>18.5</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
         <v>18.5</v>
@@ -3743,7 +3743,7 @@
         <v>140</v>
       </c>
       <c r="F13">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G13">
         <v>1.36</v>
@@ -3773,7 +3773,7 @@
         <v>1.07</v>
       </c>
       <c r="P13">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q13">
         <v>1.29</v>
@@ -3782,7 +3782,7 @@
         <v>2.12</v>
       </c>
       <c r="S13">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="T13">
         <v>1.48</v>
@@ -3988,16 +3988,16 @@
         <v>2.98</v>
       </c>
       <c r="G14">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H14">
         <v>2.1</v>
       </c>
       <c r="I14">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="J14">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K14">
         <v>5.4</v>
@@ -4033,10 +4033,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W14">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4227,23 +4227,23 @@
         <v>142</v>
       </c>
       <c r="F15">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="G15">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="H15">
+        <v>5.8</v>
+      </c>
+      <c r="I15">
+        <v>6.8</v>
+      </c>
+      <c r="J15">
         <v>5.5</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>6.4</v>
       </c>
-      <c r="J15">
-        <v>5.1</v>
-      </c>
-      <c r="K15">
-        <v>6</v>
-      </c>
       <c r="L15">
         <v>1.01</v>
       </c>
@@ -4251,34 +4251,34 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="O15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P15">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="Q15">
         <v>1.29</v>
       </c>
       <c r="R15">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="T15">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="U15">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="V15">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W15">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="X15">
         <v>75</v>
@@ -4290,100 +4290,100 @@
         <v>75</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB15">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AC15">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AD15">
         <v>32</v>
       </c>
       <c r="AE15">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF15">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AG15">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH15">
         <v>21</v>
       </c>
       <c r="AI15">
+        <v>48</v>
+      </c>
+      <c r="AJ15">
+        <v>18.5</v>
+      </c>
+      <c r="AK15">
+        <v>15</v>
+      </c>
+      <c r="AL15">
+        <v>22</v>
+      </c>
+      <c r="AM15">
         <v>55</v>
       </c>
-      <c r="AJ15">
-        <v>24</v>
-      </c>
-      <c r="AK15">
-        <v>20</v>
-      </c>
-      <c r="AL15">
-        <v>25</v>
-      </c>
-      <c r="AM15">
-        <v>60</v>
-      </c>
       <c r="AN15">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="AO15">
         <v>36</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AT15">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AV15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="AX15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY15">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BB15">
+        <v>15.5</v>
+      </c>
+      <c r="BC15">
         <v>12.5</v>
       </c>
-      <c r="BC15">
-        <v>10</v>
-      </c>
       <c r="BD15">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BF15">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="BG15">
         <v>18.5</v>
@@ -4478,7 +4478,7 @@
         <v>2.58</v>
       </c>
       <c r="I16">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J16">
         <v>2.84</v>
@@ -4487,16 +4487,16 @@
         <v>3.05</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N16">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O16">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P16">
         <v>1.52</v>
@@ -4511,49 +4511,49 @@
         <v>4.8</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U16">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V16">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
         <v>1.36</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y16">
         <v>8</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI16">
         <v>65</v>
@@ -4562,31 +4562,31 @@
         <v>75</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL16">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN16">
         <v>75</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ16">
         <v>6.8</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
         <v>8.800000000000001</v>
@@ -4595,34 +4595,34 @@
         <v>6</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
         <v>1.01</v>
@@ -4720,10 +4720,10 @@
         <v>2.4</v>
       </c>
       <c r="I17">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K17">
         <v>3.4</v>
@@ -4735,31 +4735,31 @@
         <v>1.1</v>
       </c>
       <c r="N17">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="O17">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="P17">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Q17">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R17">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S17">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V17">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W17">
         <v>1.37</v>
@@ -4840,7 +4840,7 @@
         <v>10</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
         <v>19</v>
@@ -4852,25 +4852,25 @@
         <v>17</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
         <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>3.5</v>
@@ -4882,55 +4882,55 @@
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="CB17" t="s">
         <v>157</v>
@@ -4956,16 +4956,16 @@
         <v>2.42</v>
       </c>
       <c r="G18">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I18">
         <v>2.72</v>
       </c>
       <c r="J18">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="K18">
         <v>5</v>
@@ -4977,10 +4977,10 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P18">
         <v>3.65</v>
@@ -4992,127 +4992,127 @@
         <v>2.08</v>
       </c>
       <c r="S18">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="V18">
         <v>1.58</v>
       </c>
       <c r="W18">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Y18">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Z18">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AA18">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB18">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AC18">
+        <v>16.5</v>
+      </c>
+      <c r="AD18">
+        <v>17.5</v>
+      </c>
+      <c r="AE18">
+        <v>28</v>
+      </c>
+      <c r="AF18">
+        <v>36</v>
+      </c>
+      <c r="AG18">
+        <v>17.5</v>
+      </c>
+      <c r="AH18">
+        <v>17</v>
+      </c>
+      <c r="AI18">
+        <v>28</v>
+      </c>
+      <c r="AJ18">
+        <v>48</v>
+      </c>
+      <c r="AK18">
+        <v>28</v>
+      </c>
+      <c r="AL18">
+        <v>28</v>
+      </c>
+      <c r="AM18">
+        <v>42</v>
+      </c>
+      <c r="AN18">
+        <v>10.5</v>
+      </c>
+      <c r="AO18">
+        <v>10.5</v>
+      </c>
+      <c r="AP18">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18">
+        <v>19.5</v>
+      </c>
+      <c r="AR18">
         <v>20</v>
       </c>
-      <c r="AD18">
-        <v>21</v>
-      </c>
-      <c r="AE18">
-        <v>34</v>
-      </c>
-      <c r="AF18">
-        <v>44</v>
-      </c>
-      <c r="AG18">
-        <v>21</v>
-      </c>
-      <c r="AH18">
+      <c r="AS18">
+        <v>1.01</v>
+      </c>
+      <c r="AT18">
+        <v>19.5</v>
+      </c>
+      <c r="AU18">
+        <v>10</v>
+      </c>
+      <c r="AV18">
+        <v>10.5</v>
+      </c>
+      <c r="AW18">
+        <v>16.5</v>
+      </c>
+      <c r="AX18">
         <v>20</v>
       </c>
-      <c r="AI18">
-        <v>34</v>
-      </c>
-      <c r="AJ18">
-        <v>55</v>
-      </c>
-      <c r="AK18">
-        <v>34</v>
-      </c>
-      <c r="AL18">
-        <v>34</v>
-      </c>
-      <c r="AM18">
-        <v>50</v>
-      </c>
-      <c r="AN18">
-        <v>12.5</v>
-      </c>
-      <c r="AO18">
-        <v>12.5</v>
-      </c>
-      <c r="AP18">
-        <v>1.03</v>
-      </c>
-      <c r="AQ18">
+      <c r="AY18">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18">
+        <v>10</v>
+      </c>
+      <c r="BA18">
         <v>16.5</v>
       </c>
-      <c r="AR18">
+      <c r="BB18">
+        <v>1.01</v>
+      </c>
+      <c r="BC18">
+        <v>16</v>
+      </c>
+      <c r="BD18">
         <v>16.5</v>
       </c>
-      <c r="AS18">
-        <v>1.03</v>
-      </c>
-      <c r="AT18">
-        <v>16.5</v>
-      </c>
-      <c r="AU18">
-        <v>8.4</v>
-      </c>
-      <c r="AV18">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW18">
-        <v>14</v>
-      </c>
-      <c r="AX18">
-        <v>16.5</v>
-      </c>
-      <c r="AY18">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ18">
-        <v>8.4</v>
-      </c>
-      <c r="BA18">
-        <v>14</v>
-      </c>
-      <c r="BB18">
-        <v>1.03</v>
-      </c>
-      <c r="BC18">
-        <v>13.5</v>
-      </c>
-      <c r="BD18">
-        <v>14</v>
-      </c>
       <c r="BE18">
         <v>1.03</v>
       </c>
       <c r="BF18">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG18">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5195,19 +5195,19 @@
         <v>146</v>
       </c>
       <c r="F19">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="G19">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="H19">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="I19">
         <v>870</v>
       </c>
       <c r="J19">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <v>950</v>
@@ -5219,22 +5219,22 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="O19">
         <v>1.01</v>
       </c>
       <c r="P19">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q19">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="R19">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="S19">
-        <v>1.31</v>
+        <v>2.72</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5243,10 +5243,10 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W19">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5303,52 +5303,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5437,46 +5437,46 @@
         <v>147</v>
       </c>
       <c r="F20">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="G20">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H20">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="I20">
         <v>3.5</v>
       </c>
       <c r="J20">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="K20">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N20">
-        <v>1.36</v>
+        <v>2.48</v>
       </c>
       <c r="O20">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="P20">
         <v>1.36</v>
       </c>
       <c r="Q20">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="R20">
         <v>1.13</v>
       </c>
       <c r="S20">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -5488,7 +5488,7 @@
         <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5545,52 +5545,52 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF20">
         <v>1.01</v>
@@ -5679,31 +5679,31 @@
         <v>148</v>
       </c>
       <c r="F21">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G21">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="H21">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="I21">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="J21">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="K21">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N21">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O21">
         <v>1.6</v>
@@ -5727,10 +5727,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="W21">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5745,10 +5745,10 @@
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD21">
         <v>30</v>
@@ -5757,82 +5757,82 @@
         <v>1000</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG21">
         <v>16.5</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI21">
         <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK21">
         <v>48</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM21">
         <v>1000</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO21">
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW21">
         <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB21">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD21">
         <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF21">
         <v>1.01</v>
@@ -5924,7 +5924,7 @@
         <v>4</v>
       </c>
       <c r="G22">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H22">
         <v>1.98</v>
@@ -5933,10 +5933,10 @@
         <v>2.26</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="K22">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L22">
         <v>1.51</v>
@@ -5945,10 +5945,10 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="O22">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="P22">
         <v>1.39</v>
@@ -6029,52 +6029,52 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF22">
         <v>1.01</v>
@@ -6163,226 +6163,226 @@
         <v>150</v>
       </c>
       <c r="F23">
-        <v>1.75</v>
+        <v>1.09</v>
       </c>
       <c r="G23">
-        <v>1.89</v>
+        <v>11.5</v>
       </c>
       <c r="H23">
-        <v>4.5</v>
+        <v>2.04</v>
       </c>
       <c r="I23">
-        <v>5.4</v>
+        <v>990</v>
       </c>
       <c r="J23">
-        <v>3.95</v>
+        <v>2.04</v>
       </c>
       <c r="K23">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P23">
-        <v>2.04</v>
+        <v>1.12</v>
       </c>
       <c r="Q23">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T23">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U23">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X23">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR23">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU23">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
         <v>157</v>
@@ -6405,16 +6405,16 @@
         <v>151</v>
       </c>
       <c r="F24">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G24">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I24">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J24">
         <v>3.9</v>
@@ -6423,7 +6423,7 @@
         <v>3.95</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
         <v>1.06</v>
@@ -6435,10 +6435,10 @@
         <v>1.28</v>
       </c>
       <c r="P24">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q24">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R24">
         <v>1.43</v>
@@ -6453,22 +6453,22 @@
         <v>2.26</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X24">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y24">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z24">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB24">
         <v>10.5</v>
@@ -6477,64 +6477,64 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD24">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE24">
+        <v>50</v>
+      </c>
+      <c r="AF24">
+        <v>14</v>
+      </c>
+      <c r="AG24">
+        <v>10.5</v>
+      </c>
+      <c r="AH24">
+        <v>18.5</v>
+      </c>
+      <c r="AI24">
         <v>60</v>
-      </c>
-      <c r="AF24">
-        <v>14.5</v>
-      </c>
-      <c r="AG24">
-        <v>11</v>
-      </c>
-      <c r="AH24">
-        <v>19</v>
-      </c>
-      <c r="AI24">
-        <v>65</v>
       </c>
       <c r="AJ24">
         <v>23</v>
       </c>
       <c r="AK24">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL24">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN24">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO24">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP24">
         <v>15</v>
       </c>
       <c r="AQ24">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR24">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AS24">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AT24">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU24">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV24">
         <v>15</v>
       </c>
       <c r="AW24">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX24">
         <v>11</v>
@@ -6543,22 +6543,22 @@
         <v>9.4</v>
       </c>
       <c r="AZ24">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA24">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BB24">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC24">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD24">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BE24">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BF24">
         <v>10.5</v>
@@ -6570,61 +6570,61 @@
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK24">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO24">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ24">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS24">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA24">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="CB24" t="s">
         <v>157</v>
@@ -6665,208 +6665,208 @@
         <v>950</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P25">
         <v>1.24</v>
       </c>
       <c r="Q25">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
         <v>157</v>
@@ -6889,7 +6889,7 @@
         <v>153</v>
       </c>
       <c r="F26">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G26">
         <v>1.39</v>
@@ -6907,31 +6907,31 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M26">
         <v>1.03</v>
       </c>
       <c r="N26">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O26">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P26">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q26">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R26">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S26">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="T26">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U26">
         <v>2.2</v>
@@ -6943,7 +6943,7 @@
         <v>3.55</v>
       </c>
       <c r="X26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y26">
         <v>40</v>
@@ -6952,7 +6952,7 @@
         <v>85</v>
       </c>
       <c r="AA26">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AB26">
         <v>12.5</v>
@@ -6982,10 +6982,10 @@
         <v>12.5</v>
       </c>
       <c r="AK26">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL26">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM26">
         <v>95</v>
@@ -6994,43 +6994,43 @@
         <v>4.6</v>
       </c>
       <c r="AO26">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP26">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ26">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AR26">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AS26">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT26">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV26">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AW26">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="AX26">
         <v>9.4</v>
       </c>
       <c r="AY26">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26">
         <v>20</v>
       </c>
       <c r="BA26">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BB26">
         <v>11</v>
@@ -7045,70 +7045,70 @@
         <v>38</v>
       </c>
       <c r="BF26">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG26">
         <v>40</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI26">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK26">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO26">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ26">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS26">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BU26">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA26">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="CB26" t="s">
         <v>157</v>
@@ -7131,16 +7131,16 @@
         <v>154</v>
       </c>
       <c r="F27">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G27">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H27">
         <v>3.2</v>
       </c>
       <c r="I27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J27">
         <v>3.4</v>
@@ -7149,28 +7149,28 @@
         <v>3.45</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P27">
         <v>1.81</v>
       </c>
       <c r="Q27">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T27">
         <v>1.85</v>
@@ -7179,178 +7179,178 @@
         <v>2.04</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X27">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z27">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AA27">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC27">
         <v>7.6</v>
       </c>
       <c r="AD27">
+        <v>15</v>
+      </c>
+      <c r="AE27">
+        <v>42</v>
+      </c>
+      <c r="AF27">
         <v>15.5</v>
       </c>
-      <c r="AE27">
-        <v>85</v>
-      </c>
-      <c r="AF27">
-        <v>18</v>
-      </c>
       <c r="AG27">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH27">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AI27">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="AJ27">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AK27">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AL27">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN27">
         <v>26</v>
       </c>
       <c r="AO27">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AP27">
         <v>10.5</v>
       </c>
       <c r="AQ27">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR27">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS27">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AT27">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU27">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV27">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW27">
         <v>23</v>
       </c>
       <c r="AX27">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ27">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA27">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BB27">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BC27">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="BD27">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BE27">
         <v>38</v>
       </c>
       <c r="BF27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG27">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BH27">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BI27">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
         <v>157</v>
@@ -7379,7 +7379,7 @@
         <v>1.6</v>
       </c>
       <c r="H28">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>8</v>
@@ -7388,19 +7388,19 @@
         <v>4.2</v>
       </c>
       <c r="K28">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P28">
         <v>1.79</v>
@@ -7409,190 +7409,190 @@
         <v>2.1</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
         <v>157</v>
@@ -7615,7 +7615,7 @@
         <v>156</v>
       </c>
       <c r="F29">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G29">
         <v>2.54</v>
@@ -7633,208 +7633,208 @@
         <v>3.8</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P29">
+        <v>2.54</v>
+      </c>
+      <c r="Q29">
+        <v>1.55</v>
+      </c>
+      <c r="R29">
+        <v>1.57</v>
+      </c>
+      <c r="S29">
         <v>2.5</v>
       </c>
-      <c r="Q29">
-        <v>1.58</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
       <c r="T29">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG29">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
         <v>157</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -487,7 +487,7 @@
     <t>Dinamo Zagreb</t>
   </si>
   <si>
-    <t>2026-08-24 17:16:20</t>
+    <t>2026-08-24 19:35:23</t>
   </si>
 </sst>
 </file>
@@ -1084,16 +1084,16 @@
         <v>1.63</v>
       </c>
       <c r="G2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4.2</v>
@@ -1105,28 +1105,28 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R2">
         <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T2">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U2">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V2">
         <v>1.16</v>
@@ -1138,55 +1138,55 @@
         <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z2">
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AB2">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AC2">
         <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AE2">
         <v>150</v>
       </c>
       <c r="AF2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AI2">
         <v>150</v>
       </c>
       <c r="AJ2">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM2">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AN2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AP2">
         <v>10</v>
@@ -1195,10 +1195,10 @@
         <v>14.5</v>
       </c>
       <c r="AR2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS2">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2">
         <v>6</v>
@@ -1207,40 +1207,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
+        <v>26</v>
+      </c>
+      <c r="BA2">
+        <v>9</v>
+      </c>
+      <c r="BB2">
+        <v>12.5</v>
+      </c>
+      <c r="BC2">
+        <v>17.5</v>
+      </c>
+      <c r="BD2">
+        <v>46</v>
+      </c>
+      <c r="BE2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF2">
         <v>9.6</v>
       </c>
-      <c r="AZ2">
-        <v>25</v>
-      </c>
-      <c r="BA2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB2">
-        <v>13.5</v>
-      </c>
-      <c r="BC2">
-        <v>18</v>
-      </c>
-      <c r="BD2">
-        <v>9</v>
-      </c>
-      <c r="BE2">
-        <v>9</v>
-      </c>
-      <c r="BF2">
-        <v>11</v>
-      </c>
       <c r="BG2">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1323,22 +1323,22 @@
         <v>130</v>
       </c>
       <c r="F3">
+        <v>2.28</v>
+      </c>
+      <c r="G3">
         <v>2.36</v>
       </c>
-      <c r="G3">
-        <v>2.38</v>
-      </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="I3">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="J3">
+        <v>3.15</v>
+      </c>
+      <c r="K3">
         <v>3.3</v>
-      </c>
-      <c r="K3">
-        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1347,13 +1347,13 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O3">
         <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q3">
         <v>2.44</v>
@@ -1362,28 +1362,28 @@
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T3">
         <v>2.04</v>
       </c>
       <c r="U3">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X3">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA3">
         <v>90</v>
@@ -1392,97 +1392,97 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI3">
         <v>85</v>
       </c>
       <c r="AJ3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL3">
         <v>60</v>
       </c>
       <c r="AM3">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS3">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AX3">
         <v>11</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA3">
-        <v>8.6</v>
+        <v>60</v>
       </c>
       <c r="BB3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BC3">
+        <v>25</v>
+      </c>
+      <c r="BD3">
+        <v>46</v>
+      </c>
+      <c r="BE3">
+        <v>12</v>
+      </c>
+      <c r="BF3">
         <v>23</v>
       </c>
-      <c r="BD3">
-        <v>8.4</v>
-      </c>
-      <c r="BE3">
-        <v>9.4</v>
-      </c>
-      <c r="BF3">
-        <v>7.4</v>
-      </c>
       <c r="BG3">
-        <v>8.6</v>
+        <v>55</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1565,46 +1565,46 @@
         <v>131</v>
       </c>
       <c r="F4">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="G4">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="H4">
-        <v>10.5</v>
+        <v>1.09</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>990</v>
       </c>
       <c r="J4">
-        <v>4.7</v>
+        <v>1.09</v>
       </c>
       <c r="K4">
-        <v>5.6</v>
+        <v>950</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="O4">
         <v>1.29</v>
       </c>
       <c r="P4">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>1.87</v>
+        <v>1.29</v>
       </c>
       <c r="R4">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
-        <v>3.2</v>
+        <v>1.28</v>
       </c>
       <c r="T4">
         <v>2.18</v>
@@ -1613,10 +1613,10 @@
         <v>1.7</v>
       </c>
       <c r="V4">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
         <v>21</v>
@@ -1727,64 +1727,64 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH4">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>157</v>
@@ -1834,7 +1834,7 @@
         <v>3.1</v>
       </c>
       <c r="O5">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5">
         <v>1.72</v>
@@ -1855,10 +1855,10 @@
         <v>1.98</v>
       </c>
       <c r="V5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X5">
         <v>11.5</v>
@@ -1963,7 +1963,7 @@
         <v>7.4</v>
       </c>
       <c r="BF5">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BG5">
         <v>6.2</v>
@@ -2061,7 +2061,7 @@
         <v>3.4</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
         <v>4.2</v>
@@ -2073,7 +2073,7 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
         <v>1.21</v>
@@ -2085,10 +2085,10 @@
         <v>1.65</v>
       </c>
       <c r="R6">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S6">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="T6">
         <v>1.54</v>
@@ -2097,10 +2097,10 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2315,16 +2315,16 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
         <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R7">
         <v>1.25</v>
@@ -2342,7 +2342,7 @@
         <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X7">
         <v>15.5</v>
@@ -2429,7 +2429,7 @@
         <v>9</v>
       </c>
       <c r="AZ7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA7">
         <v>5.7</v>
@@ -2533,19 +2533,19 @@
         <v>135</v>
       </c>
       <c r="F8">
-        <v>1.05</v>
+        <v>2.26</v>
       </c>
       <c r="G8">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="I8">
-        <v>870</v>
+        <v>1.82</v>
       </c>
       <c r="J8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2557,13 +2557,13 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.26</v>
+        <v>5.5</v>
       </c>
       <c r="O8">
         <v>1.12</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q8">
         <v>1.12</v>
@@ -2575,13 +2575,13 @@
         <v>1.12</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>2.2</v>
       </c>
       <c r="W8">
         <v>1.02</v>
@@ -2775,7 +2775,7 @@
         <v>136</v>
       </c>
       <c r="F9">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G9">
         <v>2.04</v>
@@ -2802,13 +2802,13 @@
         <v>5.7</v>
       </c>
       <c r="O9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P9">
         <v>2.62</v>
       </c>
       <c r="Q9">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R9">
         <v>1.64</v>
@@ -2838,7 +2838,7 @@
         <v>36</v>
       </c>
       <c r="AA9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB9">
         <v>14.5</v>
@@ -2850,7 +2850,7 @@
         <v>18</v>
       </c>
       <c r="AE9">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF9">
         <v>18</v>
@@ -2859,7 +2859,7 @@
         <v>13</v>
       </c>
       <c r="AH9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI9">
         <v>40</v>
@@ -2934,7 +2934,7 @@
         <v>7.6</v>
       </c>
       <c r="BG9">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3017,7 +3017,7 @@
         <v>137</v>
       </c>
       <c r="F10">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G10">
         <v>2.76</v>
@@ -3047,7 +3047,7 @@
         <v>1.27</v>
       </c>
       <c r="P10">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q10">
         <v>1.8</v>
@@ -3056,7 +3056,7 @@
         <v>1.4</v>
       </c>
       <c r="S10">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T10">
         <v>1.65</v>
@@ -3074,7 +3074,7 @@
         <v>21</v>
       </c>
       <c r="Y10">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z10">
         <v>25</v>
@@ -3089,7 +3089,7 @@
         <v>10.5</v>
       </c>
       <c r="AD10">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE10">
         <v>32</v>
@@ -3104,7 +3104,7 @@
         <v>19.5</v>
       </c>
       <c r="AI10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ10">
         <v>46</v>
@@ -3122,7 +3122,7 @@
         <v>24</v>
       </c>
       <c r="AO10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP10">
         <v>14</v>
@@ -3134,7 +3134,7 @@
         <v>15</v>
       </c>
       <c r="AS10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT10">
         <v>10</v>
@@ -3146,7 +3146,7 @@
         <v>9.6</v>
       </c>
       <c r="AW10">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AX10">
         <v>13</v>
@@ -3158,19 +3158,19 @@
         <v>14</v>
       </c>
       <c r="BA10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BB10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BC10">
         <v>19.5</v>
       </c>
       <c r="BD10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BE10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF10">
         <v>14.5</v>
@@ -3262,7 +3262,7 @@
         <v>1.64</v>
       </c>
       <c r="G11">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H11">
         <v>4.2</v>
@@ -3274,7 +3274,7 @@
         <v>4.8</v>
       </c>
       <c r="K11">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3292,7 +3292,7 @@
         <v>3.9</v>
       </c>
       <c r="Q11">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="R11">
         <v>2</v>
@@ -3421,10 +3421,10 @@
         <v>12</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI11">
-        <v>2.34</v>
+        <v>4.4</v>
       </c>
       <c r="BJ11">
         <v>11.5</v>
@@ -3436,7 +3436,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>2.26</v>
+        <v>3.05</v>
       </c>
       <c r="BN11">
         <v>7.6</v>
@@ -3448,31 +3448,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ11">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="BR11">
         <v>21</v>
       </c>
       <c r="BS11">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="BT11">
         <v>13</v>
       </c>
       <c r="BU11">
-        <v>1.99</v>
+        <v>2.56</v>
       </c>
       <c r="BV11">
         <v>38</v>
       </c>
       <c r="BW11">
-        <v>2.2</v>
+        <v>2.94</v>
       </c>
       <c r="BX11">
         <v>34</v>
       </c>
       <c r="BY11">
-        <v>2.2</v>
+        <v>2.92</v>
       </c>
       <c r="BZ11">
         <v>11</v>
@@ -3528,7 +3528,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P12">
         <v>3.7</v>
@@ -3537,16 +3537,16 @@
         <v>1.3</v>
       </c>
       <c r="R12">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="S12">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="T12">
         <v>1.29</v>
       </c>
       <c r="U12">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
         <v>1.66</v>
@@ -3558,7 +3558,7 @@
         <v>60</v>
       </c>
       <c r="Y12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z12">
         <v>32</v>
@@ -3567,13 +3567,13 @@
         <v>42</v>
       </c>
       <c r="AB12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC12">
         <v>16</v>
       </c>
       <c r="AD12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE12">
         <v>25</v>
@@ -3582,7 +3582,7 @@
         <v>36</v>
       </c>
       <c r="AG12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH12">
         <v>16</v>
@@ -3609,7 +3609,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ12">
         <v>20</v>
@@ -3618,10 +3618,10 @@
         <v>20</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AU12">
         <v>11.5</v>
@@ -3633,7 +3633,7 @@
         <v>17.5</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AY12">
         <v>13</v>
@@ -3645,7 +3645,7 @@
         <v>18.5</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC12">
         <v>18.5</v>
@@ -3654,10 +3654,10 @@
         <v>18</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG12">
         <v>6.4</v>
@@ -3743,22 +3743,22 @@
         <v>140</v>
       </c>
       <c r="F13">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G13">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="H13">
         <v>8.6</v>
       </c>
       <c r="I13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J13">
         <v>6.6</v>
       </c>
       <c r="K13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3767,10 +3767,10 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>7.6</v>
+        <v>3.75</v>
       </c>
       <c r="O13">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="P13">
         <v>3.8</v>
@@ -3782,7 +3782,7 @@
         <v>2.12</v>
       </c>
       <c r="S13">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="T13">
         <v>1.48</v>
@@ -3794,7 +3794,7 @@
         <v>1.09</v>
       </c>
       <c r="W13">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3821,7 +3821,7 @@
         <v>1000</v>
       </c>
       <c r="AF13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG13">
         <v>17.5</v>
@@ -3833,10 +3833,10 @@
         <v>95</v>
       </c>
       <c r="AJ13">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK13">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL13">
         <v>34</v>
@@ -3851,16 +3851,16 @@
         <v>100</v>
       </c>
       <c r="AP13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AQ13">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AR13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AS13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AT13">
         <v>12.5</v>
@@ -3869,10 +3869,10 @@
         <v>12</v>
       </c>
       <c r="AV13">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="AW13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AX13">
         <v>9.199999999999999</v>
@@ -3884,7 +3884,7 @@
         <v>14.5</v>
       </c>
       <c r="BA13">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BB13">
         <v>8.800000000000001</v>
@@ -3896,13 +3896,13 @@
         <v>15</v>
       </c>
       <c r="BE13">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BF13">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="BG13">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4018,7 +4018,7 @@
         <v>2.84</v>
       </c>
       <c r="Q14">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="R14">
         <v>1.8</v>
@@ -4027,10 +4027,10 @@
         <v>1.98</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
         <v>1.72</v>
@@ -4227,22 +4227,22 @@
         <v>142</v>
       </c>
       <c r="F15">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="G15">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="H15">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="I15">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="J15">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4257,70 +4257,70 @@
         <v>1.08</v>
       </c>
       <c r="P15">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="Q15">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S15">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="T15">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U15">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="V15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W15">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="X15">
         <v>75</v>
       </c>
       <c r="Y15">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="Z15">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA15">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AB15">
         <v>22</v>
       </c>
       <c r="AC15">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD15">
         <v>32</v>
       </c>
       <c r="AE15">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG15">
         <v>13.5</v>
       </c>
       <c r="AH15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI15">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ15">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL15">
         <v>22</v>
@@ -4329,13 +4329,13 @@
         <v>55</v>
       </c>
       <c r="AN15">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AO15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP15">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="AQ15">
         <v>28</v>
@@ -4359,7 +4359,7 @@
         <v>36</v>
       </c>
       <c r="AX15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY15">
         <v>10.5</v>
@@ -4371,10 +4371,10 @@
         <v>27</v>
       </c>
       <c r="BB15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD15">
         <v>17.5</v>
@@ -4383,7 +4383,7 @@
         <v>29</v>
       </c>
       <c r="BF15">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="BG15">
         <v>18.5</v>
@@ -4577,7 +4577,7 @@
         <v>50</v>
       </c>
       <c r="AP16">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ16">
         <v>6.8</v>
@@ -4726,7 +4726,7 @@
         <v>3.05</v>
       </c>
       <c r="K17">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4738,7 +4738,7 @@
         <v>2.82</v>
       </c>
       <c r="O17">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="P17">
         <v>1.62</v>
@@ -4795,7 +4795,7 @@
         <v>15.5</v>
       </c>
       <c r="AH17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI17">
         <v>65</v>
@@ -4840,7 +4840,7 @@
         <v>10</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX17">
         <v>19</v>
@@ -4852,25 +4852,25 @@
         <v>17</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH17">
         <v>3.5</v>
@@ -4956,7 +4956,7 @@
         <v>2.42</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H18">
         <v>2.4</v>
@@ -4980,7 +4980,7 @@
         <v>9</v>
       </c>
       <c r="O18">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P18">
         <v>3.65</v>
@@ -4992,7 +4992,7 @@
         <v>2.08</v>
       </c>
       <c r="S18">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="T18">
         <v>1.29</v>
@@ -5001,10 +5001,10 @@
         <v>3</v>
       </c>
       <c r="V18">
+        <v>1.54</v>
+      </c>
+      <c r="W18">
         <v>1.58</v>
-      </c>
-      <c r="W18">
-        <v>1.5</v>
       </c>
       <c r="X18">
         <v>65</v>
@@ -5061,7 +5061,7 @@
         <v>10.5</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ18">
         <v>19.5</v>
@@ -5070,7 +5070,7 @@
         <v>20</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT18">
         <v>19.5</v>
@@ -5082,7 +5082,7 @@
         <v>10.5</v>
       </c>
       <c r="AW18">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX18">
         <v>20</v>
@@ -5097,7 +5097,7 @@
         <v>16.5</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC18">
         <v>16</v>
@@ -5106,7 +5106,7 @@
         <v>16.5</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BF18">
         <v>6.4</v>
@@ -5198,37 +5198,37 @@
         <v>1.2</v>
       </c>
       <c r="G19">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I19">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>1.08</v>
       </c>
       <c r="K19">
         <v>950</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M19">
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O19">
         <v>1.01</v>
       </c>
       <c r="P19">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q19">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="R19">
         <v>1.38</v>
@@ -5237,16 +5237,16 @@
         <v>2.72</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
         <v>1.01</v>
       </c>
       <c r="W19">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5446,151 +5446,151 @@
         <v>2.82</v>
       </c>
       <c r="I20">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="J20">
         <v>2.8</v>
       </c>
       <c r="K20">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M20">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N20">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="O20">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P20">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="Q20">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="R20">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="S20">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="T20">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U20">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W20">
         <v>1.44</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AS20">
         <v>1.03</v>
       </c>
       <c r="AT20">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU20">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY20">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
         <v>1.03</v>
       </c>
       <c r="BC20">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
         <v>1.01</v>
@@ -5697,7 +5697,7 @@
         <v>3.25</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M21">
         <v>1.15</v>
@@ -5721,10 +5721,10 @@
         <v>2.62</v>
       </c>
       <c r="T21">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U21">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V21">
         <v>1.21</v>
@@ -5844,61 +5844,61 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
         <v>157</v>
@@ -5963,10 +5963,10 @@
         <v>2.7</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22">
         <v>1.79</v>
@@ -6086,61 +6086,61 @@
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
         <v>157</v>
@@ -6166,16 +6166,16 @@
         <v>1.09</v>
       </c>
       <c r="G23">
-        <v>11.5</v>
+        <v>2.02</v>
       </c>
       <c r="H23">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I23">
         <v>990</v>
       </c>
       <c r="J23">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="K23">
         <v>950</v>
@@ -6193,16 +6193,16 @@
         <v>1.27</v>
       </c>
       <c r="P23">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q23">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R23">
         <v>1.12</v>
       </c>
       <c r="S23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T23">
         <v>1.11</v>
@@ -6214,7 +6214,7 @@
         <v>1.01</v>
       </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>1.99</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6405,7 +6405,7 @@
         <v>151</v>
       </c>
       <c r="F24">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G24">
         <v>1.99</v>
@@ -6417,7 +6417,7 @@
         <v>4.4</v>
       </c>
       <c r="J24">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K24">
         <v>3.95</v>
@@ -6429,43 +6429,43 @@
         <v>1.06</v>
       </c>
       <c r="N24">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O24">
         <v>1.28</v>
       </c>
       <c r="P24">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q24">
         <v>1.83</v>
       </c>
       <c r="R24">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S24">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T24">
         <v>1.75</v>
       </c>
       <c r="U24">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V24">
         <v>1.3</v>
       </c>
       <c r="W24">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X24">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y24">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA24">
         <v>90</v>
@@ -6477,19 +6477,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD24">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE24">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF24">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG24">
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI24">
         <v>60</v>
@@ -6504,22 +6504,22 @@
         <v>34</v>
       </c>
       <c r="AM24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN24">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO24">
         <v>50</v>
       </c>
       <c r="AP24">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ24">
         <v>15</v>
       </c>
       <c r="AR24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS24">
         <v>36</v>
@@ -6528,16 +6528,16 @@
         <v>9.4</v>
       </c>
       <c r="AU24">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV24">
         <v>15</v>
       </c>
       <c r="AW24">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY24">
         <v>9.4</v>
@@ -6549,7 +6549,7 @@
         <v>46</v>
       </c>
       <c r="BB24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC24">
         <v>17</v>
@@ -6558,7 +6558,7 @@
         <v>29</v>
       </c>
       <c r="BE24">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="BF24">
         <v>10.5</v>
@@ -6647,19 +6647,19 @@
         <v>152</v>
       </c>
       <c r="F25">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G25">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H25">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I25">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J25">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K25">
         <v>950</v>
@@ -6671,13 +6671,13 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O25">
         <v>1.15</v>
       </c>
       <c r="P25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q25">
         <v>1.15</v>
@@ -6689,10 +6689,10 @@
         <v>1.15</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25">
         <v>1.02</v>
@@ -6889,58 +6889,58 @@
         <v>153</v>
       </c>
       <c r="F26">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="G26">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H26">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I26">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J26">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L26">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M26">
         <v>1.03</v>
       </c>
       <c r="N26">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O26">
         <v>1.16</v>
       </c>
       <c r="P26">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="Q26">
         <v>1.48</v>
       </c>
       <c r="R26">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S26">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T26">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U26">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
         <v>1.11</v>
       </c>
       <c r="W26">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="X26">
         <v>32</v>
@@ -6949,10 +6949,10 @@
         <v>40</v>
       </c>
       <c r="Z26">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA26">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AB26">
         <v>12.5</v>
@@ -6967,7 +6967,7 @@
         <v>120</v>
       </c>
       <c r="AF26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>10.5</v>
@@ -6979,34 +6979,34 @@
         <v>90</v>
       </c>
       <c r="AJ26">
+        <v>12</v>
+      </c>
+      <c r="AK26">
         <v>12.5</v>
-      </c>
-      <c r="AK26">
-        <v>13</v>
       </c>
       <c r="AL26">
         <v>28</v>
       </c>
       <c r="AM26">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN26">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AO26">
         <v>100</v>
       </c>
       <c r="AP26">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ26">
         <v>36</v>
       </c>
       <c r="AR26">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AS26">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AT26">
         <v>11.5</v>
@@ -7018,7 +7018,7 @@
         <v>29</v>
       </c>
       <c r="AW26">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX26">
         <v>9.4</v>
@@ -7027,7 +7027,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA26">
         <v>55</v>
@@ -7036,13 +7036,13 @@
         <v>11</v>
       </c>
       <c r="BC26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD26">
         <v>25</v>
       </c>
       <c r="BE26">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BF26">
         <v>4.2</v>
@@ -7054,7 +7054,7 @@
         <v>5</v>
       </c>
       <c r="BI26">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="BJ26">
         <v>14.5</v>
@@ -7090,7 +7090,7 @@
         <v>17</v>
       </c>
       <c r="BU26">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BV26">
         <v>1000</v>
@@ -7140,13 +7140,13 @@
         <v>3.2</v>
       </c>
       <c r="I27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J27">
+        <v>3.35</v>
+      </c>
+      <c r="K27">
         <v>3.4</v>
-      </c>
-      <c r="K27">
-        <v>3.45</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7158,13 +7158,13 @@
         <v>3.35</v>
       </c>
       <c r="O27">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P27">
         <v>1.81</v>
       </c>
       <c r="Q27">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R27">
         <v>1.3</v>
@@ -7179,7 +7179,7 @@
         <v>2.04</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
         <v>1.64</v>
@@ -7209,7 +7209,7 @@
         <v>42</v>
       </c>
       <c r="AF27">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG27">
         <v>12</v>
@@ -7236,7 +7236,7 @@
         <v>26</v>
       </c>
       <c r="AO27">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AP27">
         <v>10.5</v>
@@ -7260,7 +7260,7 @@
         <v>12.5</v>
       </c>
       <c r="AW27">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AX27">
         <v>13.5</v>
@@ -7373,49 +7373,49 @@
         <v>155</v>
       </c>
       <c r="F28">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G28">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H28">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I28">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J28">
         <v>4.2</v>
       </c>
       <c r="K28">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L28">
         <v>1.33</v>
       </c>
       <c r="M28">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N28">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O28">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P28">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q28">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S28">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T28">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U28">
         <v>1.73</v>
@@ -7424,19 +7424,19 @@
         <v>1.14</v>
       </c>
       <c r="W28">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="X28">
         <v>13</v>
       </c>
       <c r="Y28">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z28">
         <v>65</v>
       </c>
       <c r="AA28">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AB28">
         <v>6.8</v>
@@ -7448,40 +7448,40 @@
         <v>32</v>
       </c>
       <c r="AE28">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG28">
         <v>10.5</v>
       </c>
       <c r="AH28">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AI28">
         <v>180</v>
       </c>
       <c r="AJ28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK28">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL28">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="AM28">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AN28">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO28">
         <v>240</v>
       </c>
       <c r="AP28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ28">
         <v>17.5</v>
@@ -7493,7 +7493,7 @@
         <v>17</v>
       </c>
       <c r="AT28">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU28">
         <v>8.800000000000001</v>
@@ -7508,7 +7508,7 @@
         <v>7.2</v>
       </c>
       <c r="AY28">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ28">
         <v>25</v>
@@ -7517,10 +7517,10 @@
         <v>42</v>
       </c>
       <c r="BB28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC28">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD28">
         <v>42</v>
@@ -7529,7 +7529,7 @@
         <v>16.5</v>
       </c>
       <c r="BF28">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG28">
         <v>16.5</v>
@@ -7538,61 +7538,61 @@
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="s">
         <v>157</v>
@@ -7615,22 +7615,22 @@
         <v>156</v>
       </c>
       <c r="F29">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G29">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H29">
         <v>2.9</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J29">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K29">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7639,7 +7639,7 @@
         <v>1.03</v>
       </c>
       <c r="N29">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O29">
         <v>1.19</v>
@@ -7648,7 +7648,7 @@
         <v>2.54</v>
       </c>
       <c r="Q29">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R29">
         <v>1.57</v>
@@ -7663,7 +7663,7 @@
         <v>2.68</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
         <v>1.64</v>
@@ -7675,10 +7675,10 @@
         <v>18.5</v>
       </c>
       <c r="Z29">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA29">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB29">
         <v>16.5</v>
@@ -7690,10 +7690,10 @@
         <v>13</v>
       </c>
       <c r="AE29">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF29">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG29">
         <v>13.5</v>
@@ -7702,37 +7702,37 @@
         <v>14.5</v>
       </c>
       <c r="AI29">
+        <v>34</v>
+      </c>
+      <c r="AJ29">
         <v>36</v>
       </c>
-      <c r="AJ29">
-        <v>38</v>
-      </c>
       <c r="AK29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL29">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM29">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN29">
         <v>14</v>
       </c>
       <c r="AO29">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AP29">
         <v>20</v>
       </c>
       <c r="AQ29">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR29">
         <v>21</v>
       </c>
       <c r="AS29">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AT29">
         <v>14</v>
@@ -7741,40 +7741,40 @@
         <v>8.4</v>
       </c>
       <c r="AV29">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW29">
+        <v>24</v>
+      </c>
+      <c r="AX29">
+        <v>17.5</v>
+      </c>
+      <c r="AY29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ29">
+        <v>12.5</v>
+      </c>
+      <c r="BA29">
+        <v>28</v>
+      </c>
+      <c r="BB29">
+        <v>28</v>
+      </c>
+      <c r="BC29">
         <v>20</v>
       </c>
-      <c r="AX29">
-        <v>17</v>
-      </c>
-      <c r="AY29">
-        <v>9.6</v>
-      </c>
-      <c r="AZ29">
-        <v>12</v>
-      </c>
-      <c r="BA29">
-        <v>21</v>
-      </c>
-      <c r="BB29">
-        <v>19.5</v>
-      </c>
-      <c r="BC29">
-        <v>19.5</v>
-      </c>
       <c r="BD29">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BE29">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BF29">
         <v>11.5</v>
       </c>
       <c r="BG29">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH29">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -487,7 +487,7 @@
     <t>Dinamo Zagreb</t>
   </si>
   <si>
-    <t>2026-08-24 19:35:23</t>
+    <t>2026-08-24 21:52:52</t>
   </si>
 </sst>
 </file>
@@ -1081,16 +1081,16 @@
         <v>129</v>
       </c>
       <c r="F2">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="G2">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -1108,10 +1108,10 @@
         <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
         <v>2.26</v>
@@ -1123,22 +1123,22 @@
         <v>4.3</v>
       </c>
       <c r="T2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U2">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="X2">
         <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z2">
         <v>60</v>
@@ -1147,19 +1147,19 @@
         <v>280</v>
       </c>
       <c r="AB2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC2">
         <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE2">
         <v>150</v>
       </c>
       <c r="AF2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AG2">
         <v>11</v>
@@ -1168,10 +1168,10 @@
         <v>32</v>
       </c>
       <c r="AI2">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AK2">
         <v>20</v>
@@ -1180,13 +1180,13 @@
         <v>75</v>
       </c>
       <c r="AM2">
+        <v>240</v>
+      </c>
+      <c r="AN2">
+        <v>12.5</v>
+      </c>
+      <c r="AO2">
         <v>260</v>
-      </c>
-      <c r="AN2">
-        <v>15</v>
-      </c>
-      <c r="AO2">
-        <v>240</v>
       </c>
       <c r="AP2">
         <v>10</v>
@@ -1195,13 +1195,13 @@
         <v>14.5</v>
       </c>
       <c r="AR2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS2">
         <v>8.199999999999999</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
         <v>8.199999999999999</v>
@@ -1210,7 +1210,7 @@
         <v>25</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX2">
         <v>7</v>
@@ -1222,7 +1222,7 @@
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1231,10 +1231,10 @@
         <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF2">
         <v>9.6</v>
@@ -1323,22 +1323,22 @@
         <v>130</v>
       </c>
       <c r="F3">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G3">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H3">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1347,43 +1347,43 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
         <v>2.04</v>
       </c>
       <c r="U3">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA3">
         <v>90</v>
@@ -1392,13 +1392,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF3">
         <v>13</v>
@@ -1407,16 +1407,16 @@
         <v>12</v>
       </c>
       <c r="AH3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL3">
         <v>60</v>
@@ -1425,13 +1425,13 @@
         <v>170</v>
       </c>
       <c r="AN3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
         <v>9.800000000000001</v>
@@ -1449,7 +1449,7 @@
         <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW3">
         <v>46</v>
@@ -1458,7 +1458,7 @@
         <v>11</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
         <v>19</v>
@@ -1467,22 +1467,22 @@
         <v>60</v>
       </c>
       <c r="BB3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC3">
         <v>25</v>
       </c>
       <c r="BD3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BF3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BG3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1568,7 +1568,7 @@
         <v>1.06</v>
       </c>
       <c r="G4">
-        <v>1.47</v>
+        <v>110</v>
       </c>
       <c r="H4">
         <v>1.09</v>
@@ -1586,16 +1586,16 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
       <c r="O4">
         <v>1.29</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q4">
         <v>1.29</v>
@@ -1604,13 +1604,13 @@
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
         <v>1.01</v>
@@ -1619,112 +1619,112 @@
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1807,13 +1807,13 @@
         <v>132</v>
       </c>
       <c r="F5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G5">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H5">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I5">
         <v>2.5</v>
@@ -1831,7 +1831,7 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O5">
         <v>1.42</v>
@@ -1840,13 +1840,13 @@
         <v>1.72</v>
       </c>
       <c r="Q5">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R5">
         <v>1.27</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T5">
         <v>1.9</v>
@@ -1858,16 +1858,16 @@
         <v>1.67</v>
       </c>
       <c r="W5">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X5">
         <v>11.5</v>
       </c>
       <c r="Y5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA5">
         <v>42</v>
@@ -1882,16 +1882,16 @@
         <v>12</v>
       </c>
       <c r="AE5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG5">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH5">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI5">
         <v>60</v>
@@ -1912,16 +1912,16 @@
         <v>65</v>
       </c>
       <c r="AO5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR5">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AS5">
         <v>6.4</v>
@@ -1942,19 +1942,19 @@
         <v>20</v>
       </c>
       <c r="AY5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ5">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB5">
         <v>7</v>
       </c>
       <c r="BC5">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD5">
         <v>38</v>
@@ -1966,7 +1966,7 @@
         <v>34</v>
       </c>
       <c r="BG5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2049,43 +2049,43 @@
         <v>133</v>
       </c>
       <c r="F6">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G6">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="H6">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S6">
         <v>2.74</v>
@@ -2094,13 +2094,13 @@
         <v>1.54</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2115,13 +2115,13 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6">
         <v>1000</v>
@@ -2130,7 +2130,7 @@
         <v>1000</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH6">
         <v>1000</v>
@@ -2157,58 +2157,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2294,22 +2294,22 @@
         <v>1.54</v>
       </c>
       <c r="G7">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="H7">
         <v>7.4</v>
       </c>
       <c r="I7">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
         <v>1.08</v>
@@ -2321,19 +2321,19 @@
         <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="Q7">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S7">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U7">
         <v>1.73</v>
@@ -2342,13 +2342,13 @@
         <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="X7">
         <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Z7">
         <v>90</v>
@@ -2360,7 +2360,7 @@
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD7">
         <v>34</v>
@@ -2369,7 +2369,7 @@
         <v>200</v>
       </c>
       <c r="AF7">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG7">
         <v>11</v>
@@ -2381,7 +2381,7 @@
         <v>180</v>
       </c>
       <c r="AJ7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK7">
         <v>20</v>
@@ -2393,34 +2393,34 @@
         <v>250</v>
       </c>
       <c r="AN7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO7">
         <v>330</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ7">
         <v>18</v>
       </c>
       <c r="AR7">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AS7">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU7">
         <v>8.4</v>
       </c>
       <c r="AV7">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AW7">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX7">
         <v>7.2</v>
@@ -2429,10 +2429,10 @@
         <v>9</v>
       </c>
       <c r="AZ7">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BA7">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7">
         <v>12</v>
@@ -2441,16 +2441,16 @@
         <v>16</v>
       </c>
       <c r="BD7">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BE7">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG7">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2539,13 +2539,13 @@
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I8">
         <v>1.82</v>
       </c>
       <c r="J8">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2563,7 +2563,7 @@
         <v>1.12</v>
       </c>
       <c r="P8">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q8">
         <v>1.12</v>
@@ -2584,7 +2584,7 @@
         <v>2.2</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2698,61 +2698,61 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>157</v>
@@ -2796,7 +2796,7 @@
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N9">
         <v>5.7</v>
@@ -2808,7 +2808,7 @@
         <v>2.62</v>
       </c>
       <c r="Q9">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R9">
         <v>1.64</v>
@@ -2820,7 +2820,7 @@
         <v>1.47</v>
       </c>
       <c r="U9">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="V9">
         <v>1.33</v>
@@ -2919,7 +2919,7 @@
         <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BC9">
         <v>15.5</v>
@@ -3023,10 +3023,10 @@
         <v>2.76</v>
       </c>
       <c r="H10">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I10">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J10">
         <v>3.45</v>
@@ -3259,22 +3259,22 @@
         <v>138</v>
       </c>
       <c r="F11">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="G11">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="H11">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="K11">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3283,16 +3283,16 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="O11">
         <v>1.06</v>
       </c>
       <c r="P11">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q11">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="R11">
         <v>2</v>
@@ -3301,25 +3301,25 @@
         <v>1.58</v>
       </c>
       <c r="T11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="U11">
         <v>2.58</v>
       </c>
       <c r="V11">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W11">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="X11">
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="Z11">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AA11">
         <v>1000</v>
@@ -3331,28 +3331,28 @@
         <v>21</v>
       </c>
       <c r="AD11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AE11">
+        <v>70</v>
+      </c>
+      <c r="AF11">
+        <v>25</v>
+      </c>
+      <c r="AG11">
+        <v>17</v>
+      </c>
+      <c r="AH11">
+        <v>22</v>
+      </c>
+      <c r="AI11">
         <v>55</v>
       </c>
-      <c r="AF11">
+      <c r="AJ11">
         <v>28</v>
       </c>
-      <c r="AG11">
-        <v>17.5</v>
-      </c>
-      <c r="AH11">
-        <v>21</v>
-      </c>
-      <c r="AI11">
-        <v>48</v>
-      </c>
-      <c r="AJ11">
-        <v>30</v>
-      </c>
       <c r="AK11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL11">
         <v>25</v>
@@ -3364,46 +3364,46 @@
         <v>5.5</v>
       </c>
       <c r="AO11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AP11">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AQ11">
+        <v>2.9</v>
+      </c>
+      <c r="AR11">
+        <v>2.94</v>
+      </c>
+      <c r="AS11">
         <v>3</v>
-      </c>
-      <c r="AR11">
-        <v>3.05</v>
-      </c>
-      <c r="AS11">
-        <v>3.2</v>
       </c>
       <c r="AT11">
         <v>14.5</v>
       </c>
       <c r="AU11">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AV11">
         <v>13.5</v>
       </c>
       <c r="AW11">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AX11">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AY11">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA11">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BB11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC11">
         <v>10</v>
@@ -3412,13 +3412,13 @@
         <v>12.5</v>
       </c>
       <c r="BE11">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BF11">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="BG11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BH11">
         <v>8.800000000000001</v>
@@ -3430,55 +3430,55 @@
         <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>5.4</v>
+        <v>2.52</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BN11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO11">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP11">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BQ11">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BR11">
         <v>21</v>
       </c>
       <c r="BS11">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BT11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BU11">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BV11">
+        <v>44</v>
+      </c>
+      <c r="BW11">
+        <v>3</v>
+      </c>
+      <c r="BX11">
         <v>38</v>
       </c>
-      <c r="BW11">
-        <v>2.94</v>
-      </c>
-      <c r="BX11">
-        <v>34</v>
-      </c>
       <c r="BY11">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BZ11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA11">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="CB11" t="s">
         <v>157</v>
@@ -3666,61 +3666,61 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
         <v>157</v>
@@ -3908,61 +3908,61 @@
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
         <v>157</v>
@@ -4150,61 +4150,61 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
         <v>157</v>
@@ -4227,22 +4227,22 @@
         <v>142</v>
       </c>
       <c r="F15">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="G15">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="H15">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="I15">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="J15">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="K15">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4251,34 +4251,34 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O15">
         <v>1.08</v>
       </c>
       <c r="P15">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="Q15">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R15">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="S15">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="T15">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="U15">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="V15">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W15">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="X15">
         <v>75</v>
@@ -4293,10 +4293,10 @@
         <v>170</v>
       </c>
       <c r="AB15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AC15">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD15">
         <v>32</v>
@@ -4305,37 +4305,37 @@
         <v>80</v>
       </c>
       <c r="AF15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG15">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH15">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI15">
         <v>55</v>
       </c>
       <c r="AJ15">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AK15">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AM15">
         <v>55</v>
       </c>
       <c r="AN15">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AO15">
         <v>38</v>
       </c>
       <c r="AP15">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ15">
         <v>28</v>
@@ -4344,10 +4344,10 @@
         <v>38</v>
       </c>
       <c r="AS15">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AT15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU15">
         <v>13</v>
@@ -4383,7 +4383,7 @@
         <v>29</v>
       </c>
       <c r="BF15">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="BG15">
         <v>18.5</v>
@@ -4392,61 +4392,61 @@
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>157</v>
@@ -4586,7 +4586,7 @@
         <v>11.5</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT16">
         <v>8.800000000000001</v>
@@ -4598,7 +4598,7 @@
         <v>9.6</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX16">
         <v>17.5</v>
@@ -4610,85 +4610,85 @@
         <v>16.5</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
         <v>157</v>
@@ -4735,7 +4735,7 @@
         <v>1.1</v>
       </c>
       <c r="N17">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="O17">
         <v>1.43</v>
@@ -4956,7 +4956,7 @@
         <v>2.42</v>
       </c>
       <c r="G18">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H18">
         <v>2.4</v>
@@ -4965,10 +4965,10 @@
         <v>2.72</v>
       </c>
       <c r="J18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -4980,7 +4980,7 @@
         <v>9</v>
       </c>
       <c r="O18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P18">
         <v>3.65</v>
@@ -5001,10 +5001,10 @@
         <v>3</v>
       </c>
       <c r="V18">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W18">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="X18">
         <v>65</v>
@@ -5118,61 +5118,61 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
         <v>157</v>
@@ -5201,13 +5201,13 @@
         <v>1.38</v>
       </c>
       <c r="H19">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I19">
         <v>990</v>
       </c>
       <c r="J19">
-        <v>1.08</v>
+        <v>3.8</v>
       </c>
       <c r="K19">
         <v>950</v>
@@ -5222,7 +5222,7 @@
         <v>3.45</v>
       </c>
       <c r="O19">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="P19">
         <v>2.02</v>
@@ -5360,61 +5360,61 @@
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
         <v>157</v>
@@ -5461,7 +5461,7 @@
         <v>1.12</v>
       </c>
       <c r="N20">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O20">
         <v>1.56</v>
@@ -5470,7 +5470,7 @@
         <v>1.53</v>
       </c>
       <c r="Q20">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R20">
         <v>1.19</v>
@@ -5554,7 +5554,7 @@
         <v>15.5</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AT20">
         <v>7.2</v>
@@ -5566,7 +5566,7 @@
         <v>12</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX20">
         <v>15.5</v>
@@ -5578,25 +5578,25 @@
         <v>20</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC20">
         <v>32</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -6169,13 +6169,13 @@
         <v>2.02</v>
       </c>
       <c r="H23">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I23">
         <v>990</v>
       </c>
       <c r="J23">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="K23">
         <v>950</v>
@@ -6328,61 +6328,61 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
         <v>157</v>
@@ -6405,16 +6405,16 @@
         <v>151</v>
       </c>
       <c r="F24">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G24">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H24">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J24">
         <v>3.85</v>
@@ -6429,7 +6429,7 @@
         <v>1.06</v>
       </c>
       <c r="N24">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O24">
         <v>1.28</v>
@@ -6444,13 +6444,13 @@
         <v>1.44</v>
       </c>
       <c r="S24">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T24">
         <v>1.75</v>
       </c>
       <c r="U24">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V24">
         <v>1.3</v>
@@ -6471,7 +6471,7 @@
         <v>90</v>
       </c>
       <c r="AB24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC24">
         <v>8.800000000000001</v>
@@ -6480,10 +6480,10 @@
         <v>17</v>
       </c>
       <c r="AE24">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG24">
         <v>10.5</v>
@@ -6510,7 +6510,7 @@
         <v>12.5</v>
       </c>
       <c r="AO24">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP24">
         <v>14.5</v>
@@ -6525,7 +6525,7 @@
         <v>36</v>
       </c>
       <c r="AT24">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU24">
         <v>7.8</v>
@@ -6534,7 +6534,7 @@
         <v>15</v>
       </c>
       <c r="AW24">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX24">
         <v>11.5</v>
@@ -6561,7 +6561,7 @@
         <v>36</v>
       </c>
       <c r="BF24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG24">
         <v>26</v>
@@ -6671,13 +6671,13 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O25">
         <v>1.15</v>
       </c>
       <c r="P25">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q25">
         <v>1.15</v>
@@ -6686,7 +6686,7 @@
         <v>1.18</v>
       </c>
       <c r="S25">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T25">
         <v>1.11</v>
@@ -6812,61 +6812,61 @@
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="s">
         <v>157</v>
@@ -6889,13 +6889,13 @@
         <v>153</v>
       </c>
       <c r="F26">
+        <v>1.35</v>
+      </c>
+      <c r="G26">
         <v>1.36</v>
       </c>
-      <c r="G26">
-        <v>1.37</v>
-      </c>
       <c r="H26">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I26">
         <v>9.800000000000001</v>
@@ -6919,34 +6919,34 @@
         <v>1.16</v>
       </c>
       <c r="P26">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="Q26">
         <v>1.48</v>
       </c>
       <c r="R26">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S26">
         <v>2.24</v>
       </c>
       <c r="T26">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U26">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V26">
         <v>1.11</v>
       </c>
       <c r="W26">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X26">
         <v>32</v>
       </c>
       <c r="Y26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z26">
         <v>90</v>
@@ -6958,7 +6958,7 @@
         <v>12.5</v>
       </c>
       <c r="AC26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD26">
         <v>34</v>
@@ -6976,10 +6976,10 @@
         <v>23</v>
       </c>
       <c r="AI26">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK26">
         <v>12.5</v>
@@ -6988,10 +6988,10 @@
         <v>28</v>
       </c>
       <c r="AM26">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN26">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO26">
         <v>100</v>
@@ -7006,16 +7006,16 @@
         <v>75</v>
       </c>
       <c r="AS26">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT26">
         <v>11.5</v>
       </c>
       <c r="AU26">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV26">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW26">
         <v>40</v>
@@ -7024,7 +7024,7 @@
         <v>9.4</v>
       </c>
       <c r="AY26">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26">
         <v>21</v>
@@ -7042,19 +7042,19 @@
         <v>25</v>
       </c>
       <c r="BE26">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="BF26">
         <v>4.2</v>
       </c>
       <c r="BG26">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="BH26">
         <v>5</v>
       </c>
       <c r="BI26">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="BJ26">
         <v>14.5</v>
@@ -7155,7 +7155,7 @@
         <v>1.09</v>
       </c>
       <c r="N27">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O27">
         <v>1.39</v>
@@ -7173,7 +7173,7 @@
         <v>4</v>
       </c>
       <c r="T27">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U27">
         <v>2.04</v>
@@ -7302,55 +7302,55 @@
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="CB27" t="s">
         <v>157</v>
@@ -7376,16 +7376,16 @@
         <v>1.54</v>
       </c>
       <c r="G28">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H28">
         <v>7.2</v>
       </c>
       <c r="I28">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J28">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K28">
         <v>4.5</v>
@@ -7412,7 +7412,7 @@
         <v>1.3</v>
       </c>
       <c r="S28">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T28">
         <v>2.22</v>
@@ -7424,19 +7424,19 @@
         <v>1.14</v>
       </c>
       <c r="W28">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="X28">
         <v>13</v>
       </c>
       <c r="Y28">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z28">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA28">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AB28">
         <v>6.8</v>
@@ -7457,7 +7457,7 @@
         <v>10.5</v>
       </c>
       <c r="AH28">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AI28">
         <v>180</v>
@@ -7469,7 +7469,7 @@
         <v>18.5</v>
       </c>
       <c r="AL28">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AM28">
         <v>220</v>
@@ -7490,7 +7490,7 @@
         <v>50</v>
       </c>
       <c r="AS28">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT28">
         <v>6.4</v>
@@ -7502,7 +7502,7 @@
         <v>25</v>
       </c>
       <c r="AW28">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX28">
         <v>7.2</v>
@@ -7526,13 +7526,13 @@
         <v>42</v>
       </c>
       <c r="BE28">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BF28">
         <v>9.199999999999999</v>
       </c>
       <c r="BG28">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7621,7 +7621,7 @@
         <v>2.56</v>
       </c>
       <c r="H29">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I29">
         <v>3.05</v>
@@ -7663,7 +7663,7 @@
         <v>2.68</v>
       </c>
       <c r="V29">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
         <v>1.64</v>
@@ -7780,61 +7780,61 @@
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="s">
         <v>157</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -487,7 +487,7 @@
     <t>Dinamo Zagreb</t>
   </si>
   <si>
-    <t>2026-08-24 21:52:52</t>
+    <t>2026-08-25 00:09:27</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1081,7 @@
         <v>129</v>
       </c>
       <c r="F2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G2">
         <v>1.64</v>
@@ -1090,7 +1090,7 @@
         <v>7</v>
       </c>
       <c r="I2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -1108,7 +1108,7 @@
         <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P2">
         <v>1.7</v>
@@ -1123,7 +1123,7 @@
         <v>4.3</v>
       </c>
       <c r="T2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
         <v>1.68</v>
@@ -1138,7 +1138,7 @@
         <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z2">
         <v>60</v>
@@ -1147,10 +1147,10 @@
         <v>280</v>
       </c>
       <c r="AB2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD2">
         <v>30</v>
@@ -1180,7 +1180,7 @@
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AN2">
         <v>12.5</v>
@@ -1192,13 +1192,13 @@
         <v>10</v>
       </c>
       <c r="AQ2">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AR2">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="AS2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1210,7 +1210,7 @@
         <v>25</v>
       </c>
       <c r="AW2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2">
         <v>7</v>
@@ -1222,7 +1222,7 @@
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1234,13 +1234,13 @@
         <v>44</v>
       </c>
       <c r="BE2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF2">
         <v>9.6</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1323,19 +1323,19 @@
         <v>130</v>
       </c>
       <c r="F3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G3">
         <v>2.32</v>
       </c>
       <c r="H3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
         <v>3.55</v>
@@ -1347,7 +1347,7 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O3">
         <v>1.47</v>
@@ -1368,7 +1368,7 @@
         <v>2.04</v>
       </c>
       <c r="U3">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V3">
         <v>1.35</v>
@@ -1431,7 +1431,7 @@
         <v>85</v>
       </c>
       <c r="AP3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3">
         <v>9.800000000000001</v>
@@ -1458,7 +1458,7 @@
         <v>11</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
         <v>19</v>
@@ -1467,19 +1467,19 @@
         <v>60</v>
       </c>
       <c r="BB3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC3">
         <v>25</v>
       </c>
       <c r="BD3">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="BE3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG3">
         <v>50</v>
@@ -1565,19 +1565,19 @@
         <v>131</v>
       </c>
       <c r="F4">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="G4">
-        <v>110</v>
+        <v>1.49</v>
       </c>
       <c r="H4">
-        <v>1.09</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>990</v>
       </c>
       <c r="J4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1586,7 +1586,7 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
         <v>1.39</v>
@@ -1595,16 +1595,16 @@
         <v>1.29</v>
       </c>
       <c r="P4">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R4">
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1613,10 +1613,10 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC4">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG4">
         <v>1000</v>
@@ -1673,58 +1673,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1816,7 +1816,7 @@
         <v>2.34</v>
       </c>
       <c r="I5">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J5">
         <v>3.2</v>
@@ -1888,7 +1888,7 @@
         <v>25</v>
       </c>
       <c r="AG5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH5">
         <v>21</v>
@@ -1912,7 +1912,7 @@
         <v>65</v>
       </c>
       <c r="AO5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -1945,7 +1945,7 @@
         <v>13</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
         <v>6.8</v>
@@ -2073,7 +2073,7 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>1.22</v>
@@ -2097,7 +2097,7 @@
         <v>2.32</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.65</v>
@@ -2294,16 +2294,16 @@
         <v>1.54</v>
       </c>
       <c r="G7">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
         <v>4.4</v>
@@ -2315,7 +2315,7 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
         <v>1.37</v>
@@ -2327,10 +2327,10 @@
         <v>2.02</v>
       </c>
       <c r="R7">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S7">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="T7">
         <v>2.22</v>
@@ -2342,7 +2342,7 @@
         <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="X7">
         <v>15.5</v>
@@ -2405,7 +2405,7 @@
         <v>18</v>
       </c>
       <c r="AR7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS7">
         <v>8.199999999999999</v>
@@ -2420,7 +2420,7 @@
         <v>6.8</v>
       </c>
       <c r="AW7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX7">
         <v>7.2</v>
@@ -2432,7 +2432,7 @@
         <v>6.8</v>
       </c>
       <c r="BA7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB7">
         <v>12</v>
@@ -2539,7 +2539,7 @@
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I8">
         <v>1.82</v>
@@ -2563,7 +2563,7 @@
         <v>1.12</v>
       </c>
       <c r="P8">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q8">
         <v>1.12</v>
@@ -2584,7 +2584,7 @@
         <v>2.2</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2638,7 +2638,7 @@
         <v>1000</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP8">
         <v>1.03</v>
@@ -2689,7 +2689,7 @@
         <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG8">
         <v>1.01</v>
@@ -2892,7 +2892,7 @@
         <v>27</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT9">
         <v>12</v>
@@ -2904,7 +2904,7 @@
         <v>14</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
@@ -2916,7 +2916,7 @@
         <v>12</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB9">
         <v>20</v>
@@ -2928,7 +2928,7 @@
         <v>20</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF9">
         <v>7.6</v>
@@ -2940,61 +2940,61 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>157</v>
@@ -3065,7 +3065,7 @@
         <v>2.26</v>
       </c>
       <c r="V10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W10">
         <v>1.57</v>
@@ -3182,61 +3182,61 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>157</v>
@@ -3283,10 +3283,10 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="O11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P11">
         <v>4.1</v>
@@ -3295,16 +3295,16 @@
         <v>1.27</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="S11">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="T11">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="U11">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="V11">
         <v>1.2</v>
@@ -3313,112 +3313,112 @@
         <v>2.66</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y11">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Z11">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB11">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AC11">
+        <v>18.5</v>
+      </c>
+      <c r="AD11">
+        <v>27</v>
+      </c>
+      <c r="AE11">
+        <v>60</v>
+      </c>
+      <c r="AF11">
+        <v>18</v>
+      </c>
+      <c r="AG11">
+        <v>12.5</v>
+      </c>
+      <c r="AH11">
+        <v>19</v>
+      </c>
+      <c r="AI11">
+        <v>48</v>
+      </c>
+      <c r="AJ11">
+        <v>19.5</v>
+      </c>
+      <c r="AK11">
+        <v>14.5</v>
+      </c>
+      <c r="AL11">
         <v>21</v>
-      </c>
-      <c r="AD11">
-        <v>36</v>
-      </c>
-      <c r="AE11">
-        <v>70</v>
-      </c>
-      <c r="AF11">
-        <v>25</v>
-      </c>
-      <c r="AG11">
-        <v>17</v>
-      </c>
-      <c r="AH11">
-        <v>22</v>
-      </c>
-      <c r="AI11">
-        <v>55</v>
-      </c>
-      <c r="AJ11">
-        <v>28</v>
-      </c>
-      <c r="AK11">
-        <v>20</v>
-      </c>
-      <c r="AL11">
-        <v>25</v>
       </c>
       <c r="AM11">
         <v>55</v>
       </c>
       <c r="AN11">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AO11">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AP11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AQ11">
-        <v>2.9</v>
+        <v>25</v>
       </c>
       <c r="AR11">
-        <v>2.94</v>
+        <v>8</v>
       </c>
       <c r="AS11">
-        <v>3</v>
+        <v>8.6</v>
       </c>
       <c r="AT11">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AU11">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AV11">
         <v>13.5</v>
       </c>
       <c r="AW11">
-        <v>2.9</v>
+        <v>28</v>
       </c>
       <c r="AX11">
+        <v>14.5</v>
+      </c>
+      <c r="AY11">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11">
+        <v>15.5</v>
+      </c>
+      <c r="BA11">
+        <v>21</v>
+      </c>
+      <c r="BB11">
+        <v>16</v>
+      </c>
+      <c r="BC11">
         <v>11.5</v>
       </c>
-      <c r="AY11">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ11">
-        <v>11</v>
-      </c>
-      <c r="BA11">
-        <v>2.88</v>
-      </c>
-      <c r="BB11">
-        <v>12</v>
-      </c>
-      <c r="BC11">
-        <v>10</v>
-      </c>
       <c r="BD11">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BE11">
-        <v>2.88</v>
+        <v>27</v>
       </c>
       <c r="BF11">
-        <v>1.95</v>
+        <v>3.15</v>
       </c>
       <c r="BG11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BH11">
         <v>8.800000000000001</v>
@@ -3534,7 +3534,7 @@
         <v>3.7</v>
       </c>
       <c r="Q12">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R12">
         <v>2.08</v>
@@ -3555,7 +3555,7 @@
         <v>1.53</v>
       </c>
       <c r="X12">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="Y12">
         <v>30</v>
@@ -3785,10 +3785,10 @@
         <v>1.71</v>
       </c>
       <c r="T13">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
         <v>1.09</v>
@@ -3800,7 +3800,7 @@
         <v>1000</v>
       </c>
       <c r="Y13">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="Z13">
         <v>1000</v>
@@ -3809,13 +3809,13 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AC13">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AD13">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="AE13">
         <v>1000</v>
@@ -3827,7 +3827,7 @@
         <v>17.5</v>
       </c>
       <c r="AH13">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI13">
         <v>95</v>
@@ -3851,16 +3851,16 @@
         <v>100</v>
       </c>
       <c r="AP13">
+        <v>3.15</v>
+      </c>
+      <c r="AQ13">
         <v>3.05</v>
       </c>
-      <c r="AQ13">
-        <v>2.98</v>
-      </c>
       <c r="AR13">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AS13">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AT13">
         <v>12.5</v>
@@ -3869,10 +3869,10 @@
         <v>12</v>
       </c>
       <c r="AV13">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AW13">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AX13">
         <v>9.199999999999999</v>
@@ -3884,7 +3884,7 @@
         <v>14.5</v>
       </c>
       <c r="BA13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BB13">
         <v>8.800000000000001</v>
@@ -3896,13 +3896,13 @@
         <v>15</v>
       </c>
       <c r="BE13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BF13">
         <v>2.38</v>
       </c>
       <c r="BG13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3994,7 +3994,7 @@
         <v>2.1</v>
       </c>
       <c r="I14">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J14">
         <v>3.85</v>
@@ -4009,13 +4009,13 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>2.84</v>
+        <v>1.1</v>
       </c>
       <c r="O14">
         <v>1.11</v>
       </c>
       <c r="P14">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="Q14">
         <v>1.39</v>
@@ -4033,7 +4033,7 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W14">
         <v>1.38</v>
@@ -4093,52 +4093,52 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -4335,7 +4335,7 @@
         <v>38</v>
       </c>
       <c r="AP15">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ15">
         <v>28</v>
@@ -4344,7 +4344,7 @@
         <v>38</v>
       </c>
       <c r="AS15">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT15">
         <v>17</v>
@@ -4490,25 +4490,25 @@
         <v>1.46</v>
       </c>
       <c r="M16">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="O16">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="P16">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R16">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S16">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="T16">
         <v>2.06</v>
@@ -4720,7 +4720,7 @@
         <v>2.4</v>
       </c>
       <c r="I17">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J17">
         <v>3.05</v>
@@ -4735,10 +4735,10 @@
         <v>1.1</v>
       </c>
       <c r="N17">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="O17">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="P17">
         <v>1.62</v>
@@ -4953,22 +4953,22 @@
         <v>145</v>
       </c>
       <c r="F18">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G18">
         <v>3.05</v>
       </c>
       <c r="H18">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I18">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="J18">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K18">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -4977,22 +4977,22 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>9</v>
+        <v>3.25</v>
       </c>
       <c r="O18">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="P18">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="Q18">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R18">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S18">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="T18">
         <v>1.29</v>
@@ -5001,10 +5001,10 @@
         <v>3</v>
       </c>
       <c r="V18">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W18">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="X18">
         <v>65</v>
@@ -5246,7 +5246,7 @@
         <v>1.01</v>
       </c>
       <c r="W19">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5303,52 +5303,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5461,13 +5461,13 @@
         <v>1.12</v>
       </c>
       <c r="N20">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="O20">
         <v>1.56</v>
       </c>
       <c r="P20">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q20">
         <v>2.68</v>
@@ -5485,7 +5485,7 @@
         <v>1.65</v>
       </c>
       <c r="V20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
         <v>1.44</v>
@@ -5602,61 +5602,61 @@
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
         <v>157</v>
@@ -5751,7 +5751,7 @@
         <v>9.6</v>
       </c>
       <c r="AD21">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AE21">
         <v>1000</v>
@@ -5763,7 +5763,7 @@
         <v>16.5</v>
       </c>
       <c r="AH21">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AI21">
         <v>1000</v>
@@ -5787,16 +5787,16 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="AQ21">
         <v>7.4</v>
       </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="AT21">
         <v>4.3</v>
@@ -5808,7 +5808,7 @@
         <v>14.5</v>
       </c>
       <c r="AW21">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AX21">
         <v>7.8</v>
@@ -5820,25 +5820,25 @@
         <v>19</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="BB21">
         <v>20</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="BD21">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5930,7 +5930,7 @@
         <v>1.98</v>
       </c>
       <c r="I22">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="J22">
         <v>2.88</v>
@@ -6029,52 +6029,52 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
         <v>1.01</v>
@@ -6166,16 +6166,16 @@
         <v>1.09</v>
       </c>
       <c r="G23">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="H23">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="I23">
         <v>990</v>
       </c>
       <c r="J23">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="K23">
         <v>950</v>
@@ -6411,7 +6411,7 @@
         <v>2.02</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I24">
         <v>4.3</v>
@@ -6420,7 +6420,7 @@
         <v>3.85</v>
       </c>
       <c r="K24">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6435,13 +6435,13 @@
         <v>1.28</v>
       </c>
       <c r="P24">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q24">
         <v>1.83</v>
       </c>
       <c r="R24">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S24">
         <v>3.1</v>
@@ -6453,7 +6453,7 @@
         <v>2.26</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W24">
         <v>1.98</v>
@@ -6468,7 +6468,7 @@
         <v>36</v>
       </c>
       <c r="AA24">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB24">
         <v>11</v>
@@ -6483,7 +6483,7 @@
         <v>50</v>
       </c>
       <c r="AF24">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG24">
         <v>10.5</v>
@@ -6492,13 +6492,13 @@
         <v>19</v>
       </c>
       <c r="AI24">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ24">
         <v>23</v>
       </c>
       <c r="AK24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL24">
         <v>34</v>
@@ -6507,10 +6507,10 @@
         <v>90</v>
       </c>
       <c r="AN24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO24">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AP24">
         <v>14.5</v>
@@ -6519,7 +6519,7 @@
         <v>15</v>
       </c>
       <c r="AR24">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS24">
         <v>36</v>
@@ -6647,19 +6647,19 @@
         <v>152</v>
       </c>
       <c r="F25">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="G25">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H25">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I25">
         <v>990</v>
       </c>
       <c r="J25">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="K25">
         <v>950</v>
@@ -6671,13 +6671,13 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O25">
         <v>1.15</v>
       </c>
       <c r="P25">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q25">
         <v>1.15</v>
@@ -6755,52 +6755,52 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
         <v>1.01</v>
@@ -6895,16 +6895,16 @@
         <v>1.36</v>
       </c>
       <c r="H26">
+        <v>9.4</v>
+      </c>
+      <c r="I26">
         <v>9.6</v>
       </c>
-      <c r="I26">
-        <v>9.800000000000001</v>
-      </c>
       <c r="J26">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L26">
         <v>1.26</v>
@@ -6919,7 +6919,7 @@
         <v>1.16</v>
       </c>
       <c r="P26">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q26">
         <v>1.48</v>
@@ -7042,13 +7042,13 @@
         <v>25</v>
       </c>
       <c r="BE26">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BF26">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG26">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="BH26">
         <v>5</v>
@@ -7209,7 +7209,7 @@
         <v>42</v>
       </c>
       <c r="AF27">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG27">
         <v>12</v>
@@ -7236,7 +7236,7 @@
         <v>26</v>
       </c>
       <c r="AO27">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AP27">
         <v>10.5</v>
@@ -7257,7 +7257,7 @@
         <v>6.8</v>
       </c>
       <c r="AV27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW27">
         <v>34</v>
@@ -7379,13 +7379,13 @@
         <v>1.57</v>
       </c>
       <c r="H28">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I28">
         <v>8.4</v>
       </c>
       <c r="J28">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K28">
         <v>4.5</v>
@@ -7397,7 +7397,7 @@
         <v>1.08</v>
       </c>
       <c r="N28">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O28">
         <v>1.37</v>
@@ -7412,7 +7412,7 @@
         <v>1.3</v>
       </c>
       <c r="S28">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T28">
         <v>2.22</v>
@@ -7436,7 +7436,7 @@
         <v>70</v>
       </c>
       <c r="AA28">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AB28">
         <v>6.8</v>
@@ -7532,7 +7532,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG28">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7663,7 +7663,7 @@
         <v>2.68</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
         <v>1.64</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="171">
   <si>
     <t>League</t>
   </si>
@@ -289,6 +289,9 @@
     <t>Spanish La Liga</t>
   </si>
   <si>
+    <t>Chilean Primera Division</t>
+  </si>
+  <si>
     <t>2026-08-26</t>
   </si>
   <si>
@@ -319,6 +322,18 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:20:00</t>
+  </si>
+  <si>
     <t>Independiente (Ecu)</t>
   </si>
   <si>
@@ -349,15 +364,15 @@
     <t>Haugesund</t>
   </si>
   <si>
+    <t>Stromsgodset</t>
+  </si>
+  <si>
+    <t>Asane</t>
+  </si>
+  <si>
     <t>Odds BK</t>
   </si>
   <si>
-    <t>Stromsgodset</t>
-  </si>
-  <si>
-    <t>Asane</t>
-  </si>
-  <si>
     <t>Stabaek</t>
   </si>
   <si>
@@ -385,9 +400,15 @@
     <t>Al Draih</t>
   </si>
   <si>
+    <t>Viking</t>
+  </si>
+  <si>
     <t>Lyon</t>
   </si>
   <si>
+    <t>AEK Athens</t>
+  </si>
+  <si>
     <t>San Antonio Bulo Bulo</t>
   </si>
   <si>
@@ -397,10 +418,16 @@
     <t>NK Celje</t>
   </si>
   <si>
-    <t>AEK Athens</t>
-  </si>
-  <si>
-    <t>Viking</t>
+    <t>Boyaca Chico</t>
+  </si>
+  <si>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
+    <t>Real Potosi</t>
+  </si>
+  <si>
+    <t>America de Cali S.A</t>
   </si>
   <si>
     <t>Tolima</t>
@@ -433,15 +460,15 @@
     <t>Egersund</t>
   </si>
   <si>
+    <t>Hodd</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
-    <t>Hodd</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
     <t>Ranheim IL</t>
   </si>
   <si>
@@ -469,9 +496,15 @@
     <t>Al-Kholood Club</t>
   </si>
   <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
     <t>Fenerbahce</t>
   </si>
   <si>
+    <t>PFC Levski Sofia</t>
+  </si>
+  <si>
     <t>The Strongest</t>
   </si>
   <si>
@@ -481,13 +514,19 @@
     <t>Slovan Bratislava</t>
   </si>
   <si>
-    <t>PFC Levski Sofia</t>
-  </si>
-  <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>2026-08-25 00:09:27</t>
+    <t>Fortaleza FC</t>
+  </si>
+  <si>
+    <t>Univ Catolica (Chile)</t>
+  </si>
+  <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
+    <t>Junior FC Barranquilla</t>
+  </si>
+  <si>
+    <t>2026-08-25 02:26:08</t>
   </si>
 </sst>
 </file>
@@ -819,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB29"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1069,22 +1108,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F2">
+        <v>1.6</v>
+      </c>
+      <c r="G2">
         <v>1.62</v>
-      </c>
-      <c r="G2">
-        <v>1.64</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -1093,7 +1132,7 @@
         <v>7.4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
         <v>4.2</v>
@@ -1105,34 +1144,34 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R2">
         <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V2">
         <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X2">
         <v>11.5</v>
@@ -1147,10 +1186,10 @@
         <v>280</v>
       </c>
       <c r="AB2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
         <v>30</v>
@@ -1159,7 +1198,7 @@
         <v>150</v>
       </c>
       <c r="AF2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG2">
         <v>11</v>
@@ -1177,31 +1216,31 @@
         <v>20</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN2">
         <v>12.5</v>
       </c>
       <c r="AO2">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AP2">
         <v>10</v>
       </c>
       <c r="AQ2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="AS2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU2">
         <v>8.199999999999999</v>
@@ -1210,19 +1249,19 @@
         <v>25</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1240,10 +1279,10 @@
         <v>9.6</v>
       </c>
       <c r="BG2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI2">
         <v>1.04</v>
@@ -1252,58 +1291,58 @@
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1311,16 +1350,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F3">
         <v>2.26</v>
@@ -1329,16 +1368,16 @@
         <v>2.32</v>
       </c>
       <c r="H3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1356,7 +1395,7 @@
         <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R3">
         <v>1.24</v>
@@ -1371,7 +1410,7 @@
         <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
         <v>1.75</v>
@@ -1383,19 +1422,19 @@
         <v>11.5</v>
       </c>
       <c r="Z3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB3">
         <v>8.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
         <v>75</v>
@@ -1407,7 +1446,7 @@
         <v>12</v>
       </c>
       <c r="AH3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI3">
         <v>80</v>
@@ -1428,7 +1467,7 @@
         <v>28</v>
       </c>
       <c r="AO3">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP3">
         <v>9.199999999999999</v>
@@ -1440,19 +1479,19 @@
         <v>21</v>
       </c>
       <c r="AS3">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT3">
         <v>7</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AX3">
         <v>11</v>
@@ -1476,7 +1515,7 @@
         <v>10.5</v>
       </c>
       <c r="BE3">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BF3">
         <v>22</v>
@@ -1545,7 +1584,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1553,34 +1592,34 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F4">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="G4">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="H4">
         <v>8.6</v>
       </c>
       <c r="I4">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1598,13 +1637,13 @@
         <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R4">
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1616,7 +1655,7 @@
         <v>1.07</v>
       </c>
       <c r="W4">
-        <v>2.16</v>
+        <v>3.7</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1787,7 +1826,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1795,22 +1834,22 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H5">
         <v>2.34</v>
@@ -1819,7 +1858,7 @@
         <v>2.48</v>
       </c>
       <c r="J5">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K5">
         <v>3.45</v>
@@ -1837,7 +1876,7 @@
         <v>1.42</v>
       </c>
       <c r="P5">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q5">
         <v>2.24</v>
@@ -1858,16 +1897,16 @@
         <v>1.67</v>
       </c>
       <c r="W5">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X5">
         <v>11.5</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA5">
         <v>42</v>
@@ -1876,7 +1915,7 @@
         <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
         <v>12</v>
@@ -1888,7 +1927,7 @@
         <v>25</v>
       </c>
       <c r="AG5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH5">
         <v>21</v>
@@ -1912,7 +1951,7 @@
         <v>65</v>
       </c>
       <c r="AO5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -1924,7 +1963,7 @@
         <v>13</v>
       </c>
       <c r="AS5">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1945,7 +1984,7 @@
         <v>13</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
         <v>6.8</v>
@@ -2029,7 +2068,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2037,34 +2076,34 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F6">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G6">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H6">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I6">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J6">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2073,16 +2112,16 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R6">
         <v>1.45</v>
@@ -2094,47 +2133,47 @@
         <v>1.54</v>
       </c>
       <c r="U6">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
         <v>1.65</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AC6">
+        <v>11</v>
+      </c>
+      <c r="AD6">
+        <v>32</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>75</v>
+      </c>
+      <c r="AG6">
+        <v>15.5</v>
+      </c>
+      <c r="AH6">
         <v>970</v>
       </c>
-      <c r="AD6">
-        <v>950</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>1000</v>
-      </c>
-      <c r="AG6">
-        <v>950</v>
-      </c>
-      <c r="AH6">
-        <v>1000</v>
-      </c>
       <c r="AI6">
         <v>1000</v>
       </c>
@@ -2142,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL6">
         <v>1000</v>
@@ -2157,58 +2196,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AQ6">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AR6">
-        <v>1.24</v>
+        <v>5.3</v>
       </c>
       <c r="AS6">
-        <v>1.24</v>
+        <v>12.5</v>
       </c>
       <c r="AT6">
-        <v>1.19</v>
+        <v>10</v>
       </c>
       <c r="AU6">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV6">
-        <v>1.19</v>
+        <v>8.6</v>
       </c>
       <c r="AW6">
-        <v>1.24</v>
+        <v>10.5</v>
       </c>
       <c r="AX6">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AY6">
-        <v>1.17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>1.23</v>
+        <v>11.5</v>
       </c>
       <c r="BA6">
-        <v>1.24</v>
+        <v>11.5</v>
       </c>
       <c r="BB6">
-        <v>1.24</v>
+        <v>10.5</v>
       </c>
       <c r="BC6">
-        <v>1.24</v>
+        <v>6.6</v>
       </c>
       <c r="BD6">
-        <v>1.24</v>
+        <v>10.5</v>
       </c>
       <c r="BE6">
-        <v>1.24</v>
+        <v>15.5</v>
       </c>
       <c r="BF6">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="BG6">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2271,7 +2310,7 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2279,22 +2318,22 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F7">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G7">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="H7">
         <v>7.2</v>
@@ -2303,58 +2342,58 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T7">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U7">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V7">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W7">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="X7">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y7">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Z7">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="AA7">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -2363,10 +2402,10 @@
         <v>9.6</v>
       </c>
       <c r="AD7">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AE7">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
         <v>8.199999999999999</v>
@@ -2375,64 +2414,64 @@
         <v>11</v>
       </c>
       <c r="AH7">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AI7">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
         <v>14.5</v>
       </c>
       <c r="AK7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL7">
         <v>60</v>
       </c>
       <c r="AM7">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO7">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7">
         <v>18</v>
       </c>
       <c r="AR7">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="AS7">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
       </c>
       <c r="AU7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV7">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="AW7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX7">
         <v>7.2</v>
       </c>
       <c r="AY7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BA7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BB7">
         <v>12</v>
@@ -2441,16 +2480,16 @@
         <v>16</v>
       </c>
       <c r="BD7">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BE7">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF7">
         <v>9.4</v>
       </c>
       <c r="BG7">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2513,7 +2552,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2521,16 +2560,16 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F8">
         <v>2.26</v>
@@ -2539,7 +2578,7 @@
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I8">
         <v>1.82</v>
@@ -2584,7 +2623,7 @@
         <v>2.2</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2755,7 +2794,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2763,28 +2802,28 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F9">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G9">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H9">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I9">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J9">
         <v>4.1</v>
@@ -2805,28 +2844,28 @@
         <v>1.17</v>
       </c>
       <c r="P9">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q9">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S9">
         <v>2.28</v>
       </c>
       <c r="T9">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U9">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="X9">
         <v>28</v>
@@ -2892,7 +2931,7 @@
         <v>27</v>
       </c>
       <c r="AS9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9">
         <v>12</v>
@@ -2904,7 +2943,7 @@
         <v>14</v>
       </c>
       <c r="AW9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
@@ -2997,7 +3036,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3005,16 +3044,16 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F10">
         <v>2.5</v>
@@ -3032,7 +3071,7 @@
         <v>3.45</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3086,7 +3125,7 @@
         <v>15</v>
       </c>
       <c r="AC10">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD10">
         <v>15.5</v>
@@ -3134,7 +3173,7 @@
         <v>15</v>
       </c>
       <c r="AS10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT10">
         <v>10</v>
@@ -3146,7 +3185,7 @@
         <v>9.6</v>
       </c>
       <c r="AW10">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AX10">
         <v>13</v>
@@ -3158,19 +3197,19 @@
         <v>14</v>
       </c>
       <c r="BA10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC10">
         <v>19.5</v>
       </c>
       <c r="BD10">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF10">
         <v>14.5</v>
@@ -3239,7 +3278,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3247,16 +3286,16 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F11">
         <v>1.53</v>
@@ -3268,7 +3307,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J11">
         <v>5.6</v>
@@ -3289,7 +3328,7 @@
         <v>1.08</v>
       </c>
       <c r="P11">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q11">
         <v>1.27</v>
@@ -3298,7 +3337,7 @@
         <v>2.26</v>
       </c>
       <c r="S11">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="T11">
         <v>1.41</v>
@@ -3328,7 +3367,7 @@
         <v>23</v>
       </c>
       <c r="AC11">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AD11">
         <v>27</v>
@@ -3343,7 +3382,7 @@
         <v>12.5</v>
       </c>
       <c r="AH11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI11">
         <v>48</v>
@@ -3367,16 +3406,16 @@
         <v>26</v>
       </c>
       <c r="AP11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ11">
         <v>25</v>
       </c>
       <c r="AR11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT11">
         <v>19</v>
@@ -3415,7 +3454,7 @@
         <v>27</v>
       </c>
       <c r="BF11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BG11">
         <v>21</v>
@@ -3481,7 +3520,7 @@
         <v>5.1</v>
       </c>
       <c r="CB11" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3489,34 +3528,34 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F12">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="G12">
-        <v>2.88</v>
+        <v>1.34</v>
       </c>
       <c r="H12">
-        <v>2.24</v>
+        <v>7.2</v>
       </c>
       <c r="I12">
-        <v>2.5</v>
+        <v>990</v>
       </c>
       <c r="J12">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="K12">
-        <v>5.2</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3525,142 +3564,142 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>9.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="O12">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="P12">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q12">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="R12">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S12">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="T12">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.53</v>
+        <v>3.25</v>
       </c>
       <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
         <v>950</v>
       </c>
-      <c r="Y12">
-        <v>30</v>
-      </c>
       <c r="Z12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AC12">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="AD12">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="AE12">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AG12">
         <v>17.5</v>
       </c>
       <c r="AH12">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="AI12">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="AJ12">
-        <v>55</v>
+        <v>18.5</v>
       </c>
       <c r="AK12">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AL12">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AM12">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AN12">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="AO12">
+        <v>100</v>
+      </c>
+      <c r="AP12">
+        <v>3.15</v>
+      </c>
+      <c r="AQ12">
+        <v>3.05</v>
+      </c>
+      <c r="AR12">
+        <v>3.15</v>
+      </c>
+      <c r="AS12">
+        <v>3.15</v>
+      </c>
+      <c r="AT12">
+        <v>12.5</v>
+      </c>
+      <c r="AU12">
+        <v>12</v>
+      </c>
+      <c r="AV12">
+        <v>2.98</v>
+      </c>
+      <c r="AW12">
+        <v>3.15</v>
+      </c>
+      <c r="AX12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ12">
+        <v>14.5</v>
+      </c>
+      <c r="BA12">
+        <v>3.05</v>
+      </c>
+      <c r="BB12">
         <v>8.800000000000001</v>
       </c>
-      <c r="AP12">
-        <v>5.1</v>
-      </c>
-      <c r="AQ12">
-        <v>20</v>
-      </c>
-      <c r="AR12">
-        <v>20</v>
-      </c>
-      <c r="AS12">
-        <v>4.9</v>
-      </c>
-      <c r="AT12">
-        <v>4.7</v>
-      </c>
-      <c r="AU12">
-        <v>11.5</v>
-      </c>
-      <c r="AV12">
-        <v>10.5</v>
-      </c>
-      <c r="AW12">
-        <v>17.5</v>
-      </c>
-      <c r="AX12">
-        <v>4.8</v>
-      </c>
-      <c r="AY12">
-        <v>13</v>
-      </c>
-      <c r="AZ12">
-        <v>10.5</v>
-      </c>
-      <c r="BA12">
-        <v>18.5</v>
-      </c>
-      <c r="BB12">
-        <v>5</v>
-      </c>
       <c r="BC12">
-        <v>18.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD12">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BE12">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="BF12">
-        <v>7.6</v>
+        <v>2.38</v>
       </c>
       <c r="BG12">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3723,7 +3762,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3731,34 +3770,34 @@
         <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="F13">
-        <v>1.27</v>
+        <v>2.98</v>
       </c>
       <c r="G13">
-        <v>1.34</v>
+        <v>3.6</v>
       </c>
       <c r="H13">
-        <v>8.6</v>
+        <v>2.12</v>
       </c>
       <c r="I13">
-        <v>11.5</v>
+        <v>2.4</v>
       </c>
       <c r="J13">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="K13">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3767,22 +3806,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.75</v>
+        <v>2.86</v>
       </c>
       <c r="O13">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="P13">
-        <v>3.8</v>
+        <v>2.86</v>
       </c>
       <c r="Q13">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="R13">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="S13">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="T13">
         <v>1.11</v>
@@ -3791,16 +3830,16 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.09</v>
+        <v>1.71</v>
       </c>
       <c r="W13">
-        <v>3.9</v>
+        <v>1.38</v>
       </c>
       <c r="X13">
         <v>1000</v>
       </c>
       <c r="Y13">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
         <v>1000</v>
@@ -3809,100 +3848,100 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
         <v>1000</v>
       </c>
       <c r="AF13">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3965,7 +4004,7 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3973,34 +4012,34 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="F14">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="G14">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="H14">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="I14">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="J14">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K14">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4009,142 +4048,142 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O14">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P14">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="Q14">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="R14">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="S14">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="U14">
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="W14">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4207,7 +4246,7 @@
         <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4215,16 +4254,16 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F15">
         <v>1.46</v>
@@ -4263,7 +4302,7 @@
         <v>1.28</v>
       </c>
       <c r="R15">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S15">
         <v>1.68</v>
@@ -4449,7 +4488,7 @@
         <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4457,16 +4496,16 @@
         <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F16">
         <v>3.55</v>
@@ -4475,16 +4514,16 @@
         <v>3.75</v>
       </c>
       <c r="H16">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I16">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="J16">
         <v>2.84</v>
       </c>
       <c r="K16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L16">
         <v>1.46</v>
@@ -4496,28 +4535,28 @@
         <v>2.52</v>
       </c>
       <c r="O16">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="P16">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Q16">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S16">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="T16">
         <v>2.06</v>
       </c>
       <c r="U16">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W16">
         <v>1.36</v>
@@ -4526,16 +4565,16 @@
         <v>9.6</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z16">
         <v>18</v>
       </c>
       <c r="AA16">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB16">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC16">
         <v>7.8</v>
@@ -4553,7 +4592,7 @@
         <v>16.5</v>
       </c>
       <c r="AH16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI16">
         <v>65</v>
@@ -4565,7 +4604,7 @@
         <v>65</v>
       </c>
       <c r="AL16">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM16">
         <v>200</v>
@@ -4574,7 +4613,7 @@
         <v>75</v>
       </c>
       <c r="AO16">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP16">
         <v>6.6</v>
@@ -4586,7 +4625,7 @@
         <v>11.5</v>
       </c>
       <c r="AS16">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT16">
         <v>8.800000000000001</v>
@@ -4598,7 +4637,7 @@
         <v>9.6</v>
       </c>
       <c r="AW16">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX16">
         <v>17.5</v>
@@ -4610,26 +4649,26 @@
         <v>16.5</v>
       </c>
       <c r="BA16">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB16">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC16">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD16">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE16">
+        <v>6.6</v>
+      </c>
+      <c r="BF16">
+        <v>6.4</v>
+      </c>
+      <c r="BG16">
         <v>6</v>
       </c>
-      <c r="BF16">
-        <v>5.8</v>
-      </c>
-      <c r="BG16">
-        <v>5.6</v>
-      </c>
       <c r="BH16">
         <v>1000</v>
       </c>
@@ -4691,7 +4730,7 @@
         <v>1.04</v>
       </c>
       <c r="CB16" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4699,16 +4738,16 @@
         <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="F17">
         <v>3.3</v>
@@ -4720,7 +4759,7 @@
         <v>2.4</v>
       </c>
       <c r="I17">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J17">
         <v>3.05</v>
@@ -4735,10 +4774,10 @@
         <v>1.1</v>
       </c>
       <c r="N17">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="O17">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="P17">
         <v>1.62</v>
@@ -4768,7 +4807,7 @@
         <v>12.5</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z17">
         <v>16</v>
@@ -4840,7 +4879,7 @@
         <v>10</v>
       </c>
       <c r="AW17">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX17">
         <v>19</v>
@@ -4852,25 +4891,25 @@
         <v>17</v>
       </c>
       <c r="BA17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB17">
+        <v>7.2</v>
+      </c>
+      <c r="BC17">
         <v>7</v>
       </c>
-      <c r="BC17">
-        <v>6.8</v>
-      </c>
       <c r="BD17">
+        <v>7.2</v>
+      </c>
+      <c r="BE17">
+        <v>7.6</v>
+      </c>
+      <c r="BF17">
         <v>7</v>
       </c>
-      <c r="BE17">
-        <v>7.4</v>
-      </c>
-      <c r="BF17">
-        <v>6.8</v>
-      </c>
       <c r="BG17">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH17">
         <v>3.5</v>
@@ -4933,7 +4972,7 @@
         <v>1.41</v>
       </c>
       <c r="CB17" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4941,34 +4980,34 @@
         <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F18">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G18">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H18">
         <v>2.44</v>
       </c>
       <c r="I18">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J18">
         <v>3.7</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -4980,52 +5019,52 @@
         <v>3.25</v>
       </c>
       <c r="O18">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="P18">
         <v>3.25</v>
       </c>
       <c r="Q18">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S18">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="T18">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="U18">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V18">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="W18">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X18">
         <v>65</v>
       </c>
       <c r="Y18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z18">
         <v>36</v>
       </c>
       <c r="AA18">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC18">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD18">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE18">
         <v>28</v>
@@ -5034,7 +5073,7 @@
         <v>36</v>
       </c>
       <c r="AG18">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH18">
         <v>17</v>
@@ -5046,7 +5085,7 @@
         <v>48</v>
       </c>
       <c r="AK18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL18">
         <v>28</v>
@@ -5055,25 +5094,25 @@
         <v>42</v>
       </c>
       <c r="AN18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO18">
         <v>10.5</v>
       </c>
       <c r="AP18">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AQ18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR18">
+        <v>21</v>
+      </c>
+      <c r="AS18">
+        <v>3.9</v>
+      </c>
+      <c r="AT18">
         <v>20</v>
-      </c>
-      <c r="AS18">
-        <v>3.95</v>
-      </c>
-      <c r="AT18">
-        <v>19.5</v>
       </c>
       <c r="AU18">
         <v>10</v>
@@ -5082,10 +5121,10 @@
         <v>10.5</v>
       </c>
       <c r="AW18">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY18">
         <v>10.5</v>
@@ -5097,7 +5136,7 @@
         <v>16.5</v>
       </c>
       <c r="BB18">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BC18">
         <v>16</v>
@@ -5106,13 +5145,13 @@
         <v>16.5</v>
       </c>
       <c r="BE18">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BF18">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG18">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5175,7 +5214,7 @@
         <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5183,16 +5222,16 @@
         <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F19">
         <v>1.2</v>
@@ -5222,7 +5261,7 @@
         <v>3.45</v>
       </c>
       <c r="O19">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P19">
         <v>2.02</v>
@@ -5246,7 +5285,7 @@
         <v>1.01</v>
       </c>
       <c r="W19">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5417,7 +5456,7 @@
         <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5425,16 +5464,16 @@
         <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F20">
         <v>2.82</v>
@@ -5458,7 +5497,7 @@
         <v>1.48</v>
       </c>
       <c r="M20">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N20">
         <v>2.44</v>
@@ -5659,7 +5698,7 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5667,16 +5706,16 @@
         <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E21" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F21">
         <v>2.06</v>
@@ -5688,7 +5727,7 @@
         <v>4.4</v>
       </c>
       <c r="I21">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J21">
         <v>2.82</v>
@@ -5703,142 +5742,142 @@
         <v>1.15</v>
       </c>
       <c r="N21">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="O21">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="P21">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Q21">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="R21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S21">
-        <v>2.62</v>
+        <v>6.4</v>
       </c>
       <c r="T21">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="U21">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="V21">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W21">
         <v>1.75</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y21">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Z21">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB21">
+        <v>6.4</v>
+      </c>
+      <c r="AC21">
         <v>7.8</v>
       </c>
-      <c r="AC21">
-        <v>9.6</v>
-      </c>
       <c r="AD21">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF21">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AG21">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AH21">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ21">
+        <v>32</v>
+      </c>
+      <c r="AK21">
+        <v>38</v>
+      </c>
+      <c r="AL21">
+        <v>95</v>
+      </c>
+      <c r="AM21">
+        <v>340</v>
+      </c>
+      <c r="AN21">
         <v>40</v>
       </c>
-      <c r="AK21">
-        <v>48</v>
-      </c>
-      <c r="AL21">
-        <v>100</v>
-      </c>
-      <c r="AM21">
-        <v>1000</v>
-      </c>
-      <c r="AN21">
-        <v>50</v>
-      </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP21">
-        <v>2.38</v>
+        <v>5.6</v>
       </c>
       <c r="AQ21">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR21">
-        <v>2.26</v>
+        <v>22</v>
       </c>
       <c r="AS21">
-        <v>2.38</v>
+        <v>7.6</v>
       </c>
       <c r="AT21">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU21">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AV21">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW21">
-        <v>2.38</v>
+        <v>7.6</v>
       </c>
       <c r="AX21">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY21">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ21">
         <v>19</v>
       </c>
       <c r="BA21">
-        <v>2.38</v>
+        <v>7.6</v>
       </c>
       <c r="BB21">
         <v>20</v>
       </c>
       <c r="BC21">
-        <v>2.26</v>
+        <v>23</v>
       </c>
       <c r="BD21">
-        <v>2.32</v>
+        <v>7.4</v>
       </c>
       <c r="BE21">
-        <v>2.38</v>
+        <v>7.8</v>
       </c>
       <c r="BF21">
-        <v>2.26</v>
+        <v>24</v>
       </c>
       <c r="BG21">
-        <v>2.38</v>
+        <v>7.8</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5901,7 +5940,7 @@
         <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5909,16 +5948,16 @@
         <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E22" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="F22">
         <v>4</v>
@@ -5930,7 +5969,7 @@
         <v>1.98</v>
       </c>
       <c r="I22">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="J22">
         <v>2.88</v>
@@ -6143,7 +6182,7 @@
         <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6151,31 +6190,31 @@
         <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E23" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F23">
         <v>1.09</v>
       </c>
       <c r="G23">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H23">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I23">
         <v>990</v>
       </c>
       <c r="J23">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="K23">
         <v>950</v>
@@ -6385,7 +6424,7 @@
         <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6393,1209 +6432,1209 @@
         <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E24" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F24">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="G24">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="H24">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="I24">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="J24">
+        <v>3.75</v>
+      </c>
+      <c r="K24">
         <v>3.85</v>
       </c>
-      <c r="K24">
-        <v>3.9</v>
-      </c>
       <c r="L24">
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N24">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="O24">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="P24">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="Q24">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="R24">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="S24">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="T24">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="U24">
-        <v>2.26</v>
+        <v>2.68</v>
       </c>
       <c r="V24">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="W24">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="X24">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="Y24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z24">
+        <v>25</v>
+      </c>
+      <c r="AA24">
+        <v>48</v>
+      </c>
+      <c r="AB24">
+        <v>16</v>
+      </c>
+      <c r="AC24">
+        <v>10</v>
+      </c>
+      <c r="AD24">
+        <v>13</v>
+      </c>
+      <c r="AE24">
+        <v>29</v>
+      </c>
+      <c r="AF24">
+        <v>21</v>
+      </c>
+      <c r="AG24">
+        <v>13.5</v>
+      </c>
+      <c r="AH24">
+        <v>14.5</v>
+      </c>
+      <c r="AI24">
+        <v>34</v>
+      </c>
+      <c r="AJ24">
         <v>36</v>
       </c>
-      <c r="AA24">
-        <v>85</v>
-      </c>
-      <c r="AB24">
-        <v>11</v>
-      </c>
-      <c r="AC24">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD24">
-        <v>17</v>
-      </c>
-      <c r="AE24">
-        <v>50</v>
-      </c>
-      <c r="AF24">
-        <v>13</v>
-      </c>
-      <c r="AG24">
-        <v>10.5</v>
-      </c>
-      <c r="AH24">
-        <v>19</v>
-      </c>
-      <c r="AI24">
-        <v>55</v>
-      </c>
-      <c r="AJ24">
+      <c r="AK24">
         <v>23</v>
       </c>
-      <c r="AK24">
+      <c r="AL24">
+        <v>30</v>
+      </c>
+      <c r="AM24">
+        <v>60</v>
+      </c>
+      <c r="AN24">
+        <v>13.5</v>
+      </c>
+      <c r="AO24">
         <v>20</v>
       </c>
-      <c r="AL24">
-        <v>34</v>
-      </c>
-      <c r="AM24">
-        <v>90</v>
-      </c>
-      <c r="AN24">
-        <v>13</v>
-      </c>
-      <c r="AO24">
-        <v>50</v>
-      </c>
       <c r="AP24">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AQ24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR24">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AS24">
         <v>36</v>
       </c>
       <c r="AT24">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="AU24">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV24">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AW24">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AX24">
+        <v>17.5</v>
+      </c>
+      <c r="AY24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ24">
+        <v>12.5</v>
+      </c>
+      <c r="BA24">
+        <v>28</v>
+      </c>
+      <c r="BB24">
+        <v>28</v>
+      </c>
+      <c r="BC24">
+        <v>20</v>
+      </c>
+      <c r="BD24">
+        <v>25</v>
+      </c>
+      <c r="BE24">
+        <v>48</v>
+      </c>
+      <c r="BF24">
         <v>11.5</v>
       </c>
-      <c r="AY24">
-        <v>9.4</v>
-      </c>
-      <c r="AZ24">
-        <v>16</v>
-      </c>
-      <c r="BA24">
-        <v>46</v>
-      </c>
-      <c r="BB24">
-        <v>20</v>
-      </c>
-      <c r="BC24">
-        <v>17</v>
-      </c>
-      <c r="BD24">
-        <v>29</v>
-      </c>
-      <c r="BE24">
-        <v>36</v>
-      </c>
-      <c r="BF24">
-        <v>11</v>
-      </c>
       <c r="BG24">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="BH24">
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP24">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E25" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="F25">
-        <v>1.08</v>
+        <v>2</v>
       </c>
       <c r="G25">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H25">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="I25">
-        <v>990</v>
+        <v>4.2</v>
       </c>
       <c r="J25">
-        <v>1.12</v>
+        <v>3.8</v>
       </c>
       <c r="K25">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N25">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="O25">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="P25">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q25">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="R25">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S25">
-        <v>1.16</v>
+        <v>3.1</v>
       </c>
       <c r="T25">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="U25">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V25">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="W25">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI25">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK25">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO25">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ25">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS25">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU25">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW25">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA25">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="CB25" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E26" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F26">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="G26">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="H26">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="I26">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="J26">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="K26">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="L26">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="M26">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
+        <v>3.35</v>
+      </c>
+      <c r="O26">
+        <v>1.37</v>
+      </c>
+      <c r="P26">
+        <v>1.81</v>
+      </c>
+      <c r="Q26">
+        <v>2.08</v>
+      </c>
+      <c r="R26">
+        <v>1.3</v>
+      </c>
+      <c r="S26">
+        <v>3.85</v>
+      </c>
+      <c r="T26">
+        <v>2.24</v>
+      </c>
+      <c r="U26">
+        <v>1.73</v>
+      </c>
+      <c r="V26">
+        <v>1.14</v>
+      </c>
+      <c r="W26">
+        <v>2.74</v>
+      </c>
+      <c r="X26">
+        <v>13</v>
+      </c>
+      <c r="Y26">
+        <v>21</v>
+      </c>
+      <c r="Z26">
+        <v>70</v>
+      </c>
+      <c r="AA26">
+        <v>310</v>
+      </c>
+      <c r="AB26">
         <v>6.8</v>
       </c>
-      <c r="O26">
-        <v>1.16</v>
-      </c>
-      <c r="P26">
-        <v>2.98</v>
-      </c>
-      <c r="Q26">
-        <v>1.48</v>
-      </c>
-      <c r="R26">
-        <v>1.77</v>
-      </c>
-      <c r="S26">
-        <v>2.24</v>
-      </c>
-      <c r="T26">
-        <v>1.81</v>
-      </c>
-      <c r="U26">
-        <v>2.16</v>
-      </c>
-      <c r="V26">
-        <v>1.11</v>
-      </c>
-      <c r="W26">
-        <v>3.75</v>
-      </c>
-      <c r="X26">
+      <c r="AC26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD26">
         <v>32</v>
       </c>
-      <c r="Y26">
-        <v>42</v>
-      </c>
-      <c r="Z26">
-        <v>90</v>
-      </c>
-      <c r="AA26">
-        <v>280</v>
-      </c>
-      <c r="AB26">
-        <v>12.5</v>
-      </c>
-      <c r="AC26">
-        <v>14</v>
-      </c>
-      <c r="AD26">
-        <v>34</v>
-      </c>
       <c r="AE26">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG26">
         <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AI26">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="AJ26">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK26">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL26">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="AM26">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="AN26">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AO26">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="AP26">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="AQ26">
-        <v>36</v>
+        <v>17.5</v>
       </c>
       <c r="AR26">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AS26">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AT26">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU26">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV26">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AW26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX26">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY26">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BA26">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BB26">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC26">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BD26">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="BE26">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="BF26">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="BG26">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="BH26">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F27">
-        <v>2.52</v>
+        <v>1.09</v>
       </c>
       <c r="G27">
-        <v>2.56</v>
+        <v>990</v>
       </c>
       <c r="H27">
-        <v>3.2</v>
+        <v>1.09</v>
       </c>
       <c r="I27">
-        <v>3.3</v>
+        <v>990</v>
       </c>
       <c r="J27">
-        <v>3.35</v>
+        <v>1.17</v>
       </c>
       <c r="K27">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="O27">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="P27">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="Q27">
-        <v>2.16</v>
+        <v>1.15</v>
       </c>
       <c r="R27">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S27">
-        <v>4</v>
+        <v>1.16</v>
       </c>
       <c r="T27">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="U27">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="V27">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="W27">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
       <c r="X27">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E28" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F28">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="G28">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="H28">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="I28">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J28">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="K28">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="L28">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="M28">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N28">
-        <v>3.35</v>
+        <v>6.6</v>
       </c>
       <c r="O28">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="P28">
+        <v>2.92</v>
+      </c>
+      <c r="Q28">
+        <v>1.48</v>
+      </c>
+      <c r="R28">
+        <v>1.75</v>
+      </c>
+      <c r="S28">
+        <v>2.24</v>
+      </c>
+      <c r="T28">
         <v>1.81</v>
       </c>
-      <c r="Q28">
-        <v>2.08</v>
-      </c>
-      <c r="R28">
-        <v>1.3</v>
-      </c>
-      <c r="S28">
-        <v>3.9</v>
-      </c>
-      <c r="T28">
-        <v>2.22</v>
-      </c>
       <c r="U28">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="V28">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W28">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="X28">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="Y28">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="Z28">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AA28">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AB28">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AC28">
+        <v>14</v>
+      </c>
+      <c r="AD28">
+        <v>34</v>
+      </c>
+      <c r="AE28">
+        <v>120</v>
+      </c>
+      <c r="AF28">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AD28">
-        <v>32</v>
-      </c>
-      <c r="AE28">
-        <v>1000</v>
-      </c>
-      <c r="AF28">
-        <v>8.199999999999999</v>
       </c>
       <c r="AG28">
         <v>10.5</v>
       </c>
       <c r="AH28">
+        <v>25</v>
+      </c>
+      <c r="AI28">
+        <v>95</v>
+      </c>
+      <c r="AJ28">
+        <v>11.5</v>
+      </c>
+      <c r="AK28">
+        <v>12.5</v>
+      </c>
+      <c r="AL28">
+        <v>28</v>
+      </c>
+      <c r="AM28">
+        <v>110</v>
+      </c>
+      <c r="AN28">
+        <v>4.4</v>
+      </c>
+      <c r="AO28">
+        <v>110</v>
+      </c>
+      <c r="AP28">
         <v>30</v>
       </c>
-      <c r="AI28">
-        <v>180</v>
-      </c>
-      <c r="AJ28">
+      <c r="AQ28">
+        <v>36</v>
+      </c>
+      <c r="AR28">
+        <v>60</v>
+      </c>
+      <c r="AS28">
+        <v>23</v>
+      </c>
+      <c r="AT28">
+        <v>11</v>
+      </c>
+      <c r="AU28">
+        <v>13.5</v>
+      </c>
+      <c r="AV28">
+        <v>30</v>
+      </c>
+      <c r="AW28">
+        <v>40</v>
+      </c>
+      <c r="AX28">
+        <v>9.4</v>
+      </c>
+      <c r="AY28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ28">
+        <v>21</v>
+      </c>
+      <c r="BA28">
+        <v>55</v>
+      </c>
+      <c r="BB28">
+        <v>10.5</v>
+      </c>
+      <c r="BC28">
+        <v>11.5</v>
+      </c>
+      <c r="BD28">
+        <v>25</v>
+      </c>
+      <c r="BE28">
+        <v>75</v>
+      </c>
+      <c r="BF28">
+        <v>4.1</v>
+      </c>
+      <c r="BG28">
+        <v>75</v>
+      </c>
+      <c r="BH28">
+        <v>5</v>
+      </c>
+      <c r="BI28">
+        <v>2.12</v>
+      </c>
+      <c r="BJ28">
+        <v>14.5</v>
+      </c>
+      <c r="BK28">
+        <v>3.3</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>3.7</v>
+      </c>
+      <c r="BN28">
+        <v>5.6</v>
+      </c>
+      <c r="BO28">
+        <v>2.98</v>
+      </c>
+      <c r="BP28">
+        <v>11</v>
+      </c>
+      <c r="BQ28">
+        <v>5.2</v>
+      </c>
+      <c r="BR28">
+        <v>27</v>
+      </c>
+      <c r="BS28">
+        <v>3.25</v>
+      </c>
+      <c r="BT28">
+        <v>17</v>
+      </c>
+      <c r="BU28">
+        <v>3.45</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>3.55</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>3.55</v>
+      </c>
+      <c r="BZ28">
         <v>14</v>
       </c>
-      <c r="AK28">
-        <v>18.5</v>
-      </c>
-      <c r="AL28">
-        <v>180</v>
-      </c>
-      <c r="AM28">
-        <v>220</v>
-      </c>
-      <c r="AN28">
-        <v>10.5</v>
-      </c>
-      <c r="AO28">
-        <v>240</v>
-      </c>
-      <c r="AP28">
-        <v>12</v>
-      </c>
-      <c r="AQ28">
-        <v>17.5</v>
-      </c>
-      <c r="AR28">
-        <v>50</v>
-      </c>
-      <c r="AS28">
-        <v>16.5</v>
-      </c>
-      <c r="AT28">
-        <v>6.4</v>
-      </c>
-      <c r="AU28">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV28">
-        <v>25</v>
-      </c>
-      <c r="AW28">
-        <v>42</v>
-      </c>
-      <c r="AX28">
-        <v>7.2</v>
-      </c>
-      <c r="AY28">
-        <v>9.4</v>
-      </c>
-      <c r="AZ28">
-        <v>25</v>
-      </c>
-      <c r="BA28">
-        <v>42</v>
-      </c>
-      <c r="BB28">
-        <v>12</v>
-      </c>
-      <c r="BC28">
-        <v>16</v>
-      </c>
-      <c r="BD28">
-        <v>42</v>
-      </c>
-      <c r="BE28">
-        <v>16</v>
-      </c>
-      <c r="BF28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG28">
-        <v>17</v>
-      </c>
-      <c r="BH28">
-        <v>1000</v>
-      </c>
-      <c r="BI28">
-        <v>1.04</v>
-      </c>
-      <c r="BJ28">
-        <v>1000</v>
-      </c>
-      <c r="BK28">
-        <v>1.04</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>1.04</v>
-      </c>
-      <c r="BN28">
-        <v>1000</v>
-      </c>
-      <c r="BO28">
-        <v>1.04</v>
-      </c>
-      <c r="BP28">
-        <v>1000</v>
-      </c>
-      <c r="BQ28">
-        <v>1.04</v>
-      </c>
-      <c r="BR28">
-        <v>1000</v>
-      </c>
-      <c r="BS28">
-        <v>1.04</v>
-      </c>
-      <c r="BT28">
-        <v>1000</v>
-      </c>
-      <c r="BU28">
-        <v>1.04</v>
-      </c>
-      <c r="BV28">
-        <v>1000</v>
-      </c>
-      <c r="BW28">
-        <v>1.04</v>
-      </c>
-      <c r="BX28">
-        <v>1000</v>
-      </c>
-      <c r="BY28">
-        <v>1.04</v>
-      </c>
-      <c r="BZ28">
-        <v>1000</v>
-      </c>
       <c r="CA28">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="CB28" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7603,241 +7642,1209 @@
         <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F29">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="G29">
         <v>2.56</v>
       </c>
       <c r="H29">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="I29">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="J29">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="K29">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="L29">
         <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="N29">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="O29">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="P29">
-        <v>2.54</v>
+        <v>1.81</v>
       </c>
       <c r="Q29">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="R29">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="S29">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="T29">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="U29">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="V29">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
         <v>1.64</v>
       </c>
       <c r="X29">
+        <v>12.5</v>
+      </c>
+      <c r="Y29">
+        <v>11.5</v>
+      </c>
+      <c r="Z29">
+        <v>21</v>
+      </c>
+      <c r="AA29">
+        <v>60</v>
+      </c>
+      <c r="AB29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC29">
+        <v>7.6</v>
+      </c>
+      <c r="AD29">
+        <v>15</v>
+      </c>
+      <c r="AE29">
+        <v>42</v>
+      </c>
+      <c r="AF29">
+        <v>15.5</v>
+      </c>
+      <c r="AG29">
+        <v>12</v>
+      </c>
+      <c r="AH29">
+        <v>19</v>
+      </c>
+      <c r="AI29">
+        <v>55</v>
+      </c>
+      <c r="AJ29">
+        <v>38</v>
+      </c>
+      <c r="AK29">
+        <v>30</v>
+      </c>
+      <c r="AL29">
+        <v>46</v>
+      </c>
+      <c r="AM29">
+        <v>110</v>
+      </c>
+      <c r="AN29">
+        <v>26</v>
+      </c>
+      <c r="AO29">
+        <v>42</v>
+      </c>
+      <c r="AP29">
+        <v>10.5</v>
+      </c>
+      <c r="AQ29">
+        <v>10.5</v>
+      </c>
+      <c r="AR29">
+        <v>18.5</v>
+      </c>
+      <c r="AS29">
+        <v>50</v>
+      </c>
+      <c r="AT29">
+        <v>9</v>
+      </c>
+      <c r="AU29">
+        <v>6.8</v>
+      </c>
+      <c r="AV29">
+        <v>13</v>
+      </c>
+      <c r="AW29">
+        <v>34</v>
+      </c>
+      <c r="AX29">
+        <v>13.5</v>
+      </c>
+      <c r="AY29">
+        <v>11</v>
+      </c>
+      <c r="AZ29">
+        <v>16.5</v>
+      </c>
+      <c r="BA29">
+        <v>44</v>
+      </c>
+      <c r="BB29">
+        <v>32</v>
+      </c>
+      <c r="BC29">
+        <v>26</v>
+      </c>
+      <c r="BD29">
+        <v>36</v>
+      </c>
+      <c r="BE29">
+        <v>38</v>
+      </c>
+      <c r="BF29">
+        <v>22</v>
+      </c>
+      <c r="BG29">
+        <v>34</v>
+      </c>
+      <c r="BH29">
+        <v>3.95</v>
+      </c>
+      <c r="BI29">
+        <v>2.56</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
+        <v>1.35</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>1.35</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>1.35</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>1.35</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>1.35</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>1.35</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>1.35</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>1.35</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>1.35</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" t="s">
+        <v>166</v>
+      </c>
+      <c r="F30">
+        <v>2.78</v>
+      </c>
+      <c r="G30">
+        <v>3.15</v>
+      </c>
+      <c r="H30">
+        <v>2.76</v>
+      </c>
+      <c r="I30">
+        <v>3.15</v>
+      </c>
+      <c r="J30">
+        <v>2.96</v>
+      </c>
+      <c r="K30">
+        <v>3.35</v>
+      </c>
+      <c r="L30">
+        <v>1.01</v>
+      </c>
+      <c r="M30">
+        <v>1.12</v>
+      </c>
+      <c r="N30">
+        <v>2.64</v>
+      </c>
+      <c r="O30">
+        <v>1.5</v>
+      </c>
+      <c r="P30">
+        <v>1.55</v>
+      </c>
+      <c r="Q30">
+        <v>2.48</v>
+      </c>
+      <c r="R30">
+        <v>1.2</v>
+      </c>
+      <c r="S30">
+        <v>5</v>
+      </c>
+      <c r="T30">
+        <v>2</v>
+      </c>
+      <c r="U30">
+        <v>1.81</v>
+      </c>
+      <c r="V30">
+        <v>1.47</v>
+      </c>
+      <c r="W30">
+        <v>1.47</v>
+      </c>
+      <c r="X30">
+        <v>10.5</v>
+      </c>
+      <c r="Y30">
+        <v>10.5</v>
+      </c>
+      <c r="Z30">
+        <v>21</v>
+      </c>
+      <c r="AA30">
+        <v>60</v>
+      </c>
+      <c r="AB30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC30">
+        <v>7.4</v>
+      </c>
+      <c r="AD30">
+        <v>14</v>
+      </c>
+      <c r="AE30">
+        <v>50</v>
+      </c>
+      <c r="AF30">
+        <v>22</v>
+      </c>
+      <c r="AG30">
+        <v>14.5</v>
+      </c>
+      <c r="AH30">
+        <v>25</v>
+      </c>
+      <c r="AI30">
+        <v>75</v>
+      </c>
+      <c r="AJ30">
+        <v>65</v>
+      </c>
+      <c r="AK30">
+        <v>50</v>
+      </c>
+      <c r="AL30">
+        <v>75</v>
+      </c>
+      <c r="AM30">
+        <v>190</v>
+      </c>
+      <c r="AN30">
+        <v>60</v>
+      </c>
+      <c r="AO30">
+        <v>60</v>
+      </c>
+      <c r="AP30">
+        <v>7</v>
+      </c>
+      <c r="AQ30">
+        <v>7.4</v>
+      </c>
+      <c r="AR30">
+        <v>15.5</v>
+      </c>
+      <c r="AS30">
+        <v>5.8</v>
+      </c>
+      <c r="AT30">
+        <v>7.6</v>
+      </c>
+      <c r="AU30">
+        <v>5.6</v>
+      </c>
+      <c r="AV30">
+        <v>11.5</v>
+      </c>
+      <c r="AW30">
+        <v>5.7</v>
+      </c>
+      <c r="AX30">
+        <v>15.5</v>
+      </c>
+      <c r="AY30">
+        <v>11.5</v>
+      </c>
+      <c r="AZ30">
+        <v>17.5</v>
+      </c>
+      <c r="BA30">
+        <v>5.9</v>
+      </c>
+      <c r="BB30">
+        <v>5.8</v>
+      </c>
+      <c r="BC30">
+        <v>5.7</v>
+      </c>
+      <c r="BD30">
+        <v>5.9</v>
+      </c>
+      <c r="BE30">
+        <v>6.2</v>
+      </c>
+      <c r="BF30">
+        <v>5.8</v>
+      </c>
+      <c r="BG30">
+        <v>5.8</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
+        <v>1.04</v>
+      </c>
+      <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
+        <v>1.04</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>1.04</v>
+      </c>
+      <c r="BN30">
+        <v>1000</v>
+      </c>
+      <c r="BO30">
+        <v>1.04</v>
+      </c>
+      <c r="BP30">
+        <v>1000</v>
+      </c>
+      <c r="BQ30">
+        <v>1.04</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>1.04</v>
+      </c>
+      <c r="BT30">
+        <v>1000</v>
+      </c>
+      <c r="BU30">
+        <v>1.04</v>
+      </c>
+      <c r="BV30">
+        <v>1000</v>
+      </c>
+      <c r="BW30">
+        <v>1.04</v>
+      </c>
+      <c r="BX30">
+        <v>1000</v>
+      </c>
+      <c r="BY30">
+        <v>1.04</v>
+      </c>
+      <c r="BZ30">
+        <v>1000</v>
+      </c>
+      <c r="CA30">
+        <v>1.04</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" t="s">
+        <v>135</v>
+      </c>
+      <c r="E31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31">
+        <v>2.06</v>
+      </c>
+      <c r="G31">
+        <v>2.46</v>
+      </c>
+      <c r="H31">
+        <v>3.1</v>
+      </c>
+      <c r="I31">
+        <v>4.3</v>
+      </c>
+      <c r="J31">
+        <v>3.1</v>
+      </c>
+      <c r="K31">
+        <v>5.3</v>
+      </c>
+      <c r="L31">
+        <v>1.28</v>
+      </c>
+      <c r="M31">
+        <v>1.01</v>
+      </c>
+      <c r="N31">
+        <v>2.74</v>
+      </c>
+      <c r="O31">
+        <v>1.28</v>
+      </c>
+      <c r="P31">
+        <v>1.87</v>
+      </c>
+      <c r="Q31">
+        <v>1.84</v>
+      </c>
+      <c r="R31">
+        <v>1.31</v>
+      </c>
+      <c r="S31">
+        <v>2.6</v>
+      </c>
+      <c r="T31">
+        <v>1.11</v>
+      </c>
+      <c r="U31">
+        <v>1.11</v>
+      </c>
+      <c r="V31">
+        <v>1.3</v>
+      </c>
+      <c r="W31">
+        <v>1.68</v>
+      </c>
+      <c r="X31">
+        <v>1000</v>
+      </c>
+      <c r="Y31">
+        <v>1000</v>
+      </c>
+      <c r="Z31">
+        <v>1000</v>
+      </c>
+      <c r="AA31">
+        <v>1000</v>
+      </c>
+      <c r="AB31">
+        <v>1000</v>
+      </c>
+      <c r="AC31">
+        <v>1000</v>
+      </c>
+      <c r="AD31">
+        <v>1000</v>
+      </c>
+      <c r="AE31">
+        <v>1000</v>
+      </c>
+      <c r="AF31">
+        <v>1000</v>
+      </c>
+      <c r="AG31">
+        <v>1000</v>
+      </c>
+      <c r="AH31">
+        <v>1000</v>
+      </c>
+      <c r="AI31">
+        <v>1000</v>
+      </c>
+      <c r="AJ31">
+        <v>1000</v>
+      </c>
+      <c r="AK31">
+        <v>1000</v>
+      </c>
+      <c r="AL31">
+        <v>1000</v>
+      </c>
+      <c r="AM31">
+        <v>1000</v>
+      </c>
+      <c r="AN31">
+        <v>1000</v>
+      </c>
+      <c r="AO31">
+        <v>1000</v>
+      </c>
+      <c r="AP31">
+        <v>1.01</v>
+      </c>
+      <c r="AQ31">
+        <v>1.01</v>
+      </c>
+      <c r="AR31">
+        <v>1.01</v>
+      </c>
+      <c r="AS31">
+        <v>1.01</v>
+      </c>
+      <c r="AT31">
+        <v>1.01</v>
+      </c>
+      <c r="AU31">
+        <v>1.01</v>
+      </c>
+      <c r="AV31">
+        <v>1.01</v>
+      </c>
+      <c r="AW31">
+        <v>1.01</v>
+      </c>
+      <c r="AX31">
+        <v>1.01</v>
+      </c>
+      <c r="AY31">
+        <v>1.01</v>
+      </c>
+      <c r="AZ31">
+        <v>1.01</v>
+      </c>
+      <c r="BA31">
+        <v>1.01</v>
+      </c>
+      <c r="BB31">
+        <v>1.01</v>
+      </c>
+      <c r="BC31">
+        <v>1.01</v>
+      </c>
+      <c r="BD31">
+        <v>1.01</v>
+      </c>
+      <c r="BE31">
+        <v>1.01</v>
+      </c>
+      <c r="BF31">
+        <v>1.01</v>
+      </c>
+      <c r="BG31">
+        <v>1.01</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>1.04</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>1.04</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.04</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.04</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>1.04</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>1.04</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.04</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>1.04</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.04</v>
+      </c>
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
+        <v>1.04</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" t="s">
+        <v>168</v>
+      </c>
+      <c r="F32">
+        <v>1.08</v>
+      </c>
+      <c r="G32">
+        <v>990</v>
+      </c>
+      <c r="H32">
+        <v>1.08</v>
+      </c>
+      <c r="I32">
+        <v>990</v>
+      </c>
+      <c r="J32">
+        <v>1.12</v>
+      </c>
+      <c r="K32">
+        <v>950</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.01</v>
+      </c>
+      <c r="N32">
+        <v>1.3</v>
+      </c>
+      <c r="O32">
+        <v>1.12</v>
+      </c>
+      <c r="P32">
+        <v>1.3</v>
+      </c>
+      <c r="Q32">
+        <v>1.12</v>
+      </c>
+      <c r="R32">
+        <v>1.18</v>
+      </c>
+      <c r="S32">
+        <v>1.13</v>
+      </c>
+      <c r="T32">
+        <v>1.11</v>
+      </c>
+      <c r="U32">
+        <v>1.11</v>
+      </c>
+      <c r="V32">
+        <v>1.01</v>
+      </c>
+      <c r="W32">
+        <v>1.01</v>
+      </c>
+      <c r="X32">
+        <v>1000</v>
+      </c>
+      <c r="Y32">
+        <v>1000</v>
+      </c>
+      <c r="Z32">
+        <v>1000</v>
+      </c>
+      <c r="AA32">
+        <v>1000</v>
+      </c>
+      <c r="AB32">
+        <v>1000</v>
+      </c>
+      <c r="AC32">
+        <v>1000</v>
+      </c>
+      <c r="AD32">
+        <v>1000</v>
+      </c>
+      <c r="AE32">
+        <v>1000</v>
+      </c>
+      <c r="AF32">
+        <v>1000</v>
+      </c>
+      <c r="AG32">
+        <v>1000</v>
+      </c>
+      <c r="AH32">
+        <v>1000</v>
+      </c>
+      <c r="AI32">
+        <v>1000</v>
+      </c>
+      <c r="AJ32">
+        <v>1000</v>
+      </c>
+      <c r="AK32">
+        <v>1000</v>
+      </c>
+      <c r="AL32">
+        <v>1000</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
+        <v>1000</v>
+      </c>
+      <c r="AO32">
+        <v>1000</v>
+      </c>
+      <c r="AP32">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32">
+        <v>1.01</v>
+      </c>
+      <c r="AR32">
+        <v>1.01</v>
+      </c>
+      <c r="AS32">
+        <v>1.01</v>
+      </c>
+      <c r="AT32">
+        <v>1.01</v>
+      </c>
+      <c r="AU32">
+        <v>1.01</v>
+      </c>
+      <c r="AV32">
+        <v>1.01</v>
+      </c>
+      <c r="AW32">
+        <v>1.01</v>
+      </c>
+      <c r="AX32">
+        <v>1.01</v>
+      </c>
+      <c r="AY32">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32">
+        <v>1.01</v>
+      </c>
+      <c r="BA32">
+        <v>1.01</v>
+      </c>
+      <c r="BB32">
+        <v>1.01</v>
+      </c>
+      <c r="BC32">
+        <v>1.01</v>
+      </c>
+      <c r="BD32">
+        <v>1.01</v>
+      </c>
+      <c r="BE32">
+        <v>1.01</v>
+      </c>
+      <c r="BF32">
+        <v>1.01</v>
+      </c>
+      <c r="BG32">
+        <v>1.01</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>1.04</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.04</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.04</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.04</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.04</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.04</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.04</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.04</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.04</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" t="s">
+        <v>169</v>
+      </c>
+      <c r="F33">
+        <v>1.93</v>
+      </c>
+      <c r="G33">
+        <v>2.08</v>
+      </c>
+      <c r="H33">
+        <v>4.4</v>
+      </c>
+      <c r="I33">
+        <v>5</v>
+      </c>
+      <c r="J33">
+        <v>3.35</v>
+      </c>
+      <c r="K33">
+        <v>3.65</v>
+      </c>
+      <c r="L33">
+        <v>1.01</v>
+      </c>
+      <c r="M33">
+        <v>1.09</v>
+      </c>
+      <c r="N33">
+        <v>3.05</v>
+      </c>
+      <c r="O33">
+        <v>1.42</v>
+      </c>
+      <c r="P33">
+        <v>1.71</v>
+      </c>
+      <c r="Q33">
+        <v>2.22</v>
+      </c>
+      <c r="R33">
+        <v>1.26</v>
+      </c>
+      <c r="S33">
+        <v>4.2</v>
+      </c>
+      <c r="T33">
+        <v>1.98</v>
+      </c>
+      <c r="U33">
+        <v>1.89</v>
+      </c>
+      <c r="V33">
+        <v>1.25</v>
+      </c>
+      <c r="W33">
+        <v>1.92</v>
+      </c>
+      <c r="X33">
+        <v>11.5</v>
+      </c>
+      <c r="Y33">
+        <v>14</v>
+      </c>
+      <c r="Z33">
+        <v>36</v>
+      </c>
+      <c r="AA33">
+        <v>140</v>
+      </c>
+      <c r="AB33">
+        <v>7.8</v>
+      </c>
+      <c r="AC33">
+        <v>8</v>
+      </c>
+      <c r="AD33">
+        <v>970</v>
+      </c>
+      <c r="AE33">
+        <v>75</v>
+      </c>
+      <c r="AF33">
+        <v>12</v>
+      </c>
+      <c r="AG33">
+        <v>11</v>
+      </c>
+      <c r="AH33">
+        <v>950</v>
+      </c>
+      <c r="AI33">
+        <v>80</v>
+      </c>
+      <c r="AJ33">
+        <v>25</v>
+      </c>
+      <c r="AK33">
         <v>24</v>
       </c>
-      <c r="Y29">
-        <v>18.5</v>
-      </c>
-      <c r="Z29">
-        <v>25</v>
-      </c>
-      <c r="AA29">
-        <v>48</v>
-      </c>
-      <c r="AB29">
-        <v>16.5</v>
-      </c>
-      <c r="AC29">
+      <c r="AL33">
+        <v>46</v>
+      </c>
+      <c r="AM33">
+        <v>180</v>
+      </c>
+      <c r="AN33">
+        <v>970</v>
+      </c>
+      <c r="AO33">
+        <v>120</v>
+      </c>
+      <c r="AP33">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ33">
+        <v>12</v>
+      </c>
+      <c r="AR33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS33">
+        <v>10.5</v>
+      </c>
+      <c r="AT33">
+        <v>6.6</v>
+      </c>
+      <c r="AU33">
+        <v>7</v>
+      </c>
+      <c r="AV33">
+        <v>7.2</v>
+      </c>
+      <c r="AW33">
         <v>10</v>
       </c>
-      <c r="AD29">
-        <v>13</v>
-      </c>
-      <c r="AE29">
-        <v>28</v>
-      </c>
-      <c r="AF29">
-        <v>23</v>
-      </c>
-      <c r="AG29">
-        <v>13.5</v>
-      </c>
-      <c r="AH29">
-        <v>14.5</v>
-      </c>
-      <c r="AI29">
+      <c r="AX33">
+        <v>10</v>
+      </c>
+      <c r="AY33">
+        <v>9.4</v>
+      </c>
+      <c r="AZ33">
+        <v>7.6</v>
+      </c>
+      <c r="BA33">
+        <v>10</v>
+      </c>
+      <c r="BB33">
+        <v>7.8</v>
+      </c>
+      <c r="BC33">
+        <v>20</v>
+      </c>
+      <c r="BD33">
         <v>34</v>
       </c>
-      <c r="AJ29">
-        <v>36</v>
-      </c>
-      <c r="AK29">
-        <v>23</v>
-      </c>
-      <c r="AL29">
-        <v>30</v>
-      </c>
-      <c r="AM29">
-        <v>60</v>
-      </c>
-      <c r="AN29">
-        <v>14</v>
-      </c>
-      <c r="AO29">
-        <v>20</v>
-      </c>
-      <c r="AP29">
-        <v>20</v>
-      </c>
-      <c r="AQ29">
-        <v>16</v>
-      </c>
-      <c r="AR29">
-        <v>21</v>
-      </c>
-      <c r="AS29">
-        <v>36</v>
-      </c>
-      <c r="AT29">
-        <v>14</v>
-      </c>
-      <c r="AU29">
-        <v>8.4</v>
-      </c>
-      <c r="AV29">
-        <v>11.5</v>
-      </c>
-      <c r="AW29">
-        <v>24</v>
-      </c>
-      <c r="AX29">
-        <v>17.5</v>
-      </c>
-      <c r="AY29">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ29">
-        <v>12.5</v>
-      </c>
-      <c r="BA29">
-        <v>28</v>
-      </c>
-      <c r="BB29">
-        <v>28</v>
-      </c>
-      <c r="BC29">
-        <v>20</v>
-      </c>
-      <c r="BD29">
-        <v>25</v>
-      </c>
-      <c r="BE29">
-        <v>46</v>
-      </c>
-      <c r="BF29">
-        <v>11.5</v>
-      </c>
-      <c r="BG29">
-        <v>16.5</v>
-      </c>
-      <c r="BH29">
-        <v>1000</v>
-      </c>
-      <c r="BI29">
-        <v>1.04</v>
-      </c>
-      <c r="BJ29">
-        <v>1000</v>
-      </c>
-      <c r="BK29">
-        <v>1.04</v>
-      </c>
-      <c r="BL29">
-        <v>1000</v>
-      </c>
-      <c r="BM29">
-        <v>1.04</v>
-      </c>
-      <c r="BN29">
-        <v>1000</v>
-      </c>
-      <c r="BO29">
-        <v>1.04</v>
-      </c>
-      <c r="BP29">
-        <v>1000</v>
-      </c>
-      <c r="BQ29">
-        <v>1.04</v>
-      </c>
-      <c r="BR29">
-        <v>1000</v>
-      </c>
-      <c r="BS29">
-        <v>1.04</v>
-      </c>
-      <c r="BT29">
-        <v>1000</v>
-      </c>
-      <c r="BU29">
-        <v>1.04</v>
-      </c>
-      <c r="BV29">
-        <v>1000</v>
-      </c>
-      <c r="BW29">
-        <v>1.04</v>
-      </c>
-      <c r="BX29">
-        <v>1000</v>
-      </c>
-      <c r="BY29">
-        <v>1.04</v>
-      </c>
-      <c r="BZ29">
-        <v>1000</v>
-      </c>
-      <c r="CA29">
-        <v>1.04</v>
-      </c>
-      <c r="CB29" t="s">
-        <v>157</v>
+      <c r="BE33">
+        <v>10.5</v>
+      </c>
+      <c r="BF33">
+        <v>7.2</v>
+      </c>
+      <c r="BG33">
+        <v>10.5</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>1.04</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.04</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.04</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.04</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.04</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.04</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.04</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.04</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.04</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.04</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -526,7 +526,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-25 02:26:08</t>
+    <t>2026-08-25 04:44:01</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1120,7 @@
         <v>138</v>
       </c>
       <c r="F2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G2">
         <v>1.62</v>
@@ -1138,13 +1138,13 @@
         <v>4.2</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
         <v>1.43</v>
@@ -1153,16 +1153,16 @@
         <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
         <v>1.69</v>
@@ -1177,7 +1177,7 @@
         <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z2">
         <v>60</v>
@@ -1189,13 +1189,13 @@
         <v>8</v>
       </c>
       <c r="AC2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF2">
         <v>9.800000000000001</v>
@@ -1219,7 +1219,7 @@
         <v>70</v>
       </c>
       <c r="AM2">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN2">
         <v>12.5</v>
@@ -1237,7 +1237,7 @@
         <v>50</v>
       </c>
       <c r="AS2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT2">
         <v>6</v>
@@ -1249,7 +1249,7 @@
         <v>25</v>
       </c>
       <c r="AW2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX2">
         <v>7.2</v>
@@ -1261,7 +1261,7 @@
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1270,76 +1270,76 @@
         <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2">
         <v>9.6</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK2">
-        <v>1.4</v>
+        <v>9.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO2">
-        <v>1.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ2">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS2">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU2">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA2">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="CB2" t="s">
         <v>170</v>
@@ -1362,22 +1362,22 @@
         <v>139</v>
       </c>
       <c r="F3">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G3">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I3">
         <v>3.75</v>
       </c>
       <c r="J3">
+        <v>3.2</v>
+      </c>
+      <c r="K3">
         <v>3.4</v>
-      </c>
-      <c r="K3">
-        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1386,16 +1386,16 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P3">
         <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
         <v>1.24</v>
@@ -1404,49 +1404,49 @@
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X3">
         <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA3">
         <v>80</v>
       </c>
       <c r="AB3">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
         <v>75</v>
       </c>
       <c r="AF3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AG3">
         <v>12</v>
       </c>
       <c r="AH3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI3">
         <v>80</v>
@@ -1455,43 +1455,43 @@
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3">
         <v>170</v>
       </c>
       <c r="AN3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AO3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP3">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
         <v>9.800000000000001</v>
       </c>
       <c r="AR3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS3">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AT3">
         <v>7</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AX3">
         <v>11</v>
@@ -1503,22 +1503,22 @@
         <v>19</v>
       </c>
       <c r="BA3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB3">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="BC3">
         <v>25</v>
       </c>
       <c r="BD3">
+        <v>8</v>
+      </c>
+      <c r="BE3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF3">
         <v>10.5</v>
-      </c>
-      <c r="BE3">
-        <v>10</v>
-      </c>
-      <c r="BF3">
-        <v>22</v>
       </c>
       <c r="BG3">
         <v>50</v>
@@ -1604,22 +1604,22 @@
         <v>140</v>
       </c>
       <c r="F4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G4">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J4">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K4">
-        <v>6.6</v>
+        <v>500</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1628,22 +1628,22 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="O4">
         <v>1.29</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q4">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1652,10 +1652,10 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W4">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1673,7 +1673,7 @@
         <v>970</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4">
         <v>1000</v>
@@ -1685,7 +1685,7 @@
         <v>970</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4">
         <v>1000</v>
@@ -1712,58 +1712,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="AQ4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="AR4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="AS4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="AT4">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="AU4">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AV4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="AW4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="AX4">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="AY4">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AZ4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BA4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BB4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BC4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BD4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BE4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BF4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BG4">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1846,13 +1846,13 @@
         <v>141</v>
       </c>
       <c r="F5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G5">
         <v>3.6</v>
       </c>
       <c r="H5">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I5">
         <v>2.48</v>
@@ -1876,7 +1876,7 @@
         <v>1.42</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q5">
         <v>2.24</v>
@@ -1897,7 +1897,7 @@
         <v>1.67</v>
       </c>
       <c r="W5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X5">
         <v>11.5</v>
@@ -1906,7 +1906,7 @@
         <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA5">
         <v>42</v>
@@ -1915,7 +1915,7 @@
         <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD5">
         <v>12</v>
@@ -1963,7 +1963,7 @@
         <v>13</v>
       </c>
       <c r="AS5">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1984,28 +1984,28 @@
         <v>13</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
+        <v>6.6</v>
+      </c>
+      <c r="BB5">
         <v>6.8</v>
       </c>
-      <c r="BB5">
-        <v>7</v>
-      </c>
       <c r="BC5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD5">
         <v>38</v>
       </c>
       <c r="BE5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF5">
         <v>34</v>
       </c>
       <c r="BG5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2091,19 +2091,19 @@
         <v>2.34</v>
       </c>
       <c r="G6">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H6">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I6">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J6">
         <v>3.7</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2112,142 +2112,142 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q6">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R6">
+        <v>1.48</v>
+      </c>
+      <c r="S6">
+        <v>2.84</v>
+      </c>
+      <c r="T6">
+        <v>1.64</v>
+      </c>
+      <c r="U6">
+        <v>2.4</v>
+      </c>
+      <c r="V6">
         <v>1.45</v>
       </c>
-      <c r="S6">
-        <v>2.74</v>
-      </c>
-      <c r="T6">
-        <v>1.54</v>
-      </c>
-      <c r="U6">
-        <v>2.34</v>
-      </c>
-      <c r="V6">
-        <v>1.43</v>
-      </c>
       <c r="W6">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X6">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="Y6">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="Z6">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB6">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="AC6">
+        <v>9</v>
+      </c>
+      <c r="AD6">
+        <v>14</v>
+      </c>
+      <c r="AE6">
+        <v>38</v>
+      </c>
+      <c r="AF6">
+        <v>20</v>
+      </c>
+      <c r="AG6">
+        <v>12</v>
+      </c>
+      <c r="AH6">
+        <v>16</v>
+      </c>
+      <c r="AI6">
+        <v>38</v>
+      </c>
+      <c r="AJ6">
+        <v>36</v>
+      </c>
+      <c r="AK6">
+        <v>28</v>
+      </c>
+      <c r="AL6">
+        <v>38</v>
+      </c>
+      <c r="AM6">
+        <v>85</v>
+      </c>
+      <c r="AN6">
+        <v>16</v>
+      </c>
+      <c r="AO6">
+        <v>26</v>
+      </c>
+      <c r="AP6">
+        <v>16.5</v>
+      </c>
+      <c r="AQ6">
+        <v>13</v>
+      </c>
+      <c r="AR6">
+        <v>7.2</v>
+      </c>
+      <c r="AS6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT6">
         <v>11</v>
       </c>
-      <c r="AD6">
-        <v>32</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>75</v>
-      </c>
-      <c r="AG6">
-        <v>15.5</v>
-      </c>
-      <c r="AH6">
-        <v>970</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>150</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>1.38</v>
-      </c>
-      <c r="AQ6">
-        <v>1.39</v>
-      </c>
-      <c r="AR6">
-        <v>5.3</v>
-      </c>
-      <c r="AS6">
-        <v>12.5</v>
-      </c>
-      <c r="AT6">
+      <c r="AU6">
+        <v>7.8</v>
+      </c>
+      <c r="AV6">
+        <v>12</v>
+      </c>
+      <c r="AW6">
+        <v>7.8</v>
+      </c>
+      <c r="AX6">
+        <v>15</v>
+      </c>
+      <c r="AY6">
         <v>10</v>
       </c>
-      <c r="AU6">
-        <v>6.2</v>
-      </c>
-      <c r="AV6">
-        <v>8.6</v>
-      </c>
-      <c r="AW6">
-        <v>10.5</v>
-      </c>
-      <c r="AX6">
-        <v>1.38</v>
-      </c>
-      <c r="AY6">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BC6">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BD6">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BE6">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="BF6">
-        <v>1.41</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
-        <v>1.41</v>
+        <v>18.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2330,13 +2330,13 @@
         <v>143</v>
       </c>
       <c r="F7">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G7">
         <v>1.59</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>8.199999999999999</v>
@@ -2345,52 +2345,52 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R7">
         <v>1.3</v>
       </c>
       <c r="S7">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T7">
         <v>2.26</v>
       </c>
       <c r="U7">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V7">
         <v>1.14</v>
       </c>
       <c r="W7">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="X7">
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z7">
-        <v>450</v>
+        <v>490</v>
       </c>
       <c r="AA7">
         <v>1000</v>
@@ -2402,7 +2402,7 @@
         <v>9.6</v>
       </c>
       <c r="AD7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE7">
         <v>1000</v>
@@ -2432,7 +2432,7 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO7">
         <v>1000</v>
@@ -2483,13 +2483,13 @@
         <v>28</v>
       </c>
       <c r="BE7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF7">
         <v>9.4</v>
       </c>
       <c r="BG7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2572,13 +2572,13 @@
         <v>144</v>
       </c>
       <c r="F8">
-        <v>2.26</v>
+        <v>3.95</v>
       </c>
       <c r="G8">
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="I8">
         <v>1.82</v>
@@ -2587,7 +2587,7 @@
         <v>1.1</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2596,7 +2596,7 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>5.5</v>
+        <v>1.32</v>
       </c>
       <c r="O8">
         <v>1.12</v>
@@ -2623,7 +2623,7 @@
         <v>2.2</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2817,55 +2817,55 @@
         <v>1.93</v>
       </c>
       <c r="G9">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H9">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J9">
         <v>4.1</v>
       </c>
       <c r="K9">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M9">
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P9">
         <v>2.64</v>
       </c>
       <c r="Q9">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R9">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S9">
         <v>2.28</v>
       </c>
       <c r="T9">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U9">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="X9">
         <v>28</v>
@@ -3065,7 +3065,7 @@
         <v>2.72</v>
       </c>
       <c r="I10">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J10">
         <v>3.45</v>
@@ -3104,7 +3104,7 @@
         <v>2.26</v>
       </c>
       <c r="V10">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W10">
         <v>1.57</v>
@@ -3298,22 +3298,22 @@
         <v>147</v>
       </c>
       <c r="F11">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G11">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H11">
         <v>5</v>
       </c>
       <c r="I11">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J11">
         <v>5.6</v>
       </c>
       <c r="K11">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3337,7 +3337,7 @@
         <v>2.26</v>
       </c>
       <c r="S11">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T11">
         <v>1.41</v>
@@ -3346,10 +3346,10 @@
         <v>3</v>
       </c>
       <c r="V11">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W11">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="X11">
         <v>75</v>
@@ -3367,7 +3367,7 @@
         <v>23</v>
       </c>
       <c r="AC11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD11">
         <v>27</v>
@@ -3406,13 +3406,13 @@
         <v>26</v>
       </c>
       <c r="AP11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11">
         <v>25</v>
       </c>
       <c r="AR11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS11">
         <v>8.800000000000001</v>
@@ -3421,7 +3421,7 @@
         <v>19</v>
       </c>
       <c r="AU11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AV11">
         <v>13.5</v>
@@ -3540,22 +3540,22 @@
         <v>148</v>
       </c>
       <c r="F12">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="G12">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H12">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I12">
-        <v>990</v>
+        <v>11.5</v>
       </c>
       <c r="J12">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>7.8</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3567,13 +3567,13 @@
         <v>3.75</v>
       </c>
       <c r="O12">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="P12">
         <v>3.8</v>
       </c>
       <c r="Q12">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R12">
         <v>2.12</v>
@@ -3588,10 +3588,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W12">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3785,19 +3785,19 @@
         <v>2.98</v>
       </c>
       <c r="G13">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="H13">
         <v>2.12</v>
       </c>
       <c r="I13">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J13">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="K13">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3806,142 +3806,142 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.86</v>
+        <v>7.2</v>
       </c>
       <c r="O13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P13">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="Q13">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R13">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="S13">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>2.96</v>
       </c>
       <c r="V13">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="W13">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4048,28 +4048,28 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O14">
         <v>1.09</v>
       </c>
       <c r="P14">
-        <v>2.12</v>
+        <v>3.65</v>
       </c>
       <c r="Q14">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="R14">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="S14">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="T14">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>3.1</v>
       </c>
       <c r="V14">
         <v>1.67</v>
@@ -4081,58 +4081,58 @@
         <v>950</v>
       </c>
       <c r="Y14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Z14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA14">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB14">
+        <v>950</v>
+      </c>
+      <c r="AC14">
+        <v>14.5</v>
+      </c>
+      <c r="AD14">
+        <v>15</v>
+      </c>
+      <c r="AE14">
+        <v>22</v>
+      </c>
+      <c r="AF14">
         <v>32</v>
       </c>
-      <c r="AC14">
-        <v>15.5</v>
-      </c>
-      <c r="AD14">
+      <c r="AG14">
         <v>16</v>
       </c>
-      <c r="AE14">
-        <v>25</v>
-      </c>
-      <c r="AF14">
-        <v>36</v>
-      </c>
-      <c r="AG14">
-        <v>17.5</v>
-      </c>
       <c r="AH14">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AI14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AJ14">
         <v>55</v>
       </c>
       <c r="AK14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AM14">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AN14">
         <v>10</v>
       </c>
       <c r="AO14">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP14">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ14">
         <v>20</v>
@@ -4141,46 +4141,46 @@
         <v>20</v>
       </c>
       <c r="AS14">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AT14">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU14">
         <v>11.5</v>
       </c>
       <c r="AV14">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW14">
         <v>17.5</v>
       </c>
       <c r="AX14">
-        <v>4.9</v>
+        <v>23</v>
       </c>
       <c r="AY14">
         <v>13</v>
       </c>
       <c r="AZ14">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA14">
         <v>18.5</v>
       </c>
       <c r="BB14">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BC14">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BE14">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BF14">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG14">
         <v>6.4</v>
@@ -4269,7 +4269,7 @@
         <v>1.46</v>
       </c>
       <c r="G15">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H15">
         <v>5.7</v>
@@ -4299,7 +4299,7 @@
         <v>3.75</v>
       </c>
       <c r="Q15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R15">
         <v>2.18</v>
@@ -4317,7 +4317,7 @@
         <v>1.17</v>
       </c>
       <c r="W15">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X15">
         <v>75</v>
@@ -4514,55 +4514,55 @@
         <v>3.75</v>
       </c>
       <c r="H16">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I16">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J16">
         <v>2.84</v>
       </c>
       <c r="K16">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L16">
         <v>1.46</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N16">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O16">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="P16">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R16">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S16">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="T16">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U16">
         <v>1.81</v>
       </c>
       <c r="V16">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W16">
         <v>1.36</v>
       </c>
       <c r="X16">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y16">
         <v>7.8</v>
@@ -4574,7 +4574,7 @@
         <v>48</v>
       </c>
       <c r="AB16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC16">
         <v>7.8</v>
@@ -4604,7 +4604,7 @@
         <v>65</v>
       </c>
       <c r="AL16">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AM16">
         <v>200</v>
@@ -4625,7 +4625,7 @@
         <v>11.5</v>
       </c>
       <c r="AS16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT16">
         <v>8.800000000000001</v>
@@ -4637,7 +4637,7 @@
         <v>9.6</v>
       </c>
       <c r="AW16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX16">
         <v>17.5</v>
@@ -4649,25 +4649,25 @@
         <v>16.5</v>
       </c>
       <c r="BA16">
+        <v>6.4</v>
+      </c>
+      <c r="BB16">
+        <v>6.6</v>
+      </c>
+      <c r="BC16">
+        <v>6.4</v>
+      </c>
+      <c r="BD16">
+        <v>6.6</v>
+      </c>
+      <c r="BE16">
+        <v>7</v>
+      </c>
+      <c r="BF16">
+        <v>6.6</v>
+      </c>
+      <c r="BG16">
         <v>6.2</v>
-      </c>
-      <c r="BB16">
-        <v>6.4</v>
-      </c>
-      <c r="BC16">
-        <v>6.2</v>
-      </c>
-      <c r="BD16">
-        <v>6.4</v>
-      </c>
-      <c r="BE16">
-        <v>6.6</v>
-      </c>
-      <c r="BF16">
-        <v>6.4</v>
-      </c>
-      <c r="BG16">
-        <v>6</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4753,13 +4753,13 @@
         <v>3.3</v>
       </c>
       <c r="G17">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H17">
         <v>2.4</v>
       </c>
       <c r="I17">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J17">
         <v>3.05</v>
@@ -4774,7 +4774,7 @@
         <v>1.1</v>
       </c>
       <c r="N17">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="O17">
         <v>1.43</v>
@@ -4801,7 +4801,7 @@
         <v>1.59</v>
       </c>
       <c r="W17">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X17">
         <v>12.5</v>
@@ -4852,7 +4852,7 @@
         <v>170</v>
       </c>
       <c r="AN17">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO17">
         <v>34</v>
@@ -4992,79 +4992,79 @@
         <v>154</v>
       </c>
       <c r="F18">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G18">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="H18">
         <v>2.44</v>
       </c>
       <c r="I18">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="J18">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="K18">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18">
-        <v>3.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O18">
         <v>1.09</v>
       </c>
       <c r="P18">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="Q18">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="R18">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="T18">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="U18">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V18">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="X18">
         <v>65</v>
       </c>
       <c r="Y18">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z18">
         <v>36</v>
       </c>
       <c r="AA18">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB18">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AC18">
         <v>17</v>
       </c>
       <c r="AD18">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE18">
         <v>28</v>
@@ -5073,7 +5073,7 @@
         <v>36</v>
       </c>
       <c r="AG18">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH18">
         <v>17</v>
@@ -5100,7 +5100,7 @@
         <v>10.5</v>
       </c>
       <c r="AP18">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ18">
         <v>20</v>
@@ -5109,7 +5109,7 @@
         <v>21</v>
       </c>
       <c r="AS18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AT18">
         <v>20</v>
@@ -5136,7 +5136,7 @@
         <v>16.5</v>
       </c>
       <c r="BB18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BC18">
         <v>16</v>
@@ -5145,13 +5145,13 @@
         <v>16.5</v>
       </c>
       <c r="BE18">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BF18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5240,13 +5240,13 @@
         <v>1.38</v>
       </c>
       <c r="H19">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I19">
         <v>990</v>
       </c>
       <c r="J19">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="K19">
         <v>950</v>
@@ -5491,7 +5491,7 @@
         <v>2.8</v>
       </c>
       <c r="K20">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L20">
         <v>1.48</v>
@@ -5500,7 +5500,7 @@
         <v>1.13</v>
       </c>
       <c r="N20">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="O20">
         <v>1.56</v>
@@ -5718,7 +5718,7 @@
         <v>157</v>
       </c>
       <c r="F21">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G21">
         <v>2.32</v>
@@ -5823,7 +5823,7 @@
         <v>40</v>
       </c>
       <c r="AO21">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP21">
         <v>5.6</v>
@@ -5850,7 +5850,7 @@
         <v>7.6</v>
       </c>
       <c r="AX21">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY21">
         <v>10.5</v>
@@ -6205,16 +6205,16 @@
         <v>1.09</v>
       </c>
       <c r="G23">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="H23">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I23">
         <v>990</v>
       </c>
       <c r="J23">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="K23">
         <v>950</v>
@@ -6226,19 +6226,19 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="O23">
         <v>1.27</v>
       </c>
       <c r="P23">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="Q23">
         <v>1.27</v>
       </c>
       <c r="R23">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S23">
         <v>1.26</v>
@@ -6450,7 +6450,7 @@
         <v>2.52</v>
       </c>
       <c r="H24">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I24">
         <v>3.05</v>
@@ -6474,7 +6474,7 @@
         <v>1.19</v>
       </c>
       <c r="P24">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q24">
         <v>1.57</v>
@@ -6498,7 +6498,7 @@
         <v>1.66</v>
       </c>
       <c r="X24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y24">
         <v>18</v>
@@ -6513,13 +6513,13 @@
         <v>16</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD24">
         <v>13</v>
       </c>
       <c r="AE24">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF24">
         <v>21</v>
@@ -6546,7 +6546,7 @@
         <v>60</v>
       </c>
       <c r="AN24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO24">
         <v>20</v>
@@ -6558,7 +6558,7 @@
         <v>16</v>
       </c>
       <c r="AR24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS24">
         <v>36</v>
@@ -6686,7 +6686,7 @@
         <v>161</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G25">
         <v>2.02</v>
@@ -6695,7 +6695,7 @@
         <v>4</v>
       </c>
       <c r="I25">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J25">
         <v>3.8</v>
@@ -6704,7 +6704,7 @@
         <v>3.9</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M25">
         <v>1.06</v>
@@ -6713,22 +6713,22 @@
         <v>4.2</v>
       </c>
       <c r="O25">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P25">
         <v>2.1</v>
       </c>
       <c r="Q25">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R25">
         <v>1.43</v>
       </c>
       <c r="S25">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T25">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U25">
         <v>2.26</v>
@@ -6740,19 +6740,19 @@
         <v>1.98</v>
       </c>
       <c r="X25">
+        <v>16</v>
+      </c>
+      <c r="Y25">
         <v>16.5</v>
       </c>
-      <c r="Y25">
-        <v>17</v>
-      </c>
       <c r="Z25">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA25">
         <v>85</v>
       </c>
       <c r="AB25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC25">
         <v>8.800000000000001</v>
@@ -6770,7 +6770,7 @@
         <v>10.5</v>
       </c>
       <c r="AH25">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI25">
         <v>55</v>
@@ -6806,7 +6806,7 @@
         <v>36</v>
       </c>
       <c r="AT25">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU25">
         <v>7.8</v>
@@ -6815,7 +6815,7 @@
         <v>15</v>
       </c>
       <c r="AW25">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AX25">
         <v>11.5</v>
@@ -6824,7 +6824,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ25">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA25">
         <v>46</v>
@@ -6848,64 +6848,64 @@
         <v>26</v>
       </c>
       <c r="BH25">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="BJ25">
         <v>13</v>
       </c>
       <c r="BK25">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>3.55</v>
+        <v>1.99</v>
       </c>
       <c r="BN25">
         <v>6.2</v>
       </c>
       <c r="BO25">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BP25">
         <v>18</v>
       </c>
       <c r="BQ25">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="BR25">
         <v>34</v>
       </c>
       <c r="BS25">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BT25">
         <v>10</v>
       </c>
       <c r="BU25">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="BV25">
         <v>44</v>
       </c>
       <c r="BW25">
-        <v>3.3</v>
+        <v>1.91</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>3.35</v>
+        <v>1.93</v>
       </c>
       <c r="BZ25">
         <v>29</v>
       </c>
       <c r="CA25">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="CB25" t="s">
         <v>170</v>
@@ -6928,46 +6928,46 @@
         <v>162</v>
       </c>
       <c r="F26">
+        <v>1.52</v>
+      </c>
+      <c r="G26">
         <v>1.54</v>
       </c>
-      <c r="G26">
-        <v>1.57</v>
-      </c>
       <c r="H26">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I26">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J26">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K26">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L26">
         <v>1.33</v>
       </c>
       <c r="M26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O26">
         <v>1.37</v>
       </c>
       <c r="P26">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q26">
         <v>2.08</v>
       </c>
       <c r="R26">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S26">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T26">
         <v>2.24</v>
@@ -6976,28 +6976,28 @@
         <v>1.73</v>
       </c>
       <c r="V26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W26">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="X26">
         <v>13</v>
       </c>
       <c r="Y26">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z26">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA26">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="AB26">
         <v>6.8</v>
       </c>
       <c r="AC26">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD26">
         <v>32</v>
@@ -7006,88 +7006,88 @@
         <v>1000</v>
       </c>
       <c r="AF26">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG26">
         <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI26">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AK26">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL26">
         <v>180</v>
       </c>
       <c r="AM26">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN26">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO26">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AP26">
         <v>12</v>
       </c>
       <c r="AQ26">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR26">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AS26">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AT26">
         <v>6.4</v>
       </c>
       <c r="AU26">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV26">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AW26">
-        <v>42</v>
+        <v>18.5</v>
       </c>
       <c r="AX26">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY26">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BA26">
-        <v>42</v>
+        <v>18.5</v>
       </c>
       <c r="BB26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC26">
         <v>16</v>
       </c>
       <c r="BD26">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BE26">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BF26">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG26">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7170,19 +7170,19 @@
         <v>163</v>
       </c>
       <c r="F27">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="G27">
         <v>990</v>
       </c>
       <c r="H27">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="I27">
         <v>990</v>
       </c>
       <c r="J27">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -7209,7 +7209,7 @@
         <v>1.18</v>
       </c>
       <c r="S27">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T27">
         <v>1.11</v>
@@ -7218,10 +7218,10 @@
         <v>1.11</v>
       </c>
       <c r="V27">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W27">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7415,13 +7415,13 @@
         <v>1.34</v>
       </c>
       <c r="G28">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H28">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="J28">
         <v>6.4</v>
@@ -7430,25 +7430,25 @@
         <v>6.6</v>
       </c>
       <c r="L28">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="M28">
         <v>1.03</v>
       </c>
       <c r="N28">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O28">
         <v>1.16</v>
       </c>
       <c r="P28">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q28">
         <v>1.48</v>
       </c>
       <c r="R28">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S28">
         <v>2.24</v>
@@ -7457,16 +7457,16 @@
         <v>1.81</v>
       </c>
       <c r="U28">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V28">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W28">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="X28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y28">
         <v>42</v>
@@ -7481,7 +7481,7 @@
         <v>12</v>
       </c>
       <c r="AC28">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD28">
         <v>34</v>
@@ -7526,16 +7526,16 @@
         <v>36</v>
       </c>
       <c r="AR28">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AS28">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT28">
         <v>11</v>
       </c>
       <c r="AU28">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV28">
         <v>30</v>
@@ -7547,13 +7547,13 @@
         <v>9.4</v>
       </c>
       <c r="AY28">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28">
         <v>21</v>
       </c>
       <c r="BA28">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BB28">
         <v>10.5</v>
@@ -7565,73 +7565,73 @@
         <v>25</v>
       </c>
       <c r="BE28">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF28">
         <v>4.1</v>
       </c>
       <c r="BG28">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BH28">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI28">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="BJ28">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK28">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="BL28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM28">
-        <v>3.7</v>
+        <v>13</v>
       </c>
       <c r="BN28">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BO28">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="BP28">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BQ28">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR28">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BS28">
-        <v>3.25</v>
+        <v>12</v>
       </c>
       <c r="BT28">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BU28">
-        <v>3.45</v>
+        <v>7.8</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW28">
-        <v>3.55</v>
+        <v>12</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY28">
-        <v>3.55</v>
+        <v>12</v>
       </c>
       <c r="BZ28">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA28">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="CB28" t="s">
         <v>170</v>
@@ -7663,7 +7663,7 @@
         <v>3.2</v>
       </c>
       <c r="I29">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J29">
         <v>3.35</v>
@@ -7690,16 +7690,16 @@
         <v>2.16</v>
       </c>
       <c r="R29">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S29">
         <v>4</v>
       </c>
       <c r="T29">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U29">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V29">
         <v>1.44</v>
@@ -7708,7 +7708,7 @@
         <v>1.64</v>
       </c>
       <c r="X29">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y29">
         <v>11.5</v>
@@ -7732,7 +7732,7 @@
         <v>42</v>
       </c>
       <c r="AF29">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG29">
         <v>12</v>
@@ -7759,7 +7759,7 @@
         <v>26</v>
       </c>
       <c r="AO29">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP29">
         <v>10.5</v>
@@ -7905,7 +7905,7 @@
         <v>2.76</v>
       </c>
       <c r="I30">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J30">
         <v>2.96</v>
@@ -7917,19 +7917,19 @@
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N30">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O30">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P30">
         <v>1.55</v>
       </c>
       <c r="Q30">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R30">
         <v>1.2</v>
@@ -7947,10 +7947,10 @@
         <v>1.47</v>
       </c>
       <c r="W30">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y30">
         <v>10.5</v>
@@ -7968,10 +7968,10 @@
         <v>7.4</v>
       </c>
       <c r="AD30">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AE30">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF30">
         <v>22</v>
@@ -8004,28 +8004,28 @@
         <v>60</v>
       </c>
       <c r="AP30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ30">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR30">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS30">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT30">
         <v>7.6</v>
       </c>
       <c r="AU30">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV30">
         <v>11.5</v>
       </c>
       <c r="AW30">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX30">
         <v>15.5</v>
@@ -8034,28 +8034,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ30">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA30">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BB30">
+        <v>5.5</v>
+      </c>
+      <c r="BC30">
+        <v>5.3</v>
+      </c>
+      <c r="BD30">
+        <v>5.5</v>
+      </c>
+      <c r="BE30">
         <v>5.8</v>
       </c>
-      <c r="BC30">
-        <v>5.7</v>
-      </c>
-      <c r="BD30">
-        <v>5.9</v>
-      </c>
-      <c r="BE30">
-        <v>6.2</v>
-      </c>
       <c r="BF30">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG30">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8138,7 +8138,7 @@
         <v>167</v>
       </c>
       <c r="F31">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G31">
         <v>2.46</v>
@@ -8147,13 +8147,13 @@
         <v>3.1</v>
       </c>
       <c r="I31">
+        <v>3.65</v>
+      </c>
+      <c r="J31">
+        <v>3.15</v>
+      </c>
+      <c r="K31">
         <v>4.3</v>
-      </c>
-      <c r="J31">
-        <v>3.1</v>
-      </c>
-      <c r="K31">
-        <v>5.3</v>
       </c>
       <c r="L31">
         <v>1.28</v>
@@ -8162,7 +8162,7 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O31">
         <v>1.28</v>
@@ -8171,7 +8171,7 @@
         <v>1.87</v>
       </c>
       <c r="Q31">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R31">
         <v>1.31</v>
@@ -8186,7 +8186,7 @@
         <v>1.11</v>
       </c>
       <c r="V31">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W31">
         <v>1.68</v>
@@ -8380,19 +8380,19 @@
         <v>168</v>
       </c>
       <c r="F32">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G32">
-        <v>990</v>
+        <v>2.04</v>
       </c>
       <c r="H32">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="I32">
         <v>990</v>
       </c>
       <c r="J32">
-        <v>1.12</v>
+        <v>3.9</v>
       </c>
       <c r="K32">
         <v>950</v>
@@ -8404,7 +8404,7 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="O32">
         <v>1.12</v>
@@ -8428,10 +8428,10 @@
         <v>1.11</v>
       </c>
       <c r="V32">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W32">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8622,16 +8622,16 @@
         <v>169</v>
       </c>
       <c r="F33">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G33">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H33">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J33">
         <v>3.35</v>
@@ -8670,10 +8670,10 @@
         <v>1.89</v>
       </c>
       <c r="V33">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W33">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X33">
         <v>11.5</v>
@@ -8709,7 +8709,7 @@
         <v>950</v>
       </c>
       <c r="AI33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AJ33">
         <v>25</v>
@@ -8736,10 +8736,10 @@
         <v>12</v>
       </c>
       <c r="AR33">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AS33">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT33">
         <v>6.6</v>
@@ -8748,10 +8748,10 @@
         <v>7</v>
       </c>
       <c r="AV33">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AW33">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX33">
         <v>10</v>
@@ -8760,13 +8760,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ33">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BA33">
         <v>10</v>
       </c>
       <c r="BB33">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BC33">
         <v>20</v>
@@ -8778,70 +8778,70 @@
         <v>10.5</v>
       </c>
       <c r="BF33">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG33">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH33">
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="BJ33">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK33">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="BN33">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO33">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP33">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ33">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="BR33">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS33">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="BT33">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU33">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="BZ33">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA33">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="CB33" t="s">
         <v>170</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -526,7 +526,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-25 04:44:01</t>
+    <t>2026-08-25 06:53:18</t>
   </si>
 </sst>
 </file>
@@ -1120,19 +1120,19 @@
         <v>138</v>
       </c>
       <c r="F2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G2">
         <v>1.62</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4.2</v>
@@ -1150,7 +1150,7 @@
         <v>1.43</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q2">
         <v>2.28</v>
@@ -1162,7 +1162,7 @@
         <v>4.4</v>
       </c>
       <c r="T2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U2">
         <v>1.69</v>
@@ -1174,10 +1174,10 @@
         <v>2.6</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y2">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z2">
         <v>60</v>
@@ -1186,16 +1186,16 @@
         <v>280</v>
       </c>
       <c r="AB2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE2">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AF2">
         <v>9.800000000000001</v>
@@ -1207,19 +1207,19 @@
         <v>32</v>
       </c>
       <c r="AI2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ2">
         <v>15</v>
       </c>
       <c r="AK2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN2">
         <v>12.5</v>
@@ -1237,10 +1237,10 @@
         <v>50</v>
       </c>
       <c r="AS2">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
         <v>8.199999999999999</v>
@@ -1249,10 +1249,10 @@
         <v>25</v>
       </c>
       <c r="AW2">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AX2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY2">
         <v>9.800000000000001</v>
@@ -1261,7 +1261,7 @@
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1273,13 +1273,13 @@
         <v>46</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF2">
         <v>9.6</v>
       </c>
       <c r="BG2">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH2">
         <v>3.2</v>
@@ -1288,7 +1288,7 @@
         <v>2.78</v>
       </c>
       <c r="BJ2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BK2">
         <v>9.4</v>
@@ -1297,49 +1297,49 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BO2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BQ2">
         <v>8.199999999999999</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS2">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BU2">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="s">
         <v>170</v>
@@ -1362,61 +1362,61 @@
         <v>139</v>
       </c>
       <c r="F3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H3">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
         <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O3">
         <v>1.5</v>
       </c>
       <c r="P3">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U3">
         <v>1.86</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3">
         <v>10.5</v>
@@ -1428,19 +1428,19 @@
         <v>80</v>
       </c>
       <c r="AB3">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC3">
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG3">
         <v>12</v>
@@ -1452,22 +1452,22 @@
         <v>80</v>
       </c>
       <c r="AJ3">
+        <v>36</v>
+      </c>
+      <c r="AK3">
+        <v>30</v>
+      </c>
+      <c r="AL3">
+        <v>60</v>
+      </c>
+      <c r="AM3">
+        <v>160</v>
+      </c>
+      <c r="AN3">
         <v>32</v>
       </c>
-      <c r="AK3">
-        <v>38</v>
-      </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
-      <c r="AM3">
-        <v>170</v>
-      </c>
-      <c r="AN3">
-        <v>34</v>
-      </c>
       <c r="AO3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP3">
         <v>8.800000000000001</v>
@@ -1476,112 +1476,112 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS3">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
         <v>13</v>
       </c>
       <c r="AW3">
+        <v>46</v>
+      </c>
+      <c r="AX3">
+        <v>12</v>
+      </c>
+      <c r="AY3">
+        <v>11</v>
+      </c>
+      <c r="AZ3">
+        <v>20</v>
+      </c>
+      <c r="BA3">
+        <v>14.5</v>
+      </c>
+      <c r="BB3">
+        <v>29</v>
+      </c>
+      <c r="BC3">
+        <v>26</v>
+      </c>
+      <c r="BD3">
+        <v>48</v>
+      </c>
+      <c r="BE3">
+        <v>10</v>
+      </c>
+      <c r="BF3">
+        <v>22</v>
+      </c>
+      <c r="BG3">
+        <v>11.5</v>
+      </c>
+      <c r="BH3">
+        <v>2.92</v>
+      </c>
+      <c r="BI3">
+        <v>2.32</v>
+      </c>
+      <c r="BJ3">
+        <v>11.5</v>
+      </c>
+      <c r="BK3">
+        <v>5.6</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>10.5</v>
+      </c>
+      <c r="BN3">
+        <v>5.1</v>
+      </c>
+      <c r="BO3">
+        <v>3.75</v>
+      </c>
+      <c r="BP3">
+        <v>19.5</v>
+      </c>
+      <c r="BQ3">
+        <v>7</v>
+      </c>
+      <c r="BR3">
+        <v>42</v>
+      </c>
+      <c r="BS3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT3">
+        <v>7.2</v>
+      </c>
+      <c r="BU3">
+        <v>5.2</v>
+      </c>
+      <c r="BV3">
+        <v>38</v>
+      </c>
+      <c r="BW3">
+        <v>8.6</v>
+      </c>
+      <c r="BX3">
+        <v>60</v>
+      </c>
+      <c r="BY3">
+        <v>9.4</v>
+      </c>
+      <c r="BZ3">
         <v>44</v>
       </c>
-      <c r="AX3">
-        <v>11</v>
-      </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
-        <v>19</v>
-      </c>
-      <c r="BA3">
-        <v>55</v>
-      </c>
-      <c r="BB3">
-        <v>10</v>
-      </c>
-      <c r="BC3">
-        <v>25</v>
-      </c>
-      <c r="BD3">
-        <v>8</v>
-      </c>
-      <c r="BE3">
+      <c r="CA3">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BF3">
-        <v>10.5</v>
-      </c>
-      <c r="BG3">
-        <v>50</v>
-      </c>
-      <c r="BH3">
-        <v>1000</v>
-      </c>
-      <c r="BI3">
-        <v>1.04</v>
-      </c>
-      <c r="BJ3">
-        <v>1000</v>
-      </c>
-      <c r="BK3">
-        <v>1.04</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>1.04</v>
-      </c>
-      <c r="BN3">
-        <v>1000</v>
-      </c>
-      <c r="BO3">
-        <v>1.04</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>1.04</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>1.04</v>
-      </c>
-      <c r="BT3">
-        <v>1000</v>
-      </c>
-      <c r="BU3">
-        <v>1.04</v>
-      </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
-        <v>1.04</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>1.04</v>
-      </c>
-      <c r="BZ3">
-        <v>1000</v>
-      </c>
-      <c r="CA3">
-        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>170</v>
@@ -1604,7 +1604,7 @@
         <v>140</v>
       </c>
       <c r="F4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G4">
         <v>1.42</v>
@@ -1616,10 +1616,10 @@
         <v>990</v>
       </c>
       <c r="J4">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="K4">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1640,10 +1640,10 @@
         <v>1.33</v>
       </c>
       <c r="R4">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1655,10 +1655,10 @@
         <v>1.08</v>
       </c>
       <c r="W4">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y4">
         <v>1000</v>
@@ -1715,55 +1715,55 @@
         <v>1.39</v>
       </c>
       <c r="AQ4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AR4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AS4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AT4">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AU4">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AV4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AW4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AX4">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AY4">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AZ4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="BA4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="BB4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="BC4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="BD4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="BE4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="BF4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="BG4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1864,7 +1864,7 @@
         <v>3.45</v>
       </c>
       <c r="L5">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="M5">
         <v>1.09</v>
@@ -1876,7 +1876,7 @@
         <v>1.42</v>
       </c>
       <c r="P5">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
         <v>2.24</v>
@@ -1906,7 +1906,7 @@
         <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA5">
         <v>42</v>
@@ -1915,7 +1915,7 @@
         <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
         <v>12</v>
@@ -1963,7 +1963,7 @@
         <v>13</v>
       </c>
       <c r="AS5">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1984,88 +1984,88 @@
         <v>13</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>9.4</v>
       </c>
       <c r="BA5">
+        <v>6.4</v>
+      </c>
+      <c r="BB5">
         <v>6.6</v>
       </c>
-      <c r="BB5">
-        <v>6.8</v>
-      </c>
       <c r="BC5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD5">
         <v>38</v>
       </c>
       <c r="BE5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF5">
         <v>34</v>
       </c>
       <c r="BG5">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB5" t="s">
         <v>170</v>
@@ -2091,10 +2091,10 @@
         <v>2.34</v>
       </c>
       <c r="G6">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H6">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I6">
         <v>3.2</v>
@@ -2112,7 +2112,7 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O6">
         <v>1.25</v>
@@ -2124,13 +2124,13 @@
         <v>1.74</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S6">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T6">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U6">
         <v>2.4</v>
@@ -2148,7 +2148,7 @@
         <v>15</v>
       </c>
       <c r="Z6">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AA6">
         <v>60</v>
@@ -2157,13 +2157,13 @@
         <v>13</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE6">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF6">
         <v>20</v>
@@ -2172,16 +2172,16 @@
         <v>12</v>
       </c>
       <c r="AH6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI6">
         <v>38</v>
       </c>
       <c r="AJ6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK6">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL6">
         <v>38</v>
@@ -2190,10 +2190,10 @@
         <v>85</v>
       </c>
       <c r="AN6">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AO6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP6">
         <v>16.5</v>
@@ -2202,10 +2202,10 @@
         <v>13</v>
       </c>
       <c r="AR6">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS6">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT6">
         <v>11</v>
@@ -2217,7 +2217,7 @@
         <v>12</v>
       </c>
       <c r="AW6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX6">
         <v>15</v>
@@ -2229,22 +2229,22 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BB6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BC6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BE6">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BF6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG6">
         <v>18.5</v>
@@ -2357,13 +2357,13 @@
         <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P7">
         <v>1.81</v>
       </c>
       <c r="Q7">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R7">
         <v>1.3</v>
@@ -2375,7 +2375,7 @@
         <v>2.26</v>
       </c>
       <c r="U7">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V7">
         <v>1.14</v>
@@ -2387,10 +2387,10 @@
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Z7">
-        <v>490</v>
+        <v>85</v>
       </c>
       <c r="AA7">
         <v>1000</v>
@@ -2441,13 +2441,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR7">
         <v>29</v>
       </c>
       <c r="AS7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
@@ -2459,7 +2459,7 @@
         <v>19</v>
       </c>
       <c r="AW7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX7">
         <v>7.2</v>
@@ -2471,7 +2471,7 @@
         <v>24</v>
       </c>
       <c r="BA7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB7">
         <v>12</v>
@@ -2578,7 +2578,7 @@
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="I8">
         <v>1.82</v>
@@ -2814,7 +2814,7 @@
         <v>145</v>
       </c>
       <c r="F9">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G9">
         <v>2.06</v>
@@ -2829,16 +2829,16 @@
         <v>4.1</v>
       </c>
       <c r="K9">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L9">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N9">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O9">
         <v>1.18</v>
@@ -2847,10 +2847,10 @@
         <v>2.64</v>
       </c>
       <c r="Q9">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="R9">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S9">
         <v>2.28</v>
@@ -2859,13 +2859,13 @@
         <v>1.47</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="V9">
         <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="X9">
         <v>28</v>
@@ -2874,7 +2874,7 @@
         <v>25</v>
       </c>
       <c r="Z9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA9">
         <v>75</v>
@@ -2898,7 +2898,7 @@
         <v>13</v>
       </c>
       <c r="AH9">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI9">
         <v>40</v>
@@ -2907,7 +2907,7 @@
         <v>28</v>
       </c>
       <c r="AK9">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL9">
         <v>34</v>
@@ -2922,16 +2922,16 @@
         <v>26</v>
       </c>
       <c r="AP9">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR9">
         <v>27</v>
       </c>
       <c r="AS9">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT9">
         <v>12</v>
@@ -2943,10 +2943,10 @@
         <v>14</v>
       </c>
       <c r="AW9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX9">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AY9">
         <v>9.6</v>
@@ -2973,67 +2973,67 @@
         <v>7.6</v>
       </c>
       <c r="BG9">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB9" t="s">
         <v>170</v>
@@ -3068,13 +3068,13 @@
         <v>2.96</v>
       </c>
       <c r="J10">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K10">
         <v>3.95</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M10">
         <v>1.06</v>
@@ -3086,7 +3086,7 @@
         <v>1.27</v>
       </c>
       <c r="P10">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q10">
         <v>1.8</v>
@@ -3098,10 +3098,10 @@
         <v>3</v>
       </c>
       <c r="T10">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U10">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
         <v>1.51</v>
@@ -3125,22 +3125,22 @@
         <v>15</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD10">
         <v>15.5</v>
       </c>
       <c r="AE10">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AF10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG10">
         <v>15</v>
       </c>
       <c r="AH10">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI10">
         <v>46</v>
@@ -3152,130 +3152,130 @@
         <v>34</v>
       </c>
       <c r="AL10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM10">
         <v>95</v>
       </c>
       <c r="AN10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO10">
         <v>29</v>
       </c>
       <c r="AP10">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AT10">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW10">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="AX10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA10">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BB10">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BC10">
         <v>19.5</v>
       </c>
       <c r="BD10">
-        <v>4.2</v>
+        <v>26</v>
       </c>
       <c r="BE10">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BF10">
         <v>14.5</v>
       </c>
       <c r="BG10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="s">
         <v>170</v>
@@ -3316,13 +3316,13 @@
         <v>6.2</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>1.08</v>
@@ -3331,16 +3331,16 @@
         <v>4</v>
       </c>
       <c r="Q11">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R11">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="S11">
         <v>1.67</v>
       </c>
       <c r="T11">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U11">
         <v>3</v>
@@ -3409,7 +3409,7 @@
         <v>8.4</v>
       </c>
       <c r="AQ11">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="AR11">
         <v>8.4</v>
@@ -3439,7 +3439,7 @@
         <v>15.5</v>
       </c>
       <c r="BA11">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BB11">
         <v>16</v>
@@ -3454,67 +3454,67 @@
         <v>27</v>
       </c>
       <c r="BF11">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BG11">
         <v>21</v>
       </c>
       <c r="BH11">
+        <v>6.8</v>
+      </c>
+      <c r="BI11">
+        <v>5.6</v>
+      </c>
+      <c r="BJ11">
         <v>8.800000000000001</v>
       </c>
-      <c r="BI11">
-        <v>4.4</v>
-      </c>
-      <c r="BJ11">
-        <v>11.5</v>
-      </c>
       <c r="BK11">
-        <v>2.52</v>
+        <v>5.6</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM11">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="BN11">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="BO11">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BP11">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BQ11">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR11">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BS11">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="BT11">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BU11">
-        <v>2.62</v>
+        <v>6.4</v>
       </c>
       <c r="BV11">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BW11">
-        <v>3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX11">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BY11">
-        <v>2.98</v>
+        <v>7.8</v>
       </c>
       <c r="BZ11">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA11">
         <v>5.1</v>
@@ -3564,28 +3564,28 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>3.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O12">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P12">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q12">
         <v>1.29</v>
       </c>
       <c r="R12">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S12">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V12">
         <v>1.1</v>
@@ -3597,10 +3597,10 @@
         <v>1000</v>
       </c>
       <c r="Y12">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA12">
         <v>1000</v>
@@ -3609,31 +3609,31 @@
         <v>23</v>
       </c>
       <c r="AC12">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AD12">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AE12">
         <v>1000</v>
       </c>
       <c r="AF12">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AG12">
         <v>17.5</v>
       </c>
       <c r="AH12">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI12">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ12">
         <v>18.5</v>
       </c>
       <c r="AK12">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AL12">
         <v>34</v>
@@ -3642,64 +3642,64 @@
         <v>95</v>
       </c>
       <c r="AN12">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="AO12">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP12">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="AQ12">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="AR12">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="AS12">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="AT12">
         <v>12.5</v>
       </c>
       <c r="AU12">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AV12">
-        <v>2.98</v>
+        <v>4.7</v>
       </c>
       <c r="AW12">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="AX12">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AY12">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ12">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BA12">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="BB12">
         <v>8.800000000000001</v>
       </c>
       <c r="BC12">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD12">
         <v>15</v>
       </c>
       <c r="BE12">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="BF12">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="BG12">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3800,7 +3800,7 @@
         <v>4.7</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M13">
         <v>1.01</v>
@@ -3812,7 +3812,7 @@
         <v>1.13</v>
       </c>
       <c r="P13">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q13">
         <v>1.41</v>
@@ -3833,22 +3833,22 @@
         <v>1.76</v>
       </c>
       <c r="W13">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X13">
         <v>42</v>
       </c>
       <c r="Y13">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Z13">
         <v>24</v>
       </c>
       <c r="AA13">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AB13">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AC13">
         <v>13.5</v>
@@ -3860,37 +3860,37 @@
         <v>23</v>
       </c>
       <c r="AF13">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AG13">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AH13">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI13">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AJ13">
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AL13">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AM13">
         <v>50</v>
       </c>
       <c r="AN13">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO13">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP13">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AQ13">
         <v>14.5</v>
@@ -3899,22 +3899,22 @@
         <v>15.5</v>
       </c>
       <c r="AS13">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU13">
         <v>9</v>
       </c>
       <c r="AV13">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW13">
         <v>15</v>
       </c>
       <c r="AX13">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="AY13">
         <v>11.5</v>
@@ -3923,10 +3923,10 @@
         <v>11</v>
       </c>
       <c r="BA13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB13">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC13">
         <v>21</v>
@@ -3935,73 +3935,73 @@
         <v>21</v>
       </c>
       <c r="BE13">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF13">
         <v>11</v>
       </c>
       <c r="BG13">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="CB13" t="s">
         <v>170</v>
@@ -4027,22 +4027,22 @@
         <v>2.62</v>
       </c>
       <c r="G14">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="H14">
         <v>2.28</v>
       </c>
       <c r="I14">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K14">
         <v>5.6</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M14">
         <v>1.01</v>
@@ -4051,7 +4051,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O14">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P14">
         <v>3.65</v>
@@ -4063,7 +4063,7 @@
         <v>2.22</v>
       </c>
       <c r="S14">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="T14">
         <v>1.3</v>
@@ -4072,46 +4072,46 @@
         <v>3.1</v>
       </c>
       <c r="V14">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W14">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X14">
         <v>950</v>
       </c>
       <c r="Y14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Z14">
         <v>28</v>
       </c>
       <c r="AA14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AB14">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AC14">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AD14">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE14">
         <v>22</v>
       </c>
       <c r="AF14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AG14">
+        <v>17.5</v>
+      </c>
+      <c r="AH14">
         <v>16</v>
       </c>
-      <c r="AH14">
-        <v>14.5</v>
-      </c>
       <c r="AI14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AJ14">
         <v>55</v>
@@ -4120,7 +4120,7 @@
         <v>26</v>
       </c>
       <c r="AL14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AM14">
         <v>36</v>
@@ -4132,7 +4132,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP14">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="AQ14">
         <v>20</v>
@@ -4141,109 +4141,109 @@
         <v>20</v>
       </c>
       <c r="AS14">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT14">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AU14">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AV14">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AX14">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="AY14">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ14">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA14">
         <v>18.5</v>
       </c>
       <c r="BB14">
+        <v>32</v>
+      </c>
+      <c r="BC14">
+        <v>18.5</v>
+      </c>
+      <c r="BD14">
+        <v>18</v>
+      </c>
+      <c r="BE14">
+        <v>5.2</v>
+      </c>
+      <c r="BF14">
+        <v>7.4</v>
+      </c>
+      <c r="BG14">
+        <v>6</v>
+      </c>
+      <c r="BH14">
+        <v>7</v>
+      </c>
+      <c r="BI14">
+        <v>4.9</v>
+      </c>
+      <c r="BJ14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK14">
+        <v>3.4</v>
+      </c>
+      <c r="BL14">
+        <v>55</v>
+      </c>
+      <c r="BM14">
+        <v>4.9</v>
+      </c>
+      <c r="BN14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO14">
+        <v>5.6</v>
+      </c>
+      <c r="BP14">
+        <v>19.5</v>
+      </c>
+      <c r="BQ14">
+        <v>4.2</v>
+      </c>
+      <c r="BR14">
+        <v>22</v>
+      </c>
+      <c r="BS14">
+        <v>4.3</v>
+      </c>
+      <c r="BT14">
         <v>7.6</v>
       </c>
-      <c r="BC14">
-        <v>20</v>
-      </c>
-      <c r="BD14">
-        <v>20</v>
-      </c>
-      <c r="BE14">
-        <v>7.2</v>
-      </c>
-      <c r="BF14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG14">
-        <v>6.4</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.04</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.04</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.04</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>1.04</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>1.04</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.04</v>
-      </c>
-      <c r="BT14">
-        <v>1000</v>
-      </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="CB14" t="s">
         <v>170</v>
@@ -4266,7 +4266,7 @@
         <v>151</v>
       </c>
       <c r="F15">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G15">
         <v>1.53</v>
@@ -4275,7 +4275,7 @@
         <v>5.7</v>
       </c>
       <c r="I15">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J15">
         <v>5.4</v>
@@ -4308,10 +4308,10 @@
         <v>1.68</v>
       </c>
       <c r="T15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U15">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V15">
         <v>1.17</v>
@@ -4356,10 +4356,10 @@
         <v>55</v>
       </c>
       <c r="AJ15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL15">
         <v>25</v>
@@ -4374,22 +4374,22 @@
         <v>38</v>
       </c>
       <c r="AP15">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ15">
         <v>28</v>
       </c>
       <c r="AR15">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="AS15">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT15">
         <v>17</v>
       </c>
       <c r="AU15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV15">
         <v>21</v>
@@ -4407,7 +4407,7 @@
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>27</v>
+        <v>7.8</v>
       </c>
       <c r="BB15">
         <v>15</v>
@@ -4419,10 +4419,10 @@
         <v>17.5</v>
       </c>
       <c r="BE15">
-        <v>29</v>
+        <v>7.8</v>
       </c>
       <c r="BF15">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BG15">
         <v>18.5</v>
@@ -4511,7 +4511,7 @@
         <v>3.55</v>
       </c>
       <c r="G16">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H16">
         <v>2.54</v>
@@ -4523,10 +4523,10 @@
         <v>2.84</v>
       </c>
       <c r="K16">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L16">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M16">
         <v>1.13</v>
@@ -4535,19 +4535,19 @@
         <v>2.6</v>
       </c>
       <c r="O16">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P16">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q16">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
         <v>1.19</v>
       </c>
       <c r="S16">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T16">
         <v>2.08</v>
@@ -4559,7 +4559,7 @@
         <v>1.6</v>
       </c>
       <c r="W16">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X16">
         <v>9.4</v>
@@ -4568,16 +4568,16 @@
         <v>7.8</v>
       </c>
       <c r="Z16">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA16">
         <v>48</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC16">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD16">
         <v>14.5</v>
@@ -4604,13 +4604,13 @@
         <v>65</v>
       </c>
       <c r="AL16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM16">
         <v>200</v>
       </c>
       <c r="AN16">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AO16">
         <v>48</v>
@@ -4625,7 +4625,7 @@
         <v>11.5</v>
       </c>
       <c r="AS16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT16">
         <v>8.800000000000001</v>
@@ -4637,97 +4637,97 @@
         <v>9.6</v>
       </c>
       <c r="AW16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX16">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AY16">
+        <v>14.5</v>
+      </c>
+      <c r="AZ16">
+        <v>19</v>
+      </c>
+      <c r="BA16">
+        <v>6.8</v>
+      </c>
+      <c r="BB16">
+        <v>7</v>
+      </c>
+      <c r="BC16">
+        <v>6.8</v>
+      </c>
+      <c r="BD16">
+        <v>7</v>
+      </c>
+      <c r="BE16">
+        <v>7.4</v>
+      </c>
+      <c r="BF16">
+        <v>7</v>
+      </c>
+      <c r="BG16">
+        <v>6.4</v>
+      </c>
+      <c r="BH16">
+        <v>2.72</v>
+      </c>
+      <c r="BI16">
+        <v>2.34</v>
+      </c>
+      <c r="BJ16">
+        <v>11</v>
+      </c>
+      <c r="BK16">
+        <v>6.6</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>2.32</v>
+      </c>
+      <c r="BN16">
+        <v>6.4</v>
+      </c>
+      <c r="BO16">
+        <v>5</v>
+      </c>
+      <c r="BP16">
+        <v>34</v>
+      </c>
+      <c r="BQ16">
+        <v>11</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>13</v>
+      </c>
+      <c r="BT16">
+        <v>5.3</v>
+      </c>
+      <c r="BU16">
+        <v>4.2</v>
+      </c>
+      <c r="BV16">
+        <v>23</v>
+      </c>
+      <c r="BW16">
+        <v>9.6</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>12</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
         <v>12.5</v>
-      </c>
-      <c r="AZ16">
-        <v>16.5</v>
-      </c>
-      <c r="BA16">
-        <v>6.4</v>
-      </c>
-      <c r="BB16">
-        <v>6.6</v>
-      </c>
-      <c r="BC16">
-        <v>6.4</v>
-      </c>
-      <c r="BD16">
-        <v>6.6</v>
-      </c>
-      <c r="BE16">
-        <v>7</v>
-      </c>
-      <c r="BF16">
-        <v>6.6</v>
-      </c>
-      <c r="BG16">
-        <v>6.2</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.04</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.04</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.04</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.04</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.04</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.04</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>1.04</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>1.04</v>
-      </c>
-      <c r="BX16">
-        <v>1000</v>
-      </c>
-      <c r="BY16">
-        <v>1.04</v>
-      </c>
-      <c r="BZ16">
-        <v>1000</v>
-      </c>
-      <c r="CA16">
-        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
         <v>170</v>
@@ -4753,13 +4753,13 @@
         <v>3.3</v>
       </c>
       <c r="G17">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="H17">
         <v>2.4</v>
       </c>
       <c r="I17">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="J17">
         <v>3.05</v>
@@ -4768,22 +4768,22 @@
         <v>3.6</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M17">
         <v>1.1</v>
       </c>
       <c r="N17">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="O17">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="P17">
         <v>1.62</v>
       </c>
       <c r="Q17">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R17">
         <v>1.23</v>
@@ -4798,25 +4798,25 @@
         <v>1.75</v>
       </c>
       <c r="V17">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W17">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X17">
         <v>12.5</v>
       </c>
       <c r="Y17">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z17">
         <v>16</v>
       </c>
       <c r="AA17">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AB17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC17">
         <v>7.6</v>
@@ -4825,16 +4825,16 @@
         <v>12.5</v>
       </c>
       <c r="AE17">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF17">
         <v>24</v>
       </c>
       <c r="AG17">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH17">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI17">
         <v>65</v>
@@ -4852,10 +4852,10 @@
         <v>170</v>
       </c>
       <c r="AN17">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO17">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP17">
         <v>7.6</v>
@@ -4867,10 +4867,10 @@
         <v>12.5</v>
       </c>
       <c r="AS17">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="AT17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU17">
         <v>6.2</v>
@@ -4879,7 +4879,7 @@
         <v>10</v>
       </c>
       <c r="AW17">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AX17">
         <v>19</v>
@@ -4891,85 +4891,85 @@
         <v>17</v>
       </c>
       <c r="BA17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB17">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD17">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE17">
+        <v>5.3</v>
+      </c>
+      <c r="BF17">
+        <v>5</v>
+      </c>
+      <c r="BG17">
+        <v>4.8</v>
+      </c>
+      <c r="BH17">
+        <v>3.35</v>
+      </c>
+      <c r="BI17">
+        <v>2.38</v>
+      </c>
+      <c r="BJ17">
+        <v>12.5</v>
+      </c>
+      <c r="BK17">
+        <v>3.55</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>4.9</v>
+      </c>
+      <c r="BN17">
         <v>7.6</v>
       </c>
-      <c r="BF17">
-        <v>7</v>
-      </c>
-      <c r="BG17">
-        <v>6.4</v>
-      </c>
-      <c r="BH17">
-        <v>3.5</v>
-      </c>
-      <c r="BI17">
-        <v>2.36</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
-        <v>1.41</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.41</v>
-      </c>
-      <c r="BN17">
-        <v>1000</v>
-      </c>
       <c r="BO17">
-        <v>1.41</v>
+        <v>4.8</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ17">
-        <v>1.41</v>
+        <v>4.4</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS17">
-        <v>1.41</v>
+        <v>4.6</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU17">
-        <v>1.41</v>
+        <v>4</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW17">
-        <v>1.41</v>
+        <v>4.1</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY17">
-        <v>1.41</v>
+        <v>4.5</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA17">
-        <v>1.41</v>
+        <v>4.5</v>
       </c>
       <c r="CB17" t="s">
         <v>170</v>
@@ -4992,28 +4992,28 @@
         <v>154</v>
       </c>
       <c r="F18">
+        <v>2.36</v>
+      </c>
+      <c r="G18">
+        <v>2.74</v>
+      </c>
+      <c r="H18">
         <v>2.4</v>
       </c>
-      <c r="G18">
-        <v>2.7</v>
-      </c>
-      <c r="H18">
-        <v>2.44</v>
-      </c>
       <c r="I18">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J18">
         <v>4.3</v>
       </c>
       <c r="K18">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
         <v>9.199999999999999</v>
@@ -5025,7 +5025,7 @@
         <v>3.7</v>
       </c>
       <c r="Q18">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="R18">
         <v>2.1</v>
@@ -5040,10 +5040,10 @@
         <v>3</v>
       </c>
       <c r="V18">
+        <v>1.58</v>
+      </c>
+      <c r="W18">
         <v>1.57</v>
-      </c>
-      <c r="W18">
-        <v>1.58</v>
       </c>
       <c r="X18">
         <v>65</v>
@@ -5055,7 +5055,7 @@
         <v>36</v>
       </c>
       <c r="AA18">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB18">
         <v>34</v>
@@ -5064,7 +5064,7 @@
         <v>17</v>
       </c>
       <c r="AD18">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE18">
         <v>28</v>
@@ -5094,22 +5094,22 @@
         <v>42</v>
       </c>
       <c r="AN18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO18">
         <v>10.5</v>
       </c>
       <c r="AP18">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AQ18">
         <v>20</v>
       </c>
       <c r="AR18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS18">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AT18">
         <v>20</v>
@@ -5124,7 +5124,7 @@
         <v>16.5</v>
       </c>
       <c r="AX18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY18">
         <v>10.5</v>
@@ -5136,7 +5136,7 @@
         <v>16.5</v>
       </c>
       <c r="BB18">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BC18">
         <v>16</v>
@@ -5145,7 +5145,7 @@
         <v>16.5</v>
       </c>
       <c r="BE18">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BF18">
         <v>6.4</v>
@@ -5154,64 +5154,64 @@
         <v>6.4</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BI18">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK18">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ18">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="CB18" t="s">
         <v>170</v>
@@ -5234,166 +5234,166 @@
         <v>155</v>
       </c>
       <c r="F19">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="G19">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="H19">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="I19">
-        <v>990</v>
+        <v>23</v>
       </c>
       <c r="J19">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="K19">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L19">
         <v>1.27</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="O19">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="P19">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q19">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R19">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S19">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="T19">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="U19">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W19">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA19">
         <v>1000</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO19">
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5476,37 +5476,37 @@
         <v>156</v>
       </c>
       <c r="F20">
+        <v>2.62</v>
+      </c>
+      <c r="G20">
+        <v>2.94</v>
+      </c>
+      <c r="H20">
+        <v>3.05</v>
+      </c>
+      <c r="I20">
+        <v>3.55</v>
+      </c>
+      <c r="J20">
         <v>2.82</v>
-      </c>
-      <c r="G20">
-        <v>3.25</v>
-      </c>
-      <c r="H20">
-        <v>2.82</v>
-      </c>
-      <c r="I20">
-        <v>3.25</v>
-      </c>
-      <c r="J20">
-        <v>2.8</v>
       </c>
       <c r="K20">
         <v>3.2</v>
       </c>
       <c r="L20">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="M20">
         <v>1.13</v>
       </c>
       <c r="N20">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="O20">
         <v>1.56</v>
       </c>
       <c r="P20">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Q20">
         <v>2.68</v>
@@ -5515,187 +5515,187 @@
         <v>1.19</v>
       </c>
       <c r="S20">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="T20">
         <v>2.1</v>
       </c>
       <c r="U20">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W20">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="X20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y20">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z20">
         <v>22</v>
       </c>
       <c r="AA20">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB20">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC20">
         <v>7.2</v>
       </c>
       <c r="AD20">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE20">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF20">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AG20">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH20">
         <v>25</v>
       </c>
       <c r="AI20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ20">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK20">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL20">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM20">
         <v>230</v>
       </c>
       <c r="AN20">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO20">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP20">
         <v>6.2</v>
       </c>
       <c r="AQ20">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR20">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS20">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT20">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU20">
         <v>6</v>
       </c>
       <c r="AV20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW20">
-        <v>38</v>
+        <v>6.8</v>
       </c>
       <c r="AX20">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ20">
         <v>20</v>
       </c>
       <c r="BA20">
+        <v>7</v>
+      </c>
+      <c r="BB20">
         <v>6.8</v>
       </c>
-      <c r="BB20">
-        <v>6.6</v>
-      </c>
       <c r="BC20">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BD20">
+        <v>7</v>
+      </c>
+      <c r="BE20">
+        <v>7.4</v>
+      </c>
+      <c r="BF20">
         <v>6.8</v>
       </c>
-      <c r="BE20">
-        <v>7.2</v>
-      </c>
-      <c r="BF20">
-        <v>6.6</v>
-      </c>
       <c r="BG20">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI20">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK20">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO20">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB20" t="s">
         <v>170</v>
@@ -5718,25 +5718,25 @@
         <v>157</v>
       </c>
       <c r="F21">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H21">
         <v>4.4</v>
       </c>
       <c r="I21">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J21">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K21">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L21">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="M21">
         <v>1.15</v>
@@ -5757,7 +5757,7 @@
         <v>1.14</v>
       </c>
       <c r="S21">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T21">
         <v>2.34</v>
@@ -5766,10 +5766,10 @@
         <v>1.53</v>
       </c>
       <c r="V21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X21">
         <v>8.199999999999999</v>
@@ -5850,7 +5850,7 @@
         <v>7.6</v>
       </c>
       <c r="AX21">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY21">
         <v>10.5</v>
@@ -5880,64 +5880,64 @@
         <v>7.8</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK21">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO21">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ21">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS21">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB21" t="s">
         <v>170</v>
@@ -5960,46 +5960,46 @@
         <v>158</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="G22">
         <v>5.7</v>
       </c>
       <c r="H22">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="I22">
         <v>2.26</v>
       </c>
       <c r="J22">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K22">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="L22">
         <v>1.51</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N22">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="O22">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P22">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
       </c>
       <c r="R22">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S22">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="T22">
         <v>1.11</v>
@@ -6011,28 +6011,28 @@
         <v>1.79</v>
       </c>
       <c r="W22">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X22">
         <v>1000</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA22">
         <v>1000</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE22">
         <v>1000</v>
@@ -6041,7 +6041,7 @@
         <v>1000</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH22">
         <v>1000</v>
@@ -6068,58 +6068,58 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6205,16 +6205,16 @@
         <v>1.09</v>
       </c>
       <c r="G23">
-        <v>1.85</v>
+        <v>11.5</v>
       </c>
       <c r="H23">
-        <v>2.22</v>
+        <v>1.1</v>
       </c>
       <c r="I23">
         <v>990</v>
       </c>
       <c r="J23">
-        <v>2.22</v>
+        <v>1.1</v>
       </c>
       <c r="K23">
         <v>950</v>
@@ -6226,13 +6226,13 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O23">
         <v>1.27</v>
       </c>
       <c r="P23">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q23">
         <v>1.27</v>
@@ -6241,7 +6241,7 @@
         <v>1.18</v>
       </c>
       <c r="S23">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
         <v>1.11</v>
@@ -6253,7 +6253,7 @@
         <v>1.01</v>
       </c>
       <c r="W23">
-        <v>1.99</v>
+        <v>1.09</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6444,16 +6444,16 @@
         <v>160</v>
       </c>
       <c r="F24">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="G24">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H24">
+        <v>2.9</v>
+      </c>
+      <c r="I24">
         <v>2.96</v>
-      </c>
-      <c r="I24">
-        <v>3.05</v>
       </c>
       <c r="J24">
         <v>3.75</v>
@@ -6462,25 +6462,25 @@
         <v>3.85</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M24">
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O24">
         <v>1.19</v>
       </c>
       <c r="P24">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q24">
         <v>1.57</v>
       </c>
       <c r="R24">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S24">
         <v>2.5</v>
@@ -6492,10 +6492,10 @@
         <v>2.68</v>
       </c>
       <c r="V24">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W24">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X24">
         <v>23</v>
@@ -6525,7 +6525,7 @@
         <v>21</v>
       </c>
       <c r="AG24">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH24">
         <v>14.5</v>
@@ -6543,13 +6543,13 @@
         <v>30</v>
       </c>
       <c r="AM24">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN24">
         <v>14</v>
       </c>
       <c r="AO24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP24">
         <v>20</v>
@@ -6576,7 +6576,7 @@
         <v>24</v>
       </c>
       <c r="AX24">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY24">
         <v>9.800000000000001</v>
@@ -6588,13 +6588,13 @@
         <v>28</v>
       </c>
       <c r="BB24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC24">
         <v>20</v>
       </c>
       <c r="BD24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE24">
         <v>48</v>
@@ -6606,61 +6606,61 @@
         <v>16.5</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK24">
         <v>1.04</v>
       </c>
       <c r="BL24">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM24">
         <v>1.04</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO24">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ24">
         <v>1.04</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS24">
         <v>1.04</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW24">
         <v>1.04</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY24">
         <v>1.04</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA24">
         <v>1.04</v>
@@ -6686,10 +6686,10 @@
         <v>161</v>
       </c>
       <c r="F25">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G25">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H25">
         <v>4</v>
@@ -6704,7 +6704,7 @@
         <v>3.9</v>
       </c>
       <c r="L25">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M25">
         <v>1.06</v>
@@ -6719,7 +6719,7 @@
         <v>2.1</v>
       </c>
       <c r="Q25">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R25">
         <v>1.43</v>
@@ -6728,16 +6728,16 @@
         <v>3.15</v>
       </c>
       <c r="T25">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U25">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V25">
         <v>1.31</v>
       </c>
       <c r="W25">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X25">
         <v>16</v>
@@ -6749,7 +6749,7 @@
         <v>32</v>
       </c>
       <c r="AA25">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB25">
         <v>10.5</v>
@@ -6776,7 +6776,7 @@
         <v>55</v>
       </c>
       <c r="AJ25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK25">
         <v>20</v>
@@ -6806,16 +6806,16 @@
         <v>36</v>
       </c>
       <c r="AT25">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU25">
         <v>7.8</v>
       </c>
       <c r="AV25">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW25">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AX25">
         <v>11.5</v>
@@ -6845,67 +6845,67 @@
         <v>11</v>
       </c>
       <c r="BG25">
+        <v>38</v>
+      </c>
+      <c r="BH25">
+        <v>4.1</v>
+      </c>
+      <c r="BI25">
+        <v>3.3</v>
+      </c>
+      <c r="BJ25">
+        <v>11</v>
+      </c>
+      <c r="BK25">
+        <v>7.2</v>
+      </c>
+      <c r="BL25">
+        <v>130</v>
+      </c>
+      <c r="BM25">
+        <v>5.6</v>
+      </c>
+      <c r="BN25">
+        <v>5.5</v>
+      </c>
+      <c r="BO25">
+        <v>4.4</v>
+      </c>
+      <c r="BP25">
+        <v>14.5</v>
+      </c>
+      <c r="BQ25">
+        <v>4.2</v>
+      </c>
+      <c r="BR25">
+        <v>28</v>
+      </c>
+      <c r="BS25">
+        <v>4.8</v>
+      </c>
+      <c r="BT25">
+        <v>8.6</v>
+      </c>
+      <c r="BU25">
+        <v>6.6</v>
+      </c>
+      <c r="BV25">
+        <v>38</v>
+      </c>
+      <c r="BW25">
+        <v>5.1</v>
+      </c>
+      <c r="BX25">
+        <v>48</v>
+      </c>
+      <c r="BY25">
+        <v>5.2</v>
+      </c>
+      <c r="BZ25">
         <v>26</v>
       </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>3.05</v>
-      </c>
-      <c r="BJ25">
-        <v>13</v>
-      </c>
-      <c r="BK25">
-        <v>6.4</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>1.99</v>
-      </c>
-      <c r="BN25">
-        <v>6.2</v>
-      </c>
-      <c r="BO25">
-        <v>3.95</v>
-      </c>
-      <c r="BP25">
-        <v>18</v>
-      </c>
-      <c r="BQ25">
-        <v>3.2</v>
-      </c>
-      <c r="BR25">
-        <v>34</v>
-      </c>
-      <c r="BS25">
-        <v>3.45</v>
-      </c>
-      <c r="BT25">
-        <v>10</v>
-      </c>
-      <c r="BU25">
-        <v>2.8</v>
-      </c>
-      <c r="BV25">
-        <v>44</v>
-      </c>
-      <c r="BW25">
-        <v>1.91</v>
-      </c>
-      <c r="BX25">
-        <v>1000</v>
-      </c>
-      <c r="BY25">
-        <v>1.93</v>
-      </c>
-      <c r="BZ25">
-        <v>29</v>
-      </c>
       <c r="CA25">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="CB25" t="s">
         <v>170</v>
@@ -6928,10 +6928,10 @@
         <v>162</v>
       </c>
       <c r="F26">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G26">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H26">
         <v>7.6</v>
@@ -6940,10 +6940,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J26">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K26">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L26">
         <v>1.33</v>
@@ -6952,16 +6952,16 @@
         <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O26">
         <v>1.37</v>
       </c>
       <c r="P26">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q26">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R26">
         <v>1.32</v>
@@ -6970,7 +6970,7 @@
         <v>3.95</v>
       </c>
       <c r="T26">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U26">
         <v>1.73</v>
@@ -6979,7 +6979,7 @@
         <v>1.13</v>
       </c>
       <c r="W26">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="X26">
         <v>13</v>
@@ -6988,13 +6988,13 @@
         <v>23</v>
       </c>
       <c r="Z26">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA26">
         <v>330</v>
       </c>
       <c r="AB26">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>10</v>
@@ -7003,7 +7003,7 @@
         <v>32</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF26">
         <v>7.8</v>
@@ -7045,7 +7045,7 @@
         <v>30</v>
       </c>
       <c r="AS26">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AT26">
         <v>6.4</v>
@@ -7057,37 +7057,37 @@
         <v>28</v>
       </c>
       <c r="AW26">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX26">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY26">
         <v>9.6</v>
       </c>
       <c r="AZ26">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BA26">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BB26">
         <v>11.5</v>
       </c>
       <c r="BC26">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD26">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BE26">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BF26">
         <v>8.800000000000001</v>
       </c>
       <c r="BG26">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7170,19 +7170,19 @@
         <v>163</v>
       </c>
       <c r="F27">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="G27">
         <v>990</v>
       </c>
       <c r="H27">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="I27">
         <v>990</v>
       </c>
       <c r="J27">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -7218,10 +7218,10 @@
         <v>1.11</v>
       </c>
       <c r="V27">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7412,10 +7412,10 @@
         <v>164</v>
       </c>
       <c r="F28">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H28">
         <v>10</v>
@@ -7424,13 +7424,13 @@
         <v>10.5</v>
       </c>
       <c r="J28">
+        <v>6.2</v>
+      </c>
+      <c r="K28">
         <v>6.4</v>
       </c>
-      <c r="K28">
-        <v>6.6</v>
-      </c>
       <c r="L28">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M28">
         <v>1.03</v>
@@ -7445,25 +7445,25 @@
         <v>2.96</v>
       </c>
       <c r="Q28">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R28">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S28">
         <v>2.24</v>
       </c>
       <c r="T28">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U28">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V28">
         <v>1.1</v>
       </c>
       <c r="W28">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="X28">
         <v>32</v>
@@ -7472,19 +7472,19 @@
         <v>42</v>
       </c>
       <c r="Z28">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA28">
-        <v>280</v>
+        <v>390</v>
       </c>
       <c r="AB28">
         <v>12</v>
       </c>
       <c r="AC28">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD28">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE28">
         <v>120</v>
@@ -7499,7 +7499,7 @@
         <v>25</v>
       </c>
       <c r="AI28">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ28">
         <v>11.5</v>
@@ -7526,16 +7526,16 @@
         <v>36</v>
       </c>
       <c r="AR28">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AS28">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT28">
         <v>11</v>
       </c>
       <c r="AU28">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV28">
         <v>30</v>
@@ -7550,7 +7550,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ28">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA28">
         <v>85</v>
@@ -7565,16 +7565,16 @@
         <v>25</v>
       </c>
       <c r="BE28">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="BF28">
         <v>4.1</v>
       </c>
       <c r="BG28">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BH28">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI28">
         <v>4.5</v>
@@ -7589,7 +7589,7 @@
         <v>110</v>
       </c>
       <c r="BM28">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN28">
         <v>4.2</v>
@@ -7619,13 +7619,13 @@
         <v>70</v>
       </c>
       <c r="BW28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX28">
         <v>60</v>
       </c>
       <c r="BY28">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ28">
         <v>9.800000000000001</v>
@@ -7654,13 +7654,13 @@
         <v>165</v>
       </c>
       <c r="F29">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G29">
         <v>2.56</v>
       </c>
       <c r="H29">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I29">
         <v>3.25</v>
@@ -7672,13 +7672,13 @@
         <v>3.4</v>
       </c>
       <c r="L29">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M29">
         <v>1.09</v>
       </c>
       <c r="N29">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O29">
         <v>1.39</v>
@@ -7732,7 +7732,7 @@
         <v>42</v>
       </c>
       <c r="AF29">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG29">
         <v>12</v>
@@ -7759,7 +7759,7 @@
         <v>26</v>
       </c>
       <c r="AO29">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AP29">
         <v>10.5</v>
@@ -7780,7 +7780,7 @@
         <v>6.8</v>
       </c>
       <c r="AV29">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW29">
         <v>34</v>
@@ -7816,64 +7816,64 @@
         <v>34</v>
       </c>
       <c r="BH29">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="BI29">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK29">
-        <v>1.35</v>
+        <v>5.2</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO29">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ29">
-        <v>1.35</v>
+        <v>7</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.35</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU29">
-        <v>1.35</v>
+        <v>4.7</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW29">
-        <v>1.35</v>
+        <v>7.6</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.35</v>
+        <v>8.4</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>1.35</v>
+        <v>8</v>
       </c>
       <c r="CB29" t="s">
         <v>170</v>
@@ -7896,7 +7896,7 @@
         <v>166</v>
       </c>
       <c r="F30">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G30">
         <v>3.15</v>
@@ -7905,7 +7905,7 @@
         <v>2.76</v>
       </c>
       <c r="I30">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J30">
         <v>2.96</v>
@@ -7914,22 +7914,22 @@
         <v>3.35</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M30">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N30">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O30">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P30">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q30">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R30">
         <v>1.2</v>
@@ -7944,13 +7944,13 @@
         <v>1.81</v>
       </c>
       <c r="V30">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W30">
         <v>1.46</v>
       </c>
       <c r="X30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y30">
         <v>10.5</v>
@@ -7959,7 +7959,7 @@
         <v>21</v>
       </c>
       <c r="AA30">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB30">
         <v>9.199999999999999</v>
@@ -7977,7 +7977,7 @@
         <v>22</v>
       </c>
       <c r="AG30">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AH30">
         <v>25</v>
@@ -8010,13 +8010,13 @@
         <v>7.6</v>
       </c>
       <c r="AR30">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS30">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT30">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU30">
         <v>6.2</v>
@@ -8025,7 +8025,7 @@
         <v>11.5</v>
       </c>
       <c r="AW30">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX30">
         <v>15.5</v>
@@ -8037,85 +8037,85 @@
         <v>18.5</v>
       </c>
       <c r="BA30">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB30">
         <v>5.5</v>
       </c>
       <c r="BC30">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD30">
+        <v>5.6</v>
+      </c>
+      <c r="BE30">
+        <v>5.9</v>
+      </c>
+      <c r="BF30">
         <v>5.5</v>
       </c>
-      <c r="BE30">
+      <c r="BG30">
+        <v>5.5</v>
+      </c>
+      <c r="BH30">
+        <v>2.82</v>
+      </c>
+      <c r="BI30">
+        <v>2.34</v>
+      </c>
+      <c r="BJ30">
+        <v>11</v>
+      </c>
+      <c r="BK30">
+        <v>6</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>13</v>
+      </c>
+      <c r="BN30">
+        <v>5.9</v>
+      </c>
+      <c r="BO30">
+        <v>4.6</v>
+      </c>
+      <c r="BP30">
+        <v>27</v>
+      </c>
+      <c r="BQ30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>10.5</v>
+      </c>
+      <c r="BT30">
         <v>5.8</v>
       </c>
-      <c r="BF30">
-        <v>5.4</v>
-      </c>
-      <c r="BG30">
-        <v>5.4</v>
-      </c>
-      <c r="BH30">
-        <v>1000</v>
-      </c>
-      <c r="BI30">
-        <v>1.04</v>
-      </c>
-      <c r="BJ30">
-        <v>1000</v>
-      </c>
-      <c r="BK30">
-        <v>1.04</v>
-      </c>
-      <c r="BL30">
-        <v>1000</v>
-      </c>
-      <c r="BM30">
-        <v>1.04</v>
-      </c>
-      <c r="BN30">
-        <v>1000</v>
-      </c>
-      <c r="BO30">
-        <v>1.04</v>
-      </c>
-      <c r="BP30">
-        <v>1000</v>
-      </c>
-      <c r="BQ30">
-        <v>1.04</v>
-      </c>
-      <c r="BR30">
-        <v>1000</v>
-      </c>
-      <c r="BS30">
-        <v>1.04</v>
-      </c>
-      <c r="BT30">
-        <v>1000</v>
-      </c>
       <c r="BU30">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW30">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB30" t="s">
         <v>170</v>
@@ -8138,58 +8138,58 @@
         <v>167</v>
       </c>
       <c r="F31">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="G31">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H31">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I31">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J31">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K31">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L31">
         <v>1.28</v>
       </c>
       <c r="M31">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N31">
-        <v>2.76</v>
+        <v>3.7</v>
       </c>
       <c r="O31">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P31">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q31">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="R31">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S31">
         <v>2.6</v>
       </c>
       <c r="T31">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U31">
         <v>1.11</v>
       </c>
       <c r="V31">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W31">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8380,19 +8380,19 @@
         <v>168</v>
       </c>
       <c r="F32">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G32">
-        <v>2.04</v>
+        <v>3.95</v>
       </c>
       <c r="H32">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="I32">
         <v>990</v>
       </c>
       <c r="J32">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K32">
         <v>950</v>
@@ -8404,13 +8404,13 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="O32">
         <v>1.12</v>
       </c>
       <c r="P32">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q32">
         <v>1.12</v>
@@ -8428,10 +8428,10 @@
         <v>1.11</v>
       </c>
       <c r="V32">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W32">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8622,7 +8622,7 @@
         <v>169</v>
       </c>
       <c r="F33">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G33">
         <v>2.06</v>
@@ -8634,13 +8634,13 @@
         <v>5.1</v>
       </c>
       <c r="J33">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K33">
         <v>3.65</v>
       </c>
       <c r="L33">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M33">
         <v>1.09</v>
@@ -8649,13 +8649,13 @@
         <v>3.05</v>
       </c>
       <c r="O33">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P33">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q33">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R33">
         <v>1.26</v>
@@ -8664,67 +8664,67 @@
         <v>4.2</v>
       </c>
       <c r="T33">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U33">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V33">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W33">
         <v>1.94</v>
       </c>
       <c r="X33">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y33">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z33">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA33">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB33">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD33">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AE33">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AF33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG33">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH33">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AI33">
         <v>100</v>
       </c>
       <c r="AJ33">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AK33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AL33">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM33">
         <v>180</v>
       </c>
       <c r="AN33">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AO33">
         <v>120</v>
@@ -8736,10 +8736,10 @@
         <v>12</v>
       </c>
       <c r="AR33">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS33">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="AT33">
         <v>6.6</v>
@@ -8748,10 +8748,10 @@
         <v>7</v>
       </c>
       <c r="AV33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AW33">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="AX33">
         <v>10</v>
@@ -8760,10 +8760,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ33">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="BA33">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="BB33">
         <v>20</v>
@@ -8775,73 +8775,73 @@
         <v>34</v>
       </c>
       <c r="BE33">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF33">
+        <v>4</v>
+      </c>
+      <c r="BG33">
+        <v>4.7</v>
+      </c>
+      <c r="BH33">
+        <v>3.1</v>
+      </c>
+      <c r="BI33">
+        <v>2.52</v>
+      </c>
+      <c r="BJ33">
+        <v>11</v>
+      </c>
+      <c r="BK33">
+        <v>6</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>12.5</v>
+      </c>
+      <c r="BN33">
+        <v>4.6</v>
+      </c>
+      <c r="BO33">
+        <v>4</v>
+      </c>
+      <c r="BP33">
+        <v>15</v>
+      </c>
+      <c r="BQ33">
         <v>7</v>
       </c>
-      <c r="BG33">
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>9.6</v>
+      </c>
+      <c r="BT33">
+        <v>8</v>
+      </c>
+      <c r="BU33">
+        <v>5.8</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
         <v>10</v>
       </c>
-      <c r="BH33">
-        <v>1000</v>
-      </c>
-      <c r="BI33">
-        <v>1.76</v>
-      </c>
-      <c r="BJ33">
-        <v>15.5</v>
-      </c>
-      <c r="BK33">
-        <v>1.58</v>
-      </c>
-      <c r="BL33">
-        <v>1000</v>
-      </c>
-      <c r="BM33">
-        <v>1.76</v>
-      </c>
-      <c r="BN33">
-        <v>6.2</v>
-      </c>
-      <c r="BO33">
-        <v>3.05</v>
-      </c>
-      <c r="BP33">
-        <v>21</v>
-      </c>
-      <c r="BQ33">
-        <v>1.63</v>
-      </c>
-      <c r="BR33">
-        <v>50</v>
-      </c>
-      <c r="BS33">
-        <v>1.7</v>
-      </c>
-      <c r="BT33">
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
         <v>11</v>
       </c>
-      <c r="BU33">
-        <v>5</v>
-      </c>
-      <c r="BV33">
-        <v>1000</v>
-      </c>
-      <c r="BW33">
-        <v>1.72</v>
-      </c>
-      <c r="BX33">
-        <v>1000</v>
-      </c>
-      <c r="BY33">
-        <v>1.73</v>
-      </c>
       <c r="BZ33">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.7</v>
+        <v>9.6</v>
       </c>
       <c r="CB33" t="s">
         <v>170</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -577,7 +577,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-25 13:22:45</t>
+    <t>2026-08-25 15:31:23</t>
   </si>
 </sst>
 </file>
@@ -1171,82 +1171,82 @@
         <v>150</v>
       </c>
       <c r="F2">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G2">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
         <v>4.2</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
         <v>4</v>
       </c>
       <c r="T2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AB2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF2">
         <v>8.199999999999999</v>
@@ -1255,7 +1255,7 @@
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI2">
         <v>140</v>
@@ -1264,97 +1264,97 @@
         <v>13.5</v>
       </c>
       <c r="AK2">
+        <v>18</v>
+      </c>
+      <c r="AL2">
+        <v>50</v>
+      </c>
+      <c r="AM2">
+        <v>200</v>
+      </c>
+      <c r="AN2">
+        <v>10.5</v>
+      </c>
+      <c r="AO2">
+        <v>220</v>
+      </c>
+      <c r="AP2">
+        <v>12</v>
+      </c>
+      <c r="AQ2">
         <v>18.5</v>
       </c>
-      <c r="AL2">
-        <v>55</v>
-      </c>
-      <c r="AM2">
-        <v>210</v>
-      </c>
-      <c r="AN2">
-        <v>11</v>
-      </c>
-      <c r="AO2">
-        <v>250</v>
-      </c>
-      <c r="AP2">
-        <v>11.5</v>
-      </c>
-      <c r="AQ2">
+      <c r="AR2">
+        <v>50</v>
+      </c>
+      <c r="AS2">
+        <v>18.5</v>
+      </c>
+      <c r="AT2">
+        <v>6.6</v>
+      </c>
+      <c r="AU2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV2">
+        <v>25</v>
+      </c>
+      <c r="AW2">
         <v>17.5</v>
       </c>
-      <c r="AR2">
-        <v>55</v>
-      </c>
-      <c r="AS2">
-        <v>14.5</v>
-      </c>
-      <c r="AT2">
-        <v>6.4</v>
-      </c>
-      <c r="AU2">
-        <v>9</v>
-      </c>
-      <c r="AV2">
-        <v>24</v>
-      </c>
-      <c r="AW2">
-        <v>14</v>
-      </c>
       <c r="AX2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY2">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA2">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BE2">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BH2">
         <v>3.6</v>
       </c>
       <c r="BI2">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2">
         <v>3.9</v>
       </c>
       <c r="BO2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP2">
         <v>10.5</v>
@@ -1366,10 +1366,10 @@
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU2">
         <v>8.6</v>
@@ -1378,19 +1378,19 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ2">
         <v>23</v>
       </c>
       <c r="CA2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
         <v>187</v>
@@ -1416,13 +1416,13 @@
         <v>2.22</v>
       </c>
       <c r="G3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>3.3</v>
@@ -1431,16 +1431,16 @@
         <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O3">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P3">
         <v>1.62</v>
@@ -1449,64 +1449,64 @@
         <v>2.5</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
         <v>5.1</v>
       </c>
       <c r="T3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U3">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y3">
         <v>11</v>
       </c>
       <c r="Z3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA3">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB3">
         <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG3">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL3">
         <v>60</v>
@@ -1527,10 +1527,10 @@
         <v>10</v>
       </c>
       <c r="AR3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AS3">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1542,10 +1542,10 @@
         <v>15</v>
       </c>
       <c r="AW3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
@@ -1563,13 +1563,13 @@
         <v>26</v>
       </c>
       <c r="BD3">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BE3">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="BF3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG3">
         <v>65</v>
@@ -1655,22 +1655,22 @@
         <v>152</v>
       </c>
       <c r="F4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G4">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
-        <v>990</v>
+        <v>15.5</v>
       </c>
       <c r="J4">
         <v>1.1</v>
       </c>
       <c r="K4">
-        <v>8.800000000000001</v>
+        <v>500</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1679,22 +1679,22 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O4">
         <v>1.29</v>
       </c>
       <c r="P4">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q4">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="R4">
         <v>1.2</v>
       </c>
       <c r="S4">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1703,10 +1703,10 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1757,64 +1757,64 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AQ4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AR4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AS4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AT4">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AU4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AV4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AW4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AX4">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AY4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AZ4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BA4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BB4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BC4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BD4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BE4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BF4">
         <v>1.04</v>
       </c>
       <c r="BG4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1897,16 +1897,16 @@
         <v>153</v>
       </c>
       <c r="F5">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G5">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="H5">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="I5">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="J5">
         <v>3.3</v>
@@ -1921,7 +1921,7 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
         <v>1.42</v>
@@ -1933,88 +1933,88 @@
         <v>2.26</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
         <v>4.3</v>
       </c>
       <c r="T5">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U5">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="W5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X5">
         <v>11.5</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB5">
         <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH5">
         <v>21</v>
       </c>
       <c r="AI5">
+        <v>70</v>
+      </c>
+      <c r="AJ5">
+        <v>90</v>
+      </c>
+      <c r="AK5">
         <v>60</v>
       </c>
-      <c r="AJ5">
-        <v>1000</v>
-      </c>
-      <c r="AK5">
-        <v>55</v>
-      </c>
       <c r="AL5">
+        <v>75</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
         <v>70</v>
       </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>65</v>
-      </c>
       <c r="AO5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AP5">
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR5">
         <v>13</v>
       </c>
       <c r="AS5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -2026,10 +2026,10 @@
         <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AX5">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AY5">
         <v>13</v>
@@ -2038,34 +2038,34 @@
         <v>17</v>
       </c>
       <c r="BA5">
+        <v>32</v>
+      </c>
+      <c r="BB5">
         <v>36</v>
       </c>
-      <c r="BB5">
-        <v>38</v>
-      </c>
       <c r="BC5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BD5">
+        <v>36</v>
+      </c>
+      <c r="BE5">
+        <v>13</v>
+      </c>
+      <c r="BF5">
         <v>34</v>
       </c>
-      <c r="BE5">
-        <v>12</v>
-      </c>
-      <c r="BF5">
-        <v>38</v>
-      </c>
       <c r="BG5">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH5">
         <v>3.5</v>
       </c>
       <c r="BI5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BK5">
         <v>8</v>
@@ -2074,49 +2074,49 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BN5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO5">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BP5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BQ5">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BR5">
         <v>60</v>
       </c>
       <c r="BS5">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BT5">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BU5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW5">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BX5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY5">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BZ5">
         <v>44</v>
       </c>
       <c r="CA5">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
         <v>187</v>
@@ -2145,7 +2145,7 @@
         <v>2.42</v>
       </c>
       <c r="H6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I6">
         <v>3.25</v>
@@ -2154,7 +2154,7 @@
         <v>3.7</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6">
         <v>1.28</v>
@@ -2172,7 +2172,7 @@
         <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R6">
         <v>1.48</v>
@@ -2181,13 +2181,13 @@
         <v>2.9</v>
       </c>
       <c r="T6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U6">
         <v>2.44</v>
       </c>
       <c r="V6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.7</v>
@@ -2211,10 +2211,10 @@
         <v>8.6</v>
       </c>
       <c r="AD6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF6">
         <v>17.5</v>
@@ -2229,7 +2229,7 @@
         <v>95</v>
       </c>
       <c r="AJ6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK6">
         <v>32</v>
@@ -2244,19 +2244,19 @@
         <v>17</v>
       </c>
       <c r="AO6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP6">
         <v>16.5</v>
       </c>
       <c r="AQ6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR6">
         <v>20</v>
       </c>
       <c r="AS6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT6">
         <v>11</v>
@@ -2277,7 +2277,7 @@
         <v>10</v>
       </c>
       <c r="AZ6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA6">
         <v>28</v>
@@ -2384,22 +2384,22 @@
         <v>1.56</v>
       </c>
       <c r="G7">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H7">
         <v>7.4</v>
       </c>
       <c r="I7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>4.1</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M7">
         <v>1.08</v>
@@ -2411,7 +2411,7 @@
         <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
         <v>2.14</v>
@@ -2420,10 +2420,10 @@
         <v>1.29</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T7">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U7">
         <v>1.76</v>
@@ -2432,10 +2432,10 @@
         <v>1.14</v>
       </c>
       <c r="W7">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y7">
         <v>22</v>
@@ -2498,7 +2498,7 @@
         <v>34</v>
       </c>
       <c r="AS7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
@@ -2510,7 +2510,7 @@
         <v>19.5</v>
       </c>
       <c r="AW7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX7">
         <v>7.4</v>
@@ -2522,7 +2522,7 @@
         <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB7">
         <v>12.5</v>
@@ -2534,13 +2534,13 @@
         <v>27</v>
       </c>
       <c r="BE7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF7">
         <v>9.199999999999999</v>
       </c>
       <c r="BG7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2623,19 +2623,19 @@
         <v>156</v>
       </c>
       <c r="F8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G8">
-        <v>990</v>
+        <v>1.2</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.06</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2647,22 +2647,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.24</v>
+        <v>4.3</v>
       </c>
       <c r="O8">
         <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>4.3</v>
       </c>
       <c r="Q8">
         <v>1.01</v>
       </c>
       <c r="R8">
-        <v>1.06</v>
+        <v>2.52</v>
       </c>
       <c r="S8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2674,7 +2674,7 @@
         <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2725,64 +2725,64 @@
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2865,19 +2865,19 @@
         <v>157</v>
       </c>
       <c r="F9">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G9">
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="I9">
-        <v>870</v>
+        <v>3.6</v>
       </c>
       <c r="J9">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2886,25 +2886,25 @@
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N9">
-        <v>1.27</v>
+        <v>3.85</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q9">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="R9">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S9">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2913,10 +2913,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2970,55 +2970,55 @@
         <v>1000</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -3155,7 +3155,7 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W10">
         <v>2.22</v>
@@ -3173,7 +3173,7 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AC10">
         <v>970</v>
@@ -3185,7 +3185,7 @@
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG10">
         <v>950</v>
@@ -3197,7 +3197,7 @@
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AK10">
         <v>1000</v>
@@ -3215,16 +3215,16 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ10">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AR10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AS10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AT10">
         <v>4.6</v>
@@ -3233,10 +3233,10 @@
         <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AW10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AX10">
         <v>5.4</v>
@@ -3245,28 +3245,28 @@
         <v>8.6</v>
       </c>
       <c r="AZ10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BA10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BB10">
         <v>9.4</v>
       </c>
       <c r="BC10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BD10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BE10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BF10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BG10">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3349,34 +3349,34 @@
         <v>159</v>
       </c>
       <c r="F11">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="G11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H11">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="I11">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="K11">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L11">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P11">
         <v>2.02</v>
@@ -3385,7 +3385,7 @@
         <v>1.73</v>
       </c>
       <c r="R11">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S11">
         <v>2.72</v>
@@ -3397,10 +3397,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="W11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3409,13 +3409,13 @@
         <v>1000</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC11">
         <v>1000</v>
@@ -3430,7 +3430,7 @@
         <v>1000</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH11">
         <v>1000</v>
@@ -3454,61 +3454,61 @@
         <v>1000</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3591,22 +3591,22 @@
         <v>160</v>
       </c>
       <c r="F12">
-        <v>4.1</v>
+        <v>1.09</v>
       </c>
       <c r="G12">
         <v>990</v>
       </c>
       <c r="H12">
+        <v>1.53</v>
+      </c>
+      <c r="I12">
+        <v>1000</v>
+      </c>
+      <c r="J12">
         <v>1.1</v>
       </c>
-      <c r="I12">
-        <v>1.78</v>
-      </c>
-      <c r="J12">
-        <v>1.09</v>
-      </c>
       <c r="K12">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3639,10 +3639,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3848,7 +3848,7 @@
         <v>4.1</v>
       </c>
       <c r="K13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>1.24</v>
@@ -3863,7 +3863,7 @@
         <v>1.17</v>
       </c>
       <c r="P13">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q13">
         <v>1.52</v>
@@ -3938,10 +3938,10 @@
         <v>9</v>
       </c>
       <c r="AO13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP13">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AQ13">
         <v>17.5</v>
@@ -3950,7 +3950,7 @@
         <v>26</v>
       </c>
       <c r="AS13">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT13">
         <v>11</v>
@@ -3974,7 +3974,7 @@
         <v>12</v>
       </c>
       <c r="BA13">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB13">
         <v>20</v>
@@ -3986,7 +3986,7 @@
         <v>19</v>
       </c>
       <c r="BE13">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF13">
         <v>7.2</v>
@@ -4004,7 +4004,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -4016,16 +4016,16 @@
         <v>6</v>
       </c>
       <c r="BO13">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP13">
         <v>15</v>
       </c>
       <c r="BQ13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS13">
         <v>4.7</v>
@@ -4046,13 +4046,13 @@
         <v>34</v>
       </c>
       <c r="BY13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BZ13">
         <v>16.5</v>
       </c>
       <c r="CA13">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="CB13" t="s">
         <v>187</v>
@@ -4075,22 +4075,22 @@
         <v>162</v>
       </c>
       <c r="F14">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="G14">
+        <v>2.8</v>
+      </c>
+      <c r="H14">
         <v>2.76</v>
       </c>
-      <c r="H14">
-        <v>2.78</v>
-      </c>
       <c r="I14">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="J14">
         <v>3.45</v>
       </c>
       <c r="K14">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4102,16 +4102,16 @@
         <v>4</v>
       </c>
       <c r="O14">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P14">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q14">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R14">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14">
         <v>3</v>
@@ -4120,34 +4120,34 @@
         <v>1.67</v>
       </c>
       <c r="U14">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V14">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W14">
         <v>1.56</v>
       </c>
       <c r="X14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z14">
         <v>21</v>
       </c>
       <c r="AA14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB14">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AC14">
         <v>8.6</v>
       </c>
       <c r="AD14">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE14">
         <v>36</v>
@@ -4156,31 +4156,31 @@
         <v>23</v>
       </c>
       <c r="AG14">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI14">
         <v>40</v>
       </c>
       <c r="AJ14">
+        <v>55</v>
+      </c>
+      <c r="AK14">
         <v>40</v>
       </c>
-      <c r="AK14">
-        <v>29</v>
-      </c>
       <c r="AL14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM14">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN14">
         <v>25</v>
       </c>
       <c r="AO14">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AP14">
         <v>14</v>
@@ -4192,7 +4192,7 @@
         <v>17</v>
       </c>
       <c r="AS14">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AT14">
         <v>10.5</v>
@@ -4204,10 +4204,10 @@
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX14">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY14">
         <v>10</v>
@@ -4216,19 +4216,19 @@
         <v>14</v>
       </c>
       <c r="BA14">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB14">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BC14">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BD14">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE14">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF14">
         <v>17</v>
@@ -4317,13 +4317,13 @@
         <v>163</v>
       </c>
       <c r="F15">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="G15">
         <v>4.1</v>
       </c>
       <c r="H15">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="I15">
         <v>2.52</v>
@@ -4332,7 +4332,7 @@
         <v>3.05</v>
       </c>
       <c r="K15">
-        <v>23</v>
+        <v>3.7</v>
       </c>
       <c r="L15">
         <v>1.3</v>
@@ -4347,16 +4347,16 @@
         <v>1.01</v>
       </c>
       <c r="P15">
+        <v>1.93</v>
+      </c>
+      <c r="Q15">
         <v>1.92</v>
       </c>
-      <c r="Q15">
-        <v>1.9</v>
-      </c>
       <c r="R15">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S15">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4559,7 +4559,7 @@
         <v>164</v>
       </c>
       <c r="F16">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G16">
         <v>1.61</v>
@@ -4568,13 +4568,13 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J16">
         <v>5.5</v>
       </c>
       <c r="K16">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4586,13 +4586,13 @@
         <v>10.5</v>
       </c>
       <c r="O16">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q16">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R16">
         <v>2.24</v>
@@ -4601,13 +4601,13 @@
         <v>1.67</v>
       </c>
       <c r="T16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U16">
         <v>3</v>
       </c>
       <c r="V16">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W16">
         <v>2.62</v>
@@ -4628,7 +4628,7 @@
         <v>23</v>
       </c>
       <c r="AC16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD16">
         <v>27</v>
@@ -4655,7 +4655,7 @@
         <v>14.5</v>
       </c>
       <c r="AL16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM16">
         <v>55</v>
@@ -4667,16 +4667,16 @@
         <v>26</v>
       </c>
       <c r="AP16">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ16">
         <v>30</v>
       </c>
       <c r="AR16">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT16">
         <v>19</v>
@@ -4715,10 +4715,10 @@
         <v>34</v>
       </c>
       <c r="BF16">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BG16">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4804,16 +4804,16 @@
         <v>2.58</v>
       </c>
       <c r="G17">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H17">
         <v>2.28</v>
       </c>
       <c r="I17">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="J17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K17">
         <v>5.5</v>
@@ -4825,7 +4825,7 @@
         <v>1.02</v>
       </c>
       <c r="N17">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O17">
         <v>1.1</v>
@@ -4834,43 +4834,43 @@
         <v>3.45</v>
       </c>
       <c r="Q17">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S17">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="T17">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="U17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V17">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="W17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X17">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y17">
         <v>28</v>
       </c>
       <c r="Z17">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA17">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB17">
         <v>28</v>
       </c>
       <c r="AC17">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD17">
         <v>14.5</v>
@@ -4888,7 +4888,7 @@
         <v>16</v>
       </c>
       <c r="AI17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ17">
         <v>46</v>
@@ -4897,7 +4897,7 @@
         <v>26</v>
       </c>
       <c r="AL17">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM17">
         <v>38</v>
@@ -4909,7 +4909,7 @@
         <v>8.6</v>
       </c>
       <c r="AP17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ17">
         <v>20</v>
@@ -4918,10 +4918,10 @@
         <v>19</v>
       </c>
       <c r="AS17">
+        <v>26</v>
+      </c>
+      <c r="AT17">
         <v>5.7</v>
-      </c>
-      <c r="AT17">
-        <v>5.4</v>
       </c>
       <c r="AU17">
         <v>10</v>
@@ -4933,7 +4933,7 @@
         <v>16</v>
       </c>
       <c r="AX17">
-        <v>5.6</v>
+        <v>22</v>
       </c>
       <c r="AY17">
         <v>11</v>
@@ -4954,10 +4954,10 @@
         <v>18.5</v>
       </c>
       <c r="BE17">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF17">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BG17">
         <v>7</v>
@@ -5043,10 +5043,10 @@
         <v>166</v>
       </c>
       <c r="F18">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="G18">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H18">
         <v>9.6</v>
@@ -5058,7 +5058,7 @@
         <v>6.8</v>
       </c>
       <c r="K18">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5067,13 +5067,13 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P18">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q18">
         <v>1.3</v>
@@ -5082,7 +5082,7 @@
         <v>2.16</v>
       </c>
       <c r="S18">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="T18">
         <v>1.62</v>
@@ -5094,7 +5094,7 @@
         <v>1.09</v>
       </c>
       <c r="W18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X18">
         <v>70</v>
@@ -5121,7 +5121,7 @@
         <v>130</v>
       </c>
       <c r="AF18">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG18">
         <v>13</v>
@@ -5151,16 +5151,16 @@
         <v>90</v>
       </c>
       <c r="AP18">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ18">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR18">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS18">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT18">
         <v>14</v>
@@ -5169,10 +5169,10 @@
         <v>14.5</v>
       </c>
       <c r="AV18">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW18">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX18">
         <v>10.5</v>
@@ -5184,25 +5184,25 @@
         <v>18</v>
       </c>
       <c r="BA18">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB18">
         <v>10</v>
       </c>
       <c r="BC18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD18">
         <v>18.5</v>
       </c>
       <c r="BE18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF18">
         <v>2.72</v>
       </c>
       <c r="BG18">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5285,22 +5285,22 @@
         <v>167</v>
       </c>
       <c r="F19">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="G19">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H19">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I19">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="J19">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="K19">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5309,142 +5309,142 @@
         <v>1.02</v>
       </c>
       <c r="N19">
-        <v>6.8</v>
+        <v>2.76</v>
       </c>
       <c r="O19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P19">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="Q19">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R19">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S19">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T19">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U19">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="V19">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="W19">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X19">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Z19">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AC19">
         <v>13</v>
       </c>
       <c r="AD19">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>4.6</v>
+        <v>1.24</v>
       </c>
       <c r="AQ19">
-        <v>14.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR19">
-        <v>18</v>
+        <v>1.18</v>
       </c>
       <c r="AS19">
-        <v>4.5</v>
+        <v>1.24</v>
       </c>
       <c r="AT19">
-        <v>4.4</v>
+        <v>1.19</v>
       </c>
       <c r="AU19">
-        <v>8.800000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="AV19">
-        <v>11</v>
+        <v>1.24</v>
       </c>
       <c r="AW19">
-        <v>4.3</v>
+        <v>1.24</v>
       </c>
       <c r="AX19">
-        <v>20</v>
+        <v>1.24</v>
       </c>
       <c r="AY19">
-        <v>11</v>
+        <v>1.24</v>
       </c>
       <c r="AZ19">
-        <v>11</v>
+        <v>1.24</v>
       </c>
       <c r="BA19">
-        <v>21</v>
+        <v>1.24</v>
       </c>
       <c r="BB19">
-        <v>4.8</v>
+        <v>1.24</v>
       </c>
       <c r="BC19">
-        <v>20</v>
+        <v>1.24</v>
       </c>
       <c r="BD19">
-        <v>21</v>
+        <v>1.24</v>
       </c>
       <c r="BE19">
-        <v>4.8</v>
+        <v>1.24</v>
       </c>
       <c r="BF19">
-        <v>10.5</v>
+        <v>1.24</v>
       </c>
       <c r="BG19">
-        <v>8</v>
+        <v>1.24</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5527,22 +5527,22 @@
         <v>168</v>
       </c>
       <c r="F20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G20">
         <v>1.52</v>
       </c>
       <c r="H20">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K20">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5551,34 +5551,34 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P20">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="Q20">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R20">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="S20">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="T20">
         <v>1.46</v>
       </c>
       <c r="U20">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V20">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W20">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X20">
         <v>65</v>
@@ -5593,7 +5593,7 @@
         <v>160</v>
       </c>
       <c r="AB20">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AC20">
         <v>17</v>
@@ -5629,34 +5629,34 @@
         <v>65</v>
       </c>
       <c r="AN20">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AO20">
         <v>44</v>
       </c>
       <c r="AP20">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ20">
         <v>29</v>
       </c>
       <c r="AR20">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS20">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT20">
         <v>17</v>
       </c>
       <c r="AU20">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AV20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW20">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX20">
         <v>14</v>
@@ -5683,10 +5683,10 @@
         <v>30</v>
       </c>
       <c r="BF20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BG20">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5778,31 +5778,31 @@
         <v>2.52</v>
       </c>
       <c r="I21">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="J21">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="K21">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="L21">
         <v>1.5</v>
       </c>
       <c r="M21">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N21">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O21">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="P21">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="R21">
         <v>1.19</v>
@@ -5811,133 +5811,133 @@
         <v>5.4</v>
       </c>
       <c r="T21">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U21">
         <v>1.8</v>
       </c>
       <c r="V21">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
         <v>1.35</v>
       </c>
       <c r="X21">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y21">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AA21">
         <v>48</v>
       </c>
       <c r="AB21">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC21">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE21">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF21">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AG21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH21">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI21">
         <v>75</v>
       </c>
       <c r="AJ21">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK21">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL21">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM21">
         <v>200</v>
       </c>
       <c r="AN21">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AO21">
         <v>48</v>
       </c>
       <c r="AP21">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ21">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR21">
         <v>11.5</v>
       </c>
       <c r="AS21">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT21">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU21">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AV21">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW21">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="AX21">
         <v>20</v>
       </c>
       <c r="AY21">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ21">
         <v>19</v>
       </c>
       <c r="BA21">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BB21">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BC21">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD21">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BE21">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BF21">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BG21">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH21">
         <v>2.72</v>
       </c>
       <c r="BI21">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="BJ21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK21">
         <v>6.6</v>
@@ -5946,7 +5946,7 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BN21">
         <v>6.4</v>
@@ -5958,13 +5958,13 @@
         <v>34</v>
       </c>
       <c r="BQ21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT21">
         <v>5.3</v>
@@ -5976,19 +5976,19 @@
         <v>23</v>
       </c>
       <c r="BW21">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB21" t="s">
         <v>187</v>
@@ -6011,40 +6011,40 @@
         <v>170</v>
       </c>
       <c r="F22">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G22">
         <v>3.7</v>
       </c>
       <c r="H22">
+        <v>2.42</v>
+      </c>
+      <c r="I22">
+        <v>2.62</v>
+      </c>
+      <c r="J22">
+        <v>3.05</v>
+      </c>
+      <c r="K22">
+        <v>3.15</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.11</v>
+      </c>
+      <c r="N22">
+        <v>2.8</v>
+      </c>
+      <c r="O22">
+        <v>1.43</v>
+      </c>
+      <c r="P22">
+        <v>1.63</v>
+      </c>
+      <c r="Q22">
         <v>2.36</v>
-      </c>
-      <c r="I22">
-        <v>2.66</v>
-      </c>
-      <c r="J22">
-        <v>3</v>
-      </c>
-      <c r="K22">
-        <v>3.9</v>
-      </c>
-      <c r="L22">
-        <v>1.41</v>
-      </c>
-      <c r="M22">
-        <v>1.1</v>
-      </c>
-      <c r="N22">
-        <v>2.74</v>
-      </c>
-      <c r="O22">
-        <v>1.37</v>
-      </c>
-      <c r="P22">
-        <v>1.61</v>
-      </c>
-      <c r="Q22">
-        <v>2.32</v>
       </c>
       <c r="R22">
         <v>1.23</v>
@@ -6053,19 +6053,19 @@
         <v>4.4</v>
       </c>
       <c r="T22">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U22">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="V22">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W22">
         <v>1.37</v>
       </c>
       <c r="X22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -6080,7 +6080,7 @@
         <v>11</v>
       </c>
       <c r="AC22">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD22">
         <v>12.5</v>
@@ -6113,7 +6113,7 @@
         <v>170</v>
       </c>
       <c r="AN22">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO22">
         <v>34</v>
@@ -6128,7 +6128,7 @@
         <v>12.5</v>
       </c>
       <c r="AS22">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="AT22">
         <v>9</v>
@@ -6140,7 +6140,7 @@
         <v>10</v>
       </c>
       <c r="AW22">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX22">
         <v>19</v>
@@ -6152,28 +6152,28 @@
         <v>17</v>
       </c>
       <c r="BA22">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB22">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC22">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="BD22">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE22">
+        <v>7.6</v>
+      </c>
+      <c r="BF22">
         <v>7.2</v>
       </c>
-      <c r="BF22">
-        <v>6.8</v>
-      </c>
       <c r="BG22">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI22">
         <v>1.04</v>
@@ -6182,55 +6182,55 @@
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="CB22" t="s">
         <v>187</v>
@@ -6253,16 +6253,16 @@
         <v>171</v>
       </c>
       <c r="F23">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G23">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H23">
         <v>2.4</v>
       </c>
       <c r="I23">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J23">
         <v>4.3</v>
@@ -6277,10 +6277,10 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="O23">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P23">
         <v>3.7</v>
@@ -6289,22 +6289,22 @@
         <v>1.3</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S23">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="T23">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="U23">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V23">
         <v>1.57</v>
       </c>
       <c r="W23">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X23">
         <v>65</v>
@@ -6343,7 +6343,7 @@
         <v>24</v>
       </c>
       <c r="AJ23">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AK23">
         <v>24</v>
@@ -6355,49 +6355,49 @@
         <v>36</v>
       </c>
       <c r="AN23">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO23">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AP23">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ23">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AR23">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AS23">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="AT23">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV23">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW23">
         <v>19</v>
       </c>
       <c r="AX23">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AY23">
         <v>12</v>
       </c>
       <c r="AZ23">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BA23">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BB23">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="BC23">
         <v>18.5</v>
@@ -6406,7 +6406,7 @@
         <v>19</v>
       </c>
       <c r="BE23">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF23">
         <v>7.2</v>
@@ -6442,16 +6442,16 @@
         <v>19</v>
       </c>
       <c r="BQ23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BR23">
         <v>23</v>
       </c>
       <c r="BS23">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BT23">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU23">
         <v>5.2</v>
@@ -6460,13 +6460,13 @@
         <v>19.5</v>
       </c>
       <c r="BW23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BX23">
         <v>23</v>
       </c>
       <c r="BY23">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BZ23">
         <v>11.5</v>
@@ -6495,34 +6495,34 @@
         <v>172</v>
       </c>
       <c r="F24">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="G24">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="H24">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="I24">
-        <v>23</v>
+        <v>990</v>
       </c>
       <c r="J24">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="K24">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L24">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M24">
         <v>1.02</v>
       </c>
       <c r="N24">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O24">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="P24">
         <v>2.06</v>
@@ -6537,16 +6537,16 @@
         <v>2.96</v>
       </c>
       <c r="T24">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="U24">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V24">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W24">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6561,10 +6561,10 @@
         <v>1000</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
         <v>1000</v>
@@ -6603,28 +6603,28 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="AQ24">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="AR24">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="AS24">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="AT24">
         <v>5.5</v>
       </c>
       <c r="AU24">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AV24">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="AW24">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="AX24">
         <v>5.1</v>
@@ -6633,28 +6633,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ24">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="BA24">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="BB24">
         <v>6.6</v>
       </c>
       <c r="BC24">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="BD24">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="BE24">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="BF24">
         <v>4.1</v>
       </c>
       <c r="BG24">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6740,7 +6740,7 @@
         <v>2.62</v>
       </c>
       <c r="G25">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H25">
         <v>3.05</v>
@@ -6749,7 +6749,7 @@
         <v>3.55</v>
       </c>
       <c r="J25">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K25">
         <v>3.2</v>
@@ -6758,25 +6758,25 @@
         <v>1.58</v>
       </c>
       <c r="M25">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N25">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="O25">
         <v>1.56</v>
       </c>
       <c r="P25">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Q25">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R25">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S25">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="T25">
         <v>2.08</v>
@@ -6797,16 +6797,16 @@
         <v>9.4</v>
       </c>
       <c r="Z25">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA25">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB25">
         <v>8.199999999999999</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD25">
         <v>16</v>
@@ -6815,7 +6815,7 @@
         <v>60</v>
       </c>
       <c r="AF25">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG25">
         <v>14</v>
@@ -6824,7 +6824,7 @@
         <v>24</v>
       </c>
       <c r="AI25">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ25">
         <v>60</v>
@@ -6842,7 +6842,7 @@
         <v>60</v>
       </c>
       <c r="AO25">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP25">
         <v>6.4</v>
@@ -6851,52 +6851,52 @@
         <v>7</v>
       </c>
       <c r="AR25">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS25">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT25">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU25">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV25">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW25">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX25">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ25">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA25">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB25">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC25">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD25">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE25">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF25">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG25">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH25">
         <v>2.9</v>
@@ -6988,7 +6988,7 @@
         <v>4.5</v>
       </c>
       <c r="I26">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J26">
         <v>2.84</v>
@@ -7018,7 +7018,7 @@
         <v>1.14</v>
       </c>
       <c r="S26">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T26">
         <v>2.34</v>
@@ -7027,7 +7027,7 @@
         <v>1.54</v>
       </c>
       <c r="V26">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W26">
         <v>1.78</v>
@@ -7039,10 +7039,10 @@
         <v>12</v>
       </c>
       <c r="Z26">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA26">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB26">
         <v>6.4</v>
@@ -7054,7 +7054,7 @@
         <v>24</v>
       </c>
       <c r="AE26">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF26">
         <v>12</v>
@@ -7066,7 +7066,7 @@
         <v>32</v>
       </c>
       <c r="AI26">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ26">
         <v>32</v>
@@ -7096,7 +7096,7 @@
         <v>6.4</v>
       </c>
       <c r="AS26">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT26">
         <v>5.2</v>
@@ -7108,7 +7108,7 @@
         <v>19</v>
       </c>
       <c r="AW26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX26">
         <v>9.6</v>
@@ -7120,7 +7120,7 @@
         <v>6.2</v>
       </c>
       <c r="BA26">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB26">
         <v>19</v>
@@ -7129,16 +7129,16 @@
         <v>23</v>
       </c>
       <c r="BD26">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF26">
         <v>24</v>
       </c>
       <c r="BG26">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH26">
         <v>2.74</v>
@@ -7224,10 +7224,10 @@
         <v>4.4</v>
       </c>
       <c r="G27">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H27">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I27">
         <v>2.26</v>
@@ -7245,19 +7245,19 @@
         <v>1.14</v>
       </c>
       <c r="N27">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O27">
         <v>1.6</v>
       </c>
       <c r="P27">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q27">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R27">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S27">
         <v>6</v>
@@ -7266,7 +7266,7 @@
         <v>2.28</v>
       </c>
       <c r="U27">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V27">
         <v>1.8</v>
@@ -7290,7 +7290,7 @@
         <v>14</v>
       </c>
       <c r="AC27">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD27">
         <v>14.5</v>
@@ -7308,22 +7308,22 @@
         <v>34</v>
       </c>
       <c r="AI27">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ27">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AK27">
         <v>120</v>
       </c>
       <c r="AL27">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM27">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN27">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AO27">
         <v>40</v>
@@ -7332,55 +7332,55 @@
         <v>5.8</v>
       </c>
       <c r="AQ27">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS27">
+        <v>21</v>
+      </c>
+      <c r="AT27">
         <v>9.6</v>
       </c>
-      <c r="AS27">
-        <v>20</v>
-      </c>
-      <c r="AT27">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AU27">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV27">
         <v>10</v>
       </c>
       <c r="AW27">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX27">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY27">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AZ27">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB27">
+        <v>5.5</v>
+      </c>
+      <c r="BC27">
         <v>5.4</v>
       </c>
-      <c r="BC27">
-        <v>5.3</v>
-      </c>
       <c r="BD27">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE27">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF27">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG27">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7463,10 +7463,10 @@
         <v>176</v>
       </c>
       <c r="F28">
-        <v>1.28</v>
+        <v>1.76</v>
       </c>
       <c r="G28">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="H28">
         <v>1.1</v>
@@ -7475,7 +7475,7 @@
         <v>990</v>
       </c>
       <c r="J28">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="K28">
         <v>950</v>
@@ -7487,19 +7487,19 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="O28">
         <v>1.27</v>
       </c>
       <c r="P28">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="Q28">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R28">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S28">
         <v>1.28</v>
@@ -7514,7 +7514,7 @@
         <v>1.01</v>
       </c>
       <c r="W28">
-        <v>1.47</v>
+        <v>2.12</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7723,7 +7723,7 @@
         <v>3.85</v>
       </c>
       <c r="L29">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M29">
         <v>1.04</v>
@@ -7801,7 +7801,7 @@
         <v>24</v>
       </c>
       <c r="AL29">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM29">
         <v>60</v>
@@ -7810,7 +7810,7 @@
         <v>14</v>
       </c>
       <c r="AO29">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AP29">
         <v>20</v>
@@ -7876,7 +7876,7 @@
         <v>10.5</v>
       </c>
       <c r="BK29">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BL29">
         <v>90</v>
@@ -7888,19 +7888,19 @@
         <v>7</v>
       </c>
       <c r="BO29">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP29">
         <v>20</v>
       </c>
       <c r="BQ29">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BR29">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS29">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BT29">
         <v>7.6</v>
@@ -7912,7 +7912,7 @@
         <v>24</v>
       </c>
       <c r="BW29">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BX29">
         <v>32</v>
@@ -7924,7 +7924,7 @@
         <v>20</v>
       </c>
       <c r="CA29">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="CB29" t="s">
         <v>187</v>
@@ -7947,19 +7947,19 @@
         <v>178</v>
       </c>
       <c r="F30">
+        <v>1.97</v>
+      </c>
+      <c r="G30">
         <v>1.99</v>
       </c>
-      <c r="G30">
-        <v>2</v>
-      </c>
       <c r="H30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I30">
         <v>4.3</v>
       </c>
       <c r="J30">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K30">
         <v>3.9</v>
@@ -7971,16 +7971,16 @@
         <v>1.06</v>
       </c>
       <c r="N30">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O30">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P30">
         <v>2.12</v>
       </c>
       <c r="Q30">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R30">
         <v>1.44</v>
@@ -7989,7 +7989,7 @@
         <v>3.1</v>
       </c>
       <c r="T30">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U30">
         <v>2.26</v>
@@ -8004,10 +8004,10 @@
         <v>16</v>
       </c>
       <c r="Y30">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z30">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA30">
         <v>85</v>
@@ -8019,7 +8019,7 @@
         <v>8.6</v>
       </c>
       <c r="AD30">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE30">
         <v>55</v>
@@ -8040,16 +8040,16 @@
         <v>23</v>
       </c>
       <c r="AK30">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL30">
         <v>34</v>
       </c>
       <c r="AM30">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO30">
         <v>55</v>
@@ -8079,10 +8079,10 @@
         <v>40</v>
       </c>
       <c r="AX30">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ30">
         <v>16</v>
@@ -8103,10 +8103,10 @@
         <v>36</v>
       </c>
       <c r="BF30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG30">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH30">
         <v>4.1</v>
@@ -8118,10 +8118,10 @@
         <v>11</v>
       </c>
       <c r="BK30">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BL30">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM30">
         <v>5.4</v>
@@ -8136,13 +8136,13 @@
         <v>16</v>
       </c>
       <c r="BQ30">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR30">
         <v>30</v>
       </c>
       <c r="BS30">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BT30">
         <v>8.6</v>
@@ -8154,19 +8154,19 @@
         <v>38</v>
       </c>
       <c r="BW30">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BX30">
         <v>46</v>
       </c>
       <c r="BY30">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ30">
         <v>25</v>
       </c>
       <c r="CA30">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB30" t="s">
         <v>187</v>
@@ -8192,7 +8192,7 @@
         <v>1.54</v>
       </c>
       <c r="G31">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H31">
         <v>7.4</v>
@@ -8201,7 +8201,7 @@
         <v>8.6</v>
       </c>
       <c r="J31">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K31">
         <v>4.5</v>
@@ -8228,13 +8228,13 @@
         <v>1.31</v>
       </c>
       <c r="S31">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T31">
         <v>2.26</v>
       </c>
       <c r="U31">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V31">
         <v>1.13</v>
@@ -8246,16 +8246,16 @@
         <v>13</v>
       </c>
       <c r="Y31">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z31">
         <v>70</v>
       </c>
       <c r="AA31">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AB31">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC31">
         <v>9.800000000000001</v>
@@ -8288,13 +8288,13 @@
         <v>190</v>
       </c>
       <c r="AM31">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN31">
         <v>10</v>
       </c>
       <c r="AO31">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="AP31">
         <v>11.5</v>
@@ -8306,7 +8306,7 @@
         <v>55</v>
       </c>
       <c r="AS31">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AT31">
         <v>6.6</v>
@@ -8318,7 +8318,7 @@
         <v>27</v>
       </c>
       <c r="AW31">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AX31">
         <v>7</v>
@@ -8330,7 +8330,7 @@
         <v>26</v>
       </c>
       <c r="BA31">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BB31">
         <v>12</v>
@@ -8342,13 +8342,13 @@
         <v>42</v>
       </c>
       <c r="BE31">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BF31">
         <v>9</v>
       </c>
       <c r="BG31">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8431,19 +8431,19 @@
         <v>180</v>
       </c>
       <c r="F32">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="G32">
         <v>990</v>
       </c>
       <c r="H32">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="I32">
         <v>990</v>
       </c>
       <c r="J32">
-        <v>1.08</v>
+        <v>2.04</v>
       </c>
       <c r="K32">
         <v>950</v>
@@ -8455,13 +8455,13 @@
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>4.3</v>
+        <v>1.25</v>
       </c>
       <c r="O32">
         <v>1.15</v>
       </c>
       <c r="P32">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Q32">
         <v>1.15</v>
@@ -8470,7 +8470,7 @@
         <v>1.18</v>
       </c>
       <c r="S32">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T32">
         <v>1.11</v>
@@ -8679,25 +8679,25 @@
         <v>1.35</v>
       </c>
       <c r="H33">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>10.5</v>
       </c>
       <c r="J33">
+        <v>6.2</v>
+      </c>
+      <c r="K33">
         <v>6.4</v>
       </c>
-      <c r="K33">
-        <v>6.6</v>
-      </c>
       <c r="L33">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M33">
         <v>1.03</v>
       </c>
       <c r="N33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>1.16</v>
@@ -8706,13 +8706,13 @@
         <v>3</v>
       </c>
       <c r="Q33">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R33">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="S33">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T33">
         <v>1.78</v>
@@ -8721,7 +8721,7 @@
         <v>2.2</v>
       </c>
       <c r="V33">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W33">
         <v>3.85</v>
@@ -8733,10 +8733,10 @@
         <v>42</v>
       </c>
       <c r="Z33">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AA33">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="AB33">
         <v>12.5</v>
@@ -8754,7 +8754,7 @@
         <v>10</v>
       </c>
       <c r="AG33">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH33">
         <v>24</v>
@@ -8775,7 +8775,7 @@
         <v>110</v>
       </c>
       <c r="AN33">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO33">
         <v>110</v>
@@ -8784,13 +8784,13 @@
         <v>32</v>
       </c>
       <c r="AQ33">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AR33">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AS33">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT33">
         <v>11.5</v>
@@ -8820,22 +8820,22 @@
         <v>11</v>
       </c>
       <c r="BC33">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD33">
         <v>25</v>
       </c>
       <c r="BE33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF33">
         <v>4.1</v>
       </c>
       <c r="BG33">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="BH33">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI33">
         <v>4.4</v>
@@ -8859,7 +8859,7 @@
         <v>3.9</v>
       </c>
       <c r="BP33">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BQ33">
         <v>6.6</v>
@@ -8874,7 +8874,7 @@
         <v>13.5</v>
       </c>
       <c r="BU33">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV33">
         <v>70</v>
@@ -8930,7 +8930,7 @@
         <v>3.35</v>
       </c>
       <c r="K34">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L34">
         <v>1.34</v>
@@ -8951,7 +8951,7 @@
         <v>2.18</v>
       </c>
       <c r="R34">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S34">
         <v>3.9</v>
@@ -8972,7 +8972,7 @@
         <v>12.5</v>
       </c>
       <c r="Y34">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z34">
         <v>21</v>
@@ -8984,7 +8984,7 @@
         <v>10</v>
       </c>
       <c r="AC34">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD34">
         <v>14</v>
@@ -9032,7 +9032,7 @@
         <v>18.5</v>
       </c>
       <c r="AS34">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT34">
         <v>9</v>
@@ -9056,7 +9056,7 @@
         <v>16.5</v>
       </c>
       <c r="BA34">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB34">
         <v>32</v>
@@ -9160,13 +9160,13 @@
         <v>2.82</v>
       </c>
       <c r="G35">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H35">
         <v>2.8</v>
       </c>
       <c r="I35">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J35">
         <v>2.94</v>
@@ -9178,13 +9178,13 @@
         <v>1.48</v>
       </c>
       <c r="M35">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N35">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O35">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P35">
         <v>1.56</v>
@@ -9202,25 +9202,25 @@
         <v>2</v>
       </c>
       <c r="U35">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V35">
         <v>1.5</v>
       </c>
       <c r="W35">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X35">
         <v>9.4</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z35">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA35">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB35">
         <v>9.199999999999999</v>
@@ -9232,7 +9232,7 @@
         <v>14</v>
       </c>
       <c r="AE35">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF35">
         <v>19</v>
@@ -9244,13 +9244,13 @@
         <v>25</v>
       </c>
       <c r="AI35">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ35">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK35">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL35">
         <v>80</v>
@@ -9268,16 +9268,16 @@
         <v>8</v>
       </c>
       <c r="AQ35">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR35">
         <v>15.5</v>
       </c>
       <c r="AS35">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="AT35">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU35">
         <v>6.2</v>
@@ -9289,37 +9289,37 @@
         <v>29</v>
       </c>
       <c r="AX35">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY35">
         <v>11.5</v>
       </c>
       <c r="AZ35">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB35">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BC35">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BD35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BE35">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BF35">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BG35">
         <v>34</v>
       </c>
       <c r="BH35">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI35">
         <v>2.34</v>
@@ -9328,34 +9328,34 @@
         <v>11</v>
       </c>
       <c r="BK35">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN35">
         <v>5.9</v>
       </c>
       <c r="BO35">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP35">
         <v>27</v>
       </c>
       <c r="BQ35">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT35">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU35">
         <v>4.5</v>
@@ -9364,19 +9364,19 @@
         <v>27</v>
       </c>
       <c r="BW35">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB35" t="s">
         <v>187</v>
@@ -9399,46 +9399,46 @@
         <v>184</v>
       </c>
       <c r="F36">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G36">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="H36">
+        <v>3.25</v>
+      </c>
+      <c r="I36">
+        <v>3.95</v>
+      </c>
+      <c r="J36">
         <v>3.3</v>
       </c>
-      <c r="I36">
-        <v>3.9</v>
-      </c>
-      <c r="J36">
-        <v>3.35</v>
-      </c>
       <c r="K36">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L36">
         <v>1.33</v>
       </c>
       <c r="M36">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N36">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O36">
         <v>1.3</v>
       </c>
       <c r="P36">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R36">
         <v>1.31</v>
       </c>
       <c r="S36">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="T36">
         <v>1.71</v>
@@ -9447,10 +9447,10 @@
         <v>2</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W36">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9665,13 +9665,13 @@
         <v>1.02</v>
       </c>
       <c r="N37">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="O37">
         <v>1.12</v>
       </c>
       <c r="P37">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q37">
         <v>1.12</v>
@@ -9883,10 +9883,10 @@
         <v>186</v>
       </c>
       <c r="F38">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G38">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H38">
         <v>4.4</v>
@@ -9898,10 +9898,10 @@
         <v>3.3</v>
       </c>
       <c r="K38">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L38">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M38">
         <v>1.09</v>
@@ -9910,7 +9910,7 @@
         <v>3.05</v>
       </c>
       <c r="O38">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P38">
         <v>1.71</v>
@@ -9934,7 +9934,7 @@
         <v>1.25</v>
       </c>
       <c r="W38">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="X38">
         <v>11.5</v>
@@ -9943,13 +9943,13 @@
         <v>950</v>
       </c>
       <c r="Z38">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA38">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB38">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC38">
         <v>8</v>
@@ -9973,7 +9973,7 @@
         <v>100</v>
       </c>
       <c r="AJ38">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK38">
         <v>24</v>
@@ -10000,7 +10000,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS38">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT38">
         <v>6.8</v>
@@ -10054,13 +10054,13 @@
         <v>11</v>
       </c>
       <c r="BK38">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="BN38">
         <v>4.5</v>
@@ -10081,28 +10081,28 @@
         <v>11</v>
       </c>
       <c r="BT38">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU38">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB38" t="s">
         <v>187</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -577,7 +577,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-25 15:31:23</t>
+    <t>2026-08-25 17:41:34</t>
   </si>
 </sst>
 </file>
@@ -1171,22 +1171,22 @@
         <v>150</v>
       </c>
       <c r="F2">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="G2">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
         <v>1.45</v>
@@ -1195,94 +1195,94 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R2">
         <v>1.32</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T2">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W2">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="X2">
         <v>13</v>
       </c>
       <c r="Y2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA2">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AB2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE2">
         <v>140</v>
       </c>
       <c r="AF2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI2">
         <v>140</v>
       </c>
       <c r="AJ2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AM2">
         <v>200</v>
       </c>
       <c r="AN2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO2">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AP2">
         <v>12</v>
       </c>
       <c r="AQ2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR2">
         <v>50</v>
@@ -1291,67 +1291,67 @@
         <v>18.5</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2">
-        <v>17.5</v>
+        <v>95</v>
       </c>
       <c r="AX2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY2">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA2">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="BB2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE2">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="BF2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG2">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="BH2">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BI2">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO2">
         <v>3.5</v>
@@ -1363,10 +1363,10 @@
         <v>8</v>
       </c>
       <c r="BR2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>11</v>
@@ -1378,19 +1378,19 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>187</v>
@@ -1413,70 +1413,70 @@
         <v>151</v>
       </c>
       <c r="F3">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="G3">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="H3">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M3">
         <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O3">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P3">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="Q3">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T3">
         <v>2.08</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="X3">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB3">
         <v>7.6</v>
@@ -1485,28 +1485,28 @@
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH3">
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
+        <v>36</v>
+      </c>
+      <c r="AK3">
         <v>32</v>
-      </c>
-      <c r="AK3">
-        <v>29</v>
       </c>
       <c r="AL3">
         <v>60</v>
@@ -1515,37 +1515,37 @@
         <v>170</v>
       </c>
       <c r="AN3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AO3">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS3">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW3">
         <v>50</v>
       </c>
       <c r="AX3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
@@ -1557,82 +1557,82 @@
         <v>65</v>
       </c>
       <c r="BB3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BD3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE3">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="BF3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BG3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BH3">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BI3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
         <v>5</v>
       </c>
       <c r="BO3">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BQ3">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU3">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BW3">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BX3">
         <v>60</v>
       </c>
       <c r="BY3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
         <v>44</v>
       </c>
       <c r="CA3">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>187</v>
@@ -1655,22 +1655,22 @@
         <v>152</v>
       </c>
       <c r="F4">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="G4">
-        <v>1.45</v>
+        <v>600</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="I4">
-        <v>15.5</v>
+        <v>870</v>
       </c>
       <c r="J4">
         <v>1.1</v>
       </c>
       <c r="K4">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1679,22 +1679,22 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="O4">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="P4">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1703,10 +1703,10 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1721,7 +1721,7 @@
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
         <v>1000</v>
@@ -1733,7 +1733,7 @@
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
         <v>1000</v>
@@ -1763,58 +1763,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AQ4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AR4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AS4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AT4">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AV4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AW4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AX4">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AY4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AZ4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BA4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BB4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BC4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BD4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BE4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BF4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1903,10 +1903,10 @@
         <v>3.6</v>
       </c>
       <c r="H5">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I5">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J5">
         <v>3.3</v>
@@ -1924,16 +1924,16 @@
         <v>3.25</v>
       </c>
       <c r="O5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P5">
         <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
         <v>4.3</v>
@@ -1942,13 +1942,13 @@
         <v>1.92</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X5">
         <v>11.5</v>
@@ -1960,7 +1960,7 @@
         <v>14.5</v>
       </c>
       <c r="AA5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB5">
         <v>11.5</v>
@@ -1987,7 +1987,7 @@
         <v>70</v>
       </c>
       <c r="AJ5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK5">
         <v>60</v>
@@ -1999,7 +1999,7 @@
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO5">
         <v>26</v>
@@ -2017,25 +2017,25 @@
         <v>23</v>
       </c>
       <c r="AT5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX5">
         <v>20</v>
       </c>
       <c r="AY5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
         <v>32</v>
@@ -2065,7 +2065,7 @@
         <v>2.46</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BK5">
         <v>8</v>
@@ -2074,49 +2074,49 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BN5">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BQ5">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BR5">
         <v>60</v>
       </c>
       <c r="BS5">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="BT5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BU5">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BV5">
         <v>25</v>
       </c>
       <c r="BW5">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="BX5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY5">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5">
         <v>44</v>
       </c>
       <c r="CA5">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="CB5" t="s">
         <v>187</v>
@@ -2145,7 +2145,7 @@
         <v>2.42</v>
       </c>
       <c r="H6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I6">
         <v>3.25</v>
@@ -2157,7 +2157,7 @@
         <v>3.85</v>
       </c>
       <c r="L6">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="M6">
         <v>1.05</v>
@@ -2166,34 +2166,34 @@
         <v>4.5</v>
       </c>
       <c r="O6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P6">
         <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S6">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="T6">
         <v>1.64</v>
       </c>
       <c r="U6">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W6">
         <v>1.7</v>
       </c>
       <c r="X6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y6">
         <v>15</v>
@@ -2211,7 +2211,7 @@
         <v>8.6</v>
       </c>
       <c r="AD6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE6">
         <v>60</v>
@@ -2232,10 +2232,10 @@
         <v>55</v>
       </c>
       <c r="AK6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM6">
         <v>1000</v>
@@ -2250,7 +2250,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR6">
         <v>20</v>
@@ -2396,10 +2396,10 @@
         <v>4.1</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M7">
         <v>1.08</v>
@@ -2411,22 +2411,22 @@
         <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T7">
         <v>2.22</v>
       </c>
       <c r="U7">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V7">
         <v>1.14</v>
@@ -2444,13 +2444,13 @@
         <v>80</v>
       </c>
       <c r="AA7">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD7">
         <v>32</v>
@@ -2498,7 +2498,7 @@
         <v>34</v>
       </c>
       <c r="AS7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
@@ -2507,10 +2507,10 @@
         <v>8.4</v>
       </c>
       <c r="AV7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AW7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX7">
         <v>7.4</v>
@@ -2519,10 +2519,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BB7">
         <v>12.5</v>
@@ -2534,13 +2534,13 @@
         <v>27</v>
       </c>
       <c r="BE7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF7">
         <v>9.199999999999999</v>
       </c>
       <c r="BG7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2623,19 +2623,19 @@
         <v>156</v>
       </c>
       <c r="F8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G8">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2674,7 +2674,7 @@
         <v>1.01</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2874,7 +2874,7 @@
         <v>1.45</v>
       </c>
       <c r="I9">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="J9">
         <v>1.77</v>
@@ -2889,22 +2889,22 @@
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>3.85</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P9">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R9">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2913,10 +2913,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2973,55 +2973,55 @@
         <v>25</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG9">
         <v>1.01</v>
@@ -3110,37 +3110,37 @@
         <v>1.56</v>
       </c>
       <c r="G10">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="L10">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M10">
         <v>1.1</v>
       </c>
       <c r="N10">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O10">
-        <v>1.56</v>
+        <v>1.1</v>
       </c>
       <c r="P10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q10">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R10">
         <v>1.13</v>
@@ -3158,7 +3158,7 @@
         <v>1.11</v>
       </c>
       <c r="W10">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3215,58 +3215,58 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AQ10">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AR10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AS10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AT10">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AU10">
         <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AW10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AX10">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AY10">
         <v>8.6</v>
       </c>
       <c r="AZ10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BA10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BB10">
         <v>9.4</v>
       </c>
       <c r="BC10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BD10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BE10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BF10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BG10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3349,166 +3349,166 @@
         <v>159</v>
       </c>
       <c r="F11">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="G11">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="H11">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="I11">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="J11">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K11">
+        <v>4</v>
+      </c>
+      <c r="L11">
+        <v>1.28</v>
+      </c>
+      <c r="M11">
+        <v>1.06</v>
+      </c>
+      <c r="N11">
         <v>4.1</v>
       </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>4</v>
-      </c>
       <c r="O11">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="P11">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q11">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="R11">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S11">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V11">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="W11">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z11">
         <v>16.5</v>
       </c>
       <c r="AA11">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AB11">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG11">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO11">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AP11">
-        <v>1.36</v>
+        <v>13</v>
       </c>
       <c r="AQ11">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11">
-        <v>1.26</v>
+        <v>12</v>
       </c>
       <c r="AS11">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="AT11">
-        <v>1.27</v>
+        <v>11</v>
       </c>
       <c r="AU11">
         <v>6.6</v>
       </c>
       <c r="AV11">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AX11">
-        <v>1.36</v>
+        <v>18.5</v>
       </c>
       <c r="AY11">
-        <v>1.27</v>
+        <v>11</v>
       </c>
       <c r="AZ11">
-        <v>1.36</v>
+        <v>12.5</v>
       </c>
       <c r="BA11">
-        <v>1.36</v>
+        <v>6.2</v>
       </c>
       <c r="BB11">
-        <v>1.36</v>
+        <v>6.6</v>
       </c>
       <c r="BC11">
-        <v>1.36</v>
+        <v>6.2</v>
       </c>
       <c r="BD11">
-        <v>1.36</v>
+        <v>6.4</v>
       </c>
       <c r="BE11">
-        <v>1.36</v>
+        <v>6.8</v>
       </c>
       <c r="BF11">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="BG11">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3597,40 +3597,40 @@
         <v>990</v>
       </c>
       <c r="H12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J12">
         <v>1.1</v>
       </c>
       <c r="K12">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M12">
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O12">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P12">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Q12">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S12">
-        <v>1.13</v>
+        <v>2.5</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3639,7 +3639,7 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="W12">
         <v>1.02</v>
@@ -3833,172 +3833,172 @@
         <v>161</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="G13">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="H13">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="I13">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="J13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L13">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O13">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P13">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q13">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S13">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T13">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U13">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="X13">
         <v>32</v>
       </c>
       <c r="Y13">
+        <v>25</v>
+      </c>
+      <c r="Z13">
+        <v>38</v>
+      </c>
+      <c r="AA13">
+        <v>75</v>
+      </c>
+      <c r="AB13">
+        <v>16.5</v>
+      </c>
+      <c r="AC13">
+        <v>10.5</v>
+      </c>
+      <c r="AD13">
+        <v>18.5</v>
+      </c>
+      <c r="AE13">
+        <v>44</v>
+      </c>
+      <c r="AF13">
+        <v>16.5</v>
+      </c>
+      <c r="AG13">
+        <v>11</v>
+      </c>
+      <c r="AH13">
+        <v>17</v>
+      </c>
+      <c r="AI13">
+        <v>44</v>
+      </c>
+      <c r="AJ13">
         <v>24</v>
       </c>
-      <c r="Z13">
-        <v>32</v>
-      </c>
-      <c r="AA13">
-        <v>70</v>
-      </c>
-      <c r="AB13">
-        <v>15.5</v>
-      </c>
-      <c r="AC13">
-        <v>11</v>
-      </c>
-      <c r="AD13">
-        <v>16</v>
-      </c>
-      <c r="AE13">
-        <v>40</v>
-      </c>
-      <c r="AF13">
-        <v>18</v>
-      </c>
-      <c r="AG13">
-        <v>13</v>
-      </c>
-      <c r="AH13">
-        <v>15.5</v>
-      </c>
-      <c r="AI13">
-        <v>40</v>
-      </c>
-      <c r="AJ13">
-        <v>27</v>
-      </c>
       <c r="AK13">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AL13">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AM13">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN13">
         <v>9</v>
       </c>
       <c r="AO13">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AP13">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AQ13">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR13">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="AS13">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="AT13">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13">
+        <v>12</v>
+      </c>
+      <c r="AW13">
+        <v>6.2</v>
+      </c>
+      <c r="AX13">
+        <v>14</v>
+      </c>
+      <c r="AY13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ13">
         <v>13.5</v>
       </c>
-      <c r="AW13">
-        <v>29</v>
-      </c>
-      <c r="AX13">
-        <v>14.5</v>
-      </c>
-      <c r="AY13">
-        <v>10</v>
-      </c>
-      <c r="AZ13">
+      <c r="BA13">
+        <v>6.2</v>
+      </c>
+      <c r="BB13">
+        <v>16</v>
+      </c>
+      <c r="BC13">
         <v>12</v>
       </c>
-      <c r="BA13">
-        <v>7.8</v>
-      </c>
-      <c r="BB13">
-        <v>20</v>
-      </c>
-      <c r="BC13">
-        <v>14</v>
-      </c>
       <c r="BD13">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BE13">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF13">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH13">
         <v>5.1</v>
       </c>
       <c r="BI13">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BJ13">
         <v>9.800000000000001</v>
@@ -4013,16 +4013,16 @@
         <v>5.4</v>
       </c>
       <c r="BN13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO13">
         <v>4.3</v>
       </c>
       <c r="BP13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BR13">
         <v>24</v>
@@ -4031,16 +4031,16 @@
         <v>4.7</v>
       </c>
       <c r="BT13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU13">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BW13">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BX13">
         <v>34</v>
@@ -4114,10 +4114,10 @@
         <v>1.41</v>
       </c>
       <c r="S14">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T14">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U14">
         <v>2.28</v>
@@ -4132,13 +4132,13 @@
         <v>20</v>
       </c>
       <c r="Y14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z14">
         <v>21</v>
       </c>
       <c r="AA14">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB14">
         <v>12.5</v>
@@ -4159,7 +4159,7 @@
         <v>12.5</v>
       </c>
       <c r="AH14">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI14">
         <v>40</v>
@@ -4192,7 +4192,7 @@
         <v>17</v>
       </c>
       <c r="AS14">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT14">
         <v>10.5</v>
@@ -4204,10 +4204,10 @@
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX14">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY14">
         <v>10</v>
@@ -4216,22 +4216,22 @@
         <v>14</v>
       </c>
       <c r="BA14">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC14">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD14">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE14">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG14">
         <v>19.5</v>
@@ -4317,25 +4317,25 @@
         <v>163</v>
       </c>
       <c r="F15">
+        <v>2.86</v>
+      </c>
+      <c r="G15">
+        <v>4.4</v>
+      </c>
+      <c r="H15">
+        <v>2.04</v>
+      </c>
+      <c r="I15">
+        <v>2.46</v>
+      </c>
+      <c r="J15">
         <v>3</v>
       </c>
-      <c r="G15">
-        <v>4.1</v>
-      </c>
-      <c r="H15">
-        <v>2.16</v>
-      </c>
-      <c r="I15">
-        <v>2.52</v>
-      </c>
-      <c r="J15">
-        <v>3.05</v>
-      </c>
       <c r="K15">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="L15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M15">
         <v>1.01</v>
@@ -4350,10 +4350,10 @@
         <v>1.93</v>
       </c>
       <c r="Q15">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="R15">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S15">
         <v>2.84</v>
@@ -4365,10 +4365,10 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W15">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X15">
         <v>19</v>
@@ -4476,7 +4476,7 @@
         <v>2.9</v>
       </c>
       <c r="BG15">
-        <v>2.76</v>
+        <v>13</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4559,7 +4559,7 @@
         <v>164</v>
       </c>
       <c r="F16">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G16">
         <v>1.61</v>
@@ -4568,13 +4568,13 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J16">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K16">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4586,7 +4586,7 @@
         <v>10.5</v>
       </c>
       <c r="O16">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P16">
         <v>4.1</v>
@@ -4607,13 +4607,13 @@
         <v>3</v>
       </c>
       <c r="V16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W16">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="X16">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y16">
         <v>55</v>
@@ -4631,7 +4631,7 @@
         <v>17.5</v>
       </c>
       <c r="AD16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE16">
         <v>60</v>
@@ -4643,7 +4643,7 @@
         <v>12.5</v>
       </c>
       <c r="AH16">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI16">
         <v>48</v>
@@ -4661,22 +4661,22 @@
         <v>55</v>
       </c>
       <c r="AN16">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AO16">
         <v>26</v>
       </c>
       <c r="AP16">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ16">
         <v>30</v>
       </c>
       <c r="AR16">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS16">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT16">
         <v>19</v>
@@ -4801,13 +4801,13 @@
         <v>165</v>
       </c>
       <c r="F17">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G17">
         <v>2.9</v>
       </c>
       <c r="H17">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I17">
         <v>2.44</v>
@@ -4816,7 +4816,7 @@
         <v>4.3</v>
       </c>
       <c r="K17">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4825,28 +4825,28 @@
         <v>1.02</v>
       </c>
       <c r="N17">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>1.1</v>
       </c>
       <c r="P17">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q17">
         <v>1.34</v>
       </c>
       <c r="R17">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S17">
         <v>1.81</v>
       </c>
       <c r="T17">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="U17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V17">
         <v>1.69</v>
@@ -4858,10 +4858,10 @@
         <v>50</v>
       </c>
       <c r="Y17">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z17">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA17">
         <v>38</v>
@@ -4870,13 +4870,13 @@
         <v>28</v>
       </c>
       <c r="AC17">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD17">
         <v>14.5</v>
       </c>
       <c r="AE17">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF17">
         <v>32</v>
@@ -4885,7 +4885,7 @@
         <v>15.5</v>
       </c>
       <c r="AH17">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AI17">
         <v>26</v>
@@ -4897,19 +4897,19 @@
         <v>26</v>
       </c>
       <c r="AL17">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AM17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO17">
         <v>8.6</v>
       </c>
       <c r="AP17">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ17">
         <v>20</v>
@@ -4921,10 +4921,10 @@
         <v>26</v>
       </c>
       <c r="AT17">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AU17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV17">
         <v>10.5</v>
@@ -4942,7 +4942,7 @@
         <v>10.5</v>
       </c>
       <c r="BA17">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BB17">
         <v>32</v>
@@ -4951,10 +4951,10 @@
         <v>20</v>
       </c>
       <c r="BD17">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BE17">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF17">
         <v>7.8</v>
@@ -5067,25 +5067,25 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P18">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="Q18">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="R18">
         <v>2.16</v>
       </c>
       <c r="S18">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="T18">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U18">
         <v>2.38</v>
@@ -5285,22 +5285,22 @@
         <v>167</v>
       </c>
       <c r="F19">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="G19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H19">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I19">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="J19">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K19">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5309,142 +5309,142 @@
         <v>1.02</v>
       </c>
       <c r="N19">
-        <v>2.76</v>
+        <v>4.8</v>
       </c>
       <c r="O19">
         <v>1.13</v>
       </c>
       <c r="P19">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="Q19">
         <v>1.43</v>
       </c>
       <c r="R19">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S19">
         <v>2.04</v>
       </c>
       <c r="T19">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U19">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="V19">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="W19">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y19">
+        <v>970</v>
+      </c>
+      <c r="Z19">
+        <v>21</v>
+      </c>
+      <c r="AA19">
+        <v>30</v>
+      </c>
+      <c r="AB19">
         <v>26</v>
-      </c>
-      <c r="Z19">
-        <v>26</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>950</v>
       </c>
       <c r="AC19">
         <v>13</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AP19">
-        <v>1.24</v>
+        <v>6.2</v>
       </c>
       <c r="AQ19">
-        <v>1.18</v>
+        <v>5.4</v>
       </c>
       <c r="AR19">
-        <v>1.18</v>
+        <v>15.5</v>
       </c>
       <c r="AS19">
-        <v>1.24</v>
+        <v>6</v>
       </c>
       <c r="AT19">
-        <v>1.19</v>
+        <v>17.5</v>
       </c>
       <c r="AU19">
-        <v>1.13</v>
+        <v>10</v>
       </c>
       <c r="AV19">
-        <v>1.24</v>
+        <v>11</v>
       </c>
       <c r="AW19">
-        <v>1.24</v>
+        <v>5.5</v>
       </c>
       <c r="AX19">
-        <v>1.24</v>
+        <v>21</v>
       </c>
       <c r="AY19">
-        <v>1.24</v>
+        <v>11</v>
       </c>
       <c r="AZ19">
-        <v>1.24</v>
+        <v>12.5</v>
       </c>
       <c r="BA19">
-        <v>1.24</v>
+        <v>6</v>
       </c>
       <c r="BB19">
-        <v>1.24</v>
+        <v>6.6</v>
       </c>
       <c r="BC19">
-        <v>1.24</v>
+        <v>21</v>
       </c>
       <c r="BD19">
-        <v>1.24</v>
+        <v>6.2</v>
       </c>
       <c r="BE19">
-        <v>1.24</v>
+        <v>6.6</v>
       </c>
       <c r="BF19">
-        <v>1.24</v>
+        <v>12.5</v>
       </c>
       <c r="BG19">
-        <v>1.24</v>
+        <v>7.8</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5527,16 +5527,16 @@
         <v>168</v>
       </c>
       <c r="F20">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G20">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="H20">
         <v>6</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J20">
         <v>5.7</v>
@@ -5551,34 +5551,34 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O20">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P20">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q20">
         <v>1.29</v>
       </c>
       <c r="R20">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="T20">
         <v>1.46</v>
       </c>
       <c r="U20">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="V20">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W20">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X20">
         <v>65</v>
@@ -5611,16 +5611,16 @@
         <v>14.5</v>
       </c>
       <c r="AH20">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AI20">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ20">
         <v>22</v>
       </c>
       <c r="AK20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL20">
         <v>28</v>
@@ -5629,7 +5629,7 @@
         <v>65</v>
       </c>
       <c r="AN20">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AO20">
         <v>44</v>
@@ -5641,7 +5641,7 @@
         <v>29</v>
       </c>
       <c r="AR20">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS20">
         <v>9</v>
@@ -5665,16 +5665,16 @@
         <v>9.4</v>
       </c>
       <c r="AZ20">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA20">
         <v>30</v>
       </c>
       <c r="BB20">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC20">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD20">
         <v>15.5</v>
@@ -5686,7 +5686,7 @@
         <v>3.3</v>
       </c>
       <c r="BG20">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5772,10 +5772,10 @@
         <v>3.6</v>
       </c>
       <c r="G21">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H21">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="I21">
         <v>2.74</v>
@@ -5793,7 +5793,7 @@
         <v>1.14</v>
       </c>
       <c r="N21">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="O21">
         <v>1.58</v>
@@ -5808,7 +5808,7 @@
         <v>1.19</v>
       </c>
       <c r="S21">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="T21">
         <v>2.08</v>
@@ -5823,37 +5823,37 @@
         <v>1.35</v>
       </c>
       <c r="X21">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y21">
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AA21">
         <v>48</v>
       </c>
       <c r="AB21">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC21">
         <v>7.6</v>
       </c>
       <c r="AD21">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE21">
         <v>42</v>
       </c>
       <c r="AF21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG21">
         <v>18</v>
       </c>
       <c r="AH21">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI21">
         <v>75</v>
@@ -5886,7 +5886,7 @@
         <v>11.5</v>
       </c>
       <c r="AS21">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT21">
         <v>8.800000000000001</v>
@@ -5910,61 +5910,61 @@
         <v>19</v>
       </c>
       <c r="BA21">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB21">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BC21">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BD21">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BE21">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BF21">
+        <v>6</v>
+      </c>
+      <c r="BG21">
+        <v>5.7</v>
+      </c>
+      <c r="BH21">
+        <v>2.7</v>
+      </c>
+      <c r="BI21">
+        <v>2.32</v>
+      </c>
+      <c r="BJ21">
+        <v>11.5</v>
+      </c>
+      <c r="BK21">
         <v>6.8</v>
       </c>
-      <c r="BG21">
-        <v>6.2</v>
-      </c>
-      <c r="BH21">
-        <v>2.72</v>
-      </c>
-      <c r="BI21">
-        <v>2.34</v>
-      </c>
-      <c r="BJ21">
-        <v>11</v>
-      </c>
-      <c r="BK21">
-        <v>6.6</v>
-      </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BN21">
         <v>6.4</v>
       </c>
       <c r="BO21">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP21">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT21">
         <v>5.3</v>
@@ -5973,10 +5973,10 @@
         <v>4.2</v>
       </c>
       <c r="BV21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW21">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX21">
         <v>1000</v>
@@ -6011,16 +6011,16 @@
         <v>170</v>
       </c>
       <c r="F22">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="G22">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H22">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I22">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="J22">
         <v>3.05</v>
@@ -6038,7 +6038,7 @@
         <v>2.8</v>
       </c>
       <c r="O22">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P22">
         <v>1.63</v>
@@ -6053,28 +6053,28 @@
         <v>4.4</v>
       </c>
       <c r="T22">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="U22">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="V22">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W22">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X22">
         <v>12</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z22">
         <v>16</v>
       </c>
       <c r="AA22">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB22">
         <v>11</v>
@@ -6101,19 +6101,19 @@
         <v>65</v>
       </c>
       <c r="AJ22">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK22">
         <v>60</v>
       </c>
       <c r="AL22">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM22">
         <v>170</v>
       </c>
       <c r="AN22">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO22">
         <v>34</v>
@@ -6140,7 +6140,7 @@
         <v>10</v>
       </c>
       <c r="AW22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX22">
         <v>19</v>
@@ -6152,85 +6152,85 @@
         <v>17</v>
       </c>
       <c r="BA22">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB22">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC22">
         <v>29</v>
       </c>
       <c r="BD22">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE22">
+        <v>8</v>
+      </c>
+      <c r="BF22">
         <v>7.6</v>
       </c>
-      <c r="BF22">
-        <v>7.2</v>
-      </c>
       <c r="BG22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH22">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI22">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CB22" t="s">
         <v>187</v>
@@ -6253,16 +6253,16 @@
         <v>171</v>
       </c>
       <c r="F23">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="G23">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="H23">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="I23">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="J23">
         <v>4.3</v>
@@ -6271,7 +6271,7 @@
         <v>5</v>
       </c>
       <c r="L23">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="M23">
         <v>1.01</v>
@@ -6283,7 +6283,7 @@
         <v>1.1</v>
       </c>
       <c r="P23">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q23">
         <v>1.3</v>
@@ -6295,25 +6295,25 @@
         <v>1.74</v>
       </c>
       <c r="T23">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U23">
         <v>3.4</v>
       </c>
       <c r="V23">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="X23">
         <v>65</v>
       </c>
       <c r="Y23">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="Z23">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AA23">
         <v>50</v>
@@ -6325,37 +6325,37 @@
         <v>14.5</v>
       </c>
       <c r="AD23">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AE23">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AF23">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AG23">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH23">
         <v>14.5</v>
       </c>
       <c r="AI23">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AJ23">
         <v>42</v>
       </c>
       <c r="AK23">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL23">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM23">
         <v>36</v>
       </c>
       <c r="AN23">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AO23">
         <v>10.5</v>
@@ -6364,28 +6364,28 @@
         <v>6.8</v>
       </c>
       <c r="AQ23">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR23">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AS23">
         <v>32</v>
       </c>
       <c r="AT23">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AU23">
         <v>12</v>
       </c>
       <c r="AV23">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW23">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX23">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AY23">
         <v>12</v>
@@ -6397,22 +6397,22 @@
         <v>19</v>
       </c>
       <c r="BB23">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="BC23">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BD23">
         <v>19</v>
       </c>
       <c r="BE23">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF23">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG23">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH23">
         <v>7.4</v>
@@ -6424,7 +6424,7 @@
         <v>9.6</v>
       </c>
       <c r="BK23">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="BL23">
         <v>55</v>
@@ -6433,40 +6433,40 @@
         <v>4.1</v>
       </c>
       <c r="BN23">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BO23">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BP23">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BQ23">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BR23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS23">
         <v>3.7</v>
       </c>
       <c r="BT23">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU23">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV23">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BW23">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BX23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY23">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BZ23">
         <v>11.5</v>
@@ -6495,166 +6495,166 @@
         <v>172</v>
       </c>
       <c r="F24">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="G24">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="H24">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="I24">
-        <v>990</v>
+        <v>23</v>
       </c>
       <c r="J24">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L24">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M24">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N24">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O24">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="P24">
         <v>2.06</v>
       </c>
       <c r="Q24">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R24">
         <v>1.41</v>
       </c>
       <c r="S24">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T24">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="U24">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W24">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA24">
         <v>1000</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF24">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG24">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AK24">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN24">
+        <v>5.7</v>
+      </c>
+      <c r="AO24">
+        <v>1000</v>
+      </c>
+      <c r="AP24">
+        <v>13.5</v>
+      </c>
+      <c r="AQ24">
+        <v>6.2</v>
+      </c>
+      <c r="AR24">
+        <v>6.6</v>
+      </c>
+      <c r="AS24">
+        <v>7</v>
+      </c>
+      <c r="AT24">
+        <v>6.4</v>
+      </c>
+      <c r="AU24">
+        <v>12</v>
+      </c>
+      <c r="AV24">
+        <v>6.4</v>
+      </c>
+      <c r="AW24">
         <v>6.8</v>
       </c>
-      <c r="AO24">
-        <v>1000</v>
-      </c>
-      <c r="AP24">
-        <v>1.64</v>
-      </c>
-      <c r="AQ24">
-        <v>1.64</v>
-      </c>
-      <c r="AR24">
-        <v>1.64</v>
-      </c>
-      <c r="AS24">
-        <v>1.64</v>
-      </c>
-      <c r="AT24">
-        <v>5.5</v>
-      </c>
-      <c r="AU24">
-        <v>1.64</v>
-      </c>
-      <c r="AV24">
-        <v>1.64</v>
-      </c>
-      <c r="AW24">
-        <v>1.64</v>
-      </c>
       <c r="AX24">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AY24">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24">
-        <v>1.64</v>
+        <v>6.2</v>
       </c>
       <c r="BA24">
-        <v>1.64</v>
+        <v>6.8</v>
       </c>
       <c r="BB24">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC24">
-        <v>1.52</v>
+        <v>13.5</v>
       </c>
       <c r="BD24">
-        <v>1.64</v>
+        <v>6.2</v>
       </c>
       <c r="BE24">
-        <v>1.64</v>
+        <v>6.8</v>
       </c>
       <c r="BF24">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG24">
-        <v>1.64</v>
+        <v>7</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6749,7 +6749,7 @@
         <v>3.55</v>
       </c>
       <c r="J25">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K25">
         <v>3.2</v>
@@ -6761,7 +6761,7 @@
         <v>1.13</v>
       </c>
       <c r="N25">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O25">
         <v>1.56</v>
@@ -6776,10 +6776,10 @@
         <v>1.17</v>
       </c>
       <c r="S25">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="T25">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U25">
         <v>1.75</v>
@@ -6797,7 +6797,7 @@
         <v>9.4</v>
       </c>
       <c r="Z25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA25">
         <v>70</v>
@@ -6815,7 +6815,7 @@
         <v>60</v>
       </c>
       <c r="AF25">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG25">
         <v>14</v>
@@ -6848,13 +6848,13 @@
         <v>6.4</v>
       </c>
       <c r="AQ25">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AR25">
         <v>17.5</v>
       </c>
       <c r="AS25">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT25">
         <v>6.8</v>
@@ -6866,7 +6866,7 @@
         <v>13</v>
       </c>
       <c r="AW25">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX25">
         <v>14</v>
@@ -6878,25 +6878,25 @@
         <v>20</v>
       </c>
       <c r="BA25">
+        <v>7.6</v>
+      </c>
+      <c r="BB25">
         <v>7.4</v>
       </c>
-      <c r="BB25">
+      <c r="BC25">
         <v>7.2</v>
       </c>
-      <c r="BC25">
-        <v>7</v>
-      </c>
       <c r="BD25">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE25">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BG25">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH25">
         <v>2.9</v>
@@ -6979,7 +6979,7 @@
         <v>174</v>
       </c>
       <c r="F26">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G26">
         <v>2.28</v>
@@ -7224,10 +7224,10 @@
         <v>4.4</v>
       </c>
       <c r="G27">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H27">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I27">
         <v>2.26</v>
@@ -7245,7 +7245,7 @@
         <v>1.14</v>
       </c>
       <c r="N27">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O27">
         <v>1.6</v>
@@ -7254,7 +7254,7 @@
         <v>1.45</v>
       </c>
       <c r="Q27">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R27">
         <v>1.16</v>
@@ -7353,7 +7353,7 @@
         <v>5</v>
       </c>
       <c r="AX27">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="AY27">
         <v>18</v>
@@ -7466,7 +7466,7 @@
         <v>1.76</v>
       </c>
       <c r="G28">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H28">
         <v>1.1</v>
@@ -7487,22 +7487,22 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="O28">
         <v>1.27</v>
       </c>
       <c r="P28">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="Q28">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R28">
         <v>1.43</v>
       </c>
       <c r="S28">
-        <v>1.28</v>
+        <v>1.99</v>
       </c>
       <c r="T28">
         <v>1.11</v>
@@ -7514,7 +7514,7 @@
         <v>1.01</v>
       </c>
       <c r="W28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7717,10 +7717,10 @@
         <v>2.94</v>
       </c>
       <c r="J29">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K29">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7729,19 +7729,19 @@
         <v>1.04</v>
       </c>
       <c r="N29">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O29">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P29">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q29">
+        <v>1.62</v>
+      </c>
+      <c r="R29">
         <v>1.58</v>
-      </c>
-      <c r="R29">
-        <v>1.57</v>
       </c>
       <c r="S29">
         <v>2.54</v>
@@ -7750,7 +7750,7 @@
         <v>1.54</v>
       </c>
       <c r="U29">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V29">
         <v>1.51</v>
@@ -7765,7 +7765,7 @@
         <v>17.5</v>
       </c>
       <c r="Z29">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA29">
         <v>48</v>
@@ -7774,13 +7774,13 @@
         <v>16</v>
       </c>
       <c r="AC29">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD29">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE29">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AF29">
         <v>25</v>
@@ -7813,19 +7813,19 @@
         <v>22</v>
       </c>
       <c r="AP29">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ29">
         <v>15.5</v>
       </c>
       <c r="AR29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS29">
         <v>36</v>
       </c>
       <c r="AT29">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU29">
         <v>8.4</v>
@@ -7843,13 +7843,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ29">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB29">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC29">
         <v>20</v>
@@ -7870,7 +7870,7 @@
         <v>5.1</v>
       </c>
       <c r="BI29">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BJ29">
         <v>10.5</v>
@@ -7888,7 +7888,7 @@
         <v>7</v>
       </c>
       <c r="BO29">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP29">
         <v>20</v>
@@ -7947,25 +7947,25 @@
         <v>178</v>
       </c>
       <c r="F30">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G30">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="H30">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I30">
         <v>4.3</v>
       </c>
       <c r="J30">
+        <v>3.75</v>
+      </c>
+      <c r="K30">
         <v>3.85</v>
       </c>
-      <c r="K30">
-        <v>3.9</v>
-      </c>
       <c r="L30">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M30">
         <v>1.06</v>
@@ -7980,46 +7980,46 @@
         <v>2.12</v>
       </c>
       <c r="Q30">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R30">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S30">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T30">
         <v>1.74</v>
       </c>
       <c r="U30">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y30">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z30">
         <v>32</v>
       </c>
       <c r="AA30">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB30">
         <v>10.5</v>
       </c>
       <c r="AC30">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD30">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE30">
         <v>55</v>
@@ -8028,7 +8028,7 @@
         <v>13</v>
       </c>
       <c r="AG30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH30">
         <v>17.5</v>
@@ -8052,10 +8052,10 @@
         <v>12</v>
       </c>
       <c r="AO30">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP30">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ30">
         <v>15</v>
@@ -8067,10 +8067,10 @@
         <v>36</v>
       </c>
       <c r="AT30">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU30">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV30">
         <v>15</v>
@@ -8079,13 +8079,13 @@
         <v>40</v>
       </c>
       <c r="AX30">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY30">
         <v>10</v>
       </c>
       <c r="AZ30">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA30">
         <v>46</v>
@@ -8112,25 +8112,25 @@
         <v>4.1</v>
       </c>
       <c r="BI30">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ30">
         <v>11</v>
       </c>
       <c r="BK30">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BL30">
         <v>120</v>
       </c>
       <c r="BM30">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN30">
         <v>5.5</v>
       </c>
       <c r="BO30">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BP30">
         <v>16</v>
@@ -8148,7 +8148,7 @@
         <v>8.6</v>
       </c>
       <c r="BU30">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="BV30">
         <v>38</v>
@@ -8163,7 +8163,7 @@
         <v>5.1</v>
       </c>
       <c r="BZ30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA30">
         <v>4.7</v>
@@ -8195,19 +8195,19 @@
         <v>1.55</v>
       </c>
       <c r="H31">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I31">
         <v>8.6</v>
       </c>
       <c r="J31">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K31">
         <v>4.5</v>
       </c>
       <c r="L31">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M31">
         <v>1.08</v>
@@ -8216,31 +8216,31 @@
         <v>3.45</v>
       </c>
       <c r="O31">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P31">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q31">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R31">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S31">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T31">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U31">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V31">
         <v>1.13</v>
       </c>
       <c r="W31">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X31">
         <v>13</v>
@@ -8249,16 +8249,16 @@
         <v>21</v>
       </c>
       <c r="Z31">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA31">
         <v>350</v>
       </c>
       <c r="AB31">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC31">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD31">
         <v>32</v>
@@ -8267,73 +8267,73 @@
         <v>160</v>
       </c>
       <c r="AF31">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG31">
         <v>10.5</v>
       </c>
       <c r="AH31">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AI31">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK31">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL31">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AM31">
         <v>220</v>
       </c>
       <c r="AN31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO31">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="AP31">
         <v>11.5</v>
       </c>
       <c r="AQ31">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS31">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AT31">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU31">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV31">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW31">
+        <v>17</v>
+      </c>
+      <c r="AX31">
+        <v>7.2</v>
+      </c>
+      <c r="AY31">
+        <v>9.4</v>
+      </c>
+      <c r="AZ31">
         <v>20</v>
       </c>
-      <c r="AX31">
-        <v>7</v>
-      </c>
-      <c r="AY31">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ31">
-        <v>26</v>
-      </c>
       <c r="BA31">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB31">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC31">
         <v>16.5</v>
@@ -8342,13 +8342,13 @@
         <v>42</v>
       </c>
       <c r="BE31">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BF31">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BG31">
-        <v>16.5</v>
+        <v>48</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8431,22 +8431,22 @@
         <v>180</v>
       </c>
       <c r="F32">
-        <v>1.47</v>
+        <v>2.96</v>
       </c>
       <c r="G32">
-        <v>990</v>
+        <v>3.55</v>
       </c>
       <c r="H32">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="I32">
-        <v>990</v>
+        <v>2.28</v>
       </c>
       <c r="J32">
-        <v>2.04</v>
+        <v>3.95</v>
       </c>
       <c r="K32">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8455,142 +8455,142 @@
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>1.25</v>
+        <v>5.2</v>
       </c>
       <c r="O32">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P32">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="Q32">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="R32">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="S32">
-        <v>1.14</v>
+        <v>2.22</v>
       </c>
       <c r="T32">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U32">
-        <v>1.11</v>
+        <v>2.52</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="W32">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="X32">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y32">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z32">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB32">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC32">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD32">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE32">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF32">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG32">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH32">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI32">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ32">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL32">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM32">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN32">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO32">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP32">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ32">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS32">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT32">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU32">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV32">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW32">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX32">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY32">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ32">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA32">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB32">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC32">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD32">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE32">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF32">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG32">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
         <v>7</v>
       </c>
       <c r="O33">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P33">
         <v>3</v>
@@ -8709,7 +8709,7 @@
         <v>1.47</v>
       </c>
       <c r="R33">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S33">
         <v>2.18</v>
@@ -8730,7 +8730,7 @@
         <v>34</v>
       </c>
       <c r="Y33">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z33">
         <v>100</v>
@@ -8766,19 +8766,19 @@
         <v>12</v>
       </c>
       <c r="AK33">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AL33">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM33">
         <v>110</v>
       </c>
       <c r="AN33">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO33">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AP33">
         <v>32</v>
@@ -8787,10 +8787,10 @@
         <v>38</v>
       </c>
       <c r="AR33">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AS33">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT33">
         <v>11.5</v>
@@ -8799,13 +8799,13 @@
         <v>13.5</v>
       </c>
       <c r="AV33">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AW33">
         <v>100</v>
       </c>
       <c r="AX33">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY33">
         <v>9.800000000000001</v>
@@ -8829,28 +8829,28 @@
         <v>90</v>
       </c>
       <c r="BF33">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BG33">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="BH33">
         <v>4.9</v>
       </c>
       <c r="BI33">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ33">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK33">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BL33">
         <v>110</v>
       </c>
       <c r="BM33">
-        <v>26</v>
+        <v>12.5</v>
       </c>
       <c r="BN33">
         <v>4.2</v>
@@ -8868,13 +8868,13 @@
         <v>20</v>
       </c>
       <c r="BS33">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BT33">
         <v>13.5</v>
       </c>
       <c r="BU33">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BV33">
         <v>70</v>
@@ -8889,7 +8889,7 @@
         <v>11.5</v>
       </c>
       <c r="BZ33">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CA33">
         <v>8</v>
@@ -8936,19 +8936,19 @@
         <v>1.34</v>
       </c>
       <c r="M34">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N34">
         <v>3.4</v>
       </c>
       <c r="O34">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P34">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q34">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R34">
         <v>1.31</v>
@@ -8957,7 +8957,7 @@
         <v>3.9</v>
       </c>
       <c r="T34">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U34">
         <v>2.08</v>
@@ -9020,7 +9020,7 @@
         <v>26</v>
       </c>
       <c r="AO34">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP34">
         <v>11</v>
@@ -9032,7 +9032,7 @@
         <v>18.5</v>
       </c>
       <c r="AS34">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AT34">
         <v>9</v>
@@ -9065,7 +9065,7 @@
         <v>26</v>
       </c>
       <c r="BD34">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE34">
         <v>38</v>
@@ -9178,10 +9178,10 @@
         <v>1.48</v>
       </c>
       <c r="M35">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N35">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O35">
         <v>1.49</v>
@@ -9190,10 +9190,10 @@
         <v>1.56</v>
       </c>
       <c r="Q35">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R35">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S35">
         <v>5</v>
@@ -9208,7 +9208,7 @@
         <v>1.5</v>
       </c>
       <c r="W35">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X35">
         <v>9.4</v>
@@ -9235,7 +9235,7 @@
         <v>50</v>
       </c>
       <c r="AF35">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG35">
         <v>14</v>
@@ -9289,7 +9289,7 @@
         <v>29</v>
       </c>
       <c r="AX35">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY35">
         <v>11.5</v>
@@ -9298,7 +9298,7 @@
         <v>18</v>
       </c>
       <c r="BA35">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB35">
         <v>38</v>
@@ -9328,16 +9328,16 @@
         <v>11</v>
       </c>
       <c r="BK35">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN35">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO35">
         <v>4.5</v>
@@ -9346,37 +9346,37 @@
         <v>27</v>
       </c>
       <c r="BQ35">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT35">
         <v>5.9</v>
       </c>
       <c r="BU35">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV35">
         <v>27</v>
       </c>
       <c r="BW35">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB35" t="s">
         <v>187</v>
@@ -9399,28 +9399,28 @@
         <v>184</v>
       </c>
       <c r="F36">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G36">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="H36">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I36">
+        <v>3.8</v>
+      </c>
+      <c r="J36">
+        <v>3.4</v>
+      </c>
+      <c r="K36">
         <v>3.95</v>
-      </c>
-      <c r="J36">
-        <v>3.3</v>
-      </c>
-      <c r="K36">
-        <v>3.8</v>
       </c>
       <c r="L36">
         <v>1.33</v>
       </c>
       <c r="M36">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N36">
         <v>3.55</v>
@@ -9429,28 +9429,28 @@
         <v>1.3</v>
       </c>
       <c r="P36">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q36">
         <v>1.92</v>
       </c>
       <c r="R36">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S36">
         <v>2.96</v>
       </c>
       <c r="T36">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U36">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V36">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W36">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9644,7 +9644,7 @@
         <v>1.08</v>
       </c>
       <c r="G37">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="H37">
         <v>3.05</v>
@@ -9665,22 +9665,22 @@
         <v>1.02</v>
       </c>
       <c r="N37">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="O37">
         <v>1.12</v>
       </c>
       <c r="P37">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="Q37">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="R37">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="S37">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="T37">
         <v>1.11</v>
@@ -9692,7 +9692,7 @@
         <v>1.01</v>
       </c>
       <c r="W37">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9883,10 +9883,10 @@
         <v>186</v>
       </c>
       <c r="F38">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G38">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H38">
         <v>4.4</v>
@@ -9934,7 +9934,7 @@
         <v>1.25</v>
       </c>
       <c r="W38">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X38">
         <v>11.5</v>
@@ -9997,10 +9997,10 @@
         <v>12</v>
       </c>
       <c r="AR38">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS38">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT38">
         <v>6.8</v>
@@ -10012,7 +10012,7 @@
         <v>16.5</v>
       </c>
       <c r="AW38">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX38">
         <v>10</v>
@@ -10021,10 +10021,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ38">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BA38">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB38">
         <v>20</v>
@@ -10033,22 +10033,22 @@
         <v>20</v>
       </c>
       <c r="BD38">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE38">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF38">
         <v>16</v>
       </c>
       <c r="BG38">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH38">
         <v>3.05</v>
       </c>
       <c r="BI38">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ38">
         <v>11</v>
@@ -10060,19 +10060,19 @@
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>3.45</v>
+        <v>1.63</v>
       </c>
       <c r="BN38">
         <v>4.5</v>
       </c>
       <c r="BO38">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP38">
         <v>15</v>
       </c>
       <c r="BQ38">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR38">
         <v>1000</v>
@@ -10084,7 +10084,7 @@
         <v>7.8</v>
       </c>
       <c r="BU38">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV38">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -577,7 +577,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-25 17:41:34</t>
+    <t>2026-08-25 19:51:41</t>
   </si>
 </sst>
 </file>
@@ -1171,16 +1171,16 @@
         <v>150</v>
       </c>
       <c r="F2">
+        <v>1.55</v>
+      </c>
+      <c r="G2">
         <v>1.56</v>
       </c>
-      <c r="G2">
-        <v>1.57</v>
-      </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
         <v>4.3</v>
@@ -1195,34 +1195,34 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q2">
         <v>2.12</v>
       </c>
       <c r="R2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U2">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V2">
         <v>1.14</v>
       </c>
       <c r="W2">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X2">
         <v>13</v>
@@ -1234,31 +1234,31 @@
         <v>70</v>
       </c>
       <c r="AA2">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="AB2">
         <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE2">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AF2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI2">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AJ2">
         <v>13</v>
@@ -1267,31 +1267,31 @@
         <v>17.5</v>
       </c>
       <c r="AL2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN2">
         <v>9.6</v>
       </c>
       <c r="AO2">
+        <v>290</v>
+      </c>
+      <c r="AP2">
+        <v>12.5</v>
+      </c>
+      <c r="AQ2">
+        <v>20</v>
+      </c>
+      <c r="AR2">
+        <v>55</v>
+      </c>
+      <c r="AS2">
         <v>200</v>
       </c>
-      <c r="AP2">
-        <v>12</v>
-      </c>
-      <c r="AQ2">
-        <v>19</v>
-      </c>
-      <c r="AR2">
-        <v>50</v>
-      </c>
-      <c r="AS2">
-        <v>18.5</v>
-      </c>
       <c r="AT2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU2">
         <v>9</v>
@@ -1300,19 +1300,19 @@
         <v>26</v>
       </c>
       <c r="AW2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AX2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB2">
         <v>12</v>
@@ -1324,73 +1324,73 @@
         <v>44</v>
       </c>
       <c r="BE2">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="BF2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG2">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>170</v>
       </c>
       <c r="BN2">
         <v>3.85</v>
       </c>
       <c r="BO2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP2">
         <v>10.5</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
+        <v>11.5</v>
+      </c>
+      <c r="BU2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BV2">
+        <v>100</v>
+      </c>
+      <c r="BW2">
         <v>11</v>
-      </c>
-      <c r="BU2">
-        <v>8.6</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>12.5</v>
       </c>
       <c r="BX2">
         <v>100</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
         <v>22</v>
       </c>
       <c r="CA2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>187</v>
@@ -1413,43 +1413,43 @@
         <v>151</v>
       </c>
       <c r="F3">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="G3">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="H3">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
         <v>3.15</v>
       </c>
       <c r="L3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M3">
         <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O3">
         <v>1.53</v>
       </c>
       <c r="P3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q3">
         <v>2.62</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
         <v>5.4</v>
@@ -1458,97 +1458,97 @@
         <v>2.08</v>
       </c>
       <c r="U3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y3">
         <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE3">
         <v>55</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI3">
         <v>80</v>
       </c>
       <c r="AJ3">
+        <v>40</v>
+      </c>
+      <c r="AK3">
         <v>36</v>
       </c>
-      <c r="AK3">
-        <v>32</v>
-      </c>
       <c r="AL3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM3">
         <v>170</v>
       </c>
       <c r="AN3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR3">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3">
         <v>20</v>
@@ -1557,7 +1557,7 @@
         <v>65</v>
       </c>
       <c r="BB3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC3">
         <v>29</v>
@@ -1566,19 +1566,19 @@
         <v>50</v>
       </c>
       <c r="BE3">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="BF3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BH3">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="BI3">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
@@ -1590,49 +1590,49 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN3">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BO3">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BQ3">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS3">
+        <v>11.5</v>
+      </c>
+      <c r="BT3">
+        <v>6.4</v>
+      </c>
+      <c r="BU3">
+        <v>5.6</v>
+      </c>
+      <c r="BV3">
+        <v>30</v>
+      </c>
+      <c r="BW3">
         <v>10</v>
       </c>
-      <c r="BT3">
-        <v>6.8</v>
-      </c>
-      <c r="BU3">
-        <v>6</v>
-      </c>
-      <c r="BV3">
-        <v>36</v>
-      </c>
-      <c r="BW3">
-        <v>9.6</v>
-      </c>
       <c r="BX3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="CA3">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="CB3" t="s">
         <v>187</v>
@@ -1915,7 +1915,7 @@
         <v>3.45</v>
       </c>
       <c r="L5">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M5">
         <v>1.09</v>
@@ -1924,13 +1924,13 @@
         <v>3.25</v>
       </c>
       <c r="O5">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R5">
         <v>1.28</v>
@@ -1942,10 +1942,10 @@
         <v>1.92</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W5">
         <v>1.38</v>
@@ -1954,7 +1954,7 @@
         <v>11.5</v>
       </c>
       <c r="Y5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z5">
         <v>14.5</v>
@@ -1984,10 +1984,10 @@
         <v>21</v>
       </c>
       <c r="AI5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ5">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AK5">
         <v>60</v>
@@ -1996,13 +1996,13 @@
         <v>75</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AN5">
         <v>65</v>
       </c>
       <c r="AO5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -2014,7 +2014,7 @@
         <v>13</v>
       </c>
       <c r="AS5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT5">
         <v>10.5</v>
@@ -2026,7 +2026,7 @@
         <v>10</v>
       </c>
       <c r="AW5">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AX5">
         <v>20</v>
@@ -2035,88 +2035,88 @@
         <v>13.5</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD5">
         <v>36</v>
       </c>
       <c r="BE5">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="BF5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG5">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BH5">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BI5">
         <v>2.46</v>
       </c>
       <c r="BJ5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BN5">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ5">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR5">
         <v>60</v>
       </c>
       <c r="BS5">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT5">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BU5">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BV5">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BW5">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BX5">
         <v>46</v>
       </c>
       <c r="BY5">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BZ5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA5">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="s">
         <v>187</v>
@@ -2139,7 +2139,7 @@
         <v>154</v>
       </c>
       <c r="F6">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G6">
         <v>2.42</v>
@@ -2148,7 +2148,7 @@
         <v>3.1</v>
       </c>
       <c r="I6">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J6">
         <v>3.7</v>
@@ -2172,10 +2172,10 @@
         <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S6">
         <v>2.96</v>
@@ -2184,7 +2184,7 @@
         <v>1.64</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V6">
         <v>1.45</v>
@@ -2193,19 +2193,19 @@
         <v>1.7</v>
       </c>
       <c r="X6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y6">
         <v>15</v>
       </c>
       <c r="Z6">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AA6">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AB6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC6">
         <v>8.6</v>
@@ -2226,22 +2226,22 @@
         <v>15.5</v>
       </c>
       <c r="AI6">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ6">
         <v>55</v>
       </c>
       <c r="AK6">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO6">
         <v>38</v>
@@ -2256,19 +2256,19 @@
         <v>20</v>
       </c>
       <c r="AS6">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AT6">
         <v>11</v>
       </c>
       <c r="AU6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV6">
         <v>12</v>
       </c>
       <c r="AW6">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AX6">
         <v>15</v>
@@ -2280,16 +2280,16 @@
         <v>14</v>
       </c>
       <c r="BA6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB6">
         <v>24</v>
       </c>
       <c r="BC6">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD6">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BE6">
         <v>42</v>
@@ -2301,64 +2301,64 @@
         <v>21</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="s">
         <v>187</v>
@@ -2390,22 +2390,22 @@
         <v>7.4</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O7">
         <v>1.38</v>
@@ -2426,7 +2426,7 @@
         <v>2.22</v>
       </c>
       <c r="U7">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V7">
         <v>1.14</v>
@@ -2444,7 +2444,7 @@
         <v>80</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -2456,13 +2456,13 @@
         <v>32</v>
       </c>
       <c r="AE7">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
         <v>8.4</v>
       </c>
       <c r="AG7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH7">
         <v>29</v>
@@ -2477,13 +2477,13 @@
         <v>19.5</v>
       </c>
       <c r="AL7">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM7">
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO7">
         <v>1000</v>
@@ -2495,22 +2495,22 @@
         <v>18</v>
       </c>
       <c r="AR7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU7">
         <v>8.4</v>
       </c>
       <c r="AV7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW7">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AX7">
         <v>7.4</v>
@@ -2519,7 +2519,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BA7">
         <v>11</v>
@@ -2528,79 +2528,79 @@
         <v>12.5</v>
       </c>
       <c r="BC7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD7">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BE7">
+        <v>38</v>
+      </c>
+      <c r="BF7">
+        <v>9.4</v>
+      </c>
+      <c r="BG7">
+        <v>11.5</v>
+      </c>
+      <c r="BH7">
+        <v>3.75</v>
+      </c>
+      <c r="BI7">
+        <v>2.6</v>
+      </c>
+      <c r="BJ7">
+        <v>13</v>
+      </c>
+      <c r="BK7">
+        <v>4.7</v>
+      </c>
+      <c r="BL7">
+        <v>250</v>
+      </c>
+      <c r="BM7">
+        <v>7.2</v>
+      </c>
+      <c r="BN7">
+        <v>3.95</v>
+      </c>
+      <c r="BO7">
+        <v>3.35</v>
+      </c>
+      <c r="BP7">
         <v>11</v>
       </c>
-      <c r="BF7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG7">
-        <v>11</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
-      <c r="BK7">
-        <v>1.04</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.04</v>
-      </c>
-      <c r="BN7">
-        <v>1000</v>
-      </c>
-      <c r="BO7">
-        <v>1.04</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB7" t="s">
         <v>187</v>
@@ -2656,13 +2656,13 @@
         <v>4.3</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R8">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="S8">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2725,64 +2725,64 @@
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>970</v>
+        <v>4</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AQ8">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="AR8">
-        <v>1.12</v>
+        <v>2.5</v>
       </c>
       <c r="AS8">
-        <v>1.12</v>
+        <v>2.5</v>
       </c>
       <c r="AT8">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AU8">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AV8">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="AW8">
-        <v>1.12</v>
+        <v>2.5</v>
       </c>
       <c r="AX8">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="AY8">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AZ8">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="BA8">
-        <v>1.12</v>
+        <v>2.5</v>
       </c>
       <c r="BB8">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="BC8">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="BD8">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="BE8">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2865,22 +2865,22 @@
         <v>157</v>
       </c>
       <c r="F9">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="G9">
-        <v>990</v>
+        <v>29</v>
       </c>
       <c r="H9">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="I9">
+        <v>1.6</v>
+      </c>
+      <c r="J9">
         <v>3.75</v>
       </c>
-      <c r="J9">
-        <v>1.77</v>
-      </c>
       <c r="K9">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2892,19 +2892,19 @@
         <v>1.1</v>
       </c>
       <c r="O9">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="P9">
         <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R9">
         <v>1.23</v>
       </c>
       <c r="S9">
-        <v>1.28</v>
+        <v>2.34</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2913,10 +2913,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.69</v>
+        <v>2.66</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2925,22 +2925,22 @@
         <v>1000</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9">
         <v>1000</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF9">
         <v>1000</v>
@@ -2970,61 +2970,61 @@
         <v>1000</v>
       </c>
       <c r="AO9">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AP9">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AQ9">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AR9">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AS9">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AT9">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AU9">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="AV9">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AW9">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AX9">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AY9">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AZ9">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BA9">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BB9">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BC9">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BD9">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BE9">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BF9">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3107,7 +3107,7 @@
         <v>158</v>
       </c>
       <c r="F10">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="G10">
         <v>1.8</v>
@@ -3119,10 +3119,10 @@
         <v>11</v>
       </c>
       <c r="J10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K10">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
         <v>1.48</v>
@@ -3131,7 +3131,7 @@
         <v>1.1</v>
       </c>
       <c r="N10">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="O10">
         <v>1.1</v>
@@ -3140,7 +3140,7 @@
         <v>1.39</v>
       </c>
       <c r="Q10">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R10">
         <v>1.13</v>
@@ -3149,10 +3149,10 @@
         <v>4.7</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="V10">
         <v>1.11</v>
@@ -3167,64 +3167,64 @@
         <v>950</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC10">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AE10">
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG10">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AI10">
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AM10">
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="AQ10">
-        <v>1.56</v>
+        <v>7.6</v>
       </c>
       <c r="AR10">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AS10">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AT10">
         <v>4.4</v>
@@ -3233,10 +3233,10 @@
         <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>1.6</v>
+        <v>16</v>
       </c>
       <c r="AW10">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AX10">
         <v>5.7</v>
@@ -3245,88 +3245,88 @@
         <v>8.6</v>
       </c>
       <c r="AZ10">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="BA10">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="BB10">
         <v>9.4</v>
       </c>
       <c r="BC10">
-        <v>1.6</v>
+        <v>17</v>
       </c>
       <c r="BD10">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="BE10">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="BF10">
-        <v>1.6</v>
+        <v>12</v>
       </c>
       <c r="BG10">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="CB10" t="s">
         <v>187</v>
@@ -3355,10 +3355,10 @@
         <v>3.6</v>
       </c>
       <c r="H11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I11">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J11">
         <v>3.45</v>
@@ -3379,7 +3379,7 @@
         <v>1.25</v>
       </c>
       <c r="P11">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q11">
         <v>1.78</v>
@@ -3400,10 +3400,10 @@
         <v>1.69</v>
       </c>
       <c r="W11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X11">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y11">
         <v>12.5</v>
@@ -3412,7 +3412,7 @@
         <v>16.5</v>
       </c>
       <c r="AA11">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AB11">
         <v>15</v>
@@ -3421,7 +3421,7 @@
         <v>9</v>
       </c>
       <c r="AD11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE11">
         <v>24</v>
@@ -3433,25 +3433,25 @@
         <v>15</v>
       </c>
       <c r="AH11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI11">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AJ11">
+        <v>150</v>
+      </c>
+      <c r="AK11">
+        <v>95</v>
+      </c>
+      <c r="AL11">
+        <v>150</v>
+      </c>
+      <c r="AM11">
+        <v>580</v>
+      </c>
+      <c r="AN11">
         <v>65</v>
-      </c>
-      <c r="AK11">
-        <v>42</v>
-      </c>
-      <c r="AL11">
-        <v>50</v>
-      </c>
-      <c r="AM11">
-        <v>90</v>
-      </c>
-      <c r="AN11">
-        <v>36</v>
       </c>
       <c r="AO11">
         <v>16.5</v>
@@ -3466,7 +3466,7 @@
         <v>12</v>
       </c>
       <c r="AS11">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AT11">
         <v>11</v>
@@ -3475,7 +3475,7 @@
         <v>6.6</v>
       </c>
       <c r="AV11">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW11">
         <v>18</v>
@@ -3490,22 +3490,22 @@
         <v>12.5</v>
       </c>
       <c r="BA11">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BB11">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC11">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD11">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE11">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG11">
         <v>12</v>
@@ -3591,22 +3591,22 @@
         <v>160</v>
       </c>
       <c r="F12">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="G12">
-        <v>990</v>
+        <v>5.1</v>
       </c>
       <c r="H12">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="I12">
-        <v>870</v>
+        <v>2.16</v>
       </c>
       <c r="J12">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L12">
         <v>1.23</v>
@@ -3615,19 +3615,19 @@
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O12">
         <v>1.14</v>
       </c>
       <c r="P12">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="Q12">
         <v>1.14</v>
       </c>
       <c r="R12">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S12">
         <v>2.5</v>
@@ -3636,13 +3636,13 @@
         <v>1.11</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V12">
-        <v>1.31</v>
+        <v>1.86</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3651,16 +3651,16 @@
         <v>1000</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12">
         <v>1000</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD12">
         <v>1000</v>
@@ -3699,58 +3699,58 @@
         <v>40</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF12">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3836,19 +3836,19 @@
         <v>1.89</v>
       </c>
       <c r="G13">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>3.7</v>
       </c>
       <c r="I13">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J13">
         <v>4.2</v>
       </c>
       <c r="K13">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3872,10 +3872,10 @@
         <v>1.65</v>
       </c>
       <c r="S13">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T13">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U13">
         <v>2.58</v>
@@ -3884,7 +3884,7 @@
         <v>1.33</v>
       </c>
       <c r="W13">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X13">
         <v>32</v>
@@ -3902,7 +3902,7 @@
         <v>16.5</v>
       </c>
       <c r="AC13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD13">
         <v>18.5</v>
@@ -3929,13 +3929,13 @@
         <v>21</v>
       </c>
       <c r="AL13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM13">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN13">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AO13">
         <v>29</v>
@@ -3947,7 +3947,7 @@
         <v>14.5</v>
       </c>
       <c r="AR13">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS13">
         <v>30</v>
@@ -3959,10 +3959,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV13">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW13">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="AX13">
         <v>14</v>
@@ -3974,7 +3974,7 @@
         <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BB13">
         <v>16</v>
@@ -3986,13 +3986,13 @@
         <v>16</v>
       </c>
       <c r="BE13">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF13">
         <v>6.8</v>
       </c>
       <c r="BG13">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH13">
         <v>5.1</v>
@@ -4075,16 +4075,16 @@
         <v>162</v>
       </c>
       <c r="F14">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="G14">
+        <v>2.76</v>
+      </c>
+      <c r="H14">
         <v>2.8</v>
       </c>
-      <c r="H14">
-        <v>2.76</v>
-      </c>
       <c r="I14">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="J14">
         <v>3.45</v>
@@ -4099,19 +4099,19 @@
         <v>1.06</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O14">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P14">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q14">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R14">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S14">
         <v>3.1</v>
@@ -4123,64 +4123,64 @@
         <v>2.28</v>
       </c>
       <c r="V14">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y14">
         <v>13</v>
       </c>
       <c r="Z14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AA14">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB14">
         <v>12.5</v>
       </c>
       <c r="AC14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD14">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE14">
         <v>36</v>
       </c>
       <c r="AF14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG14">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ14">
         <v>55</v>
       </c>
       <c r="AK14">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL14">
         <v>38</v>
       </c>
       <c r="AM14">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN14">
         <v>25</v>
       </c>
       <c r="AO14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AP14">
         <v>14</v>
@@ -4189,10 +4189,10 @@
         <v>11</v>
       </c>
       <c r="AR14">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS14">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT14">
         <v>10.5</v>
@@ -4204,7 +4204,7 @@
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX14">
         <v>16.5</v>
@@ -4213,22 +4213,22 @@
         <v>10</v>
       </c>
       <c r="AZ14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB14">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE14">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF14">
         <v>20</v>
@@ -4317,13 +4317,13 @@
         <v>163</v>
       </c>
       <c r="F15">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="G15">
         <v>4.4</v>
       </c>
       <c r="H15">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I15">
         <v>2.46</v>
@@ -4332,7 +4332,7 @@
         <v>3</v>
       </c>
       <c r="K15">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="L15">
         <v>1.33</v>
@@ -4347,16 +4347,16 @@
         <v>1.01</v>
       </c>
       <c r="P15">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q15">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R15">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="S15">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4368,37 +4368,37 @@
         <v>1.68</v>
       </c>
       <c r="W15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X15">
         <v>19</v>
       </c>
       <c r="Y15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA15">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AB15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC15">
         <v>10.5</v>
       </c>
       <c r="AD15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE15">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF15">
         <v>32</v>
       </c>
       <c r="AG15">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH15">
         <v>25</v>
@@ -4407,10 +4407,10 @@
         <v>55</v>
       </c>
       <c r="AJ15">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK15">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL15">
         <v>70</v>
@@ -4419,64 +4419,64 @@
         <v>1000</v>
       </c>
       <c r="AN15">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO15">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP15">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AQ15">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR15">
-        <v>2.66</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS15">
-        <v>2.86</v>
+        <v>19.5</v>
       </c>
       <c r="AT15">
-        <v>2.58</v>
+        <v>8.6</v>
       </c>
       <c r="AU15">
-        <v>2.36</v>
+        <v>5.4</v>
       </c>
       <c r="AV15">
-        <v>2.56</v>
+        <v>7.4</v>
       </c>
       <c r="AW15">
-        <v>2.82</v>
+        <v>16</v>
       </c>
       <c r="AX15">
-        <v>2.78</v>
+        <v>16</v>
       </c>
       <c r="AY15">
-        <v>2.64</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15">
-        <v>2.72</v>
+        <v>11.5</v>
       </c>
       <c r="BA15">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BB15">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BC15">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BD15">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BE15">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BF15">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BG15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4559,22 +4559,22 @@
         <v>164</v>
       </c>
       <c r="F16">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G16">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I16">
         <v>5.6</v>
       </c>
       <c r="J16">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="K16">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4586,7 +4586,7 @@
         <v>10.5</v>
       </c>
       <c r="O16">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P16">
         <v>4.1</v>
@@ -4595,22 +4595,22 @@
         <v>1.27</v>
       </c>
       <c r="R16">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="S16">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T16">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U16">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V16">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W16">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="X16">
         <v>70</v>
@@ -4619,106 +4619,106 @@
         <v>55</v>
       </c>
       <c r="Z16">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA16">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC16">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE16">
         <v>60</v>
       </c>
       <c r="AF16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH16">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI16">
         <v>48</v>
       </c>
       <c r="AJ16">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK16">
         <v>14.5</v>
       </c>
       <c r="AL16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM16">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AN16">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AO16">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ16">
         <v>30</v>
       </c>
       <c r="AR16">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="AS16">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AV16">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AW16">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX16">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ16">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BA16">
         <v>25</v>
       </c>
       <c r="BB16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC16">
         <v>12</v>
       </c>
       <c r="BD16">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BE16">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BF16">
         <v>3.45</v>
       </c>
       <c r="BG16">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4801,22 +4801,22 @@
         <v>165</v>
       </c>
       <c r="F17">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="G17">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H17">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I17">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="J17">
         <v>4.3</v>
       </c>
       <c r="K17">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4825,127 +4825,127 @@
         <v>1.02</v>
       </c>
       <c r="N17">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="O17">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q17">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="R17">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="T17">
         <v>1.34</v>
       </c>
       <c r="U17">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V17">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W17">
         <v>1.53</v>
       </c>
       <c r="X17">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y17">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z17">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="AA17">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AB17">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="AC17">
+        <v>14.5</v>
+      </c>
+      <c r="AD17">
+        <v>15</v>
+      </c>
+      <c r="AE17">
+        <v>23</v>
+      </c>
+      <c r="AF17">
+        <v>85</v>
+      </c>
+      <c r="AG17">
         <v>16</v>
-      </c>
-      <c r="AD17">
-        <v>14.5</v>
-      </c>
-      <c r="AE17">
-        <v>22</v>
-      </c>
-      <c r="AF17">
-        <v>32</v>
-      </c>
-      <c r="AG17">
-        <v>15.5</v>
       </c>
       <c r="AH17">
         <v>14.5</v>
       </c>
       <c r="AI17">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AJ17">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK17">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AL17">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="AM17">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="AN17">
         <v>10</v>
       </c>
       <c r="AO17">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP17">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ17">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="AR17">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="AS17">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AT17">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AU17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV17">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX17">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="AY17">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ17">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BB17">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BC17">
         <v>20</v>
@@ -4954,13 +4954,13 @@
         <v>20</v>
       </c>
       <c r="BE17">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF17">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5043,16 +5043,16 @@
         <v>166</v>
       </c>
       <c r="F18">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="G18">
         <v>1.32</v>
       </c>
       <c r="H18">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I18">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J18">
         <v>6.8</v>
@@ -5061,31 +5061,31 @@
         <v>8</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>3.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O18">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P18">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="Q18">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R18">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S18">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="T18">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="U18">
         <v>2.38</v>
@@ -5100,40 +5100,40 @@
         <v>70</v>
       </c>
       <c r="Y18">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Z18">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AA18">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AB18">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD18">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AE18">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG18">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH18">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI18">
         <v>90</v>
       </c>
       <c r="AJ18">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK18">
         <v>15.5</v>
@@ -5145,124 +5145,124 @@
         <v>85</v>
       </c>
       <c r="AN18">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AO18">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP18">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ18">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR18">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS18">
+        <v>7.2</v>
+      </c>
+      <c r="AT18">
+        <v>16</v>
+      </c>
+      <c r="AU18">
+        <v>16</v>
+      </c>
+      <c r="AV18">
+        <v>17.5</v>
+      </c>
+      <c r="AW18">
+        <v>7</v>
+      </c>
+      <c r="AX18">
+        <v>11</v>
+      </c>
+      <c r="AY18">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18">
+        <v>20</v>
+      </c>
+      <c r="BA18">
         <v>6.8</v>
       </c>
-      <c r="AT18">
-        <v>14</v>
-      </c>
-      <c r="AU18">
-        <v>14.5</v>
-      </c>
-      <c r="AV18">
-        <v>6</v>
-      </c>
-      <c r="AW18">
-        <v>6.6</v>
-      </c>
-      <c r="AX18">
-        <v>10.5</v>
-      </c>
-      <c r="AY18">
-        <v>9.6</v>
-      </c>
-      <c r="AZ18">
-        <v>18</v>
-      </c>
-      <c r="BA18">
-        <v>6.6</v>
-      </c>
       <c r="BB18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC18">
         <v>11</v>
       </c>
       <c r="BD18">
+        <v>21</v>
+      </c>
+      <c r="BE18">
+        <v>6.8</v>
+      </c>
+      <c r="BF18">
+        <v>2.68</v>
+      </c>
+      <c r="BG18">
+        <v>10.5</v>
+      </c>
+      <c r="BH18">
+        <v>7.4</v>
+      </c>
+      <c r="BI18">
+        <v>5.1</v>
+      </c>
+      <c r="BJ18">
+        <v>12</v>
+      </c>
+      <c r="BK18">
+        <v>4</v>
+      </c>
+      <c r="BL18">
+        <v>85</v>
+      </c>
+      <c r="BM18">
+        <v>5.7</v>
+      </c>
+      <c r="BN18">
+        <v>4.9</v>
+      </c>
+      <c r="BO18">
+        <v>3.75</v>
+      </c>
+      <c r="BP18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BQ18">
+        <v>5.6</v>
+      </c>
+      <c r="BR18">
         <v>18.5</v>
       </c>
-      <c r="BE18">
-        <v>6.4</v>
-      </c>
-      <c r="BF18">
-        <v>2.72</v>
-      </c>
-      <c r="BG18">
-        <v>6.6</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.04</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.04</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>1.04</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>1.04</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB18" t="s">
         <v>187</v>
@@ -5285,22 +5285,22 @@
         <v>167</v>
       </c>
       <c r="F19">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="G19">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="H19">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="J19">
         <v>4.2</v>
       </c>
       <c r="K19">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5309,34 +5309,34 @@
         <v>1.02</v>
       </c>
       <c r="N19">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="O19">
         <v>1.13</v>
       </c>
       <c r="P19">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="Q19">
         <v>1.43</v>
       </c>
       <c r="R19">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="S19">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="T19">
         <v>1.46</v>
       </c>
       <c r="U19">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V19">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="W19">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="X19">
         <v>950</v>
@@ -5345,106 +5345,106 @@
         <v>970</v>
       </c>
       <c r="Z19">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="AA19">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="AB19">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="AC19">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD19">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE19">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AF19">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="AG19">
+        <v>970</v>
+      </c>
+      <c r="AH19">
         <v>17</v>
       </c>
-      <c r="AH19">
-        <v>16.5</v>
-      </c>
       <c r="AI19">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AJ19">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AK19">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="AL19">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AM19">
-        <v>50</v>
+        <v>580</v>
       </c>
       <c r="AN19">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO19">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AP19">
-        <v>6.2</v>
+        <v>2.52</v>
       </c>
       <c r="AQ19">
-        <v>5.4</v>
+        <v>2.46</v>
       </c>
       <c r="AR19">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS19">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="AT19">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU19">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV19">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AW19">
-        <v>5.5</v>
+        <v>2.46</v>
       </c>
       <c r="AX19">
-        <v>21</v>
+        <v>2.52</v>
       </c>
       <c r="AY19">
-        <v>11</v>
+        <v>2.32</v>
       </c>
       <c r="AZ19">
-        <v>12.5</v>
+        <v>2.24</v>
       </c>
       <c r="BA19">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BB19">
-        <v>6.6</v>
+        <v>2.58</v>
       </c>
       <c r="BC19">
-        <v>21</v>
+        <v>2.5</v>
       </c>
       <c r="BD19">
-        <v>6.2</v>
+        <v>2.48</v>
       </c>
       <c r="BE19">
-        <v>6.6</v>
+        <v>2.52</v>
       </c>
       <c r="BF19">
-        <v>12.5</v>
+        <v>2.28</v>
       </c>
       <c r="BG19">
-        <v>7.8</v>
+        <v>1.98</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5530,16 +5530,16 @@
         <v>1.46</v>
       </c>
       <c r="G20">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I20">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K20">
         <v>6.6</v>
@@ -5551,142 +5551,142 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <v>1.09</v>
       </c>
       <c r="P20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q20">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S20">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="T20">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U20">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W20">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X20">
+        <v>60</v>
+      </c>
+      <c r="Y20">
         <v>65</v>
       </c>
-      <c r="Y20">
+      <c r="Z20">
+        <v>90</v>
+      </c>
+      <c r="AA20">
+        <v>210</v>
+      </c>
+      <c r="AB20">
+        <v>24</v>
+      </c>
+      <c r="AC20">
+        <v>18</v>
+      </c>
+      <c r="AD20">
+        <v>32</v>
+      </c>
+      <c r="AE20">
+        <v>80</v>
+      </c>
+      <c r="AF20">
+        <v>17.5</v>
+      </c>
+      <c r="AG20">
+        <v>13</v>
+      </c>
+      <c r="AH20">
+        <v>19.5</v>
+      </c>
+      <c r="AI20">
         <v>55</v>
       </c>
-      <c r="Z20">
-        <v>75</v>
-      </c>
-      <c r="AA20">
-        <v>160</v>
-      </c>
-      <c r="AB20">
-        <v>21</v>
-      </c>
-      <c r="AC20">
-        <v>17</v>
-      </c>
-      <c r="AD20">
-        <v>38</v>
-      </c>
-      <c r="AE20">
-        <v>70</v>
-      </c>
-      <c r="AF20">
-        <v>16.5</v>
-      </c>
-      <c r="AG20">
-        <v>14.5</v>
-      </c>
-      <c r="AH20">
-        <v>26</v>
-      </c>
-      <c r="AI20">
+      <c r="AJ20">
+        <v>19</v>
+      </c>
+      <c r="AK20">
+        <v>14</v>
+      </c>
+      <c r="AL20">
+        <v>20</v>
+      </c>
+      <c r="AM20">
         <v>60</v>
       </c>
-      <c r="AJ20">
-        <v>22</v>
-      </c>
-      <c r="AK20">
-        <v>14.5</v>
-      </c>
-      <c r="AL20">
+      <c r="AN20">
+        <v>3.85</v>
+      </c>
+      <c r="AO20">
+        <v>34</v>
+      </c>
+      <c r="AP20">
+        <v>8</v>
+      </c>
+      <c r="AQ20">
+        <v>44</v>
+      </c>
+      <c r="AR20">
         <v>28</v>
       </c>
-      <c r="AM20">
-        <v>65</v>
-      </c>
-      <c r="AN20">
-        <v>3.65</v>
-      </c>
-      <c r="AO20">
-        <v>44</v>
-      </c>
-      <c r="AP20">
-        <v>8.4</v>
-      </c>
-      <c r="AQ20">
-        <v>29</v>
-      </c>
-      <c r="AR20">
-        <v>8.6</v>
-      </c>
       <c r="AS20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT20">
+        <v>18</v>
+      </c>
+      <c r="AU20">
         <v>9</v>
-      </c>
-      <c r="AT20">
-        <v>17</v>
-      </c>
-      <c r="AU20">
-        <v>14</v>
       </c>
       <c r="AV20">
         <v>21</v>
       </c>
       <c r="AW20">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="AX20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY20">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AZ20">
+        <v>16.5</v>
+      </c>
+      <c r="BA20">
+        <v>40</v>
+      </c>
+      <c r="BB20">
+        <v>16</v>
+      </c>
+      <c r="BC20">
+        <v>12</v>
+      </c>
+      <c r="BD20">
         <v>17</v>
       </c>
-      <c r="BA20">
-        <v>30</v>
-      </c>
-      <c r="BB20">
-        <v>15</v>
-      </c>
-      <c r="BC20">
-        <v>12.5</v>
-      </c>
-      <c r="BD20">
-        <v>15.5</v>
-      </c>
       <c r="BE20">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BF20">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BG20">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5772,7 +5772,7 @@
         <v>3.6</v>
       </c>
       <c r="G21">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H21">
         <v>2.58</v>
@@ -5781,13 +5781,13 @@
         <v>2.74</v>
       </c>
       <c r="J21">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="K21">
         <v>2.9</v>
       </c>
       <c r="L21">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
         <v>1.14</v>
@@ -5796,34 +5796,34 @@
         <v>2.56</v>
       </c>
       <c r="O21">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P21">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q21">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="R21">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S21">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T21">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="U21">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V21">
         <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X21">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -5835,10 +5835,10 @@
         <v>48</v>
       </c>
       <c r="AB21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC21">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AD21">
         <v>14.5</v>
@@ -5847,7 +5847,7 @@
         <v>42</v>
       </c>
       <c r="AF21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG21">
         <v>18</v>
@@ -5859,13 +5859,13 @@
         <v>75</v>
       </c>
       <c r="AJ21">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AK21">
         <v>65</v>
       </c>
       <c r="AL21">
-        <v>85</v>
+        <v>460</v>
       </c>
       <c r="AM21">
         <v>200</v>
@@ -5883,25 +5883,25 @@
         <v>6.8</v>
       </c>
       <c r="AR21">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AS21">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AT21">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU21">
         <v>6</v>
       </c>
       <c r="AV21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW21">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="AX21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY21">
         <v>14.5</v>
@@ -5910,25 +5910,25 @@
         <v>19</v>
       </c>
       <c r="BA21">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BB21">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BC21">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD21">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BE21">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF21">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BG21">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BH21">
         <v>2.7</v>
@@ -6014,10 +6014,10 @@
         <v>3.45</v>
       </c>
       <c r="G22">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H22">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I22">
         <v>2.54</v>
@@ -6032,145 +6032,145 @@
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N22">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O22">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="P22">
         <v>1.63</v>
       </c>
       <c r="Q22">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R22">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="S22">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="T22">
         <v>1.95</v>
       </c>
       <c r="U22">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V22">
         <v>1.64</v>
       </c>
       <c r="W22">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X22">
+        <v>970</v>
+      </c>
+      <c r="Y22">
+        <v>11.5</v>
+      </c>
+      <c r="Z22">
+        <v>970</v>
+      </c>
+      <c r="AA22">
+        <v>130</v>
+      </c>
+      <c r="AB22">
+        <v>15</v>
+      </c>
+      <c r="AC22">
+        <v>9</v>
+      </c>
+      <c r="AD22">
+        <v>17</v>
+      </c>
+      <c r="AE22">
+        <v>100</v>
+      </c>
+      <c r="AF22">
+        <v>48</v>
+      </c>
+      <c r="AG22">
+        <v>19.5</v>
+      </c>
+      <c r="AH22">
+        <v>48</v>
+      </c>
+      <c r="AI22">
+        <v>290</v>
+      </c>
+      <c r="AJ22">
+        <v>900</v>
+      </c>
+      <c r="AK22">
+        <v>240</v>
+      </c>
+      <c r="AL22">
+        <v>370</v>
+      </c>
+      <c r="AM22">
+        <v>450</v>
+      </c>
+      <c r="AN22">
+        <v>110</v>
+      </c>
+      <c r="AO22">
+        <v>60</v>
+      </c>
+      <c r="AP22">
+        <v>2.5</v>
+      </c>
+      <c r="AQ22">
+        <v>6.6</v>
+      </c>
+      <c r="AR22">
         <v>12</v>
       </c>
-      <c r="Y22">
-        <v>8.6</v>
-      </c>
-      <c r="Z22">
-        <v>16</v>
-      </c>
-      <c r="AA22">
-        <v>38</v>
-      </c>
-      <c r="AB22">
-        <v>11</v>
-      </c>
-      <c r="AC22">
-        <v>7.4</v>
-      </c>
-      <c r="AD22">
-        <v>12.5</v>
-      </c>
-      <c r="AE22">
-        <v>34</v>
-      </c>
-      <c r="AF22">
-        <v>24</v>
-      </c>
-      <c r="AG22">
-        <v>15.5</v>
-      </c>
-      <c r="AH22">
-        <v>22</v>
-      </c>
-      <c r="AI22">
-        <v>65</v>
-      </c>
-      <c r="AJ22">
-        <v>90</v>
-      </c>
-      <c r="AK22">
-        <v>60</v>
-      </c>
-      <c r="AL22">
-        <v>85</v>
-      </c>
-      <c r="AM22">
-        <v>170</v>
-      </c>
-      <c r="AN22">
-        <v>80</v>
-      </c>
-      <c r="AO22">
-        <v>34</v>
-      </c>
-      <c r="AP22">
-        <v>7.6</v>
-      </c>
-      <c r="AQ22">
-        <v>7.2</v>
-      </c>
-      <c r="AR22">
-        <v>12.5</v>
-      </c>
       <c r="AS22">
-        <v>27</v>
+        <v>2.76</v>
       </c>
       <c r="AT22">
+        <v>7</v>
+      </c>
+      <c r="AU22">
+        <v>5.7</v>
+      </c>
+      <c r="AV22">
         <v>9</v>
       </c>
-      <c r="AU22">
-        <v>6.2</v>
-      </c>
-      <c r="AV22">
-        <v>10</v>
-      </c>
       <c r="AW22">
-        <v>6.6</v>
+        <v>2.76</v>
       </c>
       <c r="AX22">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ22">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BA22">
-        <v>7.4</v>
+        <v>2.82</v>
       </c>
       <c r="BB22">
-        <v>7.6</v>
+        <v>2.84</v>
       </c>
       <c r="BC22">
-        <v>29</v>
+        <v>2.82</v>
       </c>
       <c r="BD22">
-        <v>7.6</v>
+        <v>2.84</v>
       </c>
       <c r="BE22">
-        <v>8</v>
+        <v>2.92</v>
       </c>
       <c r="BF22">
-        <v>7.6</v>
+        <v>2.84</v>
       </c>
       <c r="BG22">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="BH22">
         <v>3.4</v>
@@ -6253,25 +6253,25 @@
         <v>171</v>
       </c>
       <c r="F23">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="G23">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H23">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K23">
         <v>5</v>
       </c>
       <c r="L23">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="M23">
         <v>1.01</v>
@@ -6283,28 +6283,28 @@
         <v>1.1</v>
       </c>
       <c r="P23">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q23">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="R23">
         <v>2.16</v>
       </c>
       <c r="S23">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="T23">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="U23">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X23">
         <v>65</v>
@@ -6313,13 +6313,13 @@
         <v>38</v>
       </c>
       <c r="Z23">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA23">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AB23">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AC23">
         <v>14.5</v>
@@ -6331,7 +6331,7 @@
         <v>32</v>
       </c>
       <c r="AF23">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="AG23">
         <v>14.5</v>
@@ -6340,31 +6340,31 @@
         <v>14.5</v>
       </c>
       <c r="AI23">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ23">
-        <v>42</v>
+        <v>280</v>
       </c>
       <c r="AK23">
         <v>21</v>
       </c>
       <c r="AL23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM23">
         <v>36</v>
       </c>
       <c r="AN23">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO23">
         <v>10.5</v>
       </c>
       <c r="AP23">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ23">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AR23">
         <v>24</v>
@@ -6385,7 +6385,7 @@
         <v>21</v>
       </c>
       <c r="AX23">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AY23">
         <v>12</v>
@@ -6397,28 +6397,28 @@
         <v>19</v>
       </c>
       <c r="BB23">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC23">
         <v>17</v>
       </c>
       <c r="BD23">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BE23">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BF23">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BG23">
         <v>8.6</v>
       </c>
       <c r="BH23">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BI23">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ23">
         <v>9.6</v>
@@ -6436,40 +6436,40 @@
         <v>7.8</v>
       </c>
       <c r="BO23">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP23">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ23">
         <v>3.55</v>
       </c>
       <c r="BR23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS23">
         <v>3.7</v>
       </c>
       <c r="BT23">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU23">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW23">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BX23">
         <v>24</v>
       </c>
       <c r="BY23">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BZ23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA23">
         <v>3.2</v>
@@ -6495,166 +6495,166 @@
         <v>172</v>
       </c>
       <c r="F24">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="G24">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="I24">
-        <v>23</v>
+        <v>990</v>
       </c>
       <c r="J24">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K24">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="L24">
         <v>1.27</v>
       </c>
       <c r="M24">
+        <v>1.03</v>
+      </c>
+      <c r="N24">
+        <v>3.75</v>
+      </c>
+      <c r="O24">
+        <v>1.03</v>
+      </c>
+      <c r="P24">
+        <v>2.02</v>
+      </c>
+      <c r="Q24">
+        <v>1.73</v>
+      </c>
+      <c r="R24">
+        <v>1.4</v>
+      </c>
+      <c r="S24">
+        <v>2.84</v>
+      </c>
+      <c r="T24">
+        <v>1.11</v>
+      </c>
+      <c r="U24">
+        <v>1.56</v>
+      </c>
+      <c r="V24">
         <v>1.05</v>
       </c>
-      <c r="N24">
-        <v>4.1</v>
-      </c>
-      <c r="O24">
-        <v>1.26</v>
-      </c>
-      <c r="P24">
-        <v>2.06</v>
-      </c>
-      <c r="Q24">
-        <v>1.77</v>
-      </c>
-      <c r="R24">
-        <v>1.41</v>
-      </c>
-      <c r="S24">
-        <v>2.98</v>
-      </c>
-      <c r="T24">
-        <v>2.44</v>
-      </c>
-      <c r="U24">
-        <v>1.57</v>
-      </c>
-      <c r="V24">
-        <v>1.04</v>
-      </c>
       <c r="W24">
+        <v>4</v>
+      </c>
+      <c r="X24">
+        <v>1000</v>
+      </c>
+      <c r="Y24">
+        <v>950</v>
+      </c>
+      <c r="Z24">
+        <v>1000</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>1000</v>
+      </c>
+      <c r="AC24">
+        <v>15.5</v>
+      </c>
+      <c r="AD24">
+        <v>1000</v>
+      </c>
+      <c r="AE24">
+        <v>1000</v>
+      </c>
+      <c r="AF24">
+        <v>7.4</v>
+      </c>
+      <c r="AG24">
+        <v>14.5</v>
+      </c>
+      <c r="AH24">
+        <v>950</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK24">
+        <v>1000</v>
+      </c>
+      <c r="AL24">
+        <v>1000</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>5.9</v>
+      </c>
+      <c r="AO24">
+        <v>1000</v>
+      </c>
+      <c r="AP24">
+        <v>2.4</v>
+      </c>
+      <c r="AQ24">
+        <v>2.3</v>
+      </c>
+      <c r="AR24">
         <v>4.2</v>
       </c>
-      <c r="X24">
-        <v>23</v>
-      </c>
-      <c r="Y24">
-        <v>55</v>
-      </c>
-      <c r="Z24">
-        <v>210</v>
-      </c>
-      <c r="AA24">
-        <v>1000</v>
-      </c>
-      <c r="AB24">
-        <v>7.6</v>
-      </c>
-      <c r="AC24">
-        <v>17.5</v>
-      </c>
-      <c r="AD24">
-        <v>950</v>
-      </c>
-      <c r="AE24">
-        <v>480</v>
-      </c>
-      <c r="AF24">
-        <v>7.2</v>
-      </c>
-      <c r="AG24">
-        <v>12</v>
-      </c>
-      <c r="AH24">
-        <v>55</v>
-      </c>
-      <c r="AI24">
-        <v>350</v>
-      </c>
-      <c r="AJ24">
-        <v>11</v>
-      </c>
-      <c r="AK24">
-        <v>16.5</v>
-      </c>
-      <c r="AL24">
-        <v>70</v>
-      </c>
-      <c r="AM24">
-        <v>380</v>
-      </c>
-      <c r="AN24">
+      <c r="AS24">
+        <v>4.2</v>
+      </c>
+      <c r="AT24">
+        <v>2.4</v>
+      </c>
+      <c r="AU24">
+        <v>2.08</v>
+      </c>
+      <c r="AV24">
+        <v>2.4</v>
+      </c>
+      <c r="AW24">
+        <v>4.2</v>
+      </c>
+      <c r="AX24">
         <v>5.7</v>
       </c>
-      <c r="AO24">
-        <v>1000</v>
-      </c>
-      <c r="AP24">
-        <v>13.5</v>
-      </c>
-      <c r="AQ24">
-        <v>6.2</v>
-      </c>
-      <c r="AR24">
-        <v>6.6</v>
-      </c>
-      <c r="AS24">
-        <v>7</v>
-      </c>
-      <c r="AT24">
-        <v>6.4</v>
-      </c>
-      <c r="AU24">
-        <v>12</v>
-      </c>
-      <c r="AV24">
-        <v>6.4</v>
-      </c>
-      <c r="AW24">
-        <v>6.8</v>
-      </c>
-      <c r="AX24">
-        <v>6</v>
-      </c>
       <c r="AY24">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AZ24">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="BA24">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB24">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC24">
-        <v>13.5</v>
+        <v>2.42</v>
       </c>
       <c r="BD24">
-        <v>6.2</v>
+        <v>2.42</v>
       </c>
       <c r="BE24">
-        <v>6.8</v>
+        <v>2.42</v>
       </c>
       <c r="BF24">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BG24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6740,16 +6740,16 @@
         <v>2.62</v>
       </c>
       <c r="G25">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H25">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I25">
         <v>3.55</v>
       </c>
       <c r="J25">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K25">
         <v>3.2</v>
@@ -6761,7 +6761,7 @@
         <v>1.13</v>
       </c>
       <c r="N25">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O25">
         <v>1.56</v>
@@ -6779,19 +6779,19 @@
         <v>5.7</v>
       </c>
       <c r="T25">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="U25">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="V25">
         <v>1.39</v>
       </c>
       <c r="W25">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X25">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y25">
         <v>9.4</v>
@@ -6803,7 +6803,7 @@
         <v>70</v>
       </c>
       <c r="AB25">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>7.2</v>
@@ -6815,10 +6815,10 @@
         <v>60</v>
       </c>
       <c r="AF25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG25">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH25">
         <v>24</v>
@@ -6827,13 +6827,13 @@
         <v>90</v>
       </c>
       <c r="AJ25">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK25">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL25">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM25">
         <v>230</v>
@@ -6854,7 +6854,7 @@
         <v>17.5</v>
       </c>
       <c r="AS25">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT25">
         <v>6.8</v>
@@ -6866,10 +6866,10 @@
         <v>13</v>
       </c>
       <c r="AW25">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX25">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AY25">
         <v>11</v>
@@ -6878,25 +6878,25 @@
         <v>20</v>
       </c>
       <c r="BA25">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB25">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BC25">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BD25">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE25">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF25">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="BG25">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH25">
         <v>2.9</v>
@@ -6979,7 +6979,7 @@
         <v>174</v>
       </c>
       <c r="F26">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G26">
         <v>2.28</v>
@@ -7006,7 +7006,7 @@
         <v>2.24</v>
       </c>
       <c r="O26">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P26">
         <v>1.41</v>
@@ -7021,10 +7021,10 @@
         <v>6.4</v>
       </c>
       <c r="T26">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U26">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="V26">
         <v>1.23</v>
@@ -7042,7 +7042,7 @@
         <v>36</v>
       </c>
       <c r="AA26">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB26">
         <v>6.4</v>
@@ -7054,7 +7054,7 @@
         <v>24</v>
       </c>
       <c r="AE26">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF26">
         <v>12</v>
@@ -7066,13 +7066,13 @@
         <v>32</v>
       </c>
       <c r="AI26">
-        <v>160</v>
+        <v>540</v>
       </c>
       <c r="AJ26">
         <v>32</v>
       </c>
       <c r="AK26">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL26">
         <v>90</v>
@@ -7084,7 +7084,7 @@
         <v>38</v>
       </c>
       <c r="AO26">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP26">
         <v>5.7</v>
@@ -7093,7 +7093,7 @@
         <v>9.4</v>
       </c>
       <c r="AR26">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AS26">
         <v>7.6</v>
@@ -7108,7 +7108,7 @@
         <v>19</v>
       </c>
       <c r="AW26">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX26">
         <v>9.6</v>
@@ -7117,7 +7117,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ26">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BA26">
         <v>7.6</v>
@@ -7126,13 +7126,13 @@
         <v>19</v>
       </c>
       <c r="BC26">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BD26">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BE26">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF26">
         <v>24</v>
@@ -7224,7 +7224,7 @@
         <v>4.4</v>
       </c>
       <c r="G27">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H27">
         <v>2.04</v>
@@ -7266,7 +7266,7 @@
         <v>2.28</v>
       </c>
       <c r="U27">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V27">
         <v>1.8</v>
@@ -7359,22 +7359,22 @@
         <v>18</v>
       </c>
       <c r="AZ27">
-        <v>17.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA27">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB27">
         <v>5.5</v>
       </c>
       <c r="BC27">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD27">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE27">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF27">
         <v>5.5</v>
@@ -7469,16 +7469,16 @@
         <v>1.91</v>
       </c>
       <c r="H28">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="I28">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="J28">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="K28">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7487,19 +7487,19 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.94</v>
+        <v>1.1</v>
       </c>
       <c r="O28">
         <v>1.27</v>
       </c>
       <c r="P28">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="Q28">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="R28">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="S28">
         <v>1.99</v>
@@ -7511,7 +7511,7 @@
         <v>1.11</v>
       </c>
       <c r="V28">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W28">
         <v>2.1</v>
@@ -7520,22 +7520,22 @@
         <v>1000</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE28">
         <v>1000</v>
@@ -7544,85 +7544,85 @@
         <v>1000</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI28">
         <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM28">
         <v>1000</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO28">
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7705,16 +7705,16 @@
         <v>177</v>
       </c>
       <c r="F29">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="G29">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="H29">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="I29">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="J29">
         <v>3.8</v>
@@ -7729,202 +7729,202 @@
         <v>1.04</v>
       </c>
       <c r="N29">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P29">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="Q29">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="R29">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="S29">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="T29">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="U29">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="V29">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="W29">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="X29">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y29">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z29">
         <v>28</v>
       </c>
       <c r="AA29">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AB29">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC29">
         <v>9.199999999999999</v>
       </c>
       <c r="AD29">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE29">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF29">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG29">
+        <v>11.5</v>
+      </c>
+      <c r="AH29">
+        <v>14</v>
+      </c>
+      <c r="AI29">
+        <v>36</v>
+      </c>
+      <c r="AJ29">
+        <v>32</v>
+      </c>
+      <c r="AK29">
+        <v>21</v>
+      </c>
+      <c r="AL29">
+        <v>28</v>
+      </c>
+      <c r="AM29">
+        <v>55</v>
+      </c>
+      <c r="AN29">
+        <v>12.5</v>
+      </c>
+      <c r="AO29">
+        <v>20</v>
+      </c>
+      <c r="AP29">
+        <v>22</v>
+      </c>
+      <c r="AQ29">
+        <v>17.5</v>
+      </c>
+      <c r="AR29">
+        <v>24</v>
+      </c>
+      <c r="AS29">
+        <v>48</v>
+      </c>
+      <c r="AT29">
+        <v>14</v>
+      </c>
+      <c r="AU29">
+        <v>8</v>
+      </c>
+      <c r="AV29">
         <v>12</v>
       </c>
-      <c r="AH29">
-        <v>14.5</v>
-      </c>
-      <c r="AI29">
-        <v>34</v>
-      </c>
-      <c r="AJ29">
-        <v>34</v>
-      </c>
-      <c r="AK29">
-        <v>24</v>
-      </c>
-      <c r="AL29">
-        <v>32</v>
-      </c>
-      <c r="AM29">
-        <v>60</v>
-      </c>
-      <c r="AN29">
-        <v>14</v>
-      </c>
-      <c r="AO29">
-        <v>22</v>
-      </c>
-      <c r="AP29">
-        <v>19.5</v>
-      </c>
-      <c r="AQ29">
-        <v>15.5</v>
-      </c>
-      <c r="AR29">
-        <v>20</v>
-      </c>
-      <c r="AS29">
-        <v>36</v>
-      </c>
-      <c r="AT29">
-        <v>14.5</v>
-      </c>
-      <c r="AU29">
-        <v>8.4</v>
-      </c>
-      <c r="AV29">
-        <v>11.5</v>
-      </c>
       <c r="AW29">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX29">
         <v>17.5</v>
       </c>
       <c r="AY29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ29">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA29">
         <v>29</v>
       </c>
       <c r="BB29">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BC29">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BD29">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BE29">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF29">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BG29">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BH29">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL29">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN29">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP29">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR29">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BT29">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV29">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX29">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="s">
         <v>187</v>
@@ -7950,16 +7950,16 @@
         <v>2.02</v>
       </c>
       <c r="G30">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H30">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J30">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K30">
         <v>3.85</v>
@@ -7971,43 +7971,43 @@
         <v>1.06</v>
       </c>
       <c r="N30">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O30">
         <v>1.28</v>
       </c>
       <c r="P30">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q30">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R30">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S30">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T30">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U30">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V30">
         <v>1.31</v>
       </c>
       <c r="W30">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="X30">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y30">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z30">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA30">
         <v>80</v>
@@ -8016,10 +8016,10 @@
         <v>10.5</v>
       </c>
       <c r="AC30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD30">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE30">
         <v>55</v>
@@ -8037,25 +8037,25 @@
         <v>55</v>
       </c>
       <c r="AJ30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK30">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL30">
         <v>34</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO30">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP30">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ30">
         <v>15</v>
@@ -8064,13 +8064,13 @@
         <v>27</v>
       </c>
       <c r="AS30">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AT30">
         <v>9.800000000000001</v>
       </c>
       <c r="AU30">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV30">
         <v>15</v>
@@ -8085,25 +8085,25 @@
         <v>10</v>
       </c>
       <c r="AZ30">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA30">
         <v>46</v>
       </c>
       <c r="BB30">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC30">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD30">
         <v>29</v>
       </c>
       <c r="BE30">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BF30">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG30">
         <v>38</v>
@@ -8115,58 +8115,58 @@
         <v>3.35</v>
       </c>
       <c r="BJ30">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK30">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="BL30">
         <v>120</v>
       </c>
       <c r="BM30">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BN30">
         <v>5.5</v>
       </c>
       <c r="BO30">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BP30">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BQ30">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="BR30">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BS30">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BT30">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU30">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BV30">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BW30">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BX30">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BY30">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BZ30">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CA30">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB30" t="s">
         <v>187</v>
@@ -8189,22 +8189,22 @@
         <v>179</v>
       </c>
       <c r="F31">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G31">
         <v>1.55</v>
       </c>
       <c r="H31">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I31">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J31">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K31">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L31">
         <v>1.34</v>
@@ -8213,22 +8213,22 @@
         <v>1.08</v>
       </c>
       <c r="N31">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O31">
         <v>1.38</v>
       </c>
       <c r="P31">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Q31">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R31">
         <v>1.3</v>
       </c>
       <c r="S31">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T31">
         <v>2.28</v>
@@ -8237,112 +8237,112 @@
         <v>1.73</v>
       </c>
       <c r="V31">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W31">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="X31">
         <v>13</v>
       </c>
       <c r="Y31">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA31">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
         <v>6.8</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD31">
         <v>32</v>
       </c>
       <c r="AE31">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF31">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG31">
         <v>10.5</v>
       </c>
       <c r="AH31">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AI31">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ31">
         <v>13.5</v>
       </c>
       <c r="AK31">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL31">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="AM31">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
         <v>10.5</v>
       </c>
       <c r="AO31">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="AP31">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ31">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR31">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AS31">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT31">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU31">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV31">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW31">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="AX31">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY31">
         <v>9.4</v>
       </c>
       <c r="AZ31">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BA31">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="BB31">
         <v>12.5</v>
       </c>
       <c r="BC31">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD31">
         <v>42</v>
       </c>
       <c r="BE31">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="BF31">
         <v>9.6</v>
@@ -8434,163 +8434,163 @@
         <v>2.96</v>
       </c>
       <c r="G32">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H32">
         <v>2.04</v>
       </c>
       <c r="I32">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="J32">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="K32">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M32">
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="O32">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P32">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="Q32">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="R32">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="S32">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="T32">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="U32">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="V32">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W32">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X32">
+        <v>32</v>
+      </c>
+      <c r="Y32">
+        <v>18</v>
+      </c>
+      <c r="Z32">
+        <v>20</v>
+      </c>
+      <c r="AA32">
         <v>30</v>
       </c>
-      <c r="Y32">
-        <v>17.5</v>
-      </c>
-      <c r="Z32">
+      <c r="AB32">
+        <v>23</v>
+      </c>
+      <c r="AC32">
+        <v>11.5</v>
+      </c>
+      <c r="AD32">
+        <v>13</v>
+      </c>
+      <c r="AE32">
         <v>21</v>
       </c>
-      <c r="AA32">
+      <c r="AF32">
         <v>34</v>
       </c>
-      <c r="AB32">
-        <v>22</v>
-      </c>
-      <c r="AC32">
-        <v>12</v>
-      </c>
-      <c r="AD32">
-        <v>13.5</v>
-      </c>
-      <c r="AE32">
-        <v>24</v>
-      </c>
-      <c r="AF32">
+      <c r="AG32">
+        <v>16</v>
+      </c>
+      <c r="AH32">
+        <v>16</v>
+      </c>
+      <c r="AI32">
+        <v>27</v>
+      </c>
+      <c r="AJ32">
+        <v>55</v>
+      </c>
+      <c r="AK32">
         <v>32</v>
       </c>
-      <c r="AG32">
-        <v>17</v>
-      </c>
-      <c r="AH32">
-        <v>17.5</v>
-      </c>
-      <c r="AI32">
-        <v>32</v>
-      </c>
-      <c r="AJ32">
-        <v>60</v>
-      </c>
-      <c r="AK32">
+      <c r="AL32">
         <v>34</v>
       </c>
-      <c r="AL32">
-        <v>36</v>
-      </c>
       <c r="AM32">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN32">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AO32">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AP32">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AQ32">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="AR32">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS32">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AT32">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AU32">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AV32">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="AW32">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX32">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY32">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="AZ32">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BA32">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BB32">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BC32">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BD32">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE32">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF32">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG32">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8673,16 +8673,16 @@
         <v>181</v>
       </c>
       <c r="F33">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G33">
         <v>1.35</v>
       </c>
       <c r="H33">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I33">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J33">
         <v>6.2</v>
@@ -8691,7 +8691,7 @@
         <v>6.4</v>
       </c>
       <c r="L33">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M33">
         <v>1.03</v>
@@ -8703,22 +8703,22 @@
         <v>1.15</v>
       </c>
       <c r="P33">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q33">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R33">
         <v>1.83</v>
       </c>
       <c r="S33">
+        <v>2.16</v>
+      </c>
+      <c r="T33">
+        <v>1.79</v>
+      </c>
+      <c r="U33">
         <v>2.18</v>
-      </c>
-      <c r="T33">
-        <v>1.78</v>
-      </c>
-      <c r="U33">
-        <v>2.2</v>
       </c>
       <c r="V33">
         <v>1.1</v>
@@ -8733,7 +8733,7 @@
         <v>44</v>
       </c>
       <c r="Z33">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA33">
         <v>330</v>
@@ -8748,22 +8748,22 @@
         <v>36</v>
       </c>
       <c r="AE33">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF33">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG33">
         <v>10.5</v>
       </c>
       <c r="AH33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI33">
         <v>100</v>
       </c>
       <c r="AJ33">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK33">
         <v>12.5</v>
@@ -8775,7 +8775,7 @@
         <v>110</v>
       </c>
       <c r="AN33">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AO33">
         <v>140</v>
@@ -8787,19 +8787,19 @@
         <v>38</v>
       </c>
       <c r="AR33">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AS33">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AT33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU33">
         <v>13.5</v>
       </c>
       <c r="AV33">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AW33">
         <v>100</v>
@@ -8811,28 +8811,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB33">
         <v>11</v>
       </c>
       <c r="BC33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD33">
         <v>25</v>
       </c>
       <c r="BE33">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BF33">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BG33">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="BH33">
         <v>4.9</v>
@@ -8850,13 +8850,13 @@
         <v>110</v>
       </c>
       <c r="BM33">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN33">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO33">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BP33">
         <v>7.4</v>
@@ -8871,28 +8871,28 @@
         <v>16</v>
       </c>
       <c r="BT33">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BU33">
         <v>11</v>
       </c>
       <c r="BV33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BW33">
         <v>12</v>
       </c>
       <c r="BX33">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ33">
         <v>9.6</v>
       </c>
       <c r="CA33">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB33" t="s">
         <v>187</v>
@@ -8927,7 +8927,7 @@
         <v>3.2</v>
       </c>
       <c r="J34">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K34">
         <v>3.45</v>
@@ -8939,22 +8939,22 @@
         <v>1.08</v>
       </c>
       <c r="N34">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O34">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P34">
         <v>1.81</v>
       </c>
       <c r="Q34">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R34">
         <v>1.31</v>
       </c>
       <c r="S34">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T34">
         <v>1.85</v>
@@ -8963,13 +8963,13 @@
         <v>2.08</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
         <v>1.63</v>
       </c>
       <c r="X34">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y34">
         <v>11.5</v>
@@ -8978,16 +8978,16 @@
         <v>21</v>
       </c>
       <c r="AA34">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB34">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC34">
         <v>7.6</v>
       </c>
       <c r="AD34">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE34">
         <v>40</v>
@@ -8996,7 +8996,7 @@
         <v>16</v>
       </c>
       <c r="AG34">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH34">
         <v>18.5</v>
@@ -9008,7 +9008,7 @@
         <v>38</v>
       </c>
       <c r="AK34">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AL34">
         <v>46</v>
@@ -9017,10 +9017,10 @@
         <v>1000</v>
       </c>
       <c r="AN34">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AO34">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="AP34">
         <v>11</v>
@@ -9035,7 +9035,7 @@
         <v>48</v>
       </c>
       <c r="AT34">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU34">
         <v>7</v>
@@ -9053,13 +9053,13 @@
         <v>11</v>
       </c>
       <c r="AZ34">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA34">
         <v>44</v>
       </c>
       <c r="BB34">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC34">
         <v>26</v>
@@ -9068,10 +9068,10 @@
         <v>40</v>
       </c>
       <c r="BE34">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BF34">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG34">
         <v>34</v>
@@ -9160,16 +9160,16 @@
         <v>2.82</v>
       </c>
       <c r="G35">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H35">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I35">
         <v>3.05</v>
       </c>
       <c r="J35">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K35">
         <v>3.3</v>
@@ -9178,16 +9178,16 @@
         <v>1.48</v>
       </c>
       <c r="M35">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N35">
         <v>2.66</v>
       </c>
       <c r="O35">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P35">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q35">
         <v>2.48</v>
@@ -9199,10 +9199,10 @@
         <v>5</v>
       </c>
       <c r="T35">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U35">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V35">
         <v>1.5</v>
@@ -9214,16 +9214,16 @@
         <v>9.4</v>
       </c>
       <c r="Y35">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z35">
         <v>19</v>
       </c>
       <c r="AA35">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB35">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC35">
         <v>7.4</v>
@@ -9232,7 +9232,7 @@
         <v>14</v>
       </c>
       <c r="AE35">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF35">
         <v>18.5</v>
@@ -9253,13 +9253,13 @@
         <v>48</v>
       </c>
       <c r="AL35">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AM35">
         <v>190</v>
       </c>
       <c r="AN35">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO35">
         <v>60</v>
@@ -9274,10 +9274,10 @@
         <v>15.5</v>
       </c>
       <c r="AS35">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT35">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU35">
         <v>6.2</v>
@@ -9286,7 +9286,7 @@
         <v>11.5</v>
       </c>
       <c r="AW35">
-        <v>29</v>
+        <v>7.8</v>
       </c>
       <c r="AX35">
         <v>15.5</v>
@@ -9298,28 +9298,28 @@
         <v>18</v>
       </c>
       <c r="BA35">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB35">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC35">
         <v>32</v>
       </c>
       <c r="BD35">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE35">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF35">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="BG35">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH35">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI35">
         <v>2.34</v>
@@ -9328,13 +9328,13 @@
         <v>11</v>
       </c>
       <c r="BK35">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN35">
         <v>5.8</v>
@@ -9343,16 +9343,16 @@
         <v>4.5</v>
       </c>
       <c r="BP35">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ35">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR35">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS35">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT35">
         <v>5.9</v>
@@ -9364,19 +9364,19 @@
         <v>27</v>
       </c>
       <c r="BW35">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB35" t="s">
         <v>187</v>
@@ -9405,40 +9405,40 @@
         <v>2.42</v>
       </c>
       <c r="H36">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I36">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J36">
         <v>3.4</v>
       </c>
       <c r="K36">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L36">
         <v>1.33</v>
       </c>
       <c r="M36">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N36">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O36">
         <v>1.3</v>
       </c>
       <c r="P36">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="Q36">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R36">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S36">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="T36">
         <v>1.72</v>
@@ -9447,118 +9447,118 @@
         <v>2.02</v>
       </c>
       <c r="V36">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W36">
         <v>1.7</v>
       </c>
       <c r="X36">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y36">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z36">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA36">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB36">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC36">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD36">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE36">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF36">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG36">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH36">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI36">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ36">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK36">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL36">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM36">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN36">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO36">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP36">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ36">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR36">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS36">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT36">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU36">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV36">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW36">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX36">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY36">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ36">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA36">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB36">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC36">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD36">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE36">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF36">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG36">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9641,22 +9641,22 @@
         <v>185</v>
       </c>
       <c r="F37">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="G37">
-        <v>2.24</v>
+        <v>1.41</v>
       </c>
       <c r="H37">
-        <v>3.05</v>
+        <v>6.6</v>
       </c>
       <c r="I37">
-        <v>990</v>
+        <v>12</v>
       </c>
       <c r="J37">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="K37">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -9668,19 +9668,19 @@
         <v>1.1</v>
       </c>
       <c r="O37">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P37">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="Q37">
         <v>1.53</v>
       </c>
       <c r="R37">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S37">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="T37">
         <v>1.11</v>
@@ -9689,10 +9689,10 @@
         <v>1.11</v>
       </c>
       <c r="V37">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W37">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9707,10 +9707,10 @@
         <v>1000</v>
       </c>
       <c r="AB37">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC37">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD37">
         <v>1000</v>
@@ -9719,10 +9719,10 @@
         <v>1000</v>
       </c>
       <c r="AF37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG37">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH37">
         <v>1000</v>
@@ -9731,13 +9731,13 @@
         <v>1000</v>
       </c>
       <c r="AJ37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM37">
         <v>1000</v>
@@ -9749,58 +9749,58 @@
         <v>1000</v>
       </c>
       <c r="AP37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AQ37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AR37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AS37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AT37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AU37">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AV37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AW37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AX37">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AY37">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AZ37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="BA37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="BB37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="BC37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="BD37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="BE37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="BF37">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BG37">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9901,7 +9901,7 @@
         <v>3.6</v>
       </c>
       <c r="L38">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M38">
         <v>1.09</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -577,7 +577,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-25 19:51:41</t>
+    <t>2026-08-25 22:00:28</t>
   </si>
 </sst>
 </file>
@@ -1171,226 +1171,226 @@
         <v>150</v>
       </c>
       <c r="F2">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="G2">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="P2">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="Q2">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="S2">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="T2">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="U2">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="V2">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y2">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Z2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA2">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE2">
         <v>160</v>
       </c>
       <c r="AF2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AI2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AJ2">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AK2">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AM2">
-        <v>250</v>
+        <v>330</v>
       </c>
       <c r="AN2">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="AO2">
         <v>290</v>
       </c>
       <c r="AP2">
+        <v>9</v>
+      </c>
+      <c r="AQ2">
+        <v>16</v>
+      </c>
+      <c r="AR2">
+        <v>46</v>
+      </c>
+      <c r="AS2">
+        <v>150</v>
+      </c>
+      <c r="AT2">
+        <v>5.6</v>
+      </c>
+      <c r="AU2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2">
+        <v>25</v>
+      </c>
+      <c r="AW2">
+        <v>85</v>
+      </c>
+      <c r="AX2">
+        <v>7.2</v>
+      </c>
+      <c r="AY2">
+        <v>10.5</v>
+      </c>
+      <c r="AZ2">
+        <v>29</v>
+      </c>
+      <c r="BA2">
+        <v>80</v>
+      </c>
+      <c r="BB2">
+        <v>13.5</v>
+      </c>
+      <c r="BC2">
+        <v>20</v>
+      </c>
+      <c r="BD2">
+        <v>60</v>
+      </c>
+      <c r="BE2">
+        <v>110</v>
+      </c>
+      <c r="BF2">
+        <v>14</v>
+      </c>
+      <c r="BG2">
+        <v>170</v>
+      </c>
+      <c r="BH2">
+        <v>1.87</v>
+      </c>
+      <c r="BI2">
+        <v>1.82</v>
+      </c>
+      <c r="BJ2">
+        <v>26</v>
+      </c>
+      <c r="BK2">
+        <v>22</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
         <v>12.5</v>
       </c>
-      <c r="AQ2">
-        <v>20</v>
-      </c>
-      <c r="AR2">
-        <v>55</v>
-      </c>
-      <c r="AS2">
-        <v>200</v>
-      </c>
-      <c r="AT2">
-        <v>7.2</v>
-      </c>
-      <c r="AU2">
-        <v>9</v>
-      </c>
-      <c r="AV2">
-        <v>26</v>
-      </c>
-      <c r="AW2">
-        <v>110</v>
-      </c>
-      <c r="AX2">
-        <v>7</v>
-      </c>
-      <c r="AY2">
-        <v>10</v>
-      </c>
-      <c r="AZ2">
-        <v>26</v>
-      </c>
-      <c r="BA2">
-        <v>70</v>
-      </c>
-      <c r="BB2">
+      <c r="BN2">
+        <v>4.3</v>
+      </c>
+      <c r="BO2">
+        <v>3.9</v>
+      </c>
+      <c r="BP2">
+        <v>25</v>
+      </c>
+      <c r="BQ2">
+        <v>21</v>
+      </c>
+      <c r="BR2">
+        <v>180</v>
+      </c>
+      <c r="BS2">
+        <v>100</v>
+      </c>
+      <c r="BT2">
+        <v>11</v>
+      </c>
+      <c r="BU2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BV2">
+        <v>140</v>
+      </c>
+      <c r="BW2">
+        <v>100</v>
+      </c>
+      <c r="BX2">
+        <v>950</v>
+      </c>
+      <c r="BY2">
         <v>12</v>
       </c>
-      <c r="BC2">
-        <v>16</v>
-      </c>
-      <c r="BD2">
-        <v>44</v>
-      </c>
-      <c r="BE2">
-        <v>170</v>
-      </c>
-      <c r="BF2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG2">
-        <v>180</v>
-      </c>
-      <c r="BH2">
-        <v>3.35</v>
-      </c>
-      <c r="BI2">
-        <v>3.05</v>
-      </c>
-      <c r="BJ2">
-        <v>12.5</v>
-      </c>
-      <c r="BK2">
-        <v>6.2</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>170</v>
-      </c>
-      <c r="BN2">
-        <v>3.85</v>
-      </c>
-      <c r="BO2">
-        <v>3.45</v>
-      </c>
-      <c r="BP2">
-        <v>10.5</v>
-      </c>
-      <c r="BQ2">
-        <v>7.8</v>
-      </c>
-      <c r="BR2">
-        <v>32</v>
-      </c>
-      <c r="BS2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT2">
-        <v>11.5</v>
-      </c>
-      <c r="BU2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BV2">
+      <c r="BZ2">
+        <v>190</v>
+      </c>
+      <c r="CA2">
         <v>100</v>
-      </c>
-      <c r="BW2">
-        <v>11</v>
-      </c>
-      <c r="BX2">
-        <v>100</v>
-      </c>
-      <c r="BY2">
-        <v>11</v>
-      </c>
-      <c r="BZ2">
-        <v>22</v>
-      </c>
-      <c r="CA2">
-        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>187</v>
@@ -1419,31 +1419,31 @@
         <v>2.62</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J3">
+        <v>2.98</v>
+      </c>
+      <c r="K3">
         <v>3.05</v>
       </c>
-      <c r="K3">
-        <v>3.15</v>
-      </c>
       <c r="L3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="O3">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q3">
         <v>2.62</v>
@@ -1452,31 +1452,31 @@
         <v>1.21</v>
       </c>
       <c r="S3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T3">
         <v>2.08</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
         <v>1.61</v>
       </c>
       <c r="X3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3">
         <v>22</v>
       </c>
       <c r="AA3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB3">
         <v>8</v>
@@ -1491,73 +1491,73 @@
         <v>55</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG3">
         <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI3">
         <v>80</v>
       </c>
       <c r="AJ3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AK3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL3">
         <v>65</v>
       </c>
       <c r="AM3">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AN3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS3">
         <v>55</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
         <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY3">
         <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
         <v>65</v>
       </c>
       <c r="BB3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BC3">
         <v>29</v>
@@ -1566,34 +1566,34 @@
         <v>50</v>
       </c>
       <c r="BE3">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="BF3">
         <v>30</v>
       </c>
       <c r="BG3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH3">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="BI3">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK3">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="BN3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO3">
         <v>4.8</v>
@@ -1602,37 +1602,37 @@
         <v>24</v>
       </c>
       <c r="BQ3">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BR3">
         <v>44</v>
       </c>
       <c r="BS3">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BX3">
         <v>55</v>
       </c>
       <c r="BY3">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="BZ3">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="CA3">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB3" t="s">
         <v>187</v>
@@ -1691,7 +1691,7 @@
         <v>1.01</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S4">
         <v>1.05</v>
@@ -1897,13 +1897,13 @@
         <v>153</v>
       </c>
       <c r="F5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G5">
         <v>3.6</v>
       </c>
       <c r="H5">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I5">
         <v>2.42</v>
@@ -1921,7 +1921,7 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O5">
         <v>1.42</v>
@@ -2047,13 +2047,13 @@
         <v>30</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BE5">
         <v>60</v>
       </c>
       <c r="BF5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BG5">
         <v>20</v>
@@ -2065,7 +2065,7 @@
         <v>2.46</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BK5">
         <v>8.199999999999999</v>
@@ -2074,7 +2074,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN5">
         <v>6.6</v>
@@ -2086,16 +2086,16 @@
         <v>38</v>
       </c>
       <c r="BQ5">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR5">
         <v>60</v>
       </c>
       <c r="BS5">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BT5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU5">
         <v>4.5</v>
@@ -2104,19 +2104,19 @@
         <v>21</v>
       </c>
       <c r="BW5">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BX5">
         <v>46</v>
       </c>
       <c r="BY5">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BZ5">
         <v>42</v>
       </c>
       <c r="CA5">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB5" t="s">
         <v>187</v>
@@ -2142,10 +2142,10 @@
         <v>2.38</v>
       </c>
       <c r="G6">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H6">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>3.2</v>
@@ -2175,7 +2175,7 @@
         <v>1.77</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S6">
         <v>2.96</v>
@@ -2187,10 +2187,10 @@
         <v>2.42</v>
       </c>
       <c r="V6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="X6">
         <v>19</v>
@@ -2199,7 +2199,7 @@
         <v>15</v>
       </c>
       <c r="Z6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA6">
         <v>120</v>
@@ -2214,7 +2214,7 @@
         <v>13.5</v>
       </c>
       <c r="AE6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF6">
         <v>17.5</v>
@@ -2229,7 +2229,7 @@
         <v>80</v>
       </c>
       <c r="AJ6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK6">
         <v>30</v>
@@ -2241,10 +2241,10 @@
         <v>200</v>
       </c>
       <c r="AN6">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP6">
         <v>16.5</v>
@@ -2256,7 +2256,7 @@
         <v>20</v>
       </c>
       <c r="AS6">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AT6">
         <v>11</v>
@@ -2268,7 +2268,7 @@
         <v>12</v>
       </c>
       <c r="AW6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX6">
         <v>15</v>
@@ -2286,13 +2286,13 @@
         <v>24</v>
       </c>
       <c r="BC6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE6">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BF6">
         <v>14.5</v>
@@ -2301,10 +2301,10 @@
         <v>21</v>
       </c>
       <c r="BH6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI6">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BJ6">
         <v>8.800000000000001</v>
@@ -2316,10 +2316,10 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN6">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO6">
         <v>4.9</v>
@@ -2328,13 +2328,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ6">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR6">
         <v>27</v>
       </c>
       <c r="BS6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
         <v>6.4</v>
@@ -2346,19 +2346,19 @@
         <v>22</v>
       </c>
       <c r="BW6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6">
         <v>20</v>
       </c>
       <c r="CA6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="s">
         <v>187</v>
@@ -2384,7 +2384,7 @@
         <v>1.56</v>
       </c>
       <c r="G7">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H7">
         <v>7.4</v>
@@ -2393,13 +2393,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K7">
         <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M7">
         <v>1.08</v>
@@ -2420,7 +2420,7 @@
         <v>1.31</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T7">
         <v>2.22</v>
@@ -2432,7 +2432,7 @@
         <v>1.14</v>
       </c>
       <c r="W7">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X7">
         <v>13</v>
@@ -2474,43 +2474,43 @@
         <v>14.5</v>
       </c>
       <c r="AK7">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL7">
         <v>60</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AN7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO7">
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR7">
         <v>36</v>
       </c>
       <c r="AS7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT7">
         <v>6.4</v>
       </c>
       <c r="AU7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV7">
         <v>22</v>
       </c>
       <c r="AW7">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AX7">
         <v>7.4</v>
@@ -2519,7 +2519,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA7">
         <v>11</v>
@@ -2540,7 +2540,7 @@
         <v>9.4</v>
       </c>
       <c r="BG7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH7">
         <v>3.75</v>
@@ -2564,13 +2564,13 @@
         <v>3.95</v>
       </c>
       <c r="BO7">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BP7">
         <v>11</v>
       </c>
       <c r="BQ7">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR7">
         <v>32</v>
@@ -2623,7 +2623,7 @@
         <v>156</v>
       </c>
       <c r="F8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G8">
         <v>1.04</v>
@@ -2632,7 +2632,7 @@
         <v>28</v>
       </c>
       <c r="I8">
-        <v>990</v>
+        <v>870</v>
       </c>
       <c r="J8">
         <v>27</v>
@@ -2662,7 +2662,7 @@
         <v>2.66</v>
       </c>
       <c r="S8">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2740,7 +2740,7 @@
         <v>2.5</v>
       </c>
       <c r="AS8">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT8">
         <v>1.34</v>
@@ -2782,7 +2782,7 @@
         <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2871,7 +2871,7 @@
         <v>29</v>
       </c>
       <c r="H9">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="I9">
         <v>1.6</v>
@@ -2880,7 +2880,7 @@
         <v>3.75</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2892,7 +2892,7 @@
         <v>1.1</v>
       </c>
       <c r="O9">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
         <v>1.25</v>
@@ -2904,7 +2904,7 @@
         <v>1.23</v>
       </c>
       <c r="S9">
-        <v>2.34</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2922,10 +2922,10 @@
         <v>1000</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z9">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AA9">
         <v>900</v>
@@ -2940,7 +2940,7 @@
         <v>950</v>
       </c>
       <c r="AE9">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AF9">
         <v>1000</v>
@@ -2952,7 +2952,7 @@
         <v>1000</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ9">
         <v>1000</v>
@@ -2970,61 +2970,61 @@
         <v>1000</v>
       </c>
       <c r="AO9">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AP9">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AQ9">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AR9">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AS9">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AT9">
-        <v>1.16</v>
+        <v>2.5</v>
       </c>
       <c r="AU9">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="AV9">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AW9">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AX9">
-        <v>1.16</v>
+        <v>2.5</v>
       </c>
       <c r="AY9">
-        <v>1.16</v>
+        <v>2.5</v>
       </c>
       <c r="AZ9">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="BA9">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="BB9">
-        <v>1.16</v>
+        <v>2.5</v>
       </c>
       <c r="BC9">
-        <v>1.16</v>
+        <v>2.5</v>
       </c>
       <c r="BD9">
-        <v>1.16</v>
+        <v>2.5</v>
       </c>
       <c r="BE9">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="BF9">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BG9">
-        <v>4</v>
+        <v>1.17</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3107,34 +3107,34 @@
         <v>158</v>
       </c>
       <c r="F10">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G10">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="H10">
         <v>6.2</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J10">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K10">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="L10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N10">
-        <v>2.12</v>
+        <v>2.52</v>
       </c>
       <c r="O10">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="P10">
         <v>1.39</v>
@@ -3155,10 +3155,10 @@
         <v>1.45</v>
       </c>
       <c r="V10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W10">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3355,13 +3355,13 @@
         <v>3.6</v>
       </c>
       <c r="H11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I11">
         <v>2.44</v>
       </c>
       <c r="J11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
         <v>4</v>
@@ -3403,7 +3403,7 @@
         <v>1.39</v>
       </c>
       <c r="X11">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y11">
         <v>12.5</v>
@@ -3457,43 +3457,43 @@
         <v>16.5</v>
       </c>
       <c r="AP11">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AQ11">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS11">
         <v>16</v>
       </c>
       <c r="AT11">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU11">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW11">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX11">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ11">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA11">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BB11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC11">
         <v>14.5</v>
@@ -3505,10 +3505,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3591,19 +3591,19 @@
         <v>160</v>
       </c>
       <c r="F12">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="G12">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>1.87</v>
       </c>
       <c r="I12">
-        <v>2.16</v>
+        <v>4.9</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K12">
         <v>3.95</v>
@@ -3615,7 +3615,7 @@
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="O12">
         <v>1.14</v>
@@ -3639,112 +3639,112 @@
         <v>1.12</v>
       </c>
       <c r="V12">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="W12">
         <v>1.25</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z12">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AA12">
         <v>900</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC12">
         <v>950</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AO12">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AP12">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AQ12">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR12">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AS12">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AT12">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AU12">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AV12">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AW12">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AX12">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AY12">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AZ12">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="BA12">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="BB12">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="BC12">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="BD12">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="BE12">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="BF12">
         <v>1.55</v>
@@ -3833,10 +3833,10 @@
         <v>161</v>
       </c>
       <c r="F13">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H13">
         <v>3.7</v>
@@ -3848,7 +3848,7 @@
         <v>4.2</v>
       </c>
       <c r="K13">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3866,13 +3866,13 @@
         <v>2.62</v>
       </c>
       <c r="Q13">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R13">
         <v>1.65</v>
       </c>
       <c r="S13">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T13">
         <v>1.56</v>
@@ -3890,7 +3890,7 @@
         <v>32</v>
       </c>
       <c r="Y13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z13">
         <v>38</v>
@@ -3911,7 +3911,7 @@
         <v>44</v>
       </c>
       <c r="AF13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG13">
         <v>11</v>
@@ -3929,13 +3929,13 @@
         <v>21</v>
       </c>
       <c r="AL13">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AM13">
         <v>200</v>
       </c>
       <c r="AN13">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO13">
         <v>29</v>
@@ -3947,7 +3947,7 @@
         <v>14.5</v>
       </c>
       <c r="AR13">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AS13">
         <v>30</v>
@@ -3986,31 +3986,31 @@
         <v>16</v>
       </c>
       <c r="BE13">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF13">
         <v>6.8</v>
       </c>
       <c r="BG13">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH13">
         <v>5.1</v>
       </c>
       <c r="BI13">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ13">
         <v>9.800000000000001</v>
       </c>
       <c r="BK13">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BN13">
         <v>5.9</v>
@@ -4019,16 +4019,16 @@
         <v>4.3</v>
       </c>
       <c r="BP13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR13">
         <v>24</v>
       </c>
       <c r="BS13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BT13">
         <v>8.6</v>
@@ -4040,16 +4040,16 @@
         <v>30</v>
       </c>
       <c r="BW13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BX13">
         <v>34</v>
       </c>
       <c r="BY13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ13">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA13">
         <v>4.3</v>
@@ -4081,10 +4081,10 @@
         <v>2.76</v>
       </c>
       <c r="H14">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I14">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J14">
         <v>3.45</v>
@@ -4123,10 +4123,10 @@
         <v>2.28</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W14">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X14">
         <v>17</v>
@@ -4135,7 +4135,7 @@
         <v>13</v>
       </c>
       <c r="Z14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA14">
         <v>55</v>
@@ -4204,7 +4204,7 @@
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX14">
         <v>16.5</v>
@@ -4216,7 +4216,7 @@
         <v>13.5</v>
       </c>
       <c r="BA14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB14">
         <v>7.4</v>
@@ -4225,10 +4225,10 @@
         <v>6.8</v>
       </c>
       <c r="BD14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF14">
         <v>20</v>
@@ -4341,19 +4341,19 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
         <v>1.01</v>
       </c>
       <c r="P15">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q15">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R15">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S15">
         <v>2.88</v>
@@ -4392,10 +4392,10 @@
         <v>15</v>
       </c>
       <c r="AE15">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF15">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AG15">
         <v>20</v>
@@ -4404,16 +4404,16 @@
         <v>25</v>
       </c>
       <c r="AI15">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ15">
         <v>900</v>
       </c>
       <c r="AK15">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL15">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM15">
         <v>1000</v>
@@ -4425,16 +4425,16 @@
         <v>27</v>
       </c>
       <c r="AP15">
-        <v>2.7</v>
+        <v>9</v>
       </c>
       <c r="AQ15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR15">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AS15">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT15">
         <v>8.6</v>
@@ -4449,10 +4449,10 @@
         <v>16</v>
       </c>
       <c r="AX15">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY15">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15">
         <v>11.5</v>
@@ -4464,7 +4464,7 @@
         <v>3</v>
       </c>
       <c r="BC15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BD15">
         <v>3</v>
@@ -4473,7 +4473,7 @@
         <v>3.1</v>
       </c>
       <c r="BF15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BG15">
         <v>12</v>
@@ -4565,7 +4565,7 @@
         <v>1.63</v>
       </c>
       <c r="H16">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>5.6</v>
@@ -4598,19 +4598,19 @@
         <v>2.28</v>
       </c>
       <c r="S16">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T16">
         <v>1.4</v>
       </c>
       <c r="U16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V16">
         <v>1.21</v>
       </c>
       <c r="W16">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X16">
         <v>70</v>
@@ -4646,7 +4646,7 @@
         <v>17</v>
       </c>
       <c r="AI16">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ16">
         <v>20</v>
@@ -4697,7 +4697,7 @@
         <v>11</v>
       </c>
       <c r="AZ16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA16">
         <v>25</v>
@@ -4804,13 +4804,13 @@
         <v>2.66</v>
       </c>
       <c r="G17">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H17">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I17">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="J17">
         <v>4.3</v>
@@ -4825,7 +4825,7 @@
         <v>1.02</v>
       </c>
       <c r="N17">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="O17">
         <v>1.09</v>
@@ -4837,22 +4837,22 @@
         <v>1.32</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S17">
         <v>1.8</v>
       </c>
       <c r="T17">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="U17">
         <v>3.35</v>
       </c>
       <c r="V17">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W17">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X17">
         <v>55</v>
@@ -4864,7 +4864,7 @@
         <v>80</v>
       </c>
       <c r="AA17">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB17">
         <v>85</v>
@@ -4873,7 +4873,7 @@
         <v>14.5</v>
       </c>
       <c r="AD17">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE17">
         <v>23</v>
@@ -4900,7 +4900,7 @@
         <v>75</v>
       </c>
       <c r="AM17">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN17">
         <v>10</v>
@@ -4909,7 +4909,7 @@
         <v>8.4</v>
       </c>
       <c r="AP17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ17">
         <v>6.4</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="AT17">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU17">
         <v>11.5</v>
@@ -4945,7 +4945,7 @@
         <v>18.5</v>
       </c>
       <c r="BB17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC17">
         <v>20</v>
@@ -4954,7 +4954,7 @@
         <v>20</v>
       </c>
       <c r="BE17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF17">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.32</v>
       </c>
       <c r="H18">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I18">
         <v>12</v>
@@ -5079,10 +5079,10 @@
         <v>1.27</v>
       </c>
       <c r="R18">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S18">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T18">
         <v>1.54</v>
@@ -5094,7 +5094,7 @@
         <v>1.09</v>
       </c>
       <c r="W18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="X18">
         <v>70</v>
@@ -5151,10 +5151,10 @@
         <v>95</v>
       </c>
       <c r="AP18">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ18">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR18">
         <v>7</v>
@@ -5199,7 +5199,7 @@
         <v>6.8</v>
       </c>
       <c r="BF18">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BG18">
         <v>10.5</v>
@@ -5214,13 +5214,13 @@
         <v>12</v>
       </c>
       <c r="BK18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BL18">
         <v>85</v>
       </c>
       <c r="BM18">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN18">
         <v>4.9</v>
@@ -5238,31 +5238,31 @@
         <v>18.5</v>
       </c>
       <c r="BS18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT18">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BU18">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV18">
         <v>75</v>
       </c>
       <c r="BW18">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX18">
         <v>55</v>
       </c>
       <c r="BY18">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ18">
         <v>7.4</v>
       </c>
       <c r="CA18">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB18" t="s">
         <v>187</v>
@@ -5285,22 +5285,22 @@
         <v>167</v>
       </c>
       <c r="F19">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G19">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I19">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J19">
         <v>4.2</v>
       </c>
       <c r="K19">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5333,10 +5333,10 @@
         <v>3</v>
       </c>
       <c r="V19">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W19">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X19">
         <v>950</v>
@@ -5345,22 +5345,22 @@
         <v>970</v>
       </c>
       <c r="Z19">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AA19">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB19">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AC19">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD19">
         <v>14.5</v>
       </c>
       <c r="AE19">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AF19">
         <v>90</v>
@@ -5372,16 +5372,16 @@
         <v>17</v>
       </c>
       <c r="AI19">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AJ19">
-        <v>290</v>
+        <v>900</v>
       </c>
       <c r="AK19">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AL19">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM19">
         <v>580</v>
@@ -5393,19 +5393,19 @@
         <v>8.4</v>
       </c>
       <c r="AP19">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AQ19">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="AR19">
         <v>14.5</v>
       </c>
       <c r="AS19">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="AT19">
-        <v>18</v>
+        <v>2.28</v>
       </c>
       <c r="AU19">
         <v>9.199999999999999</v>
@@ -5414,37 +5414,37 @@
         <v>9.6</v>
       </c>
       <c r="AW19">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="AX19">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AY19">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="AZ19">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="BA19">
         <v>19.5</v>
       </c>
       <c r="BB19">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="BC19">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BD19">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="BE19">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="BF19">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="BG19">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5536,7 +5536,7 @@
         <v>6.2</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J20">
         <v>5.9</v>
@@ -5781,10 +5781,10 @@
         <v>2.74</v>
       </c>
       <c r="J21">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K21">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5793,13 +5793,13 @@
         <v>1.14</v>
       </c>
       <c r="N21">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O21">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P21">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q21">
         <v>2.78</v>
@@ -5817,7 +5817,7 @@
         <v>1.75</v>
       </c>
       <c r="V21">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W21">
         <v>1.36</v>
@@ -5826,7 +5826,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="Z21">
         <v>17.5</v>
@@ -5835,7 +5835,7 @@
         <v>48</v>
       </c>
       <c r="AB21">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -5850,7 +5850,7 @@
         <v>25</v>
       </c>
       <c r="AG21">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH21">
         <v>25</v>
@@ -5868,10 +5868,10 @@
         <v>460</v>
       </c>
       <c r="AM21">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN21">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="AO21">
         <v>48</v>
@@ -5880,7 +5880,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ21">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR21">
         <v>13</v>
@@ -5898,7 +5898,7 @@
         <v>12</v>
       </c>
       <c r="AW21">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX21">
         <v>19</v>
@@ -5907,22 +5907,22 @@
         <v>14.5</v>
       </c>
       <c r="AZ21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA21">
+        <v>7.6</v>
+      </c>
+      <c r="BB21">
+        <v>7.6</v>
+      </c>
+      <c r="BC21">
         <v>7.4</v>
       </c>
-      <c r="BB21">
-        <v>7.4</v>
-      </c>
-      <c r="BC21">
-        <v>7.2</v>
-      </c>
       <c r="BD21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE21">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF21">
         <v>7.6</v>
@@ -5934,7 +5934,7 @@
         <v>2.7</v>
       </c>
       <c r="BI21">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="BJ21">
         <v>11.5</v>
@@ -6011,13 +6011,13 @@
         <v>170</v>
       </c>
       <c r="F22">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="G22">
         <v>3.7</v>
       </c>
       <c r="H22">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="I22">
         <v>2.54</v>
@@ -6026,7 +6026,7 @@
         <v>3.05</v>
       </c>
       <c r="K22">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6122,7 +6122,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ22">
-        <v>6.6</v>
+        <v>2.34</v>
       </c>
       <c r="AR22">
         <v>12</v>
@@ -6131,7 +6131,7 @@
         <v>2.76</v>
       </c>
       <c r="AT22">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU22">
         <v>5.7</v>
@@ -6146,7 +6146,7 @@
         <v>17</v>
       </c>
       <c r="AY22">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ22">
         <v>14.5</v>
@@ -6253,19 +6253,19 @@
         <v>171</v>
       </c>
       <c r="F23">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G23">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H23">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="I23">
         <v>3.2</v>
       </c>
       <c r="J23">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -6292,7 +6292,7 @@
         <v>2.16</v>
       </c>
       <c r="S23">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="T23">
         <v>1.33</v>
@@ -6301,7 +6301,7 @@
         <v>3.5</v>
       </c>
       <c r="V23">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W23">
         <v>1.73</v>
@@ -6337,7 +6337,7 @@
         <v>14.5</v>
       </c>
       <c r="AH23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI23">
         <v>29</v>
@@ -6355,13 +6355,13 @@
         <v>36</v>
       </c>
       <c r="AN23">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO23">
         <v>10.5</v>
       </c>
       <c r="AP23">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ23">
         <v>14.5</v>
@@ -6397,7 +6397,7 @@
         <v>19</v>
       </c>
       <c r="BB23">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC23">
         <v>17</v>
@@ -6409,7 +6409,7 @@
         <v>14.5</v>
       </c>
       <c r="BF23">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG23">
         <v>8.6</v>
@@ -6436,7 +6436,7 @@
         <v>7.8</v>
       </c>
       <c r="BO23">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP23">
         <v>16.5</v>
@@ -6504,13 +6504,13 @@
         <v>15</v>
       </c>
       <c r="I24">
-        <v>990</v>
+        <v>30</v>
       </c>
       <c r="J24">
         <v>5.6</v>
       </c>
       <c r="K24">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="L24">
         <v>1.27</v>
@@ -6519,7 +6519,7 @@
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="O24">
         <v>1.03</v>
@@ -6528,7 +6528,7 @@
         <v>2.02</v>
       </c>
       <c r="Q24">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R24">
         <v>1.4</v>
@@ -6597,16 +6597,16 @@
         <v>1000</v>
       </c>
       <c r="AN24">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="AO24">
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AQ24">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR24">
         <v>4.2</v>
@@ -6615,13 +6615,13 @@
         <v>4.2</v>
       </c>
       <c r="AT24">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AU24">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AV24">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AW24">
         <v>4.2</v>
@@ -6633,7 +6633,7 @@
         <v>8</v>
       </c>
       <c r="AZ24">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="BA24">
         <v>4.2</v>
@@ -6642,16 +6642,16 @@
         <v>7.4</v>
       </c>
       <c r="BC24">
-        <v>2.42</v>
+        <v>12</v>
       </c>
       <c r="BD24">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="BE24">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="BF24">
-        <v>4</v>
+        <v>2.02</v>
       </c>
       <c r="BG24">
         <v>5</v>
@@ -6737,7 +6737,7 @@
         <v>173</v>
       </c>
       <c r="F25">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G25">
         <v>2.92</v>
@@ -6782,7 +6782,7 @@
         <v>1.98</v>
       </c>
       <c r="U25">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="V25">
         <v>1.39</v>
@@ -6988,7 +6988,7 @@
         <v>4.5</v>
       </c>
       <c r="I26">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J26">
         <v>2.84</v>
@@ -7003,16 +7003,16 @@
         <v>1.15</v>
       </c>
       <c r="N26">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O26">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P26">
         <v>1.41</v>
       </c>
       <c r="Q26">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="R26">
         <v>1.14</v>
@@ -7036,7 +7036,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z26">
         <v>36</v>
@@ -7096,7 +7096,7 @@
         <v>23</v>
       </c>
       <c r="AS26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT26">
         <v>5.2</v>
@@ -7120,7 +7120,7 @@
         <v>16</v>
       </c>
       <c r="BA26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB26">
         <v>19</v>
@@ -7132,13 +7132,13 @@
         <v>30</v>
       </c>
       <c r="BE26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF26">
         <v>24</v>
       </c>
       <c r="BG26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH26">
         <v>2.74</v>
@@ -7227,10 +7227,10 @@
         <v>5.3</v>
       </c>
       <c r="H27">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I27">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J27">
         <v>2.9</v>
@@ -7269,7 +7269,7 @@
         <v>1.64</v>
       </c>
       <c r="V27">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="W27">
         <v>1.23</v>
@@ -7308,16 +7308,16 @@
         <v>34</v>
       </c>
       <c r="AI27">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ27">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AK27">
         <v>120</v>
       </c>
       <c r="AL27">
-        <v>150</v>
+        <v>540</v>
       </c>
       <c r="AM27">
         <v>310</v>
@@ -7329,7 +7329,7 @@
         <v>40</v>
       </c>
       <c r="AP27">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ27">
         <v>5.5</v>
@@ -7350,7 +7350,7 @@
         <v>10</v>
       </c>
       <c r="AW27">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="AX27">
         <v>28</v>
@@ -7359,16 +7359,16 @@
         <v>18</v>
       </c>
       <c r="AZ27">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="BA27">
         <v>5.4</v>
       </c>
       <c r="BB27">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC27">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD27">
         <v>5.6</v>
@@ -7377,10 +7377,10 @@
         <v>5.7</v>
       </c>
       <c r="BF27">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG27">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7463,22 +7463,22 @@
         <v>176</v>
       </c>
       <c r="F28">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="G28">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="H28">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I28">
         <v>16</v>
       </c>
       <c r="J28">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K28">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7493,7 +7493,7 @@
         <v>1.27</v>
       </c>
       <c r="P28">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="Q28">
         <v>1.36</v>
@@ -7502,7 +7502,7 @@
         <v>1.18</v>
       </c>
       <c r="S28">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
         <v>1.11</v>
@@ -7514,16 +7514,16 @@
         <v>1.22</v>
       </c>
       <c r="W28">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y28">
         <v>950</v>
       </c>
       <c r="Z28">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AA28">
         <v>900</v>
@@ -7538,49 +7538,49 @@
         <v>950</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG28">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH28">
         <v>950</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ28">
         <v>900</v>
       </c>
       <c r="AK28">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AL28">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN28">
         <v>970</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP28">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AQ28">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR28">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AS28">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AT28">
         <v>5.6</v>
@@ -7589,34 +7589,34 @@
         <v>4.9</v>
       </c>
       <c r="AV28">
+        <v>1.33</v>
+      </c>
+      <c r="AW28">
+        <v>1.34</v>
+      </c>
+      <c r="AX28">
         <v>1.3</v>
-      </c>
-      <c r="AW28">
-        <v>1.32</v>
-      </c>
-      <c r="AX28">
-        <v>1.31</v>
       </c>
       <c r="AY28">
         <v>5.8</v>
       </c>
       <c r="AZ28">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="BA28">
+        <v>1.34</v>
+      </c>
+      <c r="BB28">
+        <v>1.33</v>
+      </c>
+      <c r="BC28">
         <v>1.32</v>
       </c>
-      <c r="BB28">
-        <v>1.3</v>
-      </c>
-      <c r="BC28">
-        <v>1.29</v>
-      </c>
       <c r="BD28">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BE28">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="BF28">
         <v>3.2</v>
@@ -7705,22 +7705,22 @@
         <v>177</v>
       </c>
       <c r="F29">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="G29">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="H29">
+        <v>3</v>
+      </c>
+      <c r="I29">
         <v>3.1</v>
-      </c>
-      <c r="I29">
-        <v>3.2</v>
       </c>
       <c r="J29">
         <v>3.8</v>
       </c>
       <c r="K29">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7747,97 +7747,97 @@
         <v>2.44</v>
       </c>
       <c r="T29">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U29">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="V29">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="X29">
         <v>25</v>
       </c>
       <c r="Y29">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z29">
+        <v>26</v>
+      </c>
+      <c r="AA29">
+        <v>50</v>
+      </c>
+      <c r="AB29">
+        <v>17.5</v>
+      </c>
+      <c r="AC29">
+        <v>9</v>
+      </c>
+      <c r="AD29">
+        <v>13</v>
+      </c>
+      <c r="AE29">
         <v>28</v>
       </c>
-      <c r="AA29">
-        <v>120</v>
-      </c>
-      <c r="AB29">
-        <v>17</v>
-      </c>
-      <c r="AC29">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD29">
-        <v>14</v>
-      </c>
-      <c r="AE29">
-        <v>32</v>
-      </c>
       <c r="AF29">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AG29">
         <v>11.5</v>
       </c>
       <c r="AH29">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI29">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ29">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK29">
         <v>21</v>
       </c>
       <c r="AL29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM29">
         <v>55</v>
       </c>
       <c r="AN29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO29">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AP29">
         <v>22</v>
       </c>
       <c r="AQ29">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS29">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AT29">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU29">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV29">
         <v>12</v>
       </c>
       <c r="AW29">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX29">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY29">
         <v>10</v>
@@ -7846,13 +7846,13 @@
         <v>12.5</v>
       </c>
       <c r="BA29">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BB29">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC29">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BD29">
         <v>24</v>
@@ -7864,7 +7864,7 @@
         <v>11</v>
       </c>
       <c r="BG29">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7947,19 +7947,19 @@
         <v>178</v>
       </c>
       <c r="F30">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G30">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I30">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J30">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K30">
         <v>3.85</v>
@@ -7974,13 +7974,13 @@
         <v>4.2</v>
       </c>
       <c r="O30">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P30">
         <v>2.1</v>
       </c>
       <c r="Q30">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R30">
         <v>1.43</v>
@@ -7995,19 +7995,19 @@
         <v>2.24</v>
       </c>
       <c r="V30">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W30">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="X30">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y30">
         <v>16</v>
       </c>
       <c r="Z30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA30">
         <v>80</v>
@@ -8016,10 +8016,10 @@
         <v>10.5</v>
       </c>
       <c r="AC30">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD30">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE30">
         <v>55</v>
@@ -8049,7 +8049,7 @@
         <v>190</v>
       </c>
       <c r="AN30">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO30">
         <v>44</v>
@@ -8061,7 +8061,7 @@
         <v>15</v>
       </c>
       <c r="AR30">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AS30">
         <v>40</v>
@@ -8094,16 +8094,16 @@
         <v>21</v>
       </c>
       <c r="BC30">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE30">
         <v>46</v>
       </c>
       <c r="BF30">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG30">
         <v>38</v>
@@ -8124,7 +8124,7 @@
         <v>120</v>
       </c>
       <c r="BM30">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BN30">
         <v>5.5</v>
@@ -8157,7 +8157,7 @@
         <v>6.2</v>
       </c>
       <c r="BX30">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BY30">
         <v>6.4</v>
@@ -8166,7 +8166,7 @@
         <v>22</v>
       </c>
       <c r="CA30">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB30" t="s">
         <v>187</v>
@@ -8198,13 +8198,13 @@
         <v>7.6</v>
       </c>
       <c r="I31">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J31">
         <v>4.4</v>
       </c>
       <c r="K31">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L31">
         <v>1.34</v>
@@ -8213,16 +8213,16 @@
         <v>1.08</v>
       </c>
       <c r="N31">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O31">
         <v>1.38</v>
       </c>
       <c r="P31">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Q31">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R31">
         <v>1.3</v>
@@ -8231,16 +8231,16 @@
         <v>3.95</v>
       </c>
       <c r="T31">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U31">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V31">
         <v>1.14</v>
       </c>
       <c r="W31">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="X31">
         <v>13</v>
@@ -8249,7 +8249,7 @@
         <v>22</v>
       </c>
       <c r="Z31">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AA31">
         <v>1000</v>
@@ -8264,28 +8264,28 @@
         <v>32</v>
       </c>
       <c r="AE31">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF31">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG31">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH31">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AI31">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ31">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK31">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL31">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AM31">
         <v>1000</v>
@@ -8294,7 +8294,7 @@
         <v>10.5</v>
       </c>
       <c r="AO31">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AP31">
         <v>12</v>
@@ -8306,13 +8306,13 @@
         <v>55</v>
       </c>
       <c r="AS31">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT31">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU31">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV31">
         <v>27</v>
@@ -8321,19 +8321,19 @@
         <v>42</v>
       </c>
       <c r="AX31">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AY31">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ31">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA31">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB31">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC31">
         <v>17</v>
@@ -8342,10 +8342,10 @@
         <v>42</v>
       </c>
       <c r="BE31">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BF31">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG31">
         <v>48</v>
@@ -8431,7 +8431,7 @@
         <v>180</v>
       </c>
       <c r="F32">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G32">
         <v>3.6</v>
@@ -8440,40 +8440,40 @@
         <v>2.04</v>
       </c>
       <c r="I32">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J32">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K32">
         <v>4.6</v>
       </c>
       <c r="L32">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M32">
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>3.65</v>
+        <v>5.7</v>
       </c>
       <c r="O32">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P32">
         <v>2.56</v>
       </c>
       <c r="Q32">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R32">
         <v>1.68</v>
       </c>
       <c r="S32">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T32">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U32">
         <v>2.68</v>
@@ -8488,22 +8488,22 @@
         <v>32</v>
       </c>
       <c r="Y32">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z32">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA32">
         <v>30</v>
       </c>
       <c r="AB32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC32">
         <v>11.5</v>
       </c>
       <c r="AD32">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE32">
         <v>21</v>
@@ -8539,58 +8539,58 @@
         <v>10</v>
       </c>
       <c r="AP32">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ32">
+        <v>13.5</v>
+      </c>
+      <c r="AR32">
+        <v>15</v>
+      </c>
+      <c r="AS32">
+        <v>6.4</v>
+      </c>
+      <c r="AT32">
+        <v>5.9</v>
+      </c>
+      <c r="AU32">
+        <v>4.7</v>
+      </c>
+      <c r="AV32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW32">
+        <v>16</v>
+      </c>
+      <c r="AX32">
+        <v>6.8</v>
+      </c>
+      <c r="AY32">
+        <v>12</v>
+      </c>
+      <c r="AZ32">
         <v>5.3</v>
       </c>
-      <c r="AR32">
-        <v>5.5</v>
-      </c>
-      <c r="AS32">
-        <v>6</v>
-      </c>
-      <c r="AT32">
-        <v>5.7</v>
-      </c>
-      <c r="AU32">
-        <v>4.5</v>
-      </c>
-      <c r="AV32">
+      <c r="BA32">
         <v>6.2</v>
       </c>
-      <c r="AW32">
-        <v>5.6</v>
-      </c>
-      <c r="AX32">
-        <v>6.2</v>
-      </c>
-      <c r="AY32">
-        <v>5.1</v>
-      </c>
-      <c r="AZ32">
-        <v>5.1</v>
-      </c>
-      <c r="BA32">
-        <v>5.9</v>
-      </c>
       <c r="BB32">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC32">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BD32">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE32">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF32">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="BG32">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8694,13 +8694,13 @@
         <v>1.25</v>
       </c>
       <c r="M33">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O33">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P33">
         <v>3.05</v>
@@ -8709,7 +8709,7 @@
         <v>1.46</v>
       </c>
       <c r="R33">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S33">
         <v>2.16</v>
@@ -8727,19 +8727,19 @@
         <v>3.85</v>
       </c>
       <c r="X33">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y33">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Z33">
         <v>110</v>
       </c>
       <c r="AA33">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AB33">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC33">
         <v>14.5</v>
@@ -8751,7 +8751,7 @@
         <v>140</v>
       </c>
       <c r="AF33">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG33">
         <v>10.5</v>
@@ -8769,22 +8769,22 @@
         <v>12.5</v>
       </c>
       <c r="AL33">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM33">
         <v>110</v>
       </c>
       <c r="AN33">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AO33">
         <v>140</v>
       </c>
       <c r="AP33">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AR33">
         <v>95</v>
@@ -8799,7 +8799,7 @@
         <v>13.5</v>
       </c>
       <c r="AV33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AW33">
         <v>100</v>
@@ -8826,13 +8826,13 @@
         <v>25</v>
       </c>
       <c r="BE33">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF33">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BG33">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BH33">
         <v>4.9</v>
@@ -8874,7 +8874,7 @@
         <v>13</v>
       </c>
       <c r="BU33">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BV33">
         <v>75</v>
@@ -8939,16 +8939,16 @@
         <v>1.08</v>
       </c>
       <c r="N34">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O34">
         <v>1.38</v>
       </c>
       <c r="P34">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q34">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R34">
         <v>1.31</v>
@@ -8987,19 +8987,19 @@
         <v>7.6</v>
       </c>
       <c r="AD34">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE34">
         <v>40</v>
       </c>
       <c r="AF34">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG34">
         <v>12.5</v>
       </c>
       <c r="AH34">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI34">
         <v>55</v>
@@ -9008,19 +9008,19 @@
         <v>38</v>
       </c>
       <c r="AK34">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AL34">
         <v>46</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AN34">
         <v>38</v>
       </c>
       <c r="AO34">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP34">
         <v>11</v>
@@ -9053,7 +9053,7 @@
         <v>11</v>
       </c>
       <c r="AZ34">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA34">
         <v>44</v>
@@ -9071,10 +9071,10 @@
         <v>55</v>
       </c>
       <c r="BF34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG34">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9157,7 +9157,7 @@
         <v>183</v>
       </c>
       <c r="F35">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G35">
         <v>3.05</v>
@@ -9190,10 +9190,10 @@
         <v>1.57</v>
       </c>
       <c r="Q35">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R35">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S35">
         <v>5</v>
@@ -9205,7 +9205,7 @@
         <v>1.84</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
         <v>1.48</v>
@@ -9220,7 +9220,7 @@
         <v>19</v>
       </c>
       <c r="AA35">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB35">
         <v>9</v>
@@ -9232,7 +9232,7 @@
         <v>14</v>
       </c>
       <c r="AE35">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AF35">
         <v>18.5</v>
@@ -9241,19 +9241,19 @@
         <v>14</v>
       </c>
       <c r="AH35">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI35">
         <v>70</v>
       </c>
       <c r="AJ35">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK35">
         <v>48</v>
       </c>
       <c r="AL35">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM35">
         <v>190</v>
@@ -9274,7 +9274,7 @@
         <v>15.5</v>
       </c>
       <c r="AS35">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT35">
         <v>7.6</v>
@@ -9286,7 +9286,7 @@
         <v>11.5</v>
       </c>
       <c r="AW35">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX35">
         <v>15.5</v>
@@ -9298,28 +9298,28 @@
         <v>18</v>
       </c>
       <c r="BA35">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB35">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC35">
         <v>32</v>
       </c>
       <c r="BD35">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE35">
+        <v>10</v>
+      </c>
+      <c r="BF35">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG35">
         <v>9</v>
       </c>
-      <c r="BF35">
-        <v>8</v>
-      </c>
-      <c r="BG35">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH35">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI35">
         <v>2.34</v>
@@ -9334,7 +9334,7 @@
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN35">
         <v>5.8</v>
@@ -9346,7 +9346,7 @@
         <v>26</v>
       </c>
       <c r="BQ35">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR35">
         <v>48</v>
@@ -9364,7 +9364,7 @@
         <v>27</v>
       </c>
       <c r="BW35">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX35">
         <v>1000</v>
@@ -9399,19 +9399,19 @@
         <v>184</v>
       </c>
       <c r="F36">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G36">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H36">
         <v>3.25</v>
       </c>
       <c r="I36">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J36">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K36">
         <v>3.7</v>
@@ -9426,16 +9426,16 @@
         <v>3.65</v>
       </c>
       <c r="O36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P36">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q36">
         <v>1.96</v>
       </c>
       <c r="R36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S36">
         <v>3.45</v>
@@ -9447,16 +9447,16 @@
         <v>2.02</v>
       </c>
       <c r="V36">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X36">
         <v>17</v>
       </c>
       <c r="Y36">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z36">
         <v>24</v>
@@ -9471,16 +9471,16 @@
         <v>8</v>
       </c>
       <c r="AD36">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE36">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF36">
         <v>15.5</v>
       </c>
       <c r="AG36">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH36">
         <v>17.5</v>
@@ -9498,13 +9498,13 @@
         <v>48</v>
       </c>
       <c r="AM36">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN36">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO36">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP36">
         <v>10</v>
@@ -9528,7 +9528,7 @@
         <v>12.5</v>
       </c>
       <c r="AW36">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX36">
         <v>13</v>
@@ -9540,7 +9540,7 @@
         <v>15</v>
       </c>
       <c r="BA36">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="BB36">
         <v>16</v>
@@ -9549,16 +9549,16 @@
         <v>18.5</v>
       </c>
       <c r="BD36">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BE36">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF36">
         <v>14</v>
       </c>
       <c r="BG36">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9644,19 +9644,19 @@
         <v>1.36</v>
       </c>
       <c r="G37">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H37">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="I37">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J37">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="K37">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -9665,19 +9665,19 @@
         <v>1.02</v>
       </c>
       <c r="N37">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="O37">
         <v>1.13</v>
       </c>
       <c r="P37">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q37">
         <v>1.53</v>
       </c>
       <c r="R37">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="S37">
         <v>2.12</v>
@@ -9692,7 +9692,7 @@
         <v>1.1</v>
       </c>
       <c r="W37">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9719,10 +9719,10 @@
         <v>1000</v>
       </c>
       <c r="AF37">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG37">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH37">
         <v>1000</v>
@@ -9731,7 +9731,7 @@
         <v>1000</v>
       </c>
       <c r="AJ37">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK37">
         <v>500</v>
@@ -9743,64 +9743,64 @@
         <v>1000</v>
       </c>
       <c r="AN37">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO37">
         <v>1000</v>
       </c>
       <c r="AP37">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AQ37">
-        <v>1.34</v>
+        <v>2.5</v>
       </c>
       <c r="AR37">
-        <v>1.34</v>
+        <v>2.5</v>
       </c>
       <c r="AS37">
-        <v>1.34</v>
+        <v>2.5</v>
       </c>
       <c r="AT37">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AU37">
+        <v>1.4</v>
+      </c>
+      <c r="AV37">
+        <v>2.5</v>
+      </c>
+      <c r="AW37">
+        <v>2.5</v>
+      </c>
+      <c r="AX37">
         <v>1.3</v>
       </c>
-      <c r="AV37">
-        <v>1.34</v>
-      </c>
-      <c r="AW37">
-        <v>1.34</v>
-      </c>
-      <c r="AX37">
-        <v>1.21</v>
-      </c>
       <c r="AY37">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AZ37">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="BA37">
-        <v>1.34</v>
+        <v>2.5</v>
       </c>
       <c r="BB37">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="BC37">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="BD37">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="BE37">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="BF37">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="BG37">
-        <v>1.34</v>
+        <v>4.2</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9892,10 +9892,10 @@
         <v>4.4</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J38">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K38">
         <v>3.6</v>
@@ -9958,7 +9958,7 @@
         <v>970</v>
       </c>
       <c r="AE38">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF38">
         <v>11.5</v>
@@ -10033,7 +10033,7 @@
         <v>20</v>
       </c>
       <c r="BD38">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BE38">
         <v>11.5</v>
@@ -10042,13 +10042,13 @@
         <v>16</v>
       </c>
       <c r="BG38">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH38">
         <v>3.05</v>
       </c>
       <c r="BI38">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ38">
         <v>11</v>
@@ -10060,19 +10060,19 @@
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.63</v>
+        <v>3.45</v>
       </c>
       <c r="BN38">
         <v>4.5</v>
       </c>
       <c r="BO38">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP38">
         <v>15</v>
       </c>
       <c r="BQ38">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR38">
         <v>1000</v>
@@ -10084,7 +10084,7 @@
         <v>7.8</v>
       </c>
       <c r="BU38">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV38">
         <v>1000</v>
@@ -10099,7 +10099,7 @@
         <v>13</v>
       </c>
       <c r="BZ38">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA38">
         <v>11</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -547,7 +547,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-26 02:18:24</t>
+    <t>2026-08-26 03:53:56</t>
   </si>
 </sst>
 </file>
@@ -1144,10 +1144,10 @@
         <v>3.65</v>
       </c>
       <c r="G2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I2">
         <v>2.3</v>
@@ -1156,7 +1156,7 @@
         <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
         <v>1.51</v>
@@ -1165,10 +1165,10 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P2">
         <v>1.76</v>
@@ -1177,13 +1177,13 @@
         <v>2.26</v>
       </c>
       <c r="R2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
         <v>4.3</v>
       </c>
       <c r="T2">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U2">
         <v>2.04</v>
@@ -1192,16 +1192,16 @@
         <v>1.76</v>
       </c>
       <c r="W2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA2">
         <v>32</v>
@@ -1210,7 +1210,7 @@
         <v>12</v>
       </c>
       <c r="AC2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
@@ -1243,16 +1243,16 @@
         <v>130</v>
       </c>
       <c r="AN2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AO2">
         <v>24</v>
       </c>
       <c r="AP2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR2">
         <v>12.5</v>
@@ -1264,7 +1264,7 @@
         <v>11</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
         <v>10</v>
@@ -1282,7 +1282,7 @@
         <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB2">
         <v>48</v>
@@ -1291,10 +1291,10 @@
         <v>42</v>
       </c>
       <c r="BD2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BE2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF2">
         <v>48</v>
@@ -1303,10 +1303,10 @@
         <v>21</v>
       </c>
       <c r="BH2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI2">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
@@ -1318,7 +1318,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BN2">
         <v>6.6</v>
@@ -1330,13 +1330,13 @@
         <v>32</v>
       </c>
       <c r="BQ2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BR2">
         <v>48</v>
       </c>
       <c r="BS2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BT2">
         <v>4.9</v>
@@ -1348,19 +1348,19 @@
         <v>17.5</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX2">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2">
         <v>34</v>
       </c>
       <c r="CA2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB2" t="s">
         <v>177</v>
@@ -1386,10 +1386,10 @@
         <v>2.4</v>
       </c>
       <c r="G3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>3.15</v>
@@ -1407,7 +1407,7 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O3">
         <v>1.25</v>
@@ -1416,7 +1416,7 @@
         <v>2.24</v>
       </c>
       <c r="Q3">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R3">
         <v>1.49</v>
@@ -1434,7 +1434,7 @@
         <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X3">
         <v>19</v>
@@ -1488,7 +1488,7 @@
         <v>16</v>
       </c>
       <c r="AO3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP3">
         <v>16.5</v>
@@ -1500,7 +1500,7 @@
         <v>20</v>
       </c>
       <c r="AS3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT3">
         <v>11.5</v>
@@ -1515,7 +1515,7 @@
         <v>26</v>
       </c>
       <c r="AX3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY3">
         <v>10</v>
@@ -1554,13 +1554,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL3">
         <v>990</v>
       </c>
       <c r="BM3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN3">
         <v>5.5</v>
@@ -1578,7 +1578,7 @@
         <v>26</v>
       </c>
       <c r="BS3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT3">
         <v>6.4</v>
@@ -1587,7 +1587,7 @@
         <v>5.8</v>
       </c>
       <c r="BV3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW3">
         <v>10.5</v>
@@ -1596,13 +1596,13 @@
         <v>32</v>
       </c>
       <c r="BY3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
         <v>20</v>
       </c>
       <c r="CA3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1628,7 +1628,7 @@
         <v>1.57</v>
       </c>
       <c r="G4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -1637,49 +1637,49 @@
         <v>8.4</v>
       </c>
       <c r="J4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U4">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W4">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="X4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
         <v>21</v>
@@ -1691,7 +1691,7 @@
         <v>340</v>
       </c>
       <c r="AB4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC4">
         <v>9.4</v>
@@ -1700,10 +1700,10 @@
         <v>32</v>
       </c>
       <c r="AE4">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1712,58 +1712,58 @@
         <v>32</v>
       </c>
       <c r="AI4">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ4">
         <v>14</v>
       </c>
       <c r="AK4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AN4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AP4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR4">
         <v>32</v>
       </c>
       <c r="AS4">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="AT4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU4">
         <v>8.6</v>
       </c>
       <c r="AV4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW4">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AX4">
         <v>7.2</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA4">
         <v>44</v>
@@ -1772,7 +1772,7 @@
         <v>12.5</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD4">
         <v>42</v>
@@ -1784,28 +1784,28 @@
         <v>10</v>
       </c>
       <c r="BG4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BH4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI4">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4">
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL4">
         <v>250</v>
       </c>
       <c r="BM4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BN4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BO4">
         <v>3.45</v>
@@ -1814,37 +1814,37 @@
         <v>10.5</v>
       </c>
       <c r="BQ4">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BS4">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BT4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BU4">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BV4">
         <v>100</v>
       </c>
       <c r="BW4">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX4">
         <v>110</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BZ4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="CA4">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1873,40 +1873,40 @@
         <v>1.04</v>
       </c>
       <c r="H5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I5">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="J5">
         <v>29</v>
       </c>
       <c r="K5">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="O5">
         <v>1.01</v>
       </c>
       <c r="P5">
-        <v>4.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R5">
         <v>2.66</v>
       </c>
       <c r="S5">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -2109,172 +2109,172 @@
         <v>147</v>
       </c>
       <c r="F6">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G6">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H6">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="I6">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="J6">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="L6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O6">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P6">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q6">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="R6">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="S6">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T6">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="U6">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>32</v>
       </c>
       <c r="Y6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA6">
         <v>12</v>
       </c>
       <c r="AB6">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AC6">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AF6">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AG6">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AH6">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AI6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ6">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="AK6">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AL6">
         <v>200</v>
       </c>
       <c r="AM6">
+        <v>110</v>
+      </c>
+      <c r="AN6">
         <v>120</v>
       </c>
-      <c r="AN6">
-        <v>600</v>
-      </c>
       <c r="AO6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AP6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AQ6">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR6">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT6">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="AU6">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AV6">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX6">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="AY6">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AZ6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB6">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BC6">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="BD6">
-        <v>8.6</v>
+        <v>65</v>
       </c>
       <c r="BE6">
-        <v>8.6</v>
+        <v>70</v>
       </c>
       <c r="BF6">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="BG6">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BH6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
@@ -2286,10 +2286,10 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BO6">
         <v>9</v>
@@ -2298,22 +2298,22 @@
         <v>1000</v>
       </c>
       <c r="BQ6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
         <v>8.6</v>
-      </c>
-      <c r="BR6">
-        <v>75</v>
-      </c>
-      <c r="BS6">
-        <v>8.4</v>
       </c>
       <c r="BT6">
         <v>4.3</v>
       </c>
       <c r="BU6">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BV6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BW6">
         <v>6</v>
@@ -2325,10 +2325,10 @@
         <v>6.6</v>
       </c>
       <c r="BZ6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="s">
         <v>177</v>
@@ -2351,22 +2351,22 @@
         <v>148</v>
       </c>
       <c r="F7">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G7">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
         <v>1.63</v>
@@ -2375,16 +2375,16 @@
         <v>1.14</v>
       </c>
       <c r="N7">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O7">
         <v>1.58</v>
       </c>
       <c r="P7">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q7">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R7">
         <v>1.18</v>
@@ -2396,19 +2396,19 @@
         <v>2.56</v>
       </c>
       <c r="U7">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V7">
         <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X7">
         <v>8.6</v>
       </c>
       <c r="Y7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z7">
         <v>160</v>
@@ -2417,7 +2417,7 @@
         <v>420</v>
       </c>
       <c r="AB7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AC7">
         <v>8.800000000000001</v>
@@ -2429,7 +2429,7 @@
         <v>240</v>
       </c>
       <c r="AF7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG7">
         <v>11.5</v>
@@ -2441,19 +2441,19 @@
         <v>250</v>
       </c>
       <c r="AJ7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL7">
-        <v>230</v>
+        <v>540</v>
       </c>
       <c r="AM7">
         <v>400</v>
       </c>
       <c r="AN7">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AO7">
         <v>520</v>
@@ -2468,7 +2468,7 @@
         <v>46</v>
       </c>
       <c r="AS7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT7">
         <v>4.8</v>
@@ -2477,10 +2477,10 @@
         <v>7.6</v>
       </c>
       <c r="AV7">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AW7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX7">
         <v>7</v>
@@ -2489,10 +2489,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB7">
         <v>14.5</v>
@@ -2501,13 +2501,13 @@
         <v>21</v>
       </c>
       <c r="BD7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG7">
         <v>14</v>
@@ -2516,28 +2516,28 @@
         <v>2.7</v>
       </c>
       <c r="BI7">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BJ7">
         <v>14</v>
       </c>
       <c r="BK7">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BN7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BO7">
         <v>3.4</v>
       </c>
       <c r="BP7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ7">
         <v>10.5</v>
@@ -2546,31 +2546,31 @@
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT7">
         <v>11</v>
       </c>
       <c r="BU7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BZ7">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB7" t="s">
         <v>177</v>
@@ -2593,7 +2593,7 @@
         <v>149</v>
       </c>
       <c r="F8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G8">
         <v>3.6</v>
@@ -2602,10 +2602,10 @@
         <v>2.2</v>
       </c>
       <c r="I8">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K8">
         <v>3.9</v>
@@ -2641,7 +2641,7 @@
         <v>2.24</v>
       </c>
       <c r="V8">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W8">
         <v>1.39</v>
@@ -2707,16 +2707,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS8">
         <v>16</v>
       </c>
       <c r="AT8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV8">
         <v>9.6</v>
@@ -2758,7 +2758,7 @@
         <v>3.85</v>
       </c>
       <c r="BI8">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8">
         <v>9.4</v>
@@ -2770,7 +2770,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN8">
         <v>7</v>
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="BQ8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8">
         <v>5.5</v>
@@ -2797,13 +2797,13 @@
         <v>4.2</v>
       </c>
       <c r="BV8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW8">
         <v>6.4</v>
       </c>
       <c r="BX8">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
         <v>7.6</v>
@@ -2812,7 +2812,7 @@
         <v>23</v>
       </c>
       <c r="CA8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="s">
         <v>177</v>
@@ -2835,226 +2835,226 @@
         <v>150</v>
       </c>
       <c r="F9">
-        <v>2.44</v>
+        <v>4.8</v>
       </c>
       <c r="G9">
+        <v>5.3</v>
+      </c>
+      <c r="H9">
+        <v>1.66</v>
+      </c>
+      <c r="I9">
+        <v>1.73</v>
+      </c>
+      <c r="J9">
+        <v>4.5</v>
+      </c>
+      <c r="K9">
+        <v>4.9</v>
+      </c>
+      <c r="L9">
+        <v>1.26</v>
+      </c>
+      <c r="M9">
+        <v>1.03</v>
+      </c>
+      <c r="N9">
+        <v>6</v>
+      </c>
+      <c r="O9">
+        <v>1.17</v>
+      </c>
+      <c r="P9">
+        <v>2.76</v>
+      </c>
+      <c r="Q9">
+        <v>1.51</v>
+      </c>
+      <c r="R9">
+        <v>1.7</v>
+      </c>
+      <c r="S9">
+        <v>2.3</v>
+      </c>
+      <c r="T9">
+        <v>1.59</v>
+      </c>
+      <c r="U9">
+        <v>2.5</v>
+      </c>
+      <c r="V9">
+        <v>2.36</v>
+      </c>
+      <c r="W9">
+        <v>1.23</v>
+      </c>
+      <c r="X9">
+        <v>36</v>
+      </c>
+      <c r="Y9">
         <v>14.5</v>
       </c>
-      <c r="H9">
-        <v>1.87</v>
-      </c>
-      <c r="I9">
-        <v>5.1</v>
-      </c>
-      <c r="J9">
-        <v>2.96</v>
-      </c>
-      <c r="K9">
+      <c r="Z9">
+        <v>14</v>
+      </c>
+      <c r="AA9">
+        <v>22</v>
+      </c>
+      <c r="AB9">
+        <v>29</v>
+      </c>
+      <c r="AC9">
+        <v>12</v>
+      </c>
+      <c r="AD9">
+        <v>13</v>
+      </c>
+      <c r="AE9">
+        <v>16</v>
+      </c>
+      <c r="AF9">
+        <v>60</v>
+      </c>
+      <c r="AG9">
+        <v>26</v>
+      </c>
+      <c r="AH9">
+        <v>20</v>
+      </c>
+      <c r="AI9">
+        <v>30</v>
+      </c>
+      <c r="AJ9">
+        <v>130</v>
+      </c>
+      <c r="AK9">
+        <v>65</v>
+      </c>
+      <c r="AL9">
+        <v>60</v>
+      </c>
+      <c r="AM9">
+        <v>75</v>
+      </c>
+      <c r="AN9">
+        <v>48</v>
+      </c>
+      <c r="AO9">
+        <v>6.6</v>
+      </c>
+      <c r="AP9">
+        <v>13</v>
+      </c>
+      <c r="AQ9">
+        <v>11.5</v>
+      </c>
+      <c r="AR9">
+        <v>11</v>
+      </c>
+      <c r="AS9">
+        <v>15.5</v>
+      </c>
+      <c r="AT9">
+        <v>10</v>
+      </c>
+      <c r="AU9">
+        <v>9.4</v>
+      </c>
+      <c r="AV9">
+        <v>9</v>
+      </c>
+      <c r="AW9">
+        <v>13</v>
+      </c>
+      <c r="AX9">
+        <v>5.6</v>
+      </c>
+      <c r="AY9">
+        <v>17.5</v>
+      </c>
+      <c r="AZ9">
+        <v>14</v>
+      </c>
+      <c r="BA9">
+        <v>20</v>
+      </c>
+      <c r="BB9">
+        <v>6</v>
+      </c>
+      <c r="BC9">
+        <v>5.8</v>
+      </c>
+      <c r="BD9">
+        <v>5.7</v>
+      </c>
+      <c r="BE9">
+        <v>5.8</v>
+      </c>
+      <c r="BF9">
+        <v>5.6</v>
+      </c>
+      <c r="BG9">
+        <v>5.4</v>
+      </c>
+      <c r="BH9">
+        <v>5.6</v>
+      </c>
+      <c r="BI9">
+        <v>3.7</v>
+      </c>
+      <c r="BJ9">
+        <v>9.4</v>
+      </c>
+      <c r="BK9">
+        <v>4.2</v>
+      </c>
+      <c r="BL9">
+        <v>85</v>
+      </c>
+      <c r="BM9">
         <v>7</v>
       </c>
-      <c r="L9">
-        <v>1.23</v>
-      </c>
-      <c r="M9">
-        <v>1.02</v>
-      </c>
-      <c r="N9">
-        <v>1.44</v>
-      </c>
-      <c r="O9">
-        <v>1.16</v>
-      </c>
-      <c r="P9">
-        <v>1.64</v>
-      </c>
-      <c r="Q9">
-        <v>1.25</v>
-      </c>
-      <c r="R9">
-        <v>1.3</v>
-      </c>
-      <c r="S9">
-        <v>2.5</v>
-      </c>
-      <c r="T9">
-        <v>1.11</v>
-      </c>
-      <c r="U9">
-        <v>2.58</v>
-      </c>
-      <c r="V9">
-        <v>1.96</v>
-      </c>
-      <c r="W9">
-        <v>1.31</v>
-      </c>
-      <c r="X9">
-        <v>950</v>
-      </c>
-      <c r="Y9">
-        <v>950</v>
-      </c>
-      <c r="Z9">
-        <v>500</v>
-      </c>
-      <c r="AA9">
-        <v>500</v>
-      </c>
-      <c r="AB9">
-        <v>950</v>
-      </c>
-      <c r="AC9">
-        <v>950</v>
-      </c>
-      <c r="AD9">
-        <v>950</v>
-      </c>
-      <c r="AE9">
-        <v>500</v>
-      </c>
-      <c r="AF9">
-        <v>500</v>
-      </c>
-      <c r="AG9">
-        <v>950</v>
-      </c>
-      <c r="AH9">
-        <v>950</v>
-      </c>
-      <c r="AI9">
-        <v>500</v>
-      </c>
-      <c r="AJ9">
-        <v>700</v>
-      </c>
-      <c r="AK9">
-        <v>700</v>
-      </c>
-      <c r="AL9">
-        <v>700</v>
-      </c>
-      <c r="AM9">
-        <v>580</v>
-      </c>
-      <c r="AN9">
-        <v>700</v>
-      </c>
-      <c r="AO9">
-        <v>140</v>
-      </c>
-      <c r="AP9">
-        <v>1.23</v>
-      </c>
-      <c r="AQ9">
-        <v>1.19</v>
-      </c>
-      <c r="AR9">
-        <v>1.2</v>
-      </c>
-      <c r="AS9">
-        <v>1.22</v>
-      </c>
-      <c r="AT9">
-        <v>1.21</v>
-      </c>
-      <c r="AU9">
-        <v>1.19</v>
-      </c>
-      <c r="AV9">
-        <v>1.2</v>
-      </c>
-      <c r="AW9">
-        <v>1.22</v>
-      </c>
-      <c r="AX9">
-        <v>1.22</v>
-      </c>
-      <c r="AY9">
-        <v>1.22</v>
-      </c>
-      <c r="AZ9">
-        <v>1.22</v>
-      </c>
-      <c r="BA9">
-        <v>1.22</v>
-      </c>
-      <c r="BB9">
-        <v>1.23</v>
-      </c>
-      <c r="BC9">
-        <v>1.23</v>
-      </c>
-      <c r="BD9">
-        <v>1.23</v>
-      </c>
-      <c r="BE9">
-        <v>1.22</v>
-      </c>
-      <c r="BF9">
-        <v>1.55</v>
-      </c>
-      <c r="BG9">
-        <v>1.55</v>
-      </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
-      <c r="BI9">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9">
-        <v>1000</v>
-      </c>
-      <c r="BK9">
-        <v>1.04</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>1.04</v>
-      </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB9" t="s">
         <v>177</v>
@@ -3086,7 +3086,7 @@
         <v>3.8</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3101,22 +3101,22 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q10">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R10">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S10">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T10">
         <v>1.62</v>
@@ -3131,16 +3131,16 @@
         <v>1.98</v>
       </c>
       <c r="X10">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="Y10">
         <v>20</v>
       </c>
       <c r="Z10">
+        <v>40</v>
+      </c>
+      <c r="AA10">
         <v>90</v>
-      </c>
-      <c r="AA10">
-        <v>900</v>
       </c>
       <c r="AB10">
         <v>12.5</v>
@@ -3149,10 +3149,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE10">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AF10">
         <v>14.5</v>
@@ -3164,25 +3164,25 @@
         <v>19.5</v>
       </c>
       <c r="AI10">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AJ10">
+        <v>27</v>
+      </c>
+      <c r="AK10">
+        <v>25</v>
+      </c>
+      <c r="AL10">
         <v>40</v>
       </c>
-      <c r="AK10">
-        <v>26</v>
-      </c>
-      <c r="AL10">
-        <v>48</v>
-      </c>
       <c r="AM10">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AN10">
         <v>9.800000000000001</v>
       </c>
       <c r="AO10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP10">
         <v>18.5</v>
@@ -3194,7 +3194,7 @@
         <v>24</v>
       </c>
       <c r="AS10">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="AT10">
         <v>11</v>
@@ -3218,7 +3218,7 @@
         <v>14</v>
       </c>
       <c r="BA10">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BB10">
         <v>17.5</v>
@@ -3227,34 +3227,34 @@
         <v>16</v>
       </c>
       <c r="BD10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BE10">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BF10">
         <v>8.800000000000001</v>
       </c>
       <c r="BG10">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BH10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ10">
         <v>9</v>
       </c>
       <c r="BK10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN10">
         <v>5.1</v>
@@ -3266,37 +3266,37 @@
         <v>13</v>
       </c>
       <c r="BQ10">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR10">
         <v>25</v>
       </c>
       <c r="BS10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT10">
         <v>7.6</v>
       </c>
       <c r="BU10">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX10">
         <v>38</v>
       </c>
       <c r="BY10">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10">
         <v>20</v>
       </c>
       <c r="CA10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB10" t="s">
         <v>177</v>
@@ -3319,16 +3319,16 @@
         <v>152</v>
       </c>
       <c r="F11">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G11">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H11">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I11">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J11">
         <v>3.5</v>
@@ -3343,16 +3343,16 @@
         <v>1.06</v>
       </c>
       <c r="N11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P11">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q11">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R11">
         <v>1.42</v>
@@ -3436,7 +3436,7 @@
         <v>17.5</v>
       </c>
       <c r="AS11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AT11">
         <v>10</v>
@@ -3463,10 +3463,10 @@
         <v>29</v>
       </c>
       <c r="BB11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD11">
         <v>30</v>
@@ -3484,16 +3484,16 @@
         <v>3.8</v>
       </c>
       <c r="BI11">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ11">
         <v>9.4</v>
       </c>
       <c r="BK11">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL11">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
         <v>9.199999999999999</v>
@@ -3561,22 +3561,22 @@
         <v>153</v>
       </c>
       <c r="F12">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H12">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I12">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
         <v>1.4</v>
@@ -3585,46 +3585,46 @@
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O12">
         <v>1.32</v>
       </c>
       <c r="P12">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q12">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R12">
         <v>1.34</v>
       </c>
       <c r="S12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T12">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U12">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="V12">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="W12">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y12">
         <v>10.5</v>
       </c>
       <c r="Z12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB12">
         <v>14.5</v>
@@ -3636,7 +3636,7 @@
         <v>11.5</v>
       </c>
       <c r="AE12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF12">
         <v>27</v>
@@ -3648,7 +3648,7 @@
         <v>18.5</v>
       </c>
       <c r="AI12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ12">
         <v>80</v>
@@ -3657,76 +3657,76 @@
         <v>55</v>
       </c>
       <c r="AL12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM12">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AN12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP12">
+        <v>11</v>
+      </c>
+      <c r="AQ12">
+        <v>7.6</v>
+      </c>
+      <c r="AR12">
+        <v>11</v>
+      </c>
+      <c r="AS12">
+        <v>22</v>
+      </c>
+      <c r="AT12">
+        <v>10.5</v>
+      </c>
+      <c r="AU12">
+        <v>6.2</v>
+      </c>
+      <c r="AV12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW12">
+        <v>19.5</v>
+      </c>
+      <c r="AX12">
+        <v>20</v>
+      </c>
+      <c r="AY12">
         <v>11.5</v>
       </c>
-      <c r="AQ12">
+      <c r="AZ12">
+        <v>13.5</v>
+      </c>
+      <c r="BA12">
+        <v>29</v>
+      </c>
+      <c r="BB12">
+        <v>8</v>
+      </c>
+      <c r="BC12">
+        <v>34</v>
+      </c>
+      <c r="BD12">
+        <v>38</v>
+      </c>
+      <c r="BE12">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR12">
-        <v>12</v>
-      </c>
-      <c r="AS12">
-        <v>18.5</v>
-      </c>
-      <c r="AT12">
-        <v>11.5</v>
-      </c>
-      <c r="AU12">
-        <v>6.8</v>
-      </c>
-      <c r="AV12">
-        <v>9.4</v>
-      </c>
-      <c r="AW12">
-        <v>20</v>
-      </c>
-      <c r="AX12">
-        <v>16.5</v>
-      </c>
-      <c r="AY12">
-        <v>12.5</v>
-      </c>
-      <c r="AZ12">
+      <c r="BF12">
+        <v>36</v>
+      </c>
+      <c r="BG12">
         <v>15</v>
       </c>
-      <c r="BA12">
-        <v>25</v>
-      </c>
-      <c r="BB12">
-        <v>7.4</v>
-      </c>
-      <c r="BC12">
-        <v>27</v>
-      </c>
-      <c r="BD12">
-        <v>32</v>
-      </c>
-      <c r="BE12">
-        <v>7.6</v>
-      </c>
-      <c r="BF12">
-        <v>7</v>
-      </c>
-      <c r="BG12">
-        <v>15.5</v>
-      </c>
       <c r="BH12">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI12">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ12">
         <v>11</v>
@@ -3741,13 +3741,13 @@
         <v>5.6</v>
       </c>
       <c r="BN12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO12">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ12">
         <v>5</v>
@@ -3759,25 +3759,25 @@
         <v>5.2</v>
       </c>
       <c r="BT12">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU12">
         <v>4</v>
       </c>
       <c r="BV12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW12">
         <v>4.4</v>
       </c>
       <c r="BX12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY12">
         <v>5</v>
       </c>
       <c r="BZ12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA12">
         <v>4.9</v>
@@ -3803,25 +3803,25 @@
         <v>154</v>
       </c>
       <c r="F13">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G13">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="H13">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="J13">
         <v>5.1</v>
       </c>
       <c r="K13">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L13">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M13">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P13">
         <v>3.7</v>
@@ -3842,19 +3842,19 @@
         <v>2.08</v>
       </c>
       <c r="S13">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="T13">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="U13">
         <v>3</v>
       </c>
       <c r="V13">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="X13">
         <v>55</v>
@@ -3866,34 +3866,34 @@
         <v>65</v>
       </c>
       <c r="AA13">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB13">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AC13">
         <v>14</v>
       </c>
       <c r="AD13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE13">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AF13">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG13">
         <v>12</v>
       </c>
       <c r="AH13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI13">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AJ13">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AK13">
         <v>14.5</v>
@@ -3902,43 +3902,43 @@
         <v>22</v>
       </c>
       <c r="AM13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN13">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AO13">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP13">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AQ13">
         <v>32</v>
       </c>
       <c r="AR13">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AS13">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AT13">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV13">
         <v>20</v>
       </c>
       <c r="AW13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX13">
         <v>13.5</v>
       </c>
       <c r="AY13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ13">
         <v>14</v>
@@ -3947,7 +3947,7 @@
         <v>26</v>
       </c>
       <c r="BB13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC13">
         <v>12</v>
@@ -3956,16 +3956,16 @@
         <v>18.5</v>
       </c>
       <c r="BE13">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BF13">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG13">
         <v>20</v>
       </c>
       <c r="BH13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BI13">
         <v>4.8</v>
@@ -3974,13 +3974,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK13">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BL13">
         <v>60</v>
       </c>
       <c r="BM13">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BN13">
         <v>5.2</v>
@@ -3992,13 +3992,13 @@
         <v>9.6</v>
       </c>
       <c r="BQ13">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BR13">
         <v>16.5</v>
       </c>
       <c r="BS13">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BT13">
         <v>9.800000000000001</v>
@@ -4010,19 +4010,19 @@
         <v>36</v>
       </c>
       <c r="BW13">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BZ13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA13">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="CB13" t="s">
         <v>177</v>
@@ -4045,10 +4045,10 @@
         <v>155</v>
       </c>
       <c r="F14">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G14">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H14">
         <v>2.32</v>
@@ -4057,40 +4057,40 @@
         <v>2.42</v>
       </c>
       <c r="J14">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L14">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M14">
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="O14">
         <v>1.09</v>
       </c>
       <c r="P14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q14">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="R14">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S14">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="T14">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="U14">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="V14">
         <v>1.7</v>
@@ -4102,10 +4102,10 @@
         <v>55</v>
       </c>
       <c r="Y14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z14">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AA14">
         <v>44</v>
@@ -4114,7 +4114,7 @@
         <v>32</v>
       </c>
       <c r="AC14">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD14">
         <v>14.5</v>
@@ -4123,7 +4123,7 @@
         <v>22</v>
       </c>
       <c r="AF14">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AG14">
         <v>16</v>
@@ -4141,16 +4141,16 @@
         <v>26</v>
       </c>
       <c r="AL14">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AM14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN14">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP14">
         <v>29</v>
@@ -4162,13 +4162,13 @@
         <v>23</v>
       </c>
       <c r="AS14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT14">
         <v>23</v>
       </c>
       <c r="AU14">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AV14">
         <v>11.5</v>
@@ -4189,7 +4189,7 @@
         <v>18.5</v>
       </c>
       <c r="BB14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC14">
         <v>20</v>
@@ -4198,31 +4198,31 @@
         <v>20</v>
       </c>
       <c r="BE14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BF14">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG14">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH14">
         <v>7.4</v>
       </c>
       <c r="BI14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BJ14">
         <v>9</v>
       </c>
       <c r="BK14">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BL14">
         <v>48</v>
       </c>
       <c r="BM14">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BN14">
         <v>8.4</v>
@@ -4234,37 +4234,37 @@
         <v>19.5</v>
       </c>
       <c r="BQ14">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BR14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS14">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT14">
         <v>7.8</v>
       </c>
       <c r="BU14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW14">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BX14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BY14">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BZ14">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="CA14">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="CB14" t="s">
         <v>177</v>
@@ -4287,16 +4287,16 @@
         <v>156</v>
       </c>
       <c r="F15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G15">
         <v>3.5</v>
       </c>
       <c r="H15">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I15">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J15">
         <v>4.3</v>
@@ -4311,49 +4311,49 @@
         <v>1.02</v>
       </c>
       <c r="N15">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O15">
         <v>1.13</v>
       </c>
       <c r="P15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q15">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R15">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="S15">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T15">
         <v>1.46</v>
       </c>
       <c r="U15">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V15">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W15">
         <v>1.4</v>
       </c>
       <c r="X15">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Y15">
         <v>23</v>
       </c>
       <c r="Z15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA15">
         <v>32</v>
       </c>
       <c r="AB15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AC15">
         <v>12.5</v>
@@ -4365,10 +4365,10 @@
         <v>21</v>
       </c>
       <c r="AF15">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG15">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH15">
         <v>14.5</v>
@@ -4377,22 +4377,22 @@
         <v>27</v>
       </c>
       <c r="AJ15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK15">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AL15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM15">
         <v>48</v>
       </c>
       <c r="AN15">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AP15">
         <v>23</v>
@@ -4401,13 +4401,13 @@
         <v>16.5</v>
       </c>
       <c r="AR15">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AS15">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT15">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU15">
         <v>10.5</v>
@@ -4419,16 +4419,16 @@
         <v>16</v>
       </c>
       <c r="AX15">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AY15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ15">
         <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB15">
         <v>38</v>
@@ -4440,16 +4440,16 @@
         <v>23</v>
       </c>
       <c r="BE15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF15">
         <v>14</v>
       </c>
       <c r="BG15">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH15">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BI15">
         <v>4.3</v>
@@ -4458,55 +4458,55 @@
         <v>9.4</v>
       </c>
       <c r="BK15">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BN15">
         <v>8.6</v>
       </c>
       <c r="BO15">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="BP15">
         <v>25</v>
       </c>
       <c r="BQ15">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BR15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS15">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BT15">
         <v>6.6</v>
       </c>
       <c r="BU15">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW15">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BX15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY15">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BZ15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA15">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="CB15" t="s">
         <v>177</v>
@@ -4529,61 +4529,61 @@
         <v>157</v>
       </c>
       <c r="F16">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G16">
         <v>1.29</v>
       </c>
       <c r="H16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="K16">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L16">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M16">
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O16">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P16">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q16">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R16">
+        <v>2.06</v>
+      </c>
+      <c r="S16">
+        <v>1.87</v>
+      </c>
+      <c r="T16">
+        <v>1.76</v>
+      </c>
+      <c r="U16">
         <v>2.16</v>
       </c>
-      <c r="S16">
-        <v>1.81</v>
-      </c>
-      <c r="T16">
-        <v>1.7</v>
-      </c>
-      <c r="U16">
-        <v>2.38</v>
-      </c>
       <c r="V16">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X16">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Y16">
         <v>65</v>
@@ -4592,10 +4592,10 @@
         <v>140</v>
       </c>
       <c r="AA16">
-        <v>350</v>
+        <v>470</v>
       </c>
       <c r="AB16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC16">
         <v>19</v>
@@ -4604,7 +4604,7 @@
         <v>44</v>
       </c>
       <c r="AE16">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AF16">
         <v>12</v>
@@ -4613,10 +4613,10 @@
         <v>12</v>
       </c>
       <c r="AH16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI16">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ16">
         <v>12.5</v>
@@ -4631,22 +4631,22 @@
         <v>95</v>
       </c>
       <c r="AN16">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AO16">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AQ16">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR16">
         <v>11</v>
       </c>
       <c r="AS16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT16">
         <v>14</v>
@@ -4658,10 +4658,10 @@
         <v>34</v>
       </c>
       <c r="AW16">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
@@ -4670,10 +4670,10 @@
         <v>22</v>
       </c>
       <c r="BA16">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BB16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC16">
         <v>11</v>
@@ -4682,16 +4682,16 @@
         <v>21</v>
       </c>
       <c r="BE16">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BF16">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BG16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH16">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BI16">
         <v>5.2</v>
@@ -4700,22 +4700,22 @@
         <v>12</v>
       </c>
       <c r="BK16">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL16">
         <v>100</v>
       </c>
       <c r="BM16">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BN16">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO16">
         <v>3.8</v>
       </c>
       <c r="BP16">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BQ16">
         <v>5.7</v>
@@ -4724,31 +4724,31 @@
         <v>18</v>
       </c>
       <c r="BS16">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BT16">
         <v>16</v>
       </c>
       <c r="BU16">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV16">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BW16">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX16">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY16">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ16">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="CA16">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB16" t="s">
         <v>177</v>
@@ -4780,10 +4780,10 @@
         <v>6.4</v>
       </c>
       <c r="I17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K17">
         <v>6.6</v>
@@ -4813,7 +4813,7 @@
         <v>1.66</v>
       </c>
       <c r="T17">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="U17">
         <v>2.92</v>
@@ -4831,7 +4831,7 @@
         <v>65</v>
       </c>
       <c r="Z17">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AA17">
         <v>210</v>
@@ -4846,25 +4846,25 @@
         <v>30</v>
       </c>
       <c r="AE17">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF17">
         <v>17</v>
       </c>
       <c r="AG17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH17">
         <v>18.5</v>
       </c>
       <c r="AI17">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ17">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK17">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL17">
         <v>21</v>
@@ -4873,22 +4873,22 @@
         <v>60</v>
       </c>
       <c r="AN17">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AO17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP17">
         <v>48</v>
       </c>
       <c r="AQ17">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR17">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AS17">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AT17">
         <v>20</v>
@@ -4897,13 +4897,13 @@
         <v>15.5</v>
       </c>
       <c r="AV17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW17">
         <v>55</v>
       </c>
       <c r="AX17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY17">
         <v>11</v>
@@ -4930,7 +4930,7 @@
         <v>3.2</v>
       </c>
       <c r="BG17">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BH17">
         <v>7.6</v>
@@ -4948,7 +4948,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BN17">
         <v>5.9</v>
@@ -4963,7 +4963,7 @@
         <v>6.8</v>
       </c>
       <c r="BR17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS17">
         <v>4.3</v>
@@ -4978,13 +4978,13 @@
         <v>44</v>
       </c>
       <c r="BW17">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BX17">
         <v>36</v>
       </c>
       <c r="BY17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BZ17">
         <v>8</v>
@@ -5016,37 +5016,37 @@
         <v>3.55</v>
       </c>
       <c r="G18">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H18">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I18">
         <v>2.66</v>
       </c>
       <c r="J18">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K18">
         <v>2.94</v>
       </c>
       <c r="L18">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M18">
         <v>1.15</v>
       </c>
       <c r="N18">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O18">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P18">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q18">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R18">
         <v>1.18</v>
@@ -5055,7 +5055,7 @@
         <v>6</v>
       </c>
       <c r="T18">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U18">
         <v>1.72</v>
@@ -5067,19 +5067,19 @@
         <v>1.37</v>
       </c>
       <c r="X18">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y18">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z18">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA18">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AB18">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -5088,61 +5088,61 @@
         <v>14</v>
       </c>
       <c r="AE18">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AF18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG18">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH18">
         <v>23</v>
       </c>
       <c r="AI18">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ18">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AK18">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AL18">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="AM18">
         <v>220</v>
       </c>
       <c r="AN18">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="AO18">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP18">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ18">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR18">
         <v>13</v>
       </c>
       <c r="AS18">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AT18">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV18">
         <v>12</v>
       </c>
       <c r="AW18">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AX18">
         <v>20</v>
@@ -5151,31 +5151,31 @@
         <v>15</v>
       </c>
       <c r="AZ18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA18">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB18">
         <v>50</v>
       </c>
       <c r="BC18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BD18">
         <v>55</v>
       </c>
       <c r="BE18">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="BF18">
         <v>70</v>
       </c>
       <c r="BG18">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BH18">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BI18">
         <v>2.28</v>
@@ -5190,7 +5190,7 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN18">
         <v>6.4</v>
@@ -5202,13 +5202,13 @@
         <v>34</v>
       </c>
       <c r="BQ18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR18">
         <v>60</v>
       </c>
       <c r="BS18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT18">
         <v>5.3</v>
@@ -5220,19 +5220,19 @@
         <v>24</v>
       </c>
       <c r="BW18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ18">
         <v>55</v>
       </c>
       <c r="CA18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB18" t="s">
         <v>177</v>
@@ -5255,22 +5255,22 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G19">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="H19">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="I19">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="J19">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K19">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L19">
         <v>1.53</v>
@@ -5282,85 +5282,85 @@
         <v>3.05</v>
       </c>
       <c r="O19">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P19">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q19">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R19">
         <v>1.24</v>
       </c>
       <c r="S19">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T19">
         <v>1.99</v>
       </c>
       <c r="U19">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V19">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="W19">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="X19">
         <v>10.5</v>
       </c>
       <c r="Y19">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z19">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA19">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB19">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC19">
         <v>7.4</v>
       </c>
       <c r="AD19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF19">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AG19">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19">
         <v>55</v>
       </c>
       <c r="AJ19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK19">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AL19">
         <v>85</v>
       </c>
       <c r="AM19">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN19">
         <v>80</v>
       </c>
       <c r="AO19">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP19">
         <v>9</v>
@@ -5369,13 +5369,13 @@
         <v>7</v>
       </c>
       <c r="AR19">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AS19">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT19">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU19">
         <v>6.2</v>
@@ -5384,37 +5384,37 @@
         <v>10</v>
       </c>
       <c r="AW19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY19">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AZ19">
         <v>17</v>
       </c>
       <c r="BA19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB19">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BC19">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BD19">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BE19">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF19">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BG19">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BH19">
         <v>3.35</v>
@@ -5423,58 +5423,58 @@
         <v>2.38</v>
       </c>
       <c r="BJ19">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK19">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BN19">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BO19">
+        <v>5.3</v>
+      </c>
+      <c r="BP19">
+        <v>38</v>
+      </c>
+      <c r="BQ19">
+        <v>5.6</v>
+      </c>
+      <c r="BR19">
+        <v>65</v>
+      </c>
+      <c r="BS19">
+        <v>6</v>
+      </c>
+      <c r="BT19">
         <v>5</v>
       </c>
-      <c r="BP19">
+      <c r="BU19">
+        <v>3.75</v>
+      </c>
+      <c r="BV19">
+        <v>22</v>
+      </c>
+      <c r="BW19">
+        <v>5</v>
+      </c>
+      <c r="BX19">
         <v>40</v>
       </c>
-      <c r="BQ19">
-        <v>4.5</v>
-      </c>
-      <c r="BR19">
-        <v>60</v>
-      </c>
-      <c r="BS19">
-        <v>4.6</v>
-      </c>
-      <c r="BT19">
-        <v>6</v>
-      </c>
-      <c r="BU19">
-        <v>3.9</v>
-      </c>
-      <c r="BV19">
-        <v>24</v>
-      </c>
-      <c r="BW19">
-        <v>4.1</v>
-      </c>
-      <c r="BX19">
-        <v>48</v>
-      </c>
       <c r="BY19">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ19">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="CA19">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="CB19" t="s">
         <v>177</v>
@@ -5497,76 +5497,76 @@
         <v>161</v>
       </c>
       <c r="F20">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G20">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H20">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="I20">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P20">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q20">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="R20">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S20">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="T20">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U20">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="V20">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W20">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="X20">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Y20">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z20">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA20">
         <v>60</v>
       </c>
       <c r="AB20">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AC20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD20">
         <v>16.5</v>
@@ -5575,16 +5575,16 @@
         <v>36</v>
       </c>
       <c r="AF20">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AG20">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH20">
         <v>14</v>
       </c>
       <c r="AI20">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ20">
         <v>36</v>
@@ -5593,76 +5593,76 @@
         <v>21</v>
       </c>
       <c r="AL20">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AM20">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AN20">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AO20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP20">
         <v>29</v>
       </c>
       <c r="AQ20">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR20">
         <v>26</v>
       </c>
       <c r="AS20">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AT20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU20">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV20">
         <v>13.5</v>
       </c>
       <c r="AW20">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX20">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AY20">
+        <v>11</v>
+      </c>
+      <c r="AZ20">
         <v>11.5</v>
-      </c>
-      <c r="AZ20">
-        <v>11</v>
       </c>
       <c r="BA20">
         <v>21</v>
       </c>
       <c r="BB20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC20">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD20">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BF20">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH20">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BI20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ20">
         <v>9.6</v>
@@ -5671,52 +5671,52 @@
         <v>6</v>
       </c>
       <c r="BL20">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BM20">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BN20">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO20">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP20">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BQ20">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BR20">
         <v>23</v>
       </c>
       <c r="BS20">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BT20">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU20">
         <v>5.4</v>
       </c>
       <c r="BV20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BX20">
         <v>26</v>
       </c>
       <c r="BY20">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BZ20">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA20">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="CB20" t="s">
         <v>177</v>
@@ -5742,19 +5742,19 @@
         <v>1.28</v>
       </c>
       <c r="G21">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H21">
         <v>15.5</v>
       </c>
       <c r="I21">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="J21">
         <v>5.5</v>
       </c>
       <c r="K21">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L21">
         <v>1.36</v>
@@ -5775,7 +5775,7 @@
         <v>1.87</v>
       </c>
       <c r="R21">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S21">
         <v>3.2</v>
@@ -5790,7 +5790,7 @@
         <v>1.05</v>
       </c>
       <c r="W21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X21">
         <v>18</v>
@@ -5799,7 +5799,7 @@
         <v>950</v>
       </c>
       <c r="Z21">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AA21">
         <v>1000</v>
@@ -5808,10 +5808,10 @@
         <v>7.2</v>
       </c>
       <c r="AC21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD21">
-        <v>950</v>
+        <v>170</v>
       </c>
       <c r="AE21">
         <v>460</v>
@@ -5829,7 +5829,7 @@
         <v>340</v>
       </c>
       <c r="AJ21">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AK21">
         <v>19.5</v>
@@ -5841,7 +5841,7 @@
         <v>370</v>
       </c>
       <c r="AN21">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AO21">
         <v>1000</v>
@@ -5850,25 +5850,25 @@
         <v>13.5</v>
       </c>
       <c r="AQ21">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR21">
+        <v>9.4</v>
+      </c>
+      <c r="AS21">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AS21">
-        <v>10</v>
       </c>
       <c r="AT21">
         <v>5.6</v>
       </c>
       <c r="AU21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV21">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW21">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX21">
         <v>5.8</v>
@@ -5877,10 +5877,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ21">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BA21">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB21">
         <v>7.8</v>
@@ -5889,76 +5889,76 @@
         <v>13.5</v>
       </c>
       <c r="BD21">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BE21">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF21">
         <v>5.1</v>
       </c>
       <c r="BG21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK21">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BO21">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BQ21">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="CB21" t="s">
         <v>177</v>
@@ -5996,37 +5996,37 @@
         <v>2.8</v>
       </c>
       <c r="K22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L22">
+        <v>1.62</v>
+      </c>
+      <c r="M22">
+        <v>1.14</v>
+      </c>
+      <c r="N22">
+        <v>2.5</v>
+      </c>
+      <c r="O22">
         <v>1.63</v>
       </c>
-      <c r="M22">
-        <v>1.15</v>
-      </c>
-      <c r="N22">
-        <v>2.42</v>
-      </c>
-      <c r="O22">
-        <v>1.64</v>
-      </c>
       <c r="P22">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q22">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="R22">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S22">
         <v>6.2</v>
       </c>
       <c r="T22">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U22">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V22">
         <v>1.4</v>
@@ -6035,7 +6035,7 @@
         <v>1.53</v>
       </c>
       <c r="X22">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -6044,7 +6044,7 @@
         <v>22</v>
       </c>
       <c r="AA22">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AB22">
         <v>7.4</v>
@@ -6053,10 +6053,10 @@
         <v>7.2</v>
       </c>
       <c r="AD22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE22">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF22">
         <v>16.5</v>
@@ -6068,16 +6068,16 @@
         <v>26</v>
       </c>
       <c r="AI22">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ22">
         <v>55</v>
       </c>
       <c r="AK22">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL22">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AM22">
         <v>500</v>
@@ -6086,7 +6086,7 @@
         <v>60</v>
       </c>
       <c r="AO22">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP22">
         <v>6.4</v>
@@ -6098,7 +6098,7 @@
         <v>17.5</v>
       </c>
       <c r="AS22">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT22">
         <v>6.2</v>
@@ -6122,7 +6122,7 @@
         <v>20</v>
       </c>
       <c r="BA22">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB22">
         <v>18</v>
@@ -6131,10 +6131,10 @@
         <v>18</v>
       </c>
       <c r="BD22">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE22">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF22">
         <v>36</v>
@@ -6143,10 +6143,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH22">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BI22">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ22">
         <v>13.5</v>
@@ -6158,7 +6158,7 @@
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BN22">
         <v>6.2</v>
@@ -6167,7 +6167,7 @@
         <v>4.3</v>
       </c>
       <c r="BP22">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ22">
         <v>5.1</v>
@@ -6176,7 +6176,7 @@
         <v>60</v>
       </c>
       <c r="BS22">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BT22">
         <v>7</v>
@@ -6185,22 +6185,22 @@
         <v>4.8</v>
       </c>
       <c r="BV22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW22">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY22">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BZ22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="CA22">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB22" t="s">
         <v>177</v>
@@ -6232,10 +6232,10 @@
         <v>4.5</v>
       </c>
       <c r="I23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J23">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K23">
         <v>3.2</v>
@@ -6253,10 +6253,10 @@
         <v>1.66</v>
       </c>
       <c r="P23">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q23">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R23">
         <v>1.14</v>
@@ -6265,13 +6265,13 @@
         <v>6.6</v>
       </c>
       <c r="T23">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="U23">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V23">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W23">
         <v>1.81</v>
@@ -6340,7 +6340,7 @@
         <v>23</v>
       </c>
       <c r="AS23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT23">
         <v>5.2</v>
@@ -6364,7 +6364,7 @@
         <v>16</v>
       </c>
       <c r="BA23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB23">
         <v>19</v>
@@ -6474,13 +6474,13 @@
         <v>2.08</v>
       </c>
       <c r="I24">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J24">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="K24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L24">
         <v>1.66</v>
@@ -6495,7 +6495,7 @@
         <v>1.67</v>
       </c>
       <c r="P24">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q24">
         <v>3.05</v>
@@ -6513,10 +6513,10 @@
         <v>1.62</v>
       </c>
       <c r="V24">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W24">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X24">
         <v>7.6</v>
@@ -6567,7 +6567,7 @@
         <v>310</v>
       </c>
       <c r="AN24">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="AO24">
         <v>36</v>
@@ -6627,64 +6627,64 @@
         <v>7.2</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK24">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO24">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ24">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA24">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB24" t="s">
         <v>177</v>
@@ -6710,7 +6710,7 @@
         <v>1.8</v>
       </c>
       <c r="G25">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H25">
         <v>4.6</v>
@@ -6719,7 +6719,7 @@
         <v>5.1</v>
       </c>
       <c r="J25">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K25">
         <v>4.3</v>
@@ -6731,22 +6731,22 @@
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O25">
         <v>1.28</v>
       </c>
       <c r="P25">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q25">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R25">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S25">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T25">
         <v>1.11</v>
@@ -6758,7 +6758,7 @@
         <v>1.25</v>
       </c>
       <c r="W25">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X25">
         <v>970</v>
@@ -6809,10 +6809,10 @@
         <v>580</v>
       </c>
       <c r="AN25">
-        <v>970</v>
+        <v>600</v>
       </c>
       <c r="AO25">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP25">
         <v>1.35</v>
@@ -6949,16 +6949,16 @@
         <v>167</v>
       </c>
       <c r="F26">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G26">
         <v>2.54</v>
       </c>
       <c r="H26">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J26">
         <v>3.8</v>
@@ -6973,31 +6973,31 @@
         <v>1.04</v>
       </c>
       <c r="N26">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O26">
         <v>1.2</v>
       </c>
       <c r="P26">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q26">
         <v>1.63</v>
       </c>
       <c r="R26">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S26">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T26">
         <v>1.51</v>
       </c>
       <c r="U26">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W26">
         <v>1.65</v>
@@ -7006,16 +7006,16 @@
         <v>25</v>
       </c>
       <c r="Y26">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z26">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA26">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC26">
         <v>8.800000000000001</v>
@@ -7027,7 +7027,7 @@
         <v>30</v>
       </c>
       <c r="AF26">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AG26">
         <v>11.5</v>
@@ -7042,40 +7042,40 @@
         <v>36</v>
       </c>
       <c r="AK26">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL26">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM26">
         <v>55</v>
       </c>
       <c r="AN26">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ26">
         <v>16</v>
       </c>
       <c r="AR26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS26">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AT26">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU26">
         <v>8.199999999999999</v>
       </c>
       <c r="AV26">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW26">
         <v>25</v>
@@ -7087,7 +7087,7 @@
         <v>11</v>
       </c>
       <c r="AZ26">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA26">
         <v>30</v>
@@ -7096,10 +7096,10 @@
         <v>30</v>
       </c>
       <c r="BC26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD26">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE26">
         <v>48</v>
@@ -7111,64 +7111,64 @@
         <v>16.5</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI26">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK26">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL26">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM26">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO26">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ26">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS26">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU26">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW26">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY26">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA26">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="CB26" t="s">
         <v>177</v>
@@ -7194,13 +7194,13 @@
         <v>2.04</v>
       </c>
       <c r="G27">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H27">
+        <v>3.95</v>
+      </c>
+      <c r="I27">
         <v>4</v>
-      </c>
-      <c r="I27">
-        <v>4.1</v>
       </c>
       <c r="J27">
         <v>3.75</v>
@@ -7239,10 +7239,10 @@
         <v>2.28</v>
       </c>
       <c r="V27">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="X27">
         <v>16</v>
@@ -7251,13 +7251,13 @@
         <v>17</v>
       </c>
       <c r="Z27">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA27">
         <v>80</v>
       </c>
       <c r="AB27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC27">
         <v>8.6</v>
@@ -7266,13 +7266,13 @@
         <v>16.5</v>
       </c>
       <c r="AE27">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF27">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH27">
         <v>17</v>
@@ -7281,22 +7281,22 @@
         <v>55</v>
       </c>
       <c r="AJ27">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK27">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL27">
         <v>34</v>
       </c>
       <c r="AM27">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN27">
         <v>13</v>
       </c>
       <c r="AO27">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP27">
         <v>15</v>
@@ -7317,7 +7317,7 @@
         <v>8</v>
       </c>
       <c r="AV27">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW27">
         <v>40</v>
@@ -7326,13 +7326,13 @@
         <v>12</v>
       </c>
       <c r="AY27">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ27">
         <v>15.5</v>
       </c>
       <c r="BA27">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB27">
         <v>21</v>
@@ -7350,13 +7350,13 @@
         <v>12</v>
       </c>
       <c r="BG27">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BH27">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI27">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ27">
         <v>9.800000000000001</v>
@@ -7368,13 +7368,13 @@
         <v>120</v>
       </c>
       <c r="BM27">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BN27">
         <v>5.6</v>
       </c>
       <c r="BO27">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP27">
         <v>14.5</v>
@@ -7386,31 +7386,31 @@
         <v>27</v>
       </c>
       <c r="BS27">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BT27">
         <v>7.8</v>
       </c>
       <c r="BU27">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BV27">
         <v>34</v>
       </c>
       <c r="BW27">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX27">
         <v>44</v>
       </c>
       <c r="BY27">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BZ27">
         <v>22</v>
       </c>
       <c r="CA27">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="CB27" t="s">
         <v>177</v>
@@ -7433,22 +7433,22 @@
         <v>169</v>
       </c>
       <c r="F28">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G28">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H28">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I28">
         <v>8.6</v>
       </c>
       <c r="J28">
+        <v>4.3</v>
+      </c>
+      <c r="K28">
         <v>4.4</v>
-      </c>
-      <c r="K28">
-        <v>4.6</v>
       </c>
       <c r="L28">
         <v>1.45</v>
@@ -7463,28 +7463,28 @@
         <v>1.38</v>
       </c>
       <c r="P28">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q28">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R28">
         <v>1.3</v>
       </c>
       <c r="S28">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T28">
         <v>2.3</v>
       </c>
       <c r="U28">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V28">
         <v>1.13</v>
       </c>
       <c r="W28">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="X28">
         <v>13</v>
@@ -7493,13 +7493,13 @@
         <v>22</v>
       </c>
       <c r="Z28">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AA28">
         <v>1000</v>
       </c>
       <c r="AB28">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC28">
         <v>10.5</v>
@@ -7511,7 +7511,7 @@
         <v>170</v>
       </c>
       <c r="AF28">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AG28">
         <v>11</v>
@@ -7520,13 +7520,13 @@
         <v>46</v>
       </c>
       <c r="AI28">
-        <v>160</v>
+        <v>540</v>
       </c>
       <c r="AJ28">
         <v>13</v>
       </c>
       <c r="AK28">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL28">
         <v>50</v>
@@ -7535,10 +7535,10 @@
         <v>1000</v>
       </c>
       <c r="AN28">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP28">
         <v>12</v>
@@ -7550,7 +7550,7 @@
         <v>55</v>
       </c>
       <c r="AS28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT28">
         <v>6.2</v>
@@ -7574,22 +7574,22 @@
         <v>26</v>
       </c>
       <c r="BA28">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="BB28">
         <v>12</v>
       </c>
       <c r="BC28">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD28">
         <v>44</v>
       </c>
       <c r="BE28">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="BF28">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG28">
         <v>48</v>
@@ -7598,61 +7598,61 @@
         <v>3.25</v>
       </c>
       <c r="BI28">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="BJ28">
         <v>12.5</v>
       </c>
       <c r="BK28">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="BN28">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BO28">
         <v>3.4</v>
       </c>
       <c r="BP28">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BQ28">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT28">
         <v>12</v>
       </c>
       <c r="BU28">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="CB28" t="s">
         <v>177</v>
@@ -7675,19 +7675,19 @@
         <v>170</v>
       </c>
       <c r="F29">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G29">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H29">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I29">
         <v>2.22</v>
       </c>
       <c r="J29">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K29">
         <v>4.6</v>
@@ -7699,34 +7699,34 @@
         <v>1.03</v>
       </c>
       <c r="N29">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O29">
         <v>1.15</v>
       </c>
       <c r="P29">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q29">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R29">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S29">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T29">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V29">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W29">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X29">
         <v>36</v>
@@ -7735,13 +7735,13 @@
         <v>18.5</v>
       </c>
       <c r="Z29">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA29">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AB29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC29">
         <v>12</v>
@@ -7750,7 +7750,7 @@
         <v>12.5</v>
       </c>
       <c r="AE29">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF29">
         <v>34</v>
@@ -7759,46 +7759,46 @@
         <v>16</v>
       </c>
       <c r="AH29">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI29">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ29">
         <v>55</v>
       </c>
       <c r="AK29">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL29">
         <v>32</v>
       </c>
       <c r="AM29">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="AN29">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO29">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AP29">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AQ29">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AR29">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS29">
         <v>14.5</v>
       </c>
       <c r="AT29">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="AU29">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AV29">
         <v>6.2</v>
@@ -7807,94 +7807,94 @@
         <v>16</v>
       </c>
       <c r="AX29">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AY29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ29">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BA29">
         <v>20</v>
       </c>
       <c r="BB29">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BC29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BE29">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BF29">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="BG29">
         <v>7.2</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI29">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK29">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BL29">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM29">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO29">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ29">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS29">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU29">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW29">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY29">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA29">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB29" t="s">
         <v>177</v>
@@ -7917,49 +7917,49 @@
         <v>171</v>
       </c>
       <c r="F30">
+        <v>1.3</v>
+      </c>
+      <c r="G30">
         <v>1.31</v>
       </c>
-      <c r="G30">
-        <v>1.32</v>
-      </c>
       <c r="H30">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I30">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J30">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K30">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L30">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M30">
         <v>1.02</v>
       </c>
       <c r="N30">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="O30">
         <v>1.13</v>
       </c>
       <c r="P30">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q30">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="R30">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="S30">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T30">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U30">
         <v>2.18</v>
@@ -7968,7 +7968,7 @@
         <v>1.09</v>
       </c>
       <c r="W30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X30">
         <v>36</v>
@@ -7980,49 +7980,49 @@
         <v>120</v>
       </c>
       <c r="AA30">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="AB30">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC30">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD30">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AE30">
         <v>140</v>
       </c>
       <c r="AF30">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG30">
         <v>10.5</v>
       </c>
       <c r="AH30">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI30">
         <v>110</v>
       </c>
       <c r="AJ30">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AK30">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AL30">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AM30">
         <v>110</v>
       </c>
       <c r="AN30">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AO30">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP30">
         <v>34</v>
@@ -8034,22 +8034,22 @@
         <v>100</v>
       </c>
       <c r="AS30">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AT30">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU30">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AV30">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AW30">
         <v>110</v>
       </c>
       <c r="AX30">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY30">
         <v>10</v>
@@ -8067,13 +8067,13 @@
         <v>11.5</v>
       </c>
       <c r="BD30">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE30">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF30">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BG30">
         <v>120</v>
@@ -8082,31 +8082,31 @@
         <v>5.2</v>
       </c>
       <c r="BI30">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ30">
         <v>11</v>
       </c>
       <c r="BK30">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL30">
         <v>110</v>
       </c>
       <c r="BM30">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO30">
         <v>3.85</v>
       </c>
       <c r="BP30">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BQ30">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR30">
         <v>19.5</v>
@@ -8115,25 +8115,25 @@
         <v>16</v>
       </c>
       <c r="BT30">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BU30">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BV30">
         <v>75</v>
       </c>
       <c r="BW30">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BX30">
         <v>65</v>
       </c>
       <c r="BY30">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ30">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CA30">
         <v>7.2</v>
@@ -8159,22 +8159,22 @@
         <v>172</v>
       </c>
       <c r="F31">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G31">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="H31">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I31">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J31">
+        <v>3.35</v>
+      </c>
+      <c r="K31">
         <v>3.4</v>
-      </c>
-      <c r="K31">
-        <v>3.45</v>
       </c>
       <c r="L31">
         <v>1.45</v>
@@ -8183,13 +8183,13 @@
         <v>1.08</v>
       </c>
       <c r="N31">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O31">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P31">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q31">
         <v>2.1</v>
@@ -8198,31 +8198,31 @@
         <v>1.33</v>
       </c>
       <c r="S31">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T31">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U31">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X31">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y31">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z31">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA31">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB31">
         <v>9.800000000000001</v>
@@ -8231,52 +8231,52 @@
         <v>7.6</v>
       </c>
       <c r="AD31">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AE31">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AF31">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG31">
         <v>11.5</v>
       </c>
       <c r="AH31">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI31">
         <v>55</v>
       </c>
       <c r="AJ31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK31">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL31">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AM31">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="AN31">
         <v>25</v>
       </c>
       <c r="AO31">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ31">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR31">
         <v>20</v>
       </c>
       <c r="AS31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT31">
         <v>9.199999999999999</v>
@@ -8291,94 +8291,94 @@
         <v>34</v>
       </c>
       <c r="AX31">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY31">
         <v>10.5</v>
       </c>
       <c r="AZ31">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA31">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB31">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BC31">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD31">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF31">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BG31">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI31">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK31">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO31">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ31">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS31">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU31">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB31" t="s">
         <v>177</v>
@@ -8404,10 +8404,10 @@
         <v>2.82</v>
       </c>
       <c r="G32">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H32">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I32">
         <v>3.05</v>
@@ -8416,7 +8416,7 @@
         <v>3.15</v>
       </c>
       <c r="K32">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L32">
         <v>1.56</v>
@@ -8425,37 +8425,37 @@
         <v>1.12</v>
       </c>
       <c r="N32">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O32">
         <v>1.52</v>
       </c>
       <c r="P32">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q32">
         <v>2.62</v>
       </c>
       <c r="R32">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S32">
         <v>5.3</v>
       </c>
       <c r="T32">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U32">
         <v>1.84</v>
       </c>
       <c r="V32">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W32">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X32">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>9.199999999999999</v>
@@ -8464,7 +8464,7 @@
         <v>19</v>
       </c>
       <c r="AA32">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AB32">
         <v>8.800000000000001</v>
@@ -8530,7 +8530,7 @@
         <v>11.5</v>
       </c>
       <c r="AW32">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX32">
         <v>15.5</v>
@@ -8542,7 +8542,7 @@
         <v>18</v>
       </c>
       <c r="BA32">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB32">
         <v>10</v>
@@ -8551,10 +8551,10 @@
         <v>32</v>
       </c>
       <c r="BD32">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE32">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF32">
         <v>10</v>
@@ -8643,7 +8643,7 @@
         <v>174</v>
       </c>
       <c r="F33">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G33">
         <v>2.46</v>
@@ -8652,40 +8652,40 @@
         <v>3.35</v>
       </c>
       <c r="I33">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J33">
         <v>3.3</v>
       </c>
       <c r="K33">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L33">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M33">
         <v>1.09</v>
       </c>
       <c r="N33">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O33">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P33">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q33">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R33">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S33">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T33">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U33">
         <v>2.02</v>
@@ -8694,13 +8694,13 @@
         <v>1.4</v>
       </c>
       <c r="W33">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X33">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y33">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z33">
         <v>23</v>
@@ -8709,7 +8709,7 @@
         <v>75</v>
       </c>
       <c r="AB33">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC33">
         <v>7.6</v>
@@ -8727,7 +8727,7 @@
         <v>11.5</v>
       </c>
       <c r="AH33">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AI33">
         <v>60</v>
@@ -8736,7 +8736,7 @@
         <v>40</v>
       </c>
       <c r="AK33">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL33">
         <v>48</v>
@@ -8745,22 +8745,22 @@
         <v>120</v>
       </c>
       <c r="AN33">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO33">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AP33">
         <v>10</v>
       </c>
       <c r="AQ33">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR33">
         <v>19.5</v>
       </c>
       <c r="AS33">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT33">
         <v>8.199999999999999</v>
@@ -8790,13 +8790,13 @@
         <v>19</v>
       </c>
       <c r="BC33">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD33">
         <v>22</v>
       </c>
       <c r="BE33">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF33">
         <v>19</v>
@@ -8805,22 +8805,22 @@
         <v>34</v>
       </c>
       <c r="BH33">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BI33">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BJ33">
         <v>11.5</v>
       </c>
       <c r="BK33">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BL33">
         <v>150</v>
       </c>
       <c r="BM33">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BN33">
         <v>6.2</v>
@@ -8832,16 +8832,16 @@
         <v>22</v>
       </c>
       <c r="BQ33">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BR33">
         <v>40</v>
       </c>
       <c r="BS33">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BT33">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU33">
         <v>4.9</v>
@@ -8850,19 +8850,19 @@
         <v>34</v>
       </c>
       <c r="BW33">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BX33">
         <v>48</v>
       </c>
       <c r="BY33">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BZ33">
         <v>36</v>
       </c>
       <c r="CA33">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="CB33" t="s">
         <v>177</v>
@@ -8885,220 +8885,220 @@
         <v>175</v>
       </c>
       <c r="F34">
+        <v>1.43</v>
+      </c>
+      <c r="G34">
+        <v>1.48</v>
+      </c>
+      <c r="H34">
+        <v>7.4</v>
+      </c>
+      <c r="I34">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J34">
+        <v>4.7</v>
+      </c>
+      <c r="K34">
+        <v>5.3</v>
+      </c>
+      <c r="L34">
         <v>1.31</v>
       </c>
-      <c r="G34">
-        <v>1.34</v>
-      </c>
-      <c r="H34">
+      <c r="M34">
+        <v>1.04</v>
+      </c>
+      <c r="N34">
+        <v>4.9</v>
+      </c>
+      <c r="O34">
+        <v>1.23</v>
+      </c>
+      <c r="P34">
+        <v>2.4</v>
+      </c>
+      <c r="Q34">
+        <v>1.69</v>
+      </c>
+      <c r="R34">
+        <v>1.53</v>
+      </c>
+      <c r="S34">
+        <v>2.78</v>
+      </c>
+      <c r="T34">
+        <v>1.9</v>
+      </c>
+      <c r="U34">
+        <v>1.93</v>
+      </c>
+      <c r="V34">
+        <v>1.12</v>
+      </c>
+      <c r="W34">
+        <v>3</v>
+      </c>
+      <c r="X34">
+        <v>25</v>
+      </c>
+      <c r="Y34">
+        <v>30</v>
+      </c>
+      <c r="Z34">
+        <v>75</v>
+      </c>
+      <c r="AA34">
+        <v>250</v>
+      </c>
+      <c r="AB34">
+        <v>9.6</v>
+      </c>
+      <c r="AC34">
         <v>11.5</v>
       </c>
-      <c r="I34">
-        <v>13</v>
-      </c>
-      <c r="J34">
-        <v>6</v>
-      </c>
-      <c r="K34">
+      <c r="AD34">
+        <v>32</v>
+      </c>
+      <c r="AE34">
+        <v>260</v>
+      </c>
+      <c r="AF34">
+        <v>10.5</v>
+      </c>
+      <c r="AG34">
+        <v>11.5</v>
+      </c>
+      <c r="AH34">
+        <v>27</v>
+      </c>
+      <c r="AI34">
+        <v>240</v>
+      </c>
+      <c r="AJ34">
+        <v>15</v>
+      </c>
+      <c r="AK34">
+        <v>18.5</v>
+      </c>
+      <c r="AL34">
+        <v>38</v>
+      </c>
+      <c r="AM34">
+        <v>130</v>
+      </c>
+      <c r="AN34">
+        <v>6.6</v>
+      </c>
+      <c r="AO34">
+        <v>170</v>
+      </c>
+      <c r="AP34">
+        <v>18.5</v>
+      </c>
+      <c r="AQ34">
+        <v>21</v>
+      </c>
+      <c r="AR34">
+        <v>6.4</v>
+      </c>
+      <c r="AS34">
         <v>6.8</v>
       </c>
-      <c r="L34">
-        <v>1.27</v>
-      </c>
-      <c r="M34">
-        <v>1.03</v>
-      </c>
-      <c r="N34">
-        <v>5.8</v>
-      </c>
-      <c r="O34">
-        <v>1.18</v>
-      </c>
-      <c r="P34">
-        <v>2.7</v>
-      </c>
-      <c r="Q34">
-        <v>1.54</v>
-      </c>
-      <c r="R34">
-        <v>1.68</v>
-      </c>
-      <c r="S34">
-        <v>2.36</v>
-      </c>
-      <c r="T34">
-        <v>2.02</v>
-      </c>
-      <c r="U34">
-        <v>1.86</v>
-      </c>
-      <c r="V34">
-        <v>1.08</v>
-      </c>
-      <c r="W34">
-        <v>3.9</v>
-      </c>
-      <c r="X34">
-        <v>30</v>
-      </c>
-      <c r="Y34">
-        <v>44</v>
-      </c>
-      <c r="Z34">
-        <v>140</v>
-      </c>
-      <c r="AA34">
-        <v>510</v>
-      </c>
-      <c r="AB34">
-        <v>12</v>
-      </c>
-      <c r="AC34">
-        <v>14.5</v>
-      </c>
-      <c r="AD34">
-        <v>950</v>
-      </c>
-      <c r="AE34">
-        <v>210</v>
-      </c>
-      <c r="AF34">
-        <v>10</v>
-      </c>
-      <c r="AG34">
+      <c r="AT34">
+        <v>7.8</v>
+      </c>
+      <c r="AU34">
+        <v>8</v>
+      </c>
+      <c r="AV34">
+        <v>21</v>
+      </c>
+      <c r="AW34">
+        <v>6.6</v>
+      </c>
+      <c r="AX34">
+        <v>7.8</v>
+      </c>
+      <c r="AY34">
+        <v>7.6</v>
+      </c>
+      <c r="AZ34">
+        <v>17</v>
+      </c>
+      <c r="BA34">
+        <v>6.6</v>
+      </c>
+      <c r="BB34">
+        <v>11</v>
+      </c>
+      <c r="BC34">
         <v>12.5</v>
       </c>
-      <c r="AH34">
-        <v>34</v>
-      </c>
-      <c r="AI34">
-        <v>160</v>
-      </c>
-      <c r="AJ34">
-        <v>12</v>
-      </c>
-      <c r="AK34">
-        <v>16.5</v>
-      </c>
-      <c r="AL34">
-        <v>42</v>
-      </c>
-      <c r="AM34">
-        <v>170</v>
-      </c>
-      <c r="AN34">
-        <v>4.4</v>
-      </c>
-      <c r="AO34">
-        <v>260</v>
-      </c>
-      <c r="AP34">
-        <v>5.9</v>
-      </c>
-      <c r="AQ34">
-        <v>6.2</v>
-      </c>
-      <c r="AR34">
-        <v>7</v>
-      </c>
-      <c r="AS34">
+      <c r="BD34">
+        <v>6.4</v>
+      </c>
+      <c r="BE34">
+        <v>6.6</v>
+      </c>
+      <c r="BF34">
+        <v>5.5</v>
+      </c>
+      <c r="BG34">
         <v>7.2</v>
       </c>
-      <c r="AT34">
+      <c r="BH34">
+        <v>4.6</v>
+      </c>
+      <c r="BI34">
+        <v>3.4</v>
+      </c>
+      <c r="BJ34">
+        <v>11.5</v>
+      </c>
+      <c r="BK34">
         <v>4.5</v>
-      </c>
-      <c r="AU34">
-        <v>4.8</v>
-      </c>
-      <c r="AV34">
-        <v>6.2</v>
-      </c>
-      <c r="AW34">
-        <v>7</v>
-      </c>
-      <c r="AX34">
-        <v>6.8</v>
-      </c>
-      <c r="AY34">
-        <v>4.6</v>
-      </c>
-      <c r="AZ34">
-        <v>6</v>
-      </c>
-      <c r="BA34">
-        <v>7</v>
-      </c>
-      <c r="BB34">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC34">
-        <v>5</v>
-      </c>
-      <c r="BD34">
-        <v>6.2</v>
-      </c>
-      <c r="BE34">
-        <v>7</v>
-      </c>
-      <c r="BF34">
-        <v>3.9</v>
-      </c>
-      <c r="BG34">
-        <v>7</v>
-      </c>
-      <c r="BH34">
-        <v>1000</v>
-      </c>
-      <c r="BI34">
-        <v>1.04</v>
-      </c>
-      <c r="BJ34">
-        <v>1000</v>
-      </c>
-      <c r="BK34">
-        <v>1.04</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO34">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP34">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ34">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR34">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS34">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT34">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU34">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV34">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW34">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX34">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY34">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ34">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>176</v>
       </c>
       <c r="F35">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -9139,40 +9139,40 @@
         <v>4.9</v>
       </c>
       <c r="J35">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K35">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L35">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M35">
         <v>1.09</v>
       </c>
       <c r="N35">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O35">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="P35">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Q35">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R35">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S35">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T35">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U35">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="V35">
         <v>1.26</v>
@@ -9190,13 +9190,13 @@
         <v>44</v>
       </c>
       <c r="AA35">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB35">
         <v>9.6</v>
       </c>
       <c r="AC35">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD35">
         <v>970</v>
@@ -9226,13 +9226,13 @@
         <v>46</v>
       </c>
       <c r="AM35">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN35">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AO35">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AP35">
         <v>10</v>
@@ -9241,10 +9241,10 @@
         <v>12</v>
       </c>
       <c r="AR35">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS35">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT35">
         <v>6.8</v>
@@ -9256,7 +9256,7 @@
         <v>16.5</v>
       </c>
       <c r="AW35">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX35">
         <v>10</v>
@@ -9265,46 +9265,46 @@
         <v>9.4</v>
       </c>
       <c r="AZ35">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BA35">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB35">
         <v>20</v>
       </c>
       <c r="BC35">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BD35">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BE35">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BF35">
         <v>12.5</v>
       </c>
       <c r="BG35">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH35">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BI35">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="BJ35">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK35">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BN35">
         <v>4.5</v>
@@ -9316,16 +9316,16 @@
         <v>14</v>
       </c>
       <c r="BQ35">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT35">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU35">
         <v>5.9</v>
@@ -9334,19 +9334,19 @@
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB35" t="s">
         <v>177</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-26.xlsx
@@ -547,7 +547,7 @@
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-26 03:53:56</t>
+    <t>2026-08-26 06:03:53</t>
   </si>
 </sst>
 </file>
@@ -1147,103 +1147,103 @@
         <v>3.75</v>
       </c>
       <c r="H2">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I2">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
         <v>3.4</v>
       </c>
       <c r="L2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q2">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S2">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U2">
         <v>2.04</v>
       </c>
       <c r="V2">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB2">
+        <v>12.5</v>
+      </c>
+      <c r="AC2">
+        <v>9.4</v>
+      </c>
+      <c r="AD2">
         <v>12</v>
       </c>
-      <c r="AC2">
-        <v>7.2</v>
-      </c>
-      <c r="AD2">
-        <v>11.5</v>
-      </c>
       <c r="AE2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG2">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AH2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AK2">
         <v>55</v>
       </c>
       <c r="AL2">
+        <v>150</v>
+      </c>
+      <c r="AM2">
+        <v>450</v>
+      </c>
+      <c r="AN2">
         <v>65</v>
-      </c>
-      <c r="AM2">
-        <v>130</v>
-      </c>
-      <c r="AN2">
-        <v>70</v>
       </c>
       <c r="AO2">
         <v>24</v>
@@ -1252,7 +1252,7 @@
         <v>10</v>
       </c>
       <c r="AQ2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR2">
         <v>12.5</v>
@@ -1264,103 +1264,103 @@
         <v>11</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2">
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY2">
         <v>14</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BB2">
         <v>48</v>
       </c>
       <c r="BC2">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BD2">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="BF2">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="BG2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH2">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BI2">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>20</v>
+        <v>2.78</v>
       </c>
       <c r="BN2">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BP2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>13</v>
+        <v>2.78</v>
       </c>
       <c r="BR2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>15</v>
+        <v>2.78</v>
       </c>
       <c r="BT2">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
         <v>4.5</v>
       </c>
       <c r="BV2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.800000000000001</v>
+        <v>2.78</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>13.5</v>
+        <v>2.78</v>
       </c>
       <c r="BZ2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>13.5</v>
+        <v>2.78</v>
       </c>
       <c r="CB2" t="s">
         <v>177</v>
@@ -1386,10 +1386,10 @@
         <v>2.4</v>
       </c>
       <c r="G3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
         <v>3.15</v>
@@ -1398,7 +1398,7 @@
         <v>3.7</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
         <v>1.38</v>
@@ -1407,25 +1407,25 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
         <v>1.25</v>
       </c>
       <c r="P3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R3">
         <v>1.49</v>
       </c>
       <c r="S3">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U3">
         <v>2.46</v>
@@ -1434,31 +1434,31 @@
         <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AB3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3">
         <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF3">
         <v>17.5</v>
@@ -1467,40 +1467,40 @@
         <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN3">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AO3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP3">
         <v>16.5</v>
       </c>
       <c r="AQ3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AT3">
         <v>11.5</v>
@@ -1512,10 +1512,10 @@
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AX3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY3">
         <v>10</v>
@@ -1524,85 +1524,85 @@
         <v>14</v>
       </c>
       <c r="BA3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BB3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD3">
         <v>27</v>
       </c>
       <c r="BE3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BF3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG3">
         <v>21</v>
       </c>
       <c r="BH3">
-        <v>3.8</v>
+        <v>980</v>
       </c>
       <c r="BI3">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BJ3">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="BL3">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16.5</v>
+        <v>2.42</v>
       </c>
       <c r="BN3">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>2.42</v>
       </c>
       <c r="BR3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>11.5</v>
+        <v>2.76</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>2.76</v>
       </c>
       <c r="BX3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>2.42</v>
       </c>
       <c r="BZ3">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>10</v>
+        <v>2.76</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1628,154 +1628,154 @@
         <v>1.57</v>
       </c>
       <c r="G4">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P4">
         <v>1.77</v>
       </c>
       <c r="Q4">
+        <v>2.24</v>
+      </c>
+      <c r="R4">
+        <v>1.28</v>
+      </c>
+      <c r="S4">
+        <v>4.3</v>
+      </c>
+      <c r="T4">
         <v>2.28</v>
       </c>
-      <c r="R4">
-        <v>1.27</v>
-      </c>
-      <c r="S4">
-        <v>4.5</v>
-      </c>
-      <c r="T4">
-        <v>2.32</v>
-      </c>
       <c r="U4">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W4">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y4">
         <v>21</v>
       </c>
       <c r="Z4">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AA4">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AB4">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="AD4">
         <v>32</v>
       </c>
       <c r="AE4">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI4">
-        <v>170</v>
+        <v>530</v>
       </c>
       <c r="AJ4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AM4">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
         <v>11.5</v>
       </c>
       <c r="AO4">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR4">
         <v>32</v>
       </c>
       <c r="AS4">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AT4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU4">
         <v>8.6</v>
       </c>
       <c r="AV4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AW4">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="AX4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BA4">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="BB4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC4">
         <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BE4">
         <v>70</v>
@@ -1790,61 +1790,61 @@
         <v>3.05</v>
       </c>
       <c r="BI4">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="BJ4">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BL4">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>15</v>
+        <v>3.3</v>
       </c>
       <c r="BN4">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>3.35</v>
       </c>
       <c r="BT4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>9.6</v>
+        <v>2.88</v>
       </c>
       <c r="BV4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>13.5</v>
+        <v>3.35</v>
       </c>
       <c r="BX4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>14</v>
+        <v>3.35</v>
       </c>
       <c r="BZ4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1867,31 +1867,31 @@
         <v>146</v>
       </c>
       <c r="F5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G5">
         <v>1.04</v>
       </c>
       <c r="H5">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I5">
         <v>500</v>
       </c>
       <c r="J5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="L5">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O5">
         <v>1.01</v>
@@ -1906,13 +1906,13 @@
         <v>2.66</v>
       </c>
       <c r="S5">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="T5">
         <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V5">
         <v>1.01</v>
@@ -2109,130 +2109,130 @@
         <v>147</v>
       </c>
       <c r="F6">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="G6">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="H6">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="I6">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="J6">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="K6">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="L6">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M6">
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O6">
         <v>1.15</v>
       </c>
       <c r="P6">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="Q6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R6">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S6">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="T6">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="V6">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="Y6">
         <v>13.5</v>
       </c>
       <c r="Z6">
+        <v>9.6</v>
+      </c>
+      <c r="AA6">
+        <v>10.5</v>
+      </c>
+      <c r="AB6">
+        <v>46</v>
+      </c>
+      <c r="AC6">
+        <v>18.5</v>
+      </c>
+      <c r="AD6">
+        <v>14.5</v>
+      </c>
+      <c r="AE6">
+        <v>13.5</v>
+      </c>
+      <c r="AF6">
+        <v>120</v>
+      </c>
+      <c r="AG6">
+        <v>44</v>
+      </c>
+      <c r="AH6">
+        <v>32</v>
+      </c>
+      <c r="AI6">
+        <v>44</v>
+      </c>
+      <c r="AJ6">
+        <v>430</v>
+      </c>
+      <c r="AK6">
+        <v>170</v>
+      </c>
+      <c r="AL6">
+        <v>130</v>
+      </c>
+      <c r="AM6">
+        <v>190</v>
+      </c>
+      <c r="AN6">
+        <v>190</v>
+      </c>
+      <c r="AO6">
+        <v>3.9</v>
+      </c>
+      <c r="AP6">
+        <v>28</v>
+      </c>
+      <c r="AQ6">
         <v>11</v>
       </c>
-      <c r="AA6">
-        <v>12</v>
-      </c>
-      <c r="AB6">
-        <v>50</v>
-      </c>
-      <c r="AC6">
-        <v>14.5</v>
-      </c>
-      <c r="AD6">
-        <v>11.5</v>
-      </c>
-      <c r="AE6">
-        <v>14.5</v>
-      </c>
-      <c r="AF6">
-        <v>95</v>
-      </c>
-      <c r="AG6">
-        <v>34</v>
-      </c>
-      <c r="AH6">
-        <v>25</v>
-      </c>
-      <c r="AI6">
+      <c r="AR6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT6">
         <v>32</v>
       </c>
-      <c r="AJ6">
-        <v>270</v>
-      </c>
-      <c r="AK6">
-        <v>130</v>
-      </c>
-      <c r="AL6">
-        <v>200</v>
-      </c>
-      <c r="AM6">
-        <v>110</v>
-      </c>
-      <c r="AN6">
-        <v>120</v>
-      </c>
-      <c r="AO6">
-        <v>4.3</v>
-      </c>
-      <c r="AP6">
-        <v>22</v>
-      </c>
-      <c r="AQ6">
-        <v>11.5</v>
-      </c>
-      <c r="AR6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS6">
-        <v>10</v>
-      </c>
-      <c r="AT6">
-        <v>28</v>
-      </c>
       <c r="AU6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV6">
         <v>10.5</v>
@@ -2244,91 +2244,91 @@
         <v>16.5</v>
       </c>
       <c r="AY6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AZ6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BA6">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BB6">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC6">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD6">
-        <v>65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE6">
-        <v>70</v>
+        <v>9.4</v>
       </c>
       <c r="BF6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BG6">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="BH6">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>177</v>
@@ -2351,49 +2351,49 @@
         <v>148</v>
       </c>
       <c r="F7">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G7">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H7">
         <v>7.8</v>
       </c>
       <c r="I7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
         <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O7">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P7">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q7">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R7">
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T7">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="U7">
         <v>1.55</v>
@@ -2402,10 +2402,10 @@
         <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X7">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y7">
         <v>19.5</v>
@@ -2414,19 +2414,19 @@
         <v>160</v>
       </c>
       <c r="AA7">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="AB7">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>80</v>
       </c>
       <c r="AE7">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AF7">
         <v>8</v>
@@ -2435,10 +2435,10 @@
         <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="AI7">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AJ7">
         <v>20</v>
@@ -2447,130 +2447,130 @@
         <v>32</v>
       </c>
       <c r="AL7">
-        <v>540</v>
+        <v>230</v>
       </c>
       <c r="AM7">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="AN7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO7">
-        <v>520</v>
+        <v>580</v>
       </c>
       <c r="AP7">
         <v>7.4</v>
       </c>
       <c r="AQ7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR7">
         <v>46</v>
       </c>
       <c r="AS7">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AT7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW7">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX7">
         <v>7</v>
       </c>
       <c r="AY7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BA7">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC7">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BD7">
         <v>40</v>
       </c>
       <c r="BE7">
+        <v>11.5</v>
+      </c>
+      <c r="BF7">
         <v>15</v>
       </c>
-      <c r="BF7">
-        <v>16</v>
-      </c>
       <c r="BG7">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BH7">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>18</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>16.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>177</v>
@@ -2593,97 +2593,97 @@
         <v>149</v>
       </c>
       <c r="F8">
+        <v>3.25</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>2.08</v>
+      </c>
+      <c r="I8">
+        <v>2.26</v>
+      </c>
+      <c r="J8">
         <v>3.15</v>
       </c>
-      <c r="G8">
-        <v>3.6</v>
-      </c>
-      <c r="H8">
-        <v>2.2</v>
-      </c>
-      <c r="I8">
-        <v>2.42</v>
-      </c>
-      <c r="J8">
-        <v>3.45</v>
-      </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1.35</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P8">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R8">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S8">
-        <v>2.98</v>
+        <v>1.78</v>
       </c>
       <c r="T8">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="W8">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="X8">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y8">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z8">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AA8">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB8">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE8">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="AF8">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AG8">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH8">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI8">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AJ8">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AK8">
         <v>95</v>
@@ -2695,124 +2695,124 @@
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>65</v>
+        <v>600</v>
       </c>
       <c r="AO8">
-        <v>16.5</v>
+        <v>600</v>
       </c>
       <c r="AP8">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8">
-        <v>9.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AR8">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AS8">
-        <v>16</v>
+        <v>2.16</v>
       </c>
       <c r="AT8">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AU8">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AV8">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="AW8">
-        <v>19.5</v>
+        <v>2.1</v>
       </c>
       <c r="AX8">
-        <v>20</v>
+        <v>2.1</v>
       </c>
       <c r="AY8">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AZ8">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA8">
-        <v>7.4</v>
+        <v>2.16</v>
       </c>
       <c r="BB8">
-        <v>8</v>
+        <v>2.18</v>
       </c>
       <c r="BC8">
-        <v>14.5</v>
+        <v>2.16</v>
       </c>
       <c r="BD8">
-        <v>7.6</v>
+        <v>2.18</v>
       </c>
       <c r="BE8">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="BF8">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG8">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="BH8">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>177</v>
@@ -2841,10 +2841,10 @@
         <v>5.3</v>
       </c>
       <c r="H9">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="I9">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="J9">
         <v>4.5</v>
@@ -2859,202 +2859,202 @@
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P9">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q9">
         <v>1.51</v>
       </c>
       <c r="R9">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S9">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T9">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="U9">
         <v>2.5</v>
       </c>
       <c r="V9">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="W9">
         <v>1.23</v>
       </c>
       <c r="X9">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="Y9">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z9">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AA9">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AB9">
+        <v>950</v>
+      </c>
+      <c r="AC9">
+        <v>970</v>
+      </c>
+      <c r="AD9">
+        <v>970</v>
+      </c>
+      <c r="AE9">
+        <v>970</v>
+      </c>
+      <c r="AF9">
+        <v>500</v>
+      </c>
+      <c r="AG9">
+        <v>950</v>
+      </c>
+      <c r="AH9">
+        <v>970</v>
+      </c>
+      <c r="AI9">
+        <v>500</v>
+      </c>
+      <c r="AJ9">
+        <v>700</v>
+      </c>
+      <c r="AK9">
+        <v>700</v>
+      </c>
+      <c r="AL9">
+        <v>700</v>
+      </c>
+      <c r="AM9">
+        <v>580</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
         <v>29</v>
       </c>
-      <c r="AC9">
-        <v>12</v>
-      </c>
-      <c r="AD9">
-        <v>13</v>
-      </c>
-      <c r="AE9">
-        <v>16</v>
-      </c>
-      <c r="AF9">
-        <v>60</v>
-      </c>
-      <c r="AG9">
-        <v>26</v>
-      </c>
-      <c r="AH9">
-        <v>20</v>
-      </c>
-      <c r="AI9">
-        <v>30</v>
-      </c>
-      <c r="AJ9">
-        <v>130</v>
-      </c>
-      <c r="AK9">
-        <v>65</v>
-      </c>
-      <c r="AL9">
-        <v>60</v>
-      </c>
-      <c r="AM9">
-        <v>75</v>
-      </c>
-      <c r="AN9">
-        <v>48</v>
-      </c>
-      <c r="AO9">
-        <v>6.6</v>
-      </c>
       <c r="AP9">
-        <v>13</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AR9">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="AS9">
-        <v>15.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT9">
-        <v>10</v>
+        <v>1.37</v>
       </c>
       <c r="AU9">
-        <v>9.4</v>
+        <v>5.2</v>
       </c>
       <c r="AV9">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="AW9">
-        <v>13</v>
+        <v>2.5</v>
       </c>
       <c r="AX9">
-        <v>5.6</v>
+        <v>1.39</v>
       </c>
       <c r="AY9">
-        <v>17.5</v>
+        <v>1.39</v>
       </c>
       <c r="AZ9">
-        <v>14</v>
+        <v>1.34</v>
       </c>
       <c r="BA9">
-        <v>20</v>
+        <v>1.37</v>
       </c>
       <c r="BB9">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="BC9">
-        <v>5.8</v>
+        <v>1.39</v>
       </c>
       <c r="BD9">
-        <v>5.7</v>
+        <v>1.39</v>
       </c>
       <c r="BE9">
-        <v>5.8</v>
+        <v>1.39</v>
       </c>
       <c r="BF9">
-        <v>5.6</v>
+        <v>1.55</v>
       </c>
       <c r="BG9">
-        <v>5.4</v>
+        <v>1.55</v>
       </c>
       <c r="BH9">
         <v>5.6</v>
       </c>
       <c r="BI9">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ9">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BK9">
+        <v>3.25</v>
+      </c>
+      <c r="BL9">
+        <v>90</v>
+      </c>
+      <c r="BM9">
+        <v>4.4</v>
+      </c>
+      <c r="BN9">
+        <v>10.5</v>
+      </c>
+      <c r="BO9">
+        <v>3.2</v>
+      </c>
+      <c r="BP9">
+        <v>42</v>
+      </c>
+      <c r="BQ9">
         <v>4.2</v>
       </c>
-      <c r="BL9">
-        <v>85</v>
-      </c>
-      <c r="BM9">
-        <v>7</v>
-      </c>
-      <c r="BN9">
-        <v>9.4</v>
-      </c>
-      <c r="BO9">
+      <c r="BR9">
+        <v>42</v>
+      </c>
+      <c r="BS9">
         <v>4.2</v>
       </c>
-      <c r="BP9">
-        <v>40</v>
-      </c>
-      <c r="BQ9">
-        <v>6.4</v>
-      </c>
-      <c r="BR9">
-        <v>38</v>
-      </c>
-      <c r="BS9">
-        <v>6.4</v>
-      </c>
       <c r="BT9">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BU9">
         <v>3.75</v>
       </c>
       <c r="BV9">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BW9">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="BX9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BY9">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="BZ9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CA9">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="CB9" t="s">
         <v>177</v>
@@ -3077,25 +3077,25 @@
         <v>151</v>
       </c>
       <c r="F10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G10">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M10">
         <v>1.04</v>
@@ -3104,52 +3104,52 @@
         <v>5.2</v>
       </c>
       <c r="O10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
         <v>1.68</v>
       </c>
       <c r="R10">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S10">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T10">
         <v>1.62</v>
       </c>
       <c r="U10">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
         <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y10">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Z10">
         <v>40</v>
       </c>
       <c r="AA10">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE10">
         <v>55</v>
@@ -3161,37 +3161,37 @@
         <v>11</v>
       </c>
       <c r="AH10">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI10">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AJ10">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL10">
         <v>40</v>
       </c>
       <c r="AM10">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN10">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO10">
         <v>36</v>
       </c>
       <c r="AP10">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AQ10">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS10">
         <v>50</v>
@@ -3200,31 +3200,31 @@
         <v>11</v>
       </c>
       <c r="AU10">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10">
         <v>14</v>
       </c>
       <c r="BA10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD10">
         <v>22</v>
@@ -3233,70 +3233,70 @@
         <v>55</v>
       </c>
       <c r="BF10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BH10">
         <v>4.6</v>
       </c>
       <c r="BI10">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BJ10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK10">
+        <v>5</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
         <v>9</v>
       </c>
-      <c r="BK10">
-        <v>5.1</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>10</v>
-      </c>
       <c r="BN10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP10">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="BQ10">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BR10">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BT10">
         <v>7.6</v>
       </c>
       <c r="BU10">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BX10">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ10">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB10" t="s">
         <v>177</v>
@@ -3319,19 +3319,19 @@
         <v>152</v>
       </c>
       <c r="F11">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="G11">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="H11">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="I11">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="J11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K11">
         <v>3.7</v>
@@ -3343,16 +3343,16 @@
         <v>1.06</v>
       </c>
       <c r="N11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O11">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P11">
         <v>2.1</v>
       </c>
       <c r="Q11">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R11">
         <v>1.42</v>
@@ -3361,184 +3361,184 @@
         <v>3.2</v>
       </c>
       <c r="T11">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="W11">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="X11">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y11">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z11">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AA11">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC11">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD11">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE11">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AF11">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG11">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH11">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AI11">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AJ11">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AK11">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AL11">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM11">
-        <v>95</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="AO11">
-        <v>24</v>
+        <v>600</v>
       </c>
       <c r="AP11">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ11">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR11">
-        <v>17.5</v>
+        <v>2.62</v>
       </c>
       <c r="AS11">
-        <v>27</v>
+        <v>2.98</v>
       </c>
       <c r="AT11">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>3.85</v>
       </c>
       <c r="AV11">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AW11">
-        <v>23</v>
+        <v>2.76</v>
       </c>
       <c r="AX11">
-        <v>17.5</v>
+        <v>2.82</v>
       </c>
       <c r="AY11">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AZ11">
-        <v>13.5</v>
+        <v>2.72</v>
       </c>
       <c r="BA11">
-        <v>29</v>
+        <v>2.86</v>
       </c>
       <c r="BB11">
-        <v>27</v>
+        <v>2.98</v>
       </c>
       <c r="BC11">
-        <v>24</v>
+        <v>2.94</v>
       </c>
       <c r="BD11">
-        <v>30</v>
+        <v>2.88</v>
       </c>
       <c r="BE11">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="BF11">
-        <v>20</v>
+        <v>2.82</v>
       </c>
       <c r="BG11">
-        <v>20</v>
+        <v>2.9</v>
       </c>
       <c r="BH11">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
         <v>177</v>
@@ -3561,226 +3561,226 @@
         <v>153</v>
       </c>
       <c r="F12">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="G12">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="I12">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
         <v>4.2</v>
       </c>
       <c r="L12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O12">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P12">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q12">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R12">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S12">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="U12">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="V12">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X12">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y12">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z12">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AA12">
-        <v>29</v>
+        <v>900</v>
       </c>
       <c r="AB12">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AC12">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="AD12">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE12">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="AF12">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AG12">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH12">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI12">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AJ12">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AK12">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL12">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM12">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN12">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="AP12">
-        <v>11</v>
+        <v>1.55</v>
       </c>
       <c r="AQ12">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="AR12">
-        <v>11</v>
+        <v>1.57</v>
       </c>
       <c r="AS12">
-        <v>22</v>
+        <v>1.62</v>
       </c>
       <c r="AT12">
-        <v>10.5</v>
+        <v>1.56</v>
       </c>
       <c r="AU12">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="AV12">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="AW12">
-        <v>19.5</v>
+        <v>1.6</v>
       </c>
       <c r="AX12">
-        <v>20</v>
+        <v>1.61</v>
       </c>
       <c r="AY12">
-        <v>11.5</v>
+        <v>1.57</v>
       </c>
       <c r="AZ12">
-        <v>13.5</v>
+        <v>1.54</v>
       </c>
       <c r="BA12">
-        <v>29</v>
+        <v>1.62</v>
       </c>
       <c r="BB12">
-        <v>8</v>
+        <v>1.63</v>
       </c>
       <c r="BC12">
-        <v>34</v>
+        <v>1.63</v>
       </c>
       <c r="BD12">
-        <v>38</v>
+        <v>1.63</v>
       </c>
       <c r="BE12">
-        <v>8.199999999999999</v>
+        <v>1.64</v>
       </c>
       <c r="BF12">
-        <v>36</v>
+        <v>1.64</v>
       </c>
       <c r="BG12">
-        <v>15</v>
+        <v>1.6</v>
       </c>
       <c r="BH12">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
         <v>177</v>
@@ -3803,25 +3803,25 @@
         <v>154</v>
       </c>
       <c r="F13">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G13">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H13">
+        <v>5.1</v>
+      </c>
+      <c r="I13">
+        <v>5.4</v>
+      </c>
+      <c r="J13">
         <v>5</v>
       </c>
-      <c r="I13">
-        <v>5.5</v>
-      </c>
-      <c r="J13">
-        <v>5.1</v>
-      </c>
       <c r="K13">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L13">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M13">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P13">
         <v>3.7</v>
@@ -3839,190 +3839,190 @@
         <v>1.34</v>
       </c>
       <c r="R13">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="T13">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="U13">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="V13">
         <v>1.22</v>
       </c>
       <c r="W13">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X13">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="Y13">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="Z13">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AA13">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AB13">
+        <v>40</v>
+      </c>
+      <c r="AC13">
+        <v>15.5</v>
+      </c>
+      <c r="AD13">
+        <v>950</v>
+      </c>
+      <c r="AE13">
+        <v>700</v>
+      </c>
+      <c r="AF13">
+        <v>19.5</v>
+      </c>
+      <c r="AG13">
+        <v>13</v>
+      </c>
+      <c r="AH13">
+        <v>20</v>
+      </c>
+      <c r="AI13">
+        <v>700</v>
+      </c>
+      <c r="AJ13">
         <v>21</v>
       </c>
-      <c r="AC13">
-        <v>14</v>
-      </c>
-      <c r="AD13">
-        <v>23</v>
-      </c>
-      <c r="AE13">
-        <v>75</v>
-      </c>
-      <c r="AF13">
-        <v>17</v>
-      </c>
-      <c r="AG13">
-        <v>12</v>
-      </c>
-      <c r="AH13">
-        <v>16.5</v>
-      </c>
-      <c r="AI13">
-        <v>50</v>
-      </c>
-      <c r="AJ13">
-        <v>19.5</v>
-      </c>
       <c r="AK13">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL13">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AM13">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="AN13">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AO13">
-        <v>27</v>
+        <v>700</v>
       </c>
       <c r="AP13">
+        <v>29</v>
+      </c>
+      <c r="AQ13">
+        <v>4.2</v>
+      </c>
+      <c r="AR13">
+        <v>26</v>
+      </c>
+      <c r="AS13">
+        <v>4.3</v>
+      </c>
+      <c r="AT13">
+        <v>15</v>
+      </c>
+      <c r="AU13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV13">
+        <v>18</v>
+      </c>
+      <c r="AW13">
         <v>34</v>
       </c>
-      <c r="AQ13">
-        <v>32</v>
-      </c>
-      <c r="AR13">
-        <v>46</v>
-      </c>
-      <c r="AS13">
-        <v>70</v>
-      </c>
-      <c r="AT13">
-        <v>18</v>
-      </c>
-      <c r="AU13">
-        <v>12</v>
-      </c>
-      <c r="AV13">
-        <v>20</v>
-      </c>
-      <c r="AW13">
-        <v>36</v>
-      </c>
       <c r="AX13">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY13">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AZ13">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA13">
         <v>26</v>
       </c>
       <c r="BB13">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BC13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD13">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF13">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BG13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH13">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
         <v>177</v>
@@ -4045,19 +4045,19 @@
         <v>155</v>
       </c>
       <c r="F14">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G14">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H14">
         <v>2.32</v>
       </c>
       <c r="I14">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J14">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K14">
         <v>4.9</v>
@@ -4066,67 +4066,67 @@
         <v>1.19</v>
       </c>
       <c r="M14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O14">
         <v>1.09</v>
       </c>
       <c r="P14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q14">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R14">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="S14">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="T14">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="U14">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="V14">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W14">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X14">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="Y14">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Z14">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA14">
         <v>44</v>
       </c>
       <c r="AB14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AC14">
+        <v>15</v>
+      </c>
+      <c r="AD14">
         <v>15.5</v>
-      </c>
-      <c r="AD14">
-        <v>14.5</v>
       </c>
       <c r="AE14">
         <v>22</v>
       </c>
       <c r="AF14">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AG14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH14">
         <v>14.5</v>
@@ -4135,91 +4135,91 @@
         <v>23</v>
       </c>
       <c r="AJ14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK14">
         <v>26</v>
       </c>
       <c r="AL14">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AM14">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="AN14">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO14">
         <v>7.2</v>
       </c>
       <c r="AP14">
-        <v>29</v>
+        <v>7.8</v>
       </c>
       <c r="AQ14">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="AR14">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AS14">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AT14">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="AU14">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW14">
         <v>17.5</v>
       </c>
       <c r="AX14">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="AY14">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ14">
         <v>11.5</v>
       </c>
       <c r="BA14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BB14">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BC14">
         <v>20</v>
       </c>
       <c r="BD14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE14">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="BF14">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG14">
         <v>6</v>
       </c>
       <c r="BH14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BI14">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BJ14">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK14">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BL14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BM14">
         <v>5.2</v>
@@ -4228,7 +4228,7 @@
         <v>8.4</v>
       </c>
       <c r="BO14">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="BP14">
         <v>19.5</v>
@@ -4240,7 +4240,7 @@
         <v>21</v>
       </c>
       <c r="BS14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT14">
         <v>7.8</v>
@@ -4255,13 +4255,13 @@
         <v>4.3</v>
       </c>
       <c r="BX14">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BY14">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ14">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA14">
         <v>3.6</v>
@@ -4287,43 +4287,43 @@
         <v>156</v>
       </c>
       <c r="F15">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G15">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H15">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L15">
         <v>1.23</v>
       </c>
       <c r="M15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q15">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R15">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S15">
         <v>2.06</v>
@@ -4332,52 +4332,52 @@
         <v>1.46</v>
       </c>
       <c r="U15">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V15">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="W15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X15">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="Y15">
         <v>23</v>
       </c>
       <c r="Z15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA15">
+        <v>30</v>
+      </c>
+      <c r="AB15">
         <v>32</v>
       </c>
-      <c r="AB15">
-        <v>34</v>
-      </c>
       <c r="AC15">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG15">
         <v>19</v>
       </c>
       <c r="AH15">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AJ15">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK15">
         <v>42</v>
@@ -4386,43 +4386,43 @@
         <v>42</v>
       </c>
       <c r="AM15">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AN15">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO15">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP15">
         <v>23</v>
       </c>
       <c r="AQ15">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR15">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS15">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AT15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AU15">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AV15">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AW15">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AX15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AY15">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AZ15">
         <v>12.5</v>
@@ -4431,82 +4431,82 @@
         <v>19</v>
       </c>
       <c r="BB15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BD15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BE15">
         <v>36</v>
       </c>
       <c r="BF15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG15">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH15">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>177</v>
@@ -4529,10 +4529,10 @@
         <v>157</v>
       </c>
       <c r="F16">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G16">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H16">
         <v>11</v>
@@ -4541,10 +4541,10 @@
         <v>13</v>
       </c>
       <c r="J16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K16">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="L16">
         <v>1.2</v>
@@ -4559,34 +4559,34 @@
         <v>1.11</v>
       </c>
       <c r="P16">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q16">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R16">
         <v>2.06</v>
       </c>
       <c r="S16">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="T16">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="U16">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V16">
         <v>1.08</v>
       </c>
       <c r="W16">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="X16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Y16">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Z16">
         <v>140</v>
@@ -4595,19 +4595,19 @@
         <v>470</v>
       </c>
       <c r="AB16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC16">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="AD16">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AE16">
         <v>150</v>
       </c>
       <c r="AF16">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG16">
         <v>12</v>
@@ -4616,61 +4616,61 @@
         <v>27</v>
       </c>
       <c r="AI16">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AJ16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL16">
         <v>27</v>
       </c>
       <c r="AM16">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN16">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AO16">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AP16">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AQ16">
-        <v>48</v>
+        <v>12.5</v>
       </c>
       <c r="AR16">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AS16">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AT16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU16">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AV16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AW16">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA16">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BB16">
         <v>10.5</v>
@@ -4682,73 +4682,73 @@
         <v>21</v>
       </c>
       <c r="BE16">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="BF16">
-        <v>2.98</v>
+        <v>2.58</v>
       </c>
       <c r="BG16">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="BH16">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
         <v>177</v>
@@ -4771,19 +4771,19 @@
         <v>158</v>
       </c>
       <c r="F17">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="G17">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H17">
         <v>6.4</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J17">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K17">
         <v>6.6</v>
@@ -4801,13 +4801,13 @@
         <v>1.08</v>
       </c>
       <c r="P17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q17">
         <v>1.26</v>
       </c>
       <c r="R17">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S17">
         <v>1.66</v>
@@ -4816,52 +4816,52 @@
         <v>1.43</v>
       </c>
       <c r="U17">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="V17">
         <v>1.16</v>
       </c>
       <c r="W17">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X17">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="Y17">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="Z17">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AA17">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB17">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AC17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AD17">
         <v>30</v>
       </c>
       <c r="AE17">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AF17">
         <v>17</v>
       </c>
       <c r="AG17">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH17">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AI17">
         <v>55</v>
       </c>
       <c r="AJ17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK17">
         <v>14</v>
@@ -4870,10 +4870,10 @@
         <v>21</v>
       </c>
       <c r="AM17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN17">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="AO17">
         <v>32</v>
@@ -4882,31 +4882,31 @@
         <v>48</v>
       </c>
       <c r="AQ17">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AR17">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AS17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT17">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AU17">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV17">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW17">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AX17">
         <v>15</v>
       </c>
       <c r="AY17">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17">
         <v>16.5</v>
@@ -4915,7 +4915,7 @@
         <v>40</v>
       </c>
       <c r="BB17">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BC17">
         <v>12</v>
@@ -4927,70 +4927,70 @@
         <v>40</v>
       </c>
       <c r="BF17">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BG17">
         <v>25</v>
       </c>
       <c r="BH17">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
         <v>177</v>
@@ -5013,25 +5013,25 @@
         <v>159</v>
       </c>
       <c r="F18">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G18">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="H18">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="I18">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J18">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K18">
         <v>2.94</v>
       </c>
       <c r="L18">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M18">
         <v>1.15</v>
@@ -5040,7 +5040,7 @@
         <v>2.58</v>
       </c>
       <c r="O18">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="P18">
         <v>1.5</v>
@@ -5055,184 +5055,184 @@
         <v>6</v>
       </c>
       <c r="T18">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="U18">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V18">
         <v>1.6</v>
       </c>
       <c r="W18">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X18">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="Y18">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="Z18">
         <v>14.5</v>
       </c>
       <c r="AA18">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB18">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AC18">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD18">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AE18">
         <v>40</v>
       </c>
       <c r="AF18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG18">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AH18">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AI18">
-        <v>75</v>
+        <v>460</v>
       </c>
       <c r="AJ18">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="AK18">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AL18">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="AM18">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AN18">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="AO18">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP18">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ18">
         <v>6.8</v>
       </c>
       <c r="AR18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS18">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AT18">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU18">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV18">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW18">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AX18">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AY18">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA18">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="BB18">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BC18">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BD18">
-        <v>55</v>
+        <v>13.5</v>
       </c>
       <c r="BE18">
+        <v>4.5</v>
+      </c>
+      <c r="BF18">
         <v>65</v>
       </c>
-      <c r="BF18">
-        <v>70</v>
-      </c>
       <c r="BG18">
-        <v>38</v>
+        <v>11.5</v>
       </c>
       <c r="BH18">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
         <v>177</v>
@@ -5255,22 +5255,22 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="G19">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="H19">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="I19">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="J19">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L19">
         <v>1.53</v>
@@ -5282,73 +5282,73 @@
         <v>3.05</v>
       </c>
       <c r="O19">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P19">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q19">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R19">
         <v>1.24</v>
       </c>
       <c r="S19">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T19">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="U19">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V19">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="W19">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X19">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y19">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z19">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AA19">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC19">
         <v>7.4</v>
       </c>
       <c r="AD19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE19">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF19">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG19">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH19">
         <v>21</v>
       </c>
       <c r="AI19">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ19">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK19">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL19">
         <v>85</v>
@@ -5357,124 +5357,124 @@
         <v>580</v>
       </c>
       <c r="AN19">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AO19">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AP19">
         <v>9</v>
       </c>
       <c r="AQ19">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT19">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AU19">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV19">
         <v>10</v>
       </c>
       <c r="AW19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX19">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AY19">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA19">
         <v>38</v>
       </c>
       <c r="BB19">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BD19">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BE19">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BF19">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BG19">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH19">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
         <v>177</v>
@@ -5500,7 +5500,7 @@
         <v>2.2</v>
       </c>
       <c r="G20">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H20">
         <v>3.05</v>
@@ -5509,61 +5509,61 @@
         <v>3.2</v>
       </c>
       <c r="J20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K20">
         <v>4.5</v>
       </c>
       <c r="L20">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M20">
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="O20">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P20">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="Q20">
+        <v>1.43</v>
+      </c>
+      <c r="R20">
+        <v>1.89</v>
+      </c>
+      <c r="S20">
+        <v>2.08</v>
+      </c>
+      <c r="T20">
         <v>1.38</v>
       </c>
-      <c r="R20">
-        <v>1.98</v>
-      </c>
-      <c r="S20">
-        <v>1.96</v>
-      </c>
-      <c r="T20">
-        <v>1.33</v>
-      </c>
       <c r="U20">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="V20">
         <v>1.45</v>
       </c>
       <c r="W20">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="X20">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Y20">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="Z20">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AA20">
         <v>60</v>
       </c>
       <c r="AB20">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AC20">
         <v>12.5</v>
@@ -5572,151 +5572,151 @@
         <v>16.5</v>
       </c>
       <c r="AE20">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF20">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AG20">
         <v>14</v>
       </c>
       <c r="AH20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI20">
+        <v>40</v>
+      </c>
+      <c r="AJ20">
+        <v>32</v>
+      </c>
+      <c r="AK20">
+        <v>22</v>
+      </c>
+      <c r="AL20">
+        <v>34</v>
+      </c>
+      <c r="AM20">
+        <v>55</v>
+      </c>
+      <c r="AN20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO20">
+        <v>15</v>
+      </c>
+      <c r="AP20">
+        <v>23</v>
+      </c>
+      <c r="AQ20">
+        <v>20</v>
+      </c>
+      <c r="AR20">
+        <v>24</v>
+      </c>
+      <c r="AS20">
         <v>36</v>
       </c>
-      <c r="AJ20">
-        <v>36</v>
-      </c>
-      <c r="AK20">
-        <v>21</v>
-      </c>
-      <c r="AL20">
-        <v>24</v>
-      </c>
-      <c r="AM20">
-        <v>50</v>
-      </c>
-      <c r="AN20">
-        <v>8.4</v>
-      </c>
-      <c r="AO20">
-        <v>13</v>
-      </c>
-      <c r="AP20">
-        <v>29</v>
-      </c>
-      <c r="AQ20">
-        <v>22</v>
-      </c>
-      <c r="AR20">
-        <v>26</v>
-      </c>
-      <c r="AS20">
-        <v>40</v>
-      </c>
       <c r="AT20">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AU20">
         <v>10</v>
       </c>
       <c r="AV20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX20">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY20">
         <v>11</v>
       </c>
       <c r="AZ20">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA20">
+        <v>23</v>
+      </c>
+      <c r="BB20">
         <v>21</v>
-      </c>
-      <c r="BB20">
-        <v>24</v>
       </c>
       <c r="BC20">
         <v>17</v>
       </c>
       <c r="BD20">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE20">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BF20">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG20">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH20">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
         <v>177</v>
@@ -5739,67 +5739,67 @@
         <v>162</v>
       </c>
       <c r="F21">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="G21">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="H21">
+        <v>12.5</v>
+      </c>
+      <c r="I21">
         <v>15.5</v>
       </c>
-      <c r="I21">
-        <v>18.5</v>
-      </c>
       <c r="J21">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="K21">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L21">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N21">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P21">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q21">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R21">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S21">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T21">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="U21">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W21">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="X21">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y21">
         <v>950</v>
       </c>
       <c r="Z21">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AA21">
         <v>1000</v>
@@ -5808,157 +5808,157 @@
         <v>7.2</v>
       </c>
       <c r="AC21">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD21">
-        <v>170</v>
+        <v>950</v>
       </c>
       <c r="AE21">
-        <v>460</v>
+        <v>370</v>
       </c>
       <c r="AF21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AG21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH21">
         <v>950</v>
       </c>
       <c r="AI21">
+        <v>290</v>
+      </c>
+      <c r="AJ21">
+        <v>11</v>
+      </c>
+      <c r="AK21">
+        <v>20</v>
+      </c>
+      <c r="AL21">
+        <v>120</v>
+      </c>
+      <c r="AM21">
         <v>340</v>
       </c>
-      <c r="AJ21">
-        <v>9.6</v>
-      </c>
-      <c r="AK21">
-        <v>19.5</v>
-      </c>
-      <c r="AL21">
-        <v>160</v>
-      </c>
-      <c r="AM21">
-        <v>370</v>
-      </c>
       <c r="AN21">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AO21">
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT21">
+        <v>6</v>
+      </c>
+      <c r="AU21">
+        <v>10.5</v>
+      </c>
+      <c r="AV21">
+        <v>7.6</v>
+      </c>
+      <c r="AW21">
+        <v>8.6</v>
+      </c>
+      <c r="AX21">
+        <v>6</v>
+      </c>
+      <c r="AY21">
         <v>9.4</v>
       </c>
-      <c r="AS21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT21">
-        <v>5.6</v>
-      </c>
-      <c r="AU21">
-        <v>11.5</v>
-      </c>
-      <c r="AV21">
+      <c r="AZ21">
+        <v>7.2</v>
+      </c>
+      <c r="BA21">
+        <v>8.4</v>
+      </c>
+      <c r="BB21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC21">
+        <v>14</v>
+      </c>
+      <c r="BD21">
+        <v>7.6</v>
+      </c>
+      <c r="BE21">
         <v>8.6</v>
       </c>
-      <c r="AW21">
-        <v>9.6</v>
-      </c>
-      <c r="AX21">
+      <c r="BF21">
         <v>5.8</v>
       </c>
-      <c r="AY21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ21">
-        <v>8</v>
-      </c>
-      <c r="BA21">
-        <v>9.6</v>
-      </c>
-      <c r="BB21">
-        <v>7.8</v>
-      </c>
-      <c r="BC21">
-        <v>13.5</v>
-      </c>
-      <c r="BD21">
-        <v>8.4</v>
-      </c>
-      <c r="BE21">
-        <v>9.6</v>
-      </c>
-      <c r="BF21">
-        <v>5.1</v>
-      </c>
       <c r="BG21">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH21">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
         <v>177</v>
@@ -5981,7 +5981,7 @@
         <v>163</v>
       </c>
       <c r="F22">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G22">
         <v>2.88</v>
@@ -5990,13 +5990,13 @@
         <v>3.2</v>
       </c>
       <c r="I22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J22">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="K22">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L22">
         <v>1.62</v>
@@ -6008,25 +6008,25 @@
         <v>2.5</v>
       </c>
       <c r="O22">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="P22">
         <v>1.47</v>
       </c>
       <c r="Q22">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="R22">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S22">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="T22">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="U22">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V22">
         <v>1.4</v>
@@ -6035,172 +6035,172 @@
         <v>1.53</v>
       </c>
       <c r="X22">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="Z22">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AA22">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB22">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AC22">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="AD22">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE22">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AF22">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG22">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH22">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI22">
-        <v>95</v>
+        <v>460</v>
       </c>
       <c r="AJ22">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AK22">
-        <v>55</v>
+        <v>230</v>
       </c>
       <c r="AL22">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="AM22">
         <v>500</v>
       </c>
       <c r="AN22">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ22">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="AR22">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS22">
-        <v>9.4</v>
+        <v>2.24</v>
       </c>
       <c r="AT22">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="AU22">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AV22">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW22">
-        <v>20</v>
+        <v>2.24</v>
       </c>
       <c r="AX22">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AY22">
+        <v>1.94</v>
+      </c>
+      <c r="AZ22">
         <v>11</v>
       </c>
-      <c r="AZ22">
-        <v>20</v>
-      </c>
       <c r="BA22">
-        <v>9.800000000000001</v>
+        <v>1.99</v>
       </c>
       <c r="BB22">
-        <v>18</v>
+        <v>1.97</v>
       </c>
       <c r="BC22">
-        <v>18</v>
+        <v>2.24</v>
       </c>
       <c r="BD22">
-        <v>9.6</v>
+        <v>1.98</v>
       </c>
       <c r="BE22">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BF22">
-        <v>36</v>
+        <v>1.86</v>
       </c>
       <c r="BG22">
-        <v>9.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="BH22">
-        <v>2.86</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
         <v>177</v>
@@ -6226,16 +6226,16 @@
         <v>2.08</v>
       </c>
       <c r="G23">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H23">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I23">
         <v>5.4</v>
       </c>
       <c r="J23">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K23">
         <v>3.2</v>
@@ -6244,205 +6244,205 @@
         <v>1.67</v>
       </c>
       <c r="M23">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N23">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O23">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="P23">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q23">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R23">
         <v>1.14</v>
       </c>
       <c r="S23">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T23">
-        <v>2.36</v>
+        <v>1.11</v>
       </c>
       <c r="U23">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="V23">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W23">
         <v>1.81</v>
       </c>
       <c r="X23">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y23">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z23">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AA23">
         <v>900</v>
       </c>
       <c r="AB23">
-        <v>6.2</v>
+        <v>970</v>
       </c>
       <c r="AC23">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="AD23">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AE23">
         <v>260</v>
       </c>
       <c r="AF23">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG23">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH23">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI23">
         <v>700</v>
       </c>
       <c r="AJ23">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AK23">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="AL23">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="AM23">
         <v>500</v>
       </c>
       <c r="AN23">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="AQ23">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="AR23">
-        <v>23</v>
+        <v>1.79</v>
       </c>
       <c r="AS23">
-        <v>8.199999999999999</v>
+        <v>1.82</v>
       </c>
       <c r="AT23">
-        <v>5.2</v>
+        <v>2.9</v>
       </c>
       <c r="AU23">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="AV23">
-        <v>19</v>
+        <v>1.74</v>
       </c>
       <c r="AW23">
-        <v>8</v>
+        <v>1.81</v>
       </c>
       <c r="AX23">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="AY23">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ23">
-        <v>16</v>
+        <v>1.8</v>
       </c>
       <c r="BA23">
-        <v>8.199999999999999</v>
+        <v>1.82</v>
       </c>
       <c r="BB23">
-        <v>19</v>
+        <v>1.8</v>
       </c>
       <c r="BC23">
-        <v>16</v>
+        <v>2.86</v>
       </c>
       <c r="BD23">
-        <v>30</v>
+        <v>1.81</v>
       </c>
       <c r="BE23">
-        <v>8.199999999999999</v>
+        <v>1.82</v>
       </c>
       <c r="BF23">
-        <v>24</v>
+        <v>1.83</v>
       </c>
       <c r="BG23">
-        <v>8.199999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="BH23">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
         <v>177</v>
@@ -6465,7 +6465,7 @@
         <v>165</v>
       </c>
       <c r="F24">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G24">
         <v>5.3</v>
@@ -6474,28 +6474,28 @@
         <v>2.08</v>
       </c>
       <c r="I24">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J24">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K24">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L24">
         <v>1.66</v>
       </c>
       <c r="M24">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N24">
         <v>2.34</v>
       </c>
       <c r="O24">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="P24">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q24">
         <v>3.05</v>
@@ -6504,55 +6504,55 @@
         <v>1.14</v>
       </c>
       <c r="S24">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T24">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U24">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V24">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W24">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X24">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="Y24">
-        <v>6.4</v>
+        <v>970</v>
       </c>
       <c r="Z24">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AA24">
-        <v>30</v>
+        <v>900</v>
       </c>
       <c r="AB24">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC24">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AD24">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE24">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="AF24">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AG24">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AH24">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI24">
-        <v>190</v>
+        <v>460</v>
       </c>
       <c r="AJ24">
         <v>900</v>
@@ -6564,127 +6564,127 @@
         <v>540</v>
       </c>
       <c r="AM24">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
+        <v>1000</v>
+      </c>
+      <c r="AO24">
         <v>600</v>
       </c>
-      <c r="AO24">
-        <v>36</v>
-      </c>
       <c r="AP24">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="AQ24">
+        <v>3.5</v>
+      </c>
+      <c r="AR24">
         <v>5.3</v>
       </c>
-      <c r="AR24">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AS24">
-        <v>21</v>
+        <v>1.87</v>
       </c>
       <c r="AT24">
-        <v>9.6</v>
+        <v>1.87</v>
       </c>
       <c r="AU24">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV24">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AW24">
-        <v>14.5</v>
+        <v>1.86</v>
       </c>
       <c r="AX24">
-        <v>28</v>
+        <v>1.88</v>
       </c>
       <c r="AY24">
-        <v>18</v>
+        <v>1.88</v>
       </c>
       <c r="AZ24">
-        <v>14.5</v>
+        <v>1.86</v>
       </c>
       <c r="BA24">
-        <v>8</v>
+        <v>1.89</v>
       </c>
       <c r="BB24">
-        <v>8.4</v>
+        <v>1.9</v>
       </c>
       <c r="BC24">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="BD24">
-        <v>8.4</v>
+        <v>1.91</v>
       </c>
       <c r="BE24">
-        <v>8.6</v>
+        <v>1.91</v>
       </c>
       <c r="BF24">
-        <v>8.6</v>
+        <v>1.91</v>
       </c>
       <c r="BG24">
-        <v>7.2</v>
+        <v>1.91</v>
       </c>
       <c r="BH24">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP24">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="s">
         <v>177</v>
@@ -6707,46 +6707,46 @@
         <v>166</v>
       </c>
       <c r="F25">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="G25">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H25">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I25">
         <v>5.1</v>
       </c>
       <c r="J25">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K25">
         <v>4.3</v>
       </c>
       <c r="L25">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M25">
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O25">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P25">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q25">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R25">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S25">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T25">
         <v>1.11</v>
@@ -6758,115 +6758,115 @@
         <v>1.25</v>
       </c>
       <c r="W25">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X25">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Y25">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="Z25">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AA25">
-        <v>900</v>
+        <v>340</v>
       </c>
       <c r="AB25">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC25">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="AD25">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AE25">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF25">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG25">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AH25">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AI25">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ25">
-        <v>900</v>
+        <v>22</v>
       </c>
       <c r="AK25">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AL25">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AM25">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN25">
-        <v>600</v>
+        <v>12</v>
       </c>
       <c r="AO25">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AP25">
-        <v>1.35</v>
+        <v>14.5</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>16</v>
       </c>
       <c r="AR25">
-        <v>1.34</v>
+        <v>16</v>
       </c>
       <c r="AS25">
-        <v>1.35</v>
+        <v>5.4</v>
       </c>
       <c r="AT25">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU25">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AV25">
-        <v>1.34</v>
+        <v>15</v>
       </c>
       <c r="AW25">
-        <v>1.35</v>
+        <v>5.2</v>
       </c>
       <c r="AX25">
-        <v>1.31</v>
+        <v>9</v>
       </c>
       <c r="AY25">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ25">
-        <v>1.32</v>
+        <v>15</v>
       </c>
       <c r="BA25">
-        <v>1.35</v>
+        <v>5.2</v>
       </c>
       <c r="BB25">
-        <v>1.34</v>
+        <v>15.5</v>
       </c>
       <c r="BC25">
-        <v>1.33</v>
+        <v>14.5</v>
       </c>
       <c r="BD25">
-        <v>1.34</v>
+        <v>25</v>
       </c>
       <c r="BE25">
-        <v>1.35</v>
+        <v>5.3</v>
       </c>
       <c r="BF25">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="BG25">
-        <v>1.55</v>
+        <v>5.1</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6949,19 +6949,19 @@
         <v>167</v>
       </c>
       <c r="F26">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G26">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H26">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="I26">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J26">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K26">
         <v>3.85</v>
@@ -6973,34 +6973,34 @@
         <v>1.04</v>
       </c>
       <c r="N26">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O26">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P26">
+        <v>2.62</v>
+      </c>
+      <c r="Q26">
+        <v>1.6</v>
+      </c>
+      <c r="R26">
+        <v>1.65</v>
+      </c>
+      <c r="S26">
         <v>2.5</v>
       </c>
-      <c r="Q26">
-        <v>1.63</v>
-      </c>
-      <c r="R26">
-        <v>1.61</v>
-      </c>
-      <c r="S26">
-        <v>2.58</v>
-      </c>
       <c r="T26">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U26">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V26">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W26">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X26">
         <v>25</v>
@@ -7009,13 +7009,13 @@
         <v>19</v>
       </c>
       <c r="Z26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA26">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB26">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AC26">
         <v>8.800000000000001</v>
@@ -7024,37 +7024,37 @@
         <v>12.5</v>
       </c>
       <c r="AE26">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG26">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH26">
         <v>14</v>
       </c>
       <c r="AI26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ26">
         <v>36</v>
       </c>
       <c r="AK26">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL26">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM26">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN26">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO26">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AP26">
         <v>20</v>
@@ -7066,10 +7066,10 @@
         <v>21</v>
       </c>
       <c r="AS26">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT26">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU26">
         <v>8.199999999999999</v>
@@ -7078,10 +7078,10 @@
         <v>11.5</v>
       </c>
       <c r="AW26">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AX26">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY26">
         <v>11</v>
@@ -7090,85 +7090,85 @@
         <v>13</v>
       </c>
       <c r="BA26">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB26">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD26">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE26">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BF26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BG26">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH26">
         <v>4.9</v>
       </c>
       <c r="BI26">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BJ26">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="BL26">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>4.5</v>
+        <v>2.68</v>
       </c>
       <c r="BN26">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP26">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>3.85</v>
+        <v>2.32</v>
       </c>
       <c r="BR26">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="BT26">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV26">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>3.95</v>
+        <v>2.72</v>
       </c>
       <c r="BX26">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>4.1</v>
+        <v>2.64</v>
       </c>
       <c r="BZ26">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>3.9</v>
+        <v>2.64</v>
       </c>
       <c r="CB26" t="s">
         <v>177</v>
@@ -7191,19 +7191,19 @@
         <v>168</v>
       </c>
       <c r="F27">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G27">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H27">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J27">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K27">
         <v>3.85</v>
@@ -7218,43 +7218,43 @@
         <v>4.4</v>
       </c>
       <c r="O27">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P27">
         <v>2.16</v>
       </c>
       <c r="Q27">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R27">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S27">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T27">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U27">
         <v>2.28</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W27">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="X27">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y27">
         <v>17</v>
       </c>
       <c r="Z27">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA27">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB27">
         <v>11</v>
@@ -7263,10 +7263,10 @@
         <v>8.6</v>
       </c>
       <c r="AD27">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE27">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF27">
         <v>13.5</v>
@@ -7278,19 +7278,19 @@
         <v>17</v>
       </c>
       <c r="AI27">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ27">
         <v>24</v>
       </c>
       <c r="AK27">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM27">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AN27">
         <v>13</v>
@@ -7299,34 +7299,34 @@
         <v>46</v>
       </c>
       <c r="AP27">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ27">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR27">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AS27">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT27">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU27">
         <v>8</v>
       </c>
       <c r="AV27">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW27">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AX27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY27">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ27">
         <v>15.5</v>
@@ -7338,79 +7338,79 @@
         <v>21</v>
       </c>
       <c r="BC27">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD27">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BE27">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BF27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG27">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH27">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BJ27">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL27">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BN27">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>4.3</v>
+        <v>2.08</v>
       </c>
       <c r="BP27">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>10.5</v>
+        <v>2.58</v>
       </c>
       <c r="BR27">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="BT27">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>6.6</v>
+        <v>2.44</v>
       </c>
       <c r="BV27">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="BX27">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>6</v>
+        <v>2.92</v>
       </c>
       <c r="BZ27">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="CB27" t="s">
         <v>177</v>
@@ -7433,7 +7433,7 @@
         <v>169</v>
       </c>
       <c r="F28">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G28">
         <v>1.55</v>
@@ -7442,7 +7442,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I28">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J28">
         <v>4.3</v>
@@ -7451,19 +7451,19 @@
         <v>4.4</v>
       </c>
       <c r="L28">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M28">
         <v>1.08</v>
       </c>
       <c r="N28">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P28">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q28">
         <v>2.18</v>
@@ -7475,7 +7475,7 @@
         <v>4.1</v>
       </c>
       <c r="T28">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U28">
         <v>1.71</v>
@@ -7493,22 +7493,22 @@
         <v>22</v>
       </c>
       <c r="Z28">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB28">
         <v>6.6</v>
       </c>
       <c r="AC28">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD28">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AE28">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF28">
         <v>7.8</v>
@@ -7517,7 +7517,7 @@
         <v>11</v>
       </c>
       <c r="AH28">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AI28">
         <v>540</v>
@@ -7526,7 +7526,7 @@
         <v>13</v>
       </c>
       <c r="AK28">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL28">
         <v>50</v>
@@ -7535,22 +7535,22 @@
         <v>1000</v>
       </c>
       <c r="AN28">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO28">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28">
         <v>18</v>
       </c>
       <c r="AR28">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS28">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AT28">
         <v>6.2</v>
@@ -7559,22 +7559,22 @@
         <v>9.4</v>
       </c>
       <c r="AV28">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW28">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX28">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY28">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BA28">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="BB28">
         <v>12</v>
@@ -7583,76 +7583,76 @@
         <v>17</v>
       </c>
       <c r="BD28">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE28">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BF28">
         <v>9.4</v>
       </c>
       <c r="BG28">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH28">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BI28">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ28">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>11.5</v>
+        <v>3</v>
       </c>
       <c r="BN28">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BO28">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BP28">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>6.6</v>
+        <v>2.62</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>8.800000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="BT28">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>10.5</v>
+        <v>3.15</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>10.5</v>
+        <v>3.15</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>7.8</v>
+        <v>3.15</v>
       </c>
       <c r="CB28" t="s">
         <v>177</v>
@@ -7675,22 +7675,22 @@
         <v>170</v>
       </c>
       <c r="F29">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="G29">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="H29">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="I29">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="J29">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L29">
         <v>1.25</v>
@@ -7699,97 +7699,97 @@
         <v>1.03</v>
       </c>
       <c r="N29">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O29">
         <v>1.15</v>
       </c>
       <c r="P29">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="Q29">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R29">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="S29">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="T29">
+        <v>1.11</v>
+      </c>
+      <c r="U29">
+        <v>1.11</v>
+      </c>
+      <c r="V29">
+        <v>1.76</v>
+      </c>
+      <c r="W29">
         <v>1.44</v>
-      </c>
-      <c r="U29">
-        <v>2.82</v>
-      </c>
-      <c r="V29">
-        <v>1.81</v>
-      </c>
-      <c r="W29">
-        <v>1.42</v>
       </c>
       <c r="X29">
         <v>36</v>
       </c>
       <c r="Y29">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Z29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA29">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC29">
         <v>12</v>
       </c>
       <c r="AD29">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE29">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF29">
         <v>34</v>
       </c>
       <c r="AG29">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH29">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ29">
         <v>55</v>
       </c>
       <c r="AK29">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL29">
         <v>32</v>
       </c>
       <c r="AM29">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AN29">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO29">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP29">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ29">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AR29">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS29">
         <v>14.5</v>
@@ -7798,103 +7798,103 @@
         <v>18</v>
       </c>
       <c r="AU29">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="AV29">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AW29">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX29">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY29">
         <v>12</v>
       </c>
       <c r="AZ29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA29">
         <v>20</v>
       </c>
       <c r="BB29">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC29">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BD29">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BE29">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF29">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BG29">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH29">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL29">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN29">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP29">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR29">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT29">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV29">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX29">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="s">
         <v>177</v>
@@ -7917,10 +7917,10 @@
         <v>171</v>
       </c>
       <c r="F30">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G30">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H30">
         <v>11.5</v>
@@ -7929,214 +7929,214 @@
         <v>12</v>
       </c>
       <c r="J30">
+        <v>6.4</v>
+      </c>
+      <c r="K30">
         <v>6.6</v>
-      </c>
-      <c r="K30">
-        <v>6.8</v>
       </c>
       <c r="L30">
         <v>1.24</v>
       </c>
       <c r="M30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N30">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="O30">
         <v>1.13</v>
       </c>
       <c r="P30">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="Q30">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R30">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="S30">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T30">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U30">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V30">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W30">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X30">
         <v>36</v>
       </c>
       <c r="Y30">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z30">
         <v>120</v>
       </c>
       <c r="AA30">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="AB30">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC30">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD30">
         <v>42</v>
       </c>
       <c r="AE30">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AF30">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG30">
+        <v>11</v>
+      </c>
+      <c r="AH30">
+        <v>27</v>
+      </c>
+      <c r="AI30">
+        <v>230</v>
+      </c>
+      <c r="AJ30">
         <v>10.5</v>
-      </c>
-      <c r="AH30">
-        <v>25</v>
-      </c>
-      <c r="AI30">
-        <v>110</v>
-      </c>
-      <c r="AJ30">
-        <v>11.5</v>
       </c>
       <c r="AK30">
         <v>12</v>
       </c>
       <c r="AL30">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM30">
         <v>110</v>
       </c>
       <c r="AN30">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AO30">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AP30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AQ30">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AR30">
         <v>100</v>
       </c>
       <c r="AS30">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AT30">
         <v>14</v>
       </c>
       <c r="AU30">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AV30">
         <v>38</v>
       </c>
       <c r="AW30">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AX30">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY30">
+        <v>10.5</v>
+      </c>
+      <c r="AZ30">
+        <v>25</v>
+      </c>
+      <c r="BA30">
+        <v>100</v>
+      </c>
+      <c r="BB30">
         <v>10</v>
-      </c>
-      <c r="AZ30">
-        <v>23</v>
-      </c>
-      <c r="BA30">
-        <v>90</v>
-      </c>
-      <c r="BB30">
-        <v>10.5</v>
       </c>
       <c r="BC30">
         <v>11.5</v>
       </c>
       <c r="BD30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BF30">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BG30">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="BH30">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BI30">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
+        <v>7.6</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>2.2</v>
+      </c>
+      <c r="BN30">
+        <v>4.9</v>
+      </c>
+      <c r="BO30">
+        <v>3.55</v>
+      </c>
+      <c r="BP30">
+        <v>9</v>
+      </c>
+      <c r="BQ30">
+        <v>5.1</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
         <v>11</v>
       </c>
-      <c r="BK30">
-        <v>9.6</v>
-      </c>
-      <c r="BL30">
-        <v>110</v>
-      </c>
-      <c r="BM30">
-        <v>14</v>
-      </c>
-      <c r="BN30">
-        <v>4.2</v>
-      </c>
-      <c r="BO30">
-        <v>3.85</v>
-      </c>
-      <c r="BP30">
-        <v>7</v>
-      </c>
-      <c r="BQ30">
-        <v>6.2</v>
-      </c>
-      <c r="BR30">
-        <v>19.5</v>
-      </c>
-      <c r="BS30">
-        <v>16</v>
-      </c>
       <c r="BT30">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV30">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>14</v>
+        <v>2.2</v>
       </c>
       <c r="BX30">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>12.5</v>
+        <v>2.2</v>
       </c>
       <c r="BZ30">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>7.2</v>
+        <v>2.28</v>
       </c>
       <c r="CB30" t="s">
         <v>177</v>
@@ -8159,22 +8159,22 @@
         <v>172</v>
       </c>
       <c r="F31">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G31">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H31">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I31">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J31">
         <v>3.35</v>
       </c>
       <c r="K31">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L31">
         <v>1.45</v>
@@ -8186,7 +8186,7 @@
         <v>3.65</v>
       </c>
       <c r="O31">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P31">
         <v>1.88</v>
@@ -8201,40 +8201,40 @@
         <v>3.85</v>
       </c>
       <c r="T31">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U31">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W31">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X31">
         <v>12.5</v>
       </c>
       <c r="Y31">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z31">
         <v>23</v>
       </c>
       <c r="AA31">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB31">
         <v>9.800000000000001</v>
       </c>
       <c r="AC31">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD31">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE31">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="AF31">
         <v>15</v>
@@ -8252,16 +8252,16 @@
         <v>34</v>
       </c>
       <c r="AK31">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL31">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AM31">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="AN31">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO31">
         <v>42</v>
@@ -8276,7 +8276,7 @@
         <v>20</v>
       </c>
       <c r="AS31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT31">
         <v>9.199999999999999</v>
@@ -8288,10 +8288,10 @@
         <v>12.5</v>
       </c>
       <c r="AW31">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX31">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY31">
         <v>10.5</v>
@@ -8300,85 +8300,85 @@
         <v>16.5</v>
       </c>
       <c r="BA31">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC31">
         <v>24</v>
       </c>
       <c r="BD31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE31">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BF31">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG31">
         <v>36</v>
       </c>
       <c r="BH31">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BI31">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="BJ31">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="BN31">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO31">
-        <v>3.95</v>
+        <v>1.92</v>
       </c>
       <c r="BP31">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="BR31">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
-        <v>8.6</v>
+        <v>2.7</v>
       </c>
       <c r="BT31">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU31">
-        <v>5</v>
+        <v>2.06</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>8.199999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>8.4</v>
+        <v>2.7</v>
       </c>
       <c r="CB31" t="s">
         <v>177</v>
@@ -8401,19 +8401,19 @@
         <v>173</v>
       </c>
       <c r="F32">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G32">
+        <v>2.96</v>
+      </c>
+      <c r="H32">
         <v>2.94</v>
       </c>
-      <c r="H32">
-        <v>2.92</v>
-      </c>
       <c r="I32">
+        <v>3.1</v>
+      </c>
+      <c r="J32">
         <v>3.05</v>
-      </c>
-      <c r="J32">
-        <v>3.15</v>
       </c>
       <c r="K32">
         <v>3.25</v>
@@ -8422,49 +8422,49 @@
         <v>1.56</v>
       </c>
       <c r="M32">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N32">
         <v>2.78</v>
       </c>
       <c r="O32">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P32">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q32">
         <v>2.62</v>
       </c>
       <c r="R32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S32">
         <v>5.3</v>
       </c>
       <c r="T32">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U32">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V32">
         <v>1.48</v>
       </c>
       <c r="W32">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X32">
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z32">
         <v>19</v>
       </c>
       <c r="AA32">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AB32">
         <v>8.800000000000001</v>
@@ -8473,22 +8473,22 @@
         <v>7.2</v>
       </c>
       <c r="AD32">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE32">
         <v>110</v>
       </c>
       <c r="AF32">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG32">
         <v>14</v>
       </c>
       <c r="AH32">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI32">
-        <v>70</v>
+        <v>460</v>
       </c>
       <c r="AJ32">
         <v>55</v>
@@ -8503,124 +8503,124 @@
         <v>580</v>
       </c>
       <c r="AN32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO32">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP32">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ32">
         <v>7.8</v>
       </c>
       <c r="AR32">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS32">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT32">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU32">
         <v>6.2</v>
       </c>
       <c r="AV32">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW32">
+        <v>9</v>
+      </c>
+      <c r="AX32">
+        <v>15</v>
+      </c>
+      <c r="AY32">
+        <v>12</v>
+      </c>
+      <c r="AZ32">
+        <v>19</v>
+      </c>
+      <c r="BA32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB32">
+        <v>9.4</v>
+      </c>
+      <c r="BC32">
+        <v>9.4</v>
+      </c>
+      <c r="BD32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE32">
+        <v>11</v>
+      </c>
+      <c r="BF32">
         <v>9.6</v>
       </c>
-      <c r="AX32">
-        <v>15.5</v>
-      </c>
-      <c r="AY32">
-        <v>11.5</v>
-      </c>
-      <c r="AZ32">
-        <v>18</v>
-      </c>
-      <c r="BA32">
-        <v>10.5</v>
-      </c>
-      <c r="BB32">
-        <v>10</v>
-      </c>
-      <c r="BC32">
-        <v>32</v>
-      </c>
-      <c r="BD32">
-        <v>10.5</v>
-      </c>
-      <c r="BE32">
-        <v>11.5</v>
-      </c>
-      <c r="BF32">
-        <v>10</v>
-      </c>
       <c r="BG32">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH32">
         <v>2.78</v>
       </c>
       <c r="BI32">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ32">
         <v>11</v>
       </c>
       <c r="BK32">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN32">
         <v>5.7</v>
       </c>
       <c r="BO32">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BP32">
         <v>26</v>
       </c>
       <c r="BQ32">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BR32">
         <v>48</v>
       </c>
       <c r="BS32">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT32">
         <v>5.9</v>
       </c>
       <c r="BU32">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV32">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW32">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY32">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA32">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB32" t="s">
         <v>177</v>
@@ -8646,19 +8646,19 @@
         <v>2.38</v>
       </c>
       <c r="G33">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H33">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I33">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J33">
         <v>3.3</v>
       </c>
       <c r="K33">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L33">
         <v>1.48</v>
@@ -8670,7 +8670,7 @@
         <v>3.3</v>
       </c>
       <c r="O33">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P33">
         <v>1.76</v>
@@ -8685,94 +8685,94 @@
         <v>4.2</v>
       </c>
       <c r="T33">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U33">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W33">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X33">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Y33">
         <v>11.5</v>
       </c>
       <c r="Z33">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA33">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB33">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC33">
         <v>7.6</v>
       </c>
       <c r="AD33">
+        <v>15</v>
+      </c>
+      <c r="AE33">
+        <v>55</v>
+      </c>
+      <c r="AF33">
         <v>14.5</v>
-      </c>
-      <c r="AE33">
-        <v>48</v>
-      </c>
-      <c r="AF33">
-        <v>15</v>
       </c>
       <c r="AG33">
         <v>11.5</v>
       </c>
       <c r="AH33">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI33">
+        <v>75</v>
+      </c>
+      <c r="AJ33">
+        <v>34</v>
+      </c>
+      <c r="AK33">
+        <v>28</v>
+      </c>
+      <c r="AL33">
         <v>60</v>
       </c>
-      <c r="AJ33">
-        <v>40</v>
-      </c>
-      <c r="AK33">
+      <c r="AM33">
+        <v>570</v>
+      </c>
+      <c r="AN33">
+        <v>26</v>
+      </c>
+      <c r="AO33">
         <v>65</v>
       </c>
-      <c r="AL33">
-        <v>48</v>
-      </c>
-      <c r="AM33">
-        <v>120</v>
-      </c>
-      <c r="AN33">
-        <v>27</v>
-      </c>
-      <c r="AO33">
-        <v>60</v>
-      </c>
       <c r="AP33">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ33">
         <v>10</v>
       </c>
       <c r="AR33">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS33">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AT33">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU33">
         <v>6.8</v>
       </c>
       <c r="AV33">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW33">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AX33">
         <v>13</v>
@@ -8781,88 +8781,88 @@
         <v>10</v>
       </c>
       <c r="AZ33">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA33">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="BB33">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BC33">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BD33">
+        <v>36</v>
+      </c>
+      <c r="BE33">
+        <v>42</v>
+      </c>
+      <c r="BF33">
         <v>22</v>
       </c>
-      <c r="BE33">
-        <v>10</v>
-      </c>
-      <c r="BF33">
-        <v>19</v>
-      </c>
       <c r="BG33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH33">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI33">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK33">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BL33">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM33">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN33">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO33">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP33">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR33">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS33">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT33">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU33">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV33">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW33">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX33">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY33">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA33">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="s">
         <v>177</v>
@@ -8888,217 +8888,217 @@
         <v>1.43</v>
       </c>
       <c r="G34">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H34">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I34">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J34">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L34">
         <v>1.31</v>
       </c>
       <c r="M34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N34">
         <v>4.9</v>
       </c>
       <c r="O34">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P34">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q34">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R34">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S34">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="T34">
         <v>1.9</v>
       </c>
       <c r="U34">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V34">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W34">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="X34">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y34">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Z34">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA34">
-        <v>250</v>
+        <v>330</v>
       </c>
       <c r="AB34">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC34">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD34">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AE34">
         <v>260</v>
       </c>
       <c r="AF34">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG34">
         <v>11.5</v>
       </c>
       <c r="AH34">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI34">
         <v>240</v>
       </c>
       <c r="AJ34">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AK34">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL34">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM34">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AN34">
+        <v>6.4</v>
+      </c>
+      <c r="AO34">
+        <v>180</v>
+      </c>
+      <c r="AP34">
+        <v>19.5</v>
+      </c>
+      <c r="AQ34">
+        <v>6.4</v>
+      </c>
+      <c r="AR34">
         <v>6.6</v>
       </c>
-      <c r="AO34">
-        <v>170</v>
-      </c>
-      <c r="AP34">
-        <v>18.5</v>
-      </c>
-      <c r="AQ34">
-        <v>21</v>
-      </c>
-      <c r="AR34">
+      <c r="AS34">
+        <v>7</v>
+      </c>
+      <c r="AT34">
+        <v>7</v>
+      </c>
+      <c r="AU34">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV34">
         <v>6.4</v>
       </c>
-      <c r="AS34">
+      <c r="AW34">
         <v>6.8</v>
       </c>
-      <c r="AT34">
-        <v>7.8</v>
-      </c>
-      <c r="AU34">
-        <v>8</v>
-      </c>
-      <c r="AV34">
-        <v>21</v>
-      </c>
-      <c r="AW34">
-        <v>6.6</v>
-      </c>
       <c r="AX34">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AY34">
         <v>7.6</v>
       </c>
       <c r="AZ34">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BA34">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB34">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC34">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD34">
         <v>6.4</v>
       </c>
       <c r="BE34">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF34">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG34">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH34">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI34">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK34">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BN34">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO34">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP34">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BR34">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS34">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT34">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU34">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV34">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW34">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX34">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY34">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34">
         <v>0</v>
@@ -9127,13 +9127,13 @@
         <v>176</v>
       </c>
       <c r="F35">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G35">
         <v>2</v>
       </c>
       <c r="H35">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I35">
         <v>4.9</v>
@@ -9145,208 +9145,208 @@
         <v>3.75</v>
       </c>
       <c r="L35">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M35">
         <v>1.09</v>
       </c>
       <c r="N35">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O35">
         <v>1.36</v>
       </c>
       <c r="P35">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q35">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R35">
         <v>1.32</v>
       </c>
       <c r="S35">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T35">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="U35">
-        <v>1.99</v>
+        <v>1.11</v>
       </c>
       <c r="V35">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W35">
         <v>2</v>
       </c>
       <c r="X35">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y35">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z35">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA35">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB35">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC35">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD35">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE35">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF35">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG35">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH35">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI35">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ35">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK35">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL35">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM35">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN35">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO35">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP35">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR35">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS35">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT35">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU35">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV35">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW35">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX35">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY35">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA35">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB35">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC35">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD35">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE35">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF35">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG35">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH35">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI35">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BJ35">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK35">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>17</v>
+        <v>1.04</v>
       </c>
       <c r="BN35">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO35">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP35">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT35">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU35">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="CB35" t="s">
         <v>177</v>
